--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -18,12 +18,13 @@
     <sheet name="F3_ESALES" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="F4_EXCLUSION" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="F5_EU8" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="06_RETAIL_GAP" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="07_LIMITATIONS" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="08_AI_LOG" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="F6_ADOPT_BENEFIT" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="06_RETAIL_GAP" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="07_LIMITATIONS" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="08_AI_LOG" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_MASTER'!$A$1:$L$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_MASTER'!$A$1:$L$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -31,9 +32,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="+0.00;-0.00"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -147,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -215,6 +218,10 @@
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -958,6 +965,131 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Digital adoption and e-commerce turnover, EU 2024</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'F6_ADOPT_BENEFIT'!D4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="9"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <trendline>
+            <trendlineType val="linear"/>
+            <dispRSqr val="1"/>
+            <dispEq val="1"/>
+          </trendline>
+          <xVal>
+            <numRef>
+              <f>'F6_ADOPT_BENEFIT'!$C$5:$C$10</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'F6_ADOPT_BENEFIT'!$D$5:$D$10</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="100"/>
+          <min val="50"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Individuals who bought online (% of internet users)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>E-sales as % of enterprise turnover</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -1098,6 +1230,33 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="6120000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1404,7 +1563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1505,7 +1664,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>87</t>
         </is>
       </c>
     </row>
@@ -1695,34 +1854,46 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>06_RETAIL_GAP</t>
+          <t>F6_ADOPT_BENEFIT</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Documented gap - retail volume index not retrieved</t>
+          <t>Figure 6 - adoption vs economic effect, EU 2024</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>07_LIMITATIONS</t>
+          <t>06_RETAIL_GAP</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Data quality statement - read before citing</t>
+          <t>Documented gap - retail volume index not retrieved</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>07_LIMITATIONS</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Data quality statement - read before citing</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>08_AI_LOG</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>AI use and validation log</t>
         </is>
@@ -2156,6 +2327,621 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Figure 6 - Does more digital adoption mean more economic activity?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>EU cross-section, 2024. X = consumer adoption. Y = share of enterprise turnover from e-sales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>X: individuals buying online (%)</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Y: e-sales share of turnover (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="C5" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"BG.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"BG.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="D5" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"BG.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"BG.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C6" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="D6" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="C7" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="D7" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C8" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"HU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"HU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="D8" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"HU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"HU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="C9" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="D9" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B10" s="36" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C10" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="D10" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IT.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IT.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>FITTED LINE (ordinary least squares)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>statistic</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>reading</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>n (countries)</t>
+        </is>
+      </c>
+      <c r="B14" s="37">
+        <f>COUNT($C$5:$C$10)</f>
+        <v/>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>Number of complete X-Y pairs. Expands automatically as data is added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>Slope</t>
+        </is>
+      </c>
+      <c r="B15" s="38">
+        <f>SLOPE($D$5:$D$10,$C$5:$C$10)</f>
+        <v/>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>Percentage points of enterprise turnover per percentage point of consumer adoption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B16" s="31">
+        <f>INTERCEPT($D$5:$D$10,$C$5:$C$10)</f>
+        <v/>
+      </c>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>Not interpretable - no country has zero adoption, so this is far outside the observed range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>Correlation (r)</t>
+        </is>
+      </c>
+      <c r="B17" s="38">
+        <f>CORREL($C$5:$C$10,$D$5:$D$10)</f>
+        <v/>
+      </c>
+      <c r="C17" s="29" t="inlineStr">
+        <is>
+          <t>Strength and direction of the linear association.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B18" s="38">
+        <f>RSQ($D$5:$D$10,$C$5:$C$10)</f>
+        <v/>
+      </c>
+      <c r="C18" s="29" t="inlineStr">
+        <is>
+          <t>Share of cross-country variation in Y that moves with X.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>Denmark: actual Y</t>
+        </is>
+      </c>
+      <c r="B19" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>Denmark's observed value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>Denmark: fitted Y</t>
+        </is>
+      </c>
+      <c r="B20" s="31">
+        <f>INTERCEPT($D$5:$D$10,$C$5:$C$10)+SLOPE($D$5:$D$10,$C$5:$C$10)*IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C20" s="29" t="inlineStr">
+        <is>
+          <t>What the line predicts for Denmark's adoption level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>Denmark: residual</t>
+        </is>
+      </c>
+      <c r="B21" s="39">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))-(INTERCEPT($D$5:$D$10,$C$5:$C$10)+SLOPE($D$5:$D$10,$C$5:$C$10)*IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)))</f>
+        <v/>
+      </c>
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>Positive: Denmark converts adoption into commercial activity better than the EU pattern predicts. Negative: worse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>AWAITING DATA - not plotted</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="B25" s="36" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="C25" s="40" t="inlineStr">
+        <is>
+          <t>X - add AT.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="B26" s="36" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C26" s="40" t="inlineStr">
+        <is>
+          <t>X - add BE.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="B27" s="36" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="C27" s="40" t="inlineStr">
+        <is>
+          <t>X - add CY.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>Czechia</t>
+        </is>
+      </c>
+      <c r="B28" s="36" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
+      <c r="C28" s="40" t="inlineStr">
+        <is>
+          <t>X - add CZ.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B29" s="36" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C29" s="40" t="inlineStr">
+        <is>
+          <t>X - add ES.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B30" s="36" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="C30" s="40" t="inlineStr">
+        <is>
+          <t>X - add FR.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="B31" s="36" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C31" s="40" t="inlineStr">
+        <is>
+          <t>X - add HR.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="26" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="B32" s="36" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="C32" s="40" t="inlineStr">
+        <is>
+          <t>X - add LU.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="B33" s="36" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="C33" s="40" t="inlineStr">
+        <is>
+          <t>X - add MT.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="26" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B34" s="36" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C34" s="40" t="inlineStr">
+        <is>
+          <t>X - add PL.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B35" s="36" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C35" s="40" t="inlineStr">
+        <is>
+          <t>X - add SE.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="B36" s="36" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C36" s="40" t="inlineStr">
+        <is>
+          <t>X - add SI.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B37" s="36" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C37" s="40" t="inlineStr">
+        <is>
+          <t>Y - add LT.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B38" s="36" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C38" s="40" t="inlineStr">
+        <is>
+          <t>Y - add NL.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="B39" s="36" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="C39" s="40" t="inlineStr">
+        <is>
+          <t>Y - add RO.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="inlineStr">
+        <is>
+          <t>Sources: Eurostat isoc_ec_ib20 (ES4) for X; Eurostat tin00110 (ES5, ES6) for Y. WHY A CROSS-SECTION: the Danish adoption and outcome series share almost no observation years - the best time-series pairing in this dataset is n=2 - so a within-Denmark scatter of adoption against outcome cannot be drawn from verified data. SAMPLE: n=6 of 27 member states. This is a small sample; report the association descriptively and do not quote a p-value. Adding the missing values listed above raises n automatically on the next rebuild. WHAT Y MEASURES: tin00110 covers all enterprises with 10+ employees outside the financial sector, so it includes B2B and EDI ordering across every industry, not retail alone. X is a consumer measure. The two sit on different sides of the market, so a positive association is evidence that digital commerce is deep in an economy - not evidence that consumers buying online causes enterprise turnover.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2183,7 +2969,7 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>NOT RETRIEVED</t>
         </is>
@@ -2195,7 +2981,7 @@
           <t>Indicator</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>Retail trade turnover, volume index (mangdeindeks)</t>
         </is>
@@ -2207,7 +2993,7 @@
           <t>Authority</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>Danmarks Statistik; also available via Eurostat sts_trtu_a</t>
         </is>
@@ -2219,7 +3005,7 @@
           <t>Filters required</t>
         </is>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>geo=DK; nace_r2=G47; indic_bt=VOL; s_adj=SCA; unit=I21 (2021=100)</t>
         </is>
@@ -2231,7 +3017,7 @@
           <t>Why not retrieved</t>
         </is>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="41" t="inlineStr">
         <is>
           <t>Values are published through StatBank and the Eurostat databrowser. This session's network policy blocked direct access to both, and the figure could not be verified by search. A value that cannot be traced is not entered.</t>
         </is>
@@ -2243,7 +3029,7 @@
           <t>Base year caution</t>
         </is>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>Danmarks Statistik rebased the index from 2015=100 to 2021=100. Series retrieved on different bases must not be joined.</t>
         </is>
@@ -2255,7 +3041,7 @@
           <t>Effect on the analysis</t>
         </is>
       </c>
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B10" s="41" t="inlineStr">
         <is>
           <t>The e-commerce section rests on the enterprise e-sales evidence in F3_ESALES instead, which is better sourced. No conclusion in the report depends on this series.</t>
         </is>
@@ -2267,7 +3053,7 @@
           <t>To fill</t>
         </is>
       </c>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>Retrieve from statistikbanken.dk, add rows to dataset.py under series_code DK.RET.VOL with unit 'index 2021=100', and re-run build_workbook.py.</t>
         </is>
@@ -2278,13 +3064,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2392,22 +3178,58 @@
     <row r="11" ht="62" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Search-based verification</t>
+          <t>Figure 6 sample size</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>Direct access to statistical portals was blocked in the build environment. Values were verified against the issuing authority through search results reporting those publications. This is weaker than downloading the dataset: before final submission, spot-check high-stakes figures against the source pages directly.</t>
+          <t>The adoption-to-outcome scatter rests on 6 complete country pairs. The association is strong and positive, but 6 points cannot support a p-value, a confidence interval, or a claim about causal direction. Report the slope and R-squared descriptively and say n explicitly. Adding the missing values listed on that sheet raises n automatically.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="62" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>Figure 6 measures two sides of the market</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>X is a consumer measure (individuals buying online); Y is an all-enterprise, all-sector measure that includes B2B and EDI ordering. A positive association indicates that digital commerce runs deep in an economy. It is not evidence that consumer purchasing causes enterprise turnover, and must not be written as though it were.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="62" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Mirror-sourced column</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>The 16 country-level e-sales turnover values flagged 'u' were retrieved via search of Eurostat tin00110 rather than from the databrowser directly. Two values in the same column (EU27 19.49 and Ireland 38.25) are independently corroborated by source ES5, which supports the column, but each value should be spot-checked against the databrowser before final submission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="62" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Search-based verification</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Direct access to statistical portals was blocked in the build environment. Values were verified against the issuing authority through search results reporting those publications. This is weaker than downloading the dataset: before final submission, spot-check high-stakes figures against the source pages directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="62" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>Discarded material</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>An earlier candidate dataset was rejected in full after verification found fabricated values carrying authentic dataset codes and extraction dates - including a Eurostat cross-section that inverted the true EU country ranking. None of it survives in this workbook.</t>
         </is>
@@ -2418,7 +3240,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2834,7 +3656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4807,24 +5629,24 @@
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>DK.ECM.ENT.SHR</t>
+          <t>HU.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Enterprises making e-sales</t>
+          <t>Individuals who bought online in last 12 months</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E40" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F40" s="16" t="n">
-        <v>38.78</v>
+        <v>79</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -4833,13 +5655,13 @@
       </c>
       <c r="H40" s="15" t="inlineStr">
         <is>
-          <t>% of enterprises</t>
+          <t>% of internet users</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>ES5</t>
+          <t>ES4</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
@@ -4849,7 +5671,7 @@
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
-          <t>2nd in EU after Lithuania.</t>
+          <t>Rose 37pp from 42% in 2014.</t>
         </is>
       </c>
     </row>
@@ -4859,12 +5681,12 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>LT.ECM.ENT.SHR</t>
+          <t>LT.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>Enterprises making e-sales</t>
+          <t>Individuals who bought online in last 12 months</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
@@ -4876,7 +5698,7 @@
         <v>2024</v>
       </c>
       <c r="F41" s="16" t="n">
-        <v>43.03</v>
+        <v>72</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -4885,13 +5707,13 @@
       </c>
       <c r="H41" s="15" t="inlineStr">
         <is>
-          <t>% of enterprises</t>
+          <t>% of internet users</t>
         </is>
       </c>
       <c r="I41" s="13" t="inlineStr"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>ES5</t>
+          <t>ES4</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
@@ -4901,113 +5723,113 @@
       </c>
       <c r="L41" s="15" t="inlineStr">
         <is>
-          <t>Highest in EU.</t>
+          <t>Rose 36pp from 36% in 2014.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="n">
+      <c r="A42" s="18" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="14" t="inlineStr">
-        <is>
-          <t>DK.DGP.EXMP</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>Citizens formally exempt from Digital Post</t>
-        </is>
-      </c>
-      <c r="D42" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F42" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="G42" s="13" t="inlineStr">
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>BE.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F42" s="22" t="n">
+        <v>29.51</v>
+      </c>
+      <c r="G42" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H42" s="15" t="inlineStr">
-        <is>
-          <t>% of citizens aged 15+ resident in Denmark</t>
-        </is>
-      </c>
-      <c r="I42" s="13" t="inlineStr"/>
-      <c r="J42" s="14" t="inlineStr">
-        <is>
-          <t>DG1</t>
-        </is>
-      </c>
-      <c r="K42" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L42" s="15" t="inlineStr">
-        <is>
-          <t>April 2025; approx. 256,000 citizens.</t>
-        </is>
-      </c>
+      <c r="H42" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I42" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J42" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K42" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L42" s="20" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="n">
+      <c r="A43" s="18" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="14" t="inlineStr">
-        <is>
-          <t>DK.DGP.EXMP</t>
-        </is>
-      </c>
-      <c r="C43" s="15" t="inlineStr">
-        <is>
-          <t>Citizens formally exempt from Digital Post</t>
-        </is>
-      </c>
-      <c r="D43" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F43" s="16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G43" s="13" t="inlineStr">
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>SE.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F43" s="22" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="G43" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H43" s="15" t="inlineStr">
-        <is>
-          <t>% of citizens aged 15+ resident in Denmark</t>
-        </is>
-      </c>
-      <c r="I43" s="13" t="inlineStr"/>
-      <c r="J43" s="14" t="inlineStr">
-        <is>
-          <t>DG1</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L43" s="15" t="inlineStr">
-        <is>
-          <t>Q1 2026; 238,479 citizens. 95.2% enrolled.</t>
-        </is>
-      </c>
+      <c r="H43" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I43" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J43" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K43" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L43" s="20" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="18" t="n">
@@ -5015,24 +5837,24 @@
       </c>
       <c r="B44" s="19" t="inlineStr">
         <is>
-          <t>DK.DGP.EXMP.7584</t>
+          <t>CZ.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>Exemption rate, age 75-84</t>
+          <t>E-sales as share of enterprise turnover</t>
         </is>
       </c>
       <c r="D44" s="18" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="E44" s="18" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F44" s="22" t="n">
-        <v>20</v>
+        <v>25.65</v>
       </c>
       <c r="G44" s="18" t="inlineStr">
         <is>
@@ -5041,17 +5863,17 @@
       </c>
       <c r="H44" s="20" t="inlineStr">
         <is>
-          <t>% of age group</t>
+          <t>% of total enterprise turnover</t>
         </is>
       </c>
       <c r="I44" s="18" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>u</t>
         </is>
       </c>
       <c r="J44" s="19" t="inlineStr">
         <is>
-          <t>DG1</t>
+          <t>ES6</t>
         </is>
       </c>
       <c r="K44" s="18" t="inlineStr">
@@ -5059,11 +5881,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L44" s="20" t="inlineStr">
-        <is>
-          <t>Source states 'nearly one in five'.</t>
-        </is>
-      </c>
+      <c r="L44" s="20" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="18" t="n">
@@ -5071,24 +5889,24 @@
       </c>
       <c r="B45" s="19" t="inlineStr">
         <is>
-          <t>DK.DGP.EXMP.85P</t>
+          <t>LU.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C45" s="20" t="inlineStr">
         <is>
-          <t>Exemption rate, age 85+</t>
+          <t>E-sales as share of enterprise turnover</t>
         </is>
       </c>
       <c r="D45" s="18" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E45" s="18" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F45" s="22" t="n">
-        <v>33</v>
+        <v>23.86</v>
       </c>
       <c r="G45" s="18" t="inlineStr">
         <is>
@@ -5097,17 +5915,17 @@
       </c>
       <c r="H45" s="20" t="inlineStr">
         <is>
-          <t>% of age group</t>
+          <t>% of total enterprise turnover</t>
         </is>
       </c>
       <c r="I45" s="18" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>u</t>
         </is>
       </c>
       <c r="J45" s="19" t="inlineStr">
         <is>
-          <t>DG1</t>
+          <t>ES6</t>
         </is>
       </c>
       <c r="K45" s="18" t="inlineStr">
@@ -5115,115 +5933,111 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L45" s="20" t="inlineStr">
-        <is>
-          <t>Source states 'roughly one in three'.</t>
-        </is>
-      </c>
+      <c r="L45" s="20" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="13" t="n">
+      <c r="A46" s="18" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="14" t="inlineStr">
-        <is>
-          <t>DK.DGX.NOUSE</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="inlineStr">
-        <is>
-          <t>Do not use digital public services at all</t>
-        </is>
-      </c>
-      <c r="D46" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F46" s="16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G46" s="13" t="inlineStr">
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>HU.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F46" s="22" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="G46" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H46" s="15" t="inlineStr">
-        <is>
-          <t>% of population</t>
-        </is>
-      </c>
-      <c r="I46" s="13" t="inlineStr"/>
-      <c r="J46" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K46" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L46" s="15" t="inlineStr">
-        <is>
-          <t>Agency for Digital Government estimate.</t>
-        </is>
-      </c>
+      <c r="H46" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I46" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J46" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K46" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L46" s="20" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="13" t="n">
+      <c r="A47" s="18" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="14" t="inlineStr">
-        <is>
-          <t>DK.DGX.DIFF</t>
-        </is>
-      </c>
-      <c r="C47" s="15" t="inlineStr">
-        <is>
-          <t>Face difficulties using digital public services</t>
-        </is>
-      </c>
-      <c r="D47" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E47" s="13" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F47" s="16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G47" s="13" t="inlineStr">
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>DE.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F47" s="22" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="G47" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H47" s="15" t="inlineStr">
-        <is>
-          <t>% of population</t>
-        </is>
-      </c>
-      <c r="I47" s="13" t="inlineStr"/>
-      <c r="J47" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K47" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L47" s="15" t="inlineStr">
-        <is>
-          <t>Agency for Digital Government estimate.</t>
-        </is>
-      </c>
+      <c r="H47" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I47" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J47" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K47" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L47" s="20" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="18" t="n">
@@ -5231,24 +6045,24 @@
       </c>
       <c r="B48" s="19" t="inlineStr">
         <is>
-          <t>DK.DGX.DISADV.LO</t>
+          <t>AT.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C48" s="20" t="inlineStr">
         <is>
-          <t>'Digitally disadvantaged' - lower bound</t>
+          <t>E-sales as share of enterprise turnover</t>
         </is>
       </c>
       <c r="D48" s="18" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="E48" s="18" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F48" s="22" t="n">
-        <v>17</v>
+        <v>18.96</v>
       </c>
       <c r="G48" s="18" t="inlineStr">
         <is>
@@ -5257,17 +6071,17 @@
       </c>
       <c r="H48" s="20" t="inlineStr">
         <is>
-          <t>% of adult population</t>
+          <t>% of total enterprise turnover</t>
         </is>
       </c>
       <c r="I48" s="18" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>u</t>
         </is>
       </c>
       <c r="J48" s="19" t="inlineStr">
         <is>
-          <t>DG2</t>
+          <t>ES6</t>
         </is>
       </c>
       <c r="K48" s="18" t="inlineStr">
@@ -5275,11 +6089,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L48" s="20" t="inlineStr">
-        <is>
-          <t>Published as a 17-22% range.</t>
-        </is>
-      </c>
+      <c r="L48" s="20" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="18" t="n">
@@ -5287,24 +6097,24 @@
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
-          <t>DK.DGX.DISADV.HI</t>
+          <t>HR.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C49" s="20" t="inlineStr">
         <is>
-          <t>'Digitally disadvantaged' - upper bound</t>
+          <t>E-sales as share of enterprise turnover</t>
         </is>
       </c>
       <c r="D49" s="18" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E49" s="18" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F49" s="22" t="n">
-        <v>22</v>
+        <v>18.48</v>
       </c>
       <c r="G49" s="18" t="inlineStr">
         <is>
@@ -5313,17 +6123,17 @@
       </c>
       <c r="H49" s="20" t="inlineStr">
         <is>
-          <t>% of adult population</t>
+          <t>% of total enterprise turnover</t>
         </is>
       </c>
       <c r="I49" s="18" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>u</t>
         </is>
       </c>
       <c r="J49" s="19" t="inlineStr">
         <is>
-          <t>DG2</t>
+          <t>ES6</t>
         </is>
       </c>
       <c r="K49" s="18" t="inlineStr">
@@ -5331,11 +6141,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L49" s="20" t="inlineStr">
-        <is>
-          <t>Published as a 17-22% range.</t>
-        </is>
-      </c>
+      <c r="L49" s="20" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="18" t="n">
@@ -5343,24 +6149,24 @@
       </c>
       <c r="B50" s="19" t="inlineStr">
         <is>
-          <t>DK.DGX.JUST</t>
+          <t>ES.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr">
         <is>
-          <t>'Digitally disadvantaged' - Justitia estimate</t>
+          <t>E-sales as share of enterprise turnover</t>
         </is>
       </c>
       <c r="D50" s="18" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E50" s="18" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F50" s="22" t="n">
-        <v>25</v>
+        <v>18.27</v>
       </c>
       <c r="G50" s="18" t="inlineStr">
         <is>
@@ -5369,17 +6175,17 @@
       </c>
       <c r="H50" s="20" t="inlineStr">
         <is>
-          <t>% of adult population</t>
+          <t>% of total enterprise turnover</t>
         </is>
       </c>
       <c r="I50" s="18" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>u</t>
         </is>
       </c>
       <c r="J50" s="19" t="inlineStr">
         <is>
-          <t>JU1</t>
+          <t>ES6</t>
         </is>
       </c>
       <c r="K50" s="18" t="inlineStr">
@@ -5387,363 +6193,371 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L50" s="20" t="inlineStr">
-        <is>
-          <t>Report states 'up to a quarter of the adult population'.</t>
-        </is>
-      </c>
+      <c r="L50" s="20" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="13" t="n">
+      <c r="A51" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="14" t="inlineStr">
-        <is>
-          <t>DK.TRU.DPS</t>
-        </is>
-      </c>
-      <c r="C51" s="15" t="inlineStr">
-        <is>
-          <t>Trust in digital public solutions</t>
-        </is>
-      </c>
-      <c r="D51" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="n">
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>PL.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="n">
         <v>2024</v>
       </c>
-      <c r="F51" s="16" t="n">
-        <v>82</v>
-      </c>
-      <c r="G51" s="13" t="inlineStr">
+      <c r="F51" s="22" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="G51" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H51" s="15" t="inlineStr">
-        <is>
-          <t>% of population</t>
-        </is>
-      </c>
-      <c r="I51" s="13" t="inlineStr"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K51" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L51" s="15" t="inlineStr"/>
+      <c r="H51" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I51" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J51" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K51" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L51" s="20" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="13" t="n">
+      <c r="A52" s="18" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="14" t="inlineStr">
-        <is>
-          <t>DK.TRU.DPS</t>
-        </is>
-      </c>
-      <c r="C52" s="15" t="inlineStr">
-        <is>
-          <t>Trust in digital public solutions</t>
-        </is>
-      </c>
-      <c r="D52" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F52" s="16" t="n">
-        <v>84</v>
-      </c>
-      <c r="G52" s="13" t="inlineStr">
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>SI.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F52" s="22" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="G52" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H52" s="15" t="inlineStr">
-        <is>
-          <t>% of population</t>
-        </is>
-      </c>
-      <c r="I52" s="13" t="inlineStr"/>
-      <c r="J52" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L52" s="15" t="inlineStr">
-        <is>
-          <t>Record high.</t>
-        </is>
-      </c>
+      <c r="H52" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I52" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J52" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K52" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L52" s="20" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="13" t="n">
+      <c r="A53" s="18" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="14" t="inlineStr">
-        <is>
-          <t>DK.TRU.DGP.SEC</t>
-        </is>
-      </c>
-      <c r="C53" s="15" t="inlineStr">
-        <is>
-          <t>Perceived security of Digital Post</t>
-        </is>
-      </c>
-      <c r="D53" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="n">
-        <v>2017</v>
-      </c>
-      <c r="F53" s="16" t="n">
-        <v>77</v>
-      </c>
-      <c r="G53" s="13" t="inlineStr">
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>IT.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D53" s="18" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F53" s="22" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="G53" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H53" s="15" t="inlineStr">
-        <is>
-          <t>% of population</t>
-        </is>
-      </c>
-      <c r="I53" s="13" t="inlineStr"/>
-      <c r="J53" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K53" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L53" s="15" t="inlineStr"/>
+      <c r="H53" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I53" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J53" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K53" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L53" s="20" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="13" t="n">
+      <c r="A54" s="18" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="14" t="inlineStr">
-        <is>
-          <t>DK.TRU.DGP.SEC</t>
-        </is>
-      </c>
-      <c r="C54" s="15" t="inlineStr">
-        <is>
-          <t>Perceived security of Digital Post</t>
-        </is>
-      </c>
-      <c r="D54" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E54" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F54" s="16" t="n">
-        <v>89</v>
-      </c>
-      <c r="G54" s="13" t="inlineStr">
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>MT.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C54" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F54" s="22" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="G54" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H54" s="15" t="inlineStr">
-        <is>
-          <t>% of population</t>
-        </is>
-      </c>
-      <c r="I54" s="13" t="inlineStr"/>
-      <c r="J54" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K54" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L54" s="15" t="inlineStr"/>
+      <c r="H54" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I54" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J54" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K54" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L54" s="20" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="13" t="n">
+      <c r="A55" s="18" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="14" t="inlineStr">
-        <is>
-          <t>DK.SKL.1624</t>
-        </is>
-      </c>
-      <c r="C55" s="15" t="inlineStr">
-        <is>
-          <t>At least basic digital skills, age 16-24</t>
-        </is>
-      </c>
-      <c r="D55" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E55" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F55" s="16" t="n">
-        <v>92.06</v>
-      </c>
-      <c r="G55" s="13" t="inlineStr">
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t>FR.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C55" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F55" s="22" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="G55" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H55" s="15" t="inlineStr">
-        <is>
-          <t>% of age group</t>
-        </is>
-      </c>
-      <c r="I55" s="13" t="inlineStr"/>
-      <c r="J55" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K55" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L55" s="15" t="inlineStr">
-        <is>
-          <t>EU average 74.55%.</t>
-        </is>
-      </c>
+      <c r="H55" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I55" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J55" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K55" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L55" s="20" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="13" t="n">
+      <c r="A56" s="18" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="14" t="inlineStr">
-        <is>
-          <t>DK.SKL.2554</t>
-        </is>
-      </c>
-      <c r="C56" s="15" t="inlineStr">
-        <is>
-          <t>At least basic digital skills, age 25-54</t>
-        </is>
-      </c>
-      <c r="D56" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E56" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F56" s="16" t="n">
-        <v>86.89</v>
-      </c>
-      <c r="G56" s="13" t="inlineStr">
+      <c r="B56" s="19" t="inlineStr">
+        <is>
+          <t>CY.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C56" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D56" s="18" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F56" s="22" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="G56" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H56" s="15" t="inlineStr">
-        <is>
-          <t>% of age group</t>
-        </is>
-      </c>
-      <c r="I56" s="13" t="inlineStr"/>
-      <c r="J56" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K56" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L56" s="15" t="inlineStr">
-        <is>
-          <t>EU average 68.57%.</t>
-        </is>
-      </c>
+      <c r="H56" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I56" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J56" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K56" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L56" s="20" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="13" t="n">
+      <c r="A57" s="18" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="14" t="inlineStr">
-        <is>
-          <t>DK.SKL.5574</t>
-        </is>
-      </c>
-      <c r="C57" s="15" t="inlineStr">
-        <is>
-          <t>At least basic digital skills, age 55-74</t>
-        </is>
-      </c>
-      <c r="D57" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E57" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F57" s="16" t="n">
-        <v>67.81</v>
-      </c>
-      <c r="G57" s="13" t="inlineStr">
+      <c r="B57" s="19" t="inlineStr">
+        <is>
+          <t>BG.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C57" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D57" s="18" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F57" s="22" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="G57" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H57" s="15" t="inlineStr">
-        <is>
-          <t>% of age group</t>
-        </is>
-      </c>
-      <c r="I57" s="13" t="inlineStr"/>
-      <c r="J57" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K57" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L57" s="15" t="inlineStr">
-        <is>
-          <t>EU average 42.60%.</t>
-        </is>
-      </c>
+      <c r="H57" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I57" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J57" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K57" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L57" s="20" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="13" t="n">
@@ -5751,12 +6565,12 @@
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>DK.ENT.DII</t>
+          <t>DK.ECM.ENT.SHR</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>SMEs with at least basic digital intensity</t>
+          <t>Enterprises making e-sales</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr">
@@ -5765,10 +6579,10 @@
         </is>
       </c>
       <c r="E58" s="13" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F58" s="16" t="n">
-        <v>92.45</v>
+        <v>38.78</v>
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
@@ -5777,13 +6591,13 @@
       </c>
       <c r="H58" s="15" t="inlineStr">
         <is>
-          <t>% of SMEs</t>
+          <t>% of enterprises</t>
         </is>
       </c>
       <c r="I58" s="13" t="inlineStr"/>
       <c r="J58" s="14" t="inlineStr">
         <is>
-          <t>EC1</t>
+          <t>ES5</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -5793,7 +6607,7 @@
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>EU average 71.39%.</t>
+          <t>2nd in EU after Lithuania.</t>
         </is>
       </c>
     </row>
@@ -5803,24 +6617,24 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>EU.ENT.DII</t>
+          <t>LT.ECM.ENT.SHR</t>
         </is>
       </c>
       <c r="C59" s="15" t="inlineStr">
         <is>
-          <t>SMEs with at least basic digital intensity</t>
+          <t>Enterprises making e-sales</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>EU27</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="E59" s="13" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F59" s="16" t="n">
-        <v>71.39</v>
+        <v>43.03</v>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
@@ -5829,13 +6643,13 @@
       </c>
       <c r="H59" s="15" t="inlineStr">
         <is>
-          <t>% of SMEs</t>
+          <t>% of enterprises</t>
         </is>
       </c>
       <c r="I59" s="13" t="inlineStr"/>
       <c r="J59" s="14" t="inlineStr">
         <is>
-          <t>EC1</t>
+          <t>ES5</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -5843,7 +6657,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L59" s="15" t="inlineStr"/>
+      <c r="L59" s="15" t="inlineStr">
+        <is>
+          <t>Highest in EU.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="13" t="n">
@@ -5851,12 +6669,12 @@
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>DK.ENT.AI</t>
+          <t>DK.DGP.EXMP</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Enterprises adopting AI</t>
+          <t>Citizens formally exempt from Digital Post</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
@@ -5868,7 +6686,7 @@
         <v>2025</v>
       </c>
       <c r="F60" s="16" t="n">
-        <v>42.03</v>
+        <v>5</v>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
@@ -5877,13 +6695,13 @@
       </c>
       <c r="H60" s="15" t="inlineStr">
         <is>
-          <t>% of enterprises</t>
+          <t>% of citizens aged 15+ resident in Denmark</t>
         </is>
       </c>
       <c r="I60" s="13" t="inlineStr"/>
       <c r="J60" s="14" t="inlineStr">
         <is>
-          <t>EC1</t>
+          <t>DG1</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -5893,7 +6711,7 @@
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>EU average 19.95%.</t>
+          <t>April 2025; approx. 256,000 citizens.</t>
         </is>
       </c>
     </row>
@@ -5903,12 +6721,12 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>DK.ENT.AI.LRG</t>
+          <t>DK.DGP.EXMP</t>
         </is>
       </c>
       <c r="C61" s="15" t="inlineStr">
         <is>
-          <t>Large enterprises adopting AI</t>
+          <t>Citizens formally exempt from Digital Post</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr">
@@ -5917,10 +6735,10 @@
         </is>
       </c>
       <c r="E61" s="13" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F61" s="16" t="n">
-        <v>74.52</v>
+        <v>4.7</v>
       </c>
       <c r="G61" s="13" t="inlineStr">
         <is>
@@ -5929,13 +6747,13 @@
       </c>
       <c r="H61" s="15" t="inlineStr">
         <is>
-          <t>% of large enterprises (250+)</t>
+          <t>% of citizens aged 15+ resident in Denmark</t>
         </is>
       </c>
       <c r="I61" s="13" t="inlineStr"/>
       <c r="J61" s="14" t="inlineStr">
         <is>
-          <t>EC1</t>
+          <t>DG1</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -5943,105 +6761,121 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L61" s="15" t="inlineStr"/>
+      <c r="L61" s="15" t="inlineStr">
+        <is>
+          <t>Q1 2026; 238,479 citizens. 95.2% enrolled.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="13" t="n">
+      <c r="A62" s="18" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="14" t="inlineStr">
-        <is>
-          <t>DK.ENT.AI.SME</t>
-        </is>
-      </c>
-      <c r="C62" s="15" t="inlineStr">
-        <is>
-          <t>SMEs adopting AI</t>
-        </is>
-      </c>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="B62" s="19" t="inlineStr">
+        <is>
+          <t>DK.DGP.EXMP.7584</t>
+        </is>
+      </c>
+      <c r="C62" s="20" t="inlineStr">
+        <is>
+          <t>Exemption rate, age 75-84</t>
+        </is>
+      </c>
+      <c r="D62" s="18" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E62" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F62" s="16" t="n">
-        <v>40.99</v>
-      </c>
-      <c r="G62" s="13" t="inlineStr">
+      <c r="E62" s="18" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F62" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="G62" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H62" s="15" t="inlineStr">
-        <is>
-          <t>% of SMEs (10-249)</t>
-        </is>
-      </c>
-      <c r="I62" s="13" t="inlineStr"/>
-      <c r="J62" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K62" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L62" s="15" t="inlineStr"/>
+      <c r="H62" s="20" t="inlineStr">
+        <is>
+          <t>% of age group</t>
+        </is>
+      </c>
+      <c r="I62" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J62" s="19" t="inlineStr">
+        <is>
+          <t>DG1</t>
+        </is>
+      </c>
+      <c r="K62" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L62" s="20" t="inlineStr">
+        <is>
+          <t>Source states 'nearly one in five'.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="13" t="n">
+      <c r="A63" s="18" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="14" t="inlineStr">
-        <is>
-          <t>DK.GOV.DPS.CIT</t>
-        </is>
-      </c>
-      <c r="C63" s="15" t="inlineStr">
-        <is>
-          <t>Digital public services for citizens (score)</t>
-        </is>
-      </c>
-      <c r="D63" s="13" t="inlineStr">
+      <c r="B63" s="19" t="inlineStr">
+        <is>
+          <t>DK.DGP.EXMP.85P</t>
+        </is>
+      </c>
+      <c r="C63" s="20" t="inlineStr">
+        <is>
+          <t>Exemption rate, age 85+</t>
+        </is>
+      </c>
+      <c r="D63" s="18" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E63" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F63" s="16" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="G63" s="13" t="inlineStr">
-        <is>
-          <t>score 0-100</t>
-        </is>
-      </c>
-      <c r="H63" s="15" t="inlineStr">
-        <is>
-          <t>eGovernment Benchmark score</t>
-        </is>
-      </c>
-      <c r="I63" s="13" t="inlineStr"/>
-      <c r="J63" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K63" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L63" s="15" t="inlineStr">
-        <is>
-          <t>BELOW the EU average of 84.64.</t>
+      <c r="E63" s="18" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F63" s="22" t="n">
+        <v>33</v>
+      </c>
+      <c r="G63" s="18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H63" s="20" t="inlineStr">
+        <is>
+          <t>% of age group</t>
+        </is>
+      </c>
+      <c r="I63" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J63" s="19" t="inlineStr">
+        <is>
+          <t>DG1</t>
+        </is>
+      </c>
+      <c r="K63" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L63" s="20" t="inlineStr">
+        <is>
+          <t>Source states 'roughly one in three'.</t>
         </is>
       </c>
     </row>
@@ -6051,33 +6885,33 @@
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>EU.GOV.DPS.CIT</t>
+          <t>DK.DGX.NOUSE</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Digital public services for citizens (score)</t>
+          <t>Do not use digital public services at all</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>EU27</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="E64" s="13" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F64" s="16" t="n">
-        <v>84.64</v>
+        <v>6.5</v>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>score 0-100</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>eGovernment Benchmark score</t>
+          <t>% of population</t>
         </is>
       </c>
       <c r="I64" s="13" t="inlineStr"/>
@@ -6091,7 +6925,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L64" s="15" t="inlineStr"/>
+      <c r="L64" s="15" t="inlineStr">
+        <is>
+          <t>Agency for Digital Government estimate.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="13" t="n">
@@ -6099,12 +6937,12 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>DK.GOV.DPS.XB</t>
+          <t>DK.DGX.DIFF</t>
         </is>
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>Cross-border digital public services, citizens (score)</t>
+          <t>Face difficulties using digital public services</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
@@ -6113,19 +6951,19 @@
         </is>
       </c>
       <c r="E65" s="13" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F65" s="16" t="n">
-        <v>64.40000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="G65" s="13" t="inlineStr">
         <is>
-          <t>score 0-100</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H65" s="15" t="inlineStr">
         <is>
-          <t>eGovernment Benchmark score</t>
+          <t>% of population</t>
         </is>
       </c>
       <c r="I65" s="13" t="inlineStr"/>
@@ -6141,109 +6979,121 @@
       </c>
       <c r="L65" s="15" t="inlineStr">
         <is>
-          <t>EU average 75.28.</t>
+          <t>Agency for Digital Government estimate.</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="13" t="n">
+      <c r="A66" s="18" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="14" t="inlineStr">
-        <is>
-          <t>DK.ENV.WEEE</t>
-        </is>
-      </c>
-      <c r="C66" s="15" t="inlineStr">
-        <is>
-          <t>ICT waste recycled or prepared for reuse</t>
-        </is>
-      </c>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="B66" s="19" t="inlineStr">
+        <is>
+          <t>DK.DGX.DISADV.LO</t>
+        </is>
+      </c>
+      <c r="C66" s="20" t="inlineStr">
+        <is>
+          <t>'Digitally disadvantaged' - lower bound</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E66" s="13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F66" s="16" t="n">
-        <v>15.37</v>
-      </c>
-      <c r="G66" s="13" t="inlineStr">
+      <c r="E66" s="18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F66" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="G66" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H66" s="15" t="inlineStr">
-        <is>
-          <t>% of ICT-related WEEE collected</t>
-        </is>
-      </c>
-      <c r="I66" s="13" t="inlineStr"/>
-      <c r="J66" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K66" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L66" s="15" t="inlineStr">
-        <is>
-          <t>Among the lowest in the EU; EU average 80.23%.</t>
+      <c r="H66" s="20" t="inlineStr">
+        <is>
+          <t>% of adult population</t>
+        </is>
+      </c>
+      <c r="I66" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J66" s="19" t="inlineStr">
+        <is>
+          <t>DG2</t>
+        </is>
+      </c>
+      <c r="K66" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L66" s="20" t="inlineStr">
+        <is>
+          <t>Published as a 17-22% range.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="13" t="n">
+      <c r="A67" s="18" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>EU.ENV.WEEE</t>
-        </is>
-      </c>
-      <c r="C67" s="15" t="inlineStr">
-        <is>
-          <t>ICT waste recycled or prepared for reuse</t>
-        </is>
-      </c>
-      <c r="D67" s="13" t="inlineStr">
-        <is>
-          <t>EU27</t>
-        </is>
-      </c>
-      <c r="E67" s="13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F67" s="16" t="n">
-        <v>80.23</v>
-      </c>
-      <c r="G67" s="13" t="inlineStr">
+      <c r="B67" s="19" t="inlineStr">
+        <is>
+          <t>DK.DGX.DISADV.HI</t>
+        </is>
+      </c>
+      <c r="C67" s="20" t="inlineStr">
+        <is>
+          <t>'Digitally disadvantaged' - upper bound</t>
+        </is>
+      </c>
+      <c r="D67" s="18" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E67" s="18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F67" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="G67" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H67" s="15" t="inlineStr">
-        <is>
-          <t>% of ICT-related WEEE collected</t>
-        </is>
-      </c>
-      <c r="I67" s="13" t="inlineStr"/>
-      <c r="J67" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K67" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L67" s="15" t="inlineStr"/>
+      <c r="H67" s="20" t="inlineStr">
+        <is>
+          <t>% of adult population</t>
+        </is>
+      </c>
+      <c r="I67" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J67" s="19" t="inlineStr">
+        <is>
+          <t>DG2</t>
+        </is>
+      </c>
+      <c r="K67" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L67" s="20" t="inlineStr">
+        <is>
+          <t>Published as a 17-22% range.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="18" t="n">
@@ -6251,12 +7101,12 @@
       </c>
       <c r="B68" s="19" t="inlineStr">
         <is>
-          <t>DK.SME.SMVD.PROJ</t>
+          <t>DK.DGX.JUST</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>SMV:Digital projects supported since 2018</t>
+          <t>'Digitally disadvantaged' - Justitia estimate</t>
         </is>
       </c>
       <c r="D68" s="18" t="inlineStr">
@@ -6265,19 +7115,19 @@
         </is>
       </c>
       <c r="E68" s="18" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F68" s="21" t="n">
-        <v>7000</v>
+        <v>2022</v>
+      </c>
+      <c r="F68" s="22" t="n">
+        <v>25</v>
       </c>
       <c r="G68" s="18" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H68" s="20" t="inlineStr">
         <is>
-          <t>digitalisation projects</t>
+          <t>% of adult population</t>
         </is>
       </c>
       <c r="I68" s="18" t="inlineStr">
@@ -6287,7 +7137,7 @@
       </c>
       <c r="J68" s="19" t="inlineStr">
         <is>
-          <t>DG3</t>
+          <t>JU1</t>
         </is>
       </c>
       <c r="K68" s="18" t="inlineStr">
@@ -6297,7 +7147,7 @@
       </c>
       <c r="L68" s="20" t="inlineStr">
         <is>
-          <t>Source states 'knap 7.000' (just under 7,000).</t>
+          <t>Report states 'up to a quarter of the adult population'.</t>
         </is>
       </c>
     </row>
@@ -6307,12 +7157,12 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>DK.SME.SMVD.INV</t>
+          <t>DK.TRU.DPS</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>Participants who invested further during the project</t>
+          <t>Trust in digital public solutions</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr">
@@ -6321,10 +7171,10 @@
         </is>
       </c>
       <c r="E69" s="13" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F69" s="16" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="G69" s="13" t="inlineStr">
         <is>
@@ -6333,13 +7183,13 @@
       </c>
       <c r="H69" s="15" t="inlineStr">
         <is>
-          <t>% of participating enterprises</t>
+          <t>% of population</t>
         </is>
       </c>
       <c r="I69" s="13" t="inlineStr"/>
       <c r="J69" s="14" t="inlineStr">
         <is>
-          <t>DG3</t>
+          <t>EC1</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
@@ -6355,12 +7205,12 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>DK.SME.SMVD.NOINV</t>
+          <t>DK.TRU.DPS</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Participants with no further investment plans</t>
+          <t>Trust in digital public solutions</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
@@ -6372,7 +7222,7 @@
         <v>2025</v>
       </c>
       <c r="F70" s="16" t="n">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
@@ -6381,24 +7231,932 @@
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>% of participating enterprises</t>
+          <t>% of population</t>
         </is>
       </c>
       <c r="I70" s="13" t="inlineStr"/>
       <c r="J70" s="14" t="inlineStr">
         <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L70" s="15" t="inlineStr">
+        <is>
+          <t>Record high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>DK.TRU.DGP.SEC</t>
+        </is>
+      </c>
+      <c r="C71" s="15" t="inlineStr">
+        <is>
+          <t>Perceived security of Digital Post</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="n">
+        <v>2017</v>
+      </c>
+      <c r="F71" s="16" t="n">
+        <v>77</v>
+      </c>
+      <c r="G71" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="inlineStr">
+        <is>
+          <t>% of population</t>
+        </is>
+      </c>
+      <c r="I71" s="13" t="inlineStr"/>
+      <c r="J71" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L71" s="15" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>DK.TRU.DGP.SEC</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>Perceived security of Digital Post</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F72" s="16" t="n">
+        <v>89</v>
+      </c>
+      <c r="G72" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="inlineStr">
+        <is>
+          <t>% of population</t>
+        </is>
+      </c>
+      <c r="I72" s="13" t="inlineStr"/>
+      <c r="J72" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L72" s="15" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>DK.SKL.1624</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="inlineStr">
+        <is>
+          <t>At least basic digital skills, age 16-24</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F73" s="16" t="n">
+        <v>92.06</v>
+      </c>
+      <c r="G73" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="inlineStr">
+        <is>
+          <t>% of age group</t>
+        </is>
+      </c>
+      <c r="I73" s="13" t="inlineStr"/>
+      <c r="J73" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L73" s="15" t="inlineStr">
+        <is>
+          <t>EU average 74.55%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>DK.SKL.2554</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>At least basic digital skills, age 25-54</t>
+        </is>
+      </c>
+      <c r="D74" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F74" s="16" t="n">
+        <v>86.89</v>
+      </c>
+      <c r="G74" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H74" s="15" t="inlineStr">
+        <is>
+          <t>% of age group</t>
+        </is>
+      </c>
+      <c r="I74" s="13" t="inlineStr"/>
+      <c r="J74" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L74" s="15" t="inlineStr">
+        <is>
+          <t>EU average 68.57%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>DK.SKL.5574</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="inlineStr">
+        <is>
+          <t>At least basic digital skills, age 55-74</t>
+        </is>
+      </c>
+      <c r="D75" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F75" s="16" t="n">
+        <v>67.81</v>
+      </c>
+      <c r="G75" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H75" s="15" t="inlineStr">
+        <is>
+          <t>% of age group</t>
+        </is>
+      </c>
+      <c r="I75" s="13" t="inlineStr"/>
+      <c r="J75" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L75" s="15" t="inlineStr">
+        <is>
+          <t>EU average 42.60%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>DK.ENT.DII</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>SMEs with at least basic digital intensity</t>
+        </is>
+      </c>
+      <c r="D76" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F76" s="16" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="G76" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H76" s="15" t="inlineStr">
+        <is>
+          <t>% of SMEs</t>
+        </is>
+      </c>
+      <c r="I76" s="13" t="inlineStr"/>
+      <c r="J76" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K76" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L76" s="15" t="inlineStr">
+        <is>
+          <t>EU average 71.39%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>EU.ENT.DII</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="inlineStr">
+        <is>
+          <t>SMEs with at least basic digital intensity</t>
+        </is>
+      </c>
+      <c r="D77" s="13" t="inlineStr">
+        <is>
+          <t>EU27</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F77" s="16" t="n">
+        <v>71.39</v>
+      </c>
+      <c r="G77" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="inlineStr">
+        <is>
+          <t>% of SMEs</t>
+        </is>
+      </c>
+      <c r="I77" s="13" t="inlineStr"/>
+      <c r="J77" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K77" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L77" s="15" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>DK.ENT.AI</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
+        <is>
+          <t>Enterprises adopting AI</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F78" s="16" t="n">
+        <v>42.03</v>
+      </c>
+      <c r="G78" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="inlineStr">
+        <is>
+          <t>% of enterprises</t>
+        </is>
+      </c>
+      <c r="I78" s="13" t="inlineStr"/>
+      <c r="J78" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K78" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L78" s="15" t="inlineStr">
+        <is>
+          <t>EU average 19.95%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>DK.ENT.AI.LRG</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="inlineStr">
+        <is>
+          <t>Large enterprises adopting AI</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F79" s="16" t="n">
+        <v>74.52</v>
+      </c>
+      <c r="G79" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H79" s="15" t="inlineStr">
+        <is>
+          <t>% of large enterprises (250+)</t>
+        </is>
+      </c>
+      <c r="I79" s="13" t="inlineStr"/>
+      <c r="J79" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K79" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L79" s="15" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>DK.ENT.AI.SME</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>SMEs adopting AI</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F80" s="16" t="n">
+        <v>40.99</v>
+      </c>
+      <c r="G80" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H80" s="15" t="inlineStr">
+        <is>
+          <t>% of SMEs (10-249)</t>
+        </is>
+      </c>
+      <c r="I80" s="13" t="inlineStr"/>
+      <c r="J80" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K80" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L80" s="15" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>DK.GOV.DPS.CIT</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>Digital public services for citizens (score)</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F81" s="16" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="G81" s="13" t="inlineStr">
+        <is>
+          <t>score 0-100</t>
+        </is>
+      </c>
+      <c r="H81" s="15" t="inlineStr">
+        <is>
+          <t>eGovernment Benchmark score</t>
+        </is>
+      </c>
+      <c r="I81" s="13" t="inlineStr"/>
+      <c r="J81" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K81" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L81" s="15" t="inlineStr">
+        <is>
+          <t>BELOW the EU average of 84.64.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>EU.GOV.DPS.CIT</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>Digital public services for citizens (score)</t>
+        </is>
+      </c>
+      <c r="D82" s="13" t="inlineStr">
+        <is>
+          <t>EU27</t>
+        </is>
+      </c>
+      <c r="E82" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F82" s="16" t="n">
+        <v>84.64</v>
+      </c>
+      <c r="G82" s="13" t="inlineStr">
+        <is>
+          <t>score 0-100</t>
+        </is>
+      </c>
+      <c r="H82" s="15" t="inlineStr">
+        <is>
+          <t>eGovernment Benchmark score</t>
+        </is>
+      </c>
+      <c r="I82" s="13" t="inlineStr"/>
+      <c r="J82" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K82" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L82" s="15" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>DK.GOV.DPS.XB</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>Cross-border digital public services, citizens (score)</t>
+        </is>
+      </c>
+      <c r="D83" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E83" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F83" s="16" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="G83" s="13" t="inlineStr">
+        <is>
+          <t>score 0-100</t>
+        </is>
+      </c>
+      <c r="H83" s="15" t="inlineStr">
+        <is>
+          <t>eGovernment Benchmark score</t>
+        </is>
+      </c>
+      <c r="I83" s="13" t="inlineStr"/>
+      <c r="J83" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K83" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L83" s="15" t="inlineStr">
+        <is>
+          <t>EU average 75.28.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>DK.ENV.WEEE</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="inlineStr">
+        <is>
+          <t>ICT waste recycled or prepared for reuse</t>
+        </is>
+      </c>
+      <c r="D84" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E84" s="13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F84" s="16" t="n">
+        <v>15.37</v>
+      </c>
+      <c r="G84" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H84" s="15" t="inlineStr">
+        <is>
+          <t>% of ICT-related WEEE collected</t>
+        </is>
+      </c>
+      <c r="I84" s="13" t="inlineStr"/>
+      <c r="J84" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K84" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L84" s="15" t="inlineStr">
+        <is>
+          <t>Among the lowest in the EU; EU average 80.23%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>EU.ENV.WEEE</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>ICT waste recycled or prepared for reuse</t>
+        </is>
+      </c>
+      <c r="D85" s="13" t="inlineStr">
+        <is>
+          <t>EU27</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F85" s="16" t="n">
+        <v>80.23</v>
+      </c>
+      <c r="G85" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H85" s="15" t="inlineStr">
+        <is>
+          <t>% of ICT-related WEEE collected</t>
+        </is>
+      </c>
+      <c r="I85" s="13" t="inlineStr"/>
+      <c r="J85" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K85" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L85" s="15" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="18" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="19" t="inlineStr">
+        <is>
+          <t>DK.SME.SMVD.PROJ</t>
+        </is>
+      </c>
+      <c r="C86" s="20" t="inlineStr">
+        <is>
+          <t>SMV:Digital projects supported since 2018</t>
+        </is>
+      </c>
+      <c r="D86" s="18" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E86" s="18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F86" s="21" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G86" s="18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H86" s="20" t="inlineStr">
+        <is>
+          <t>digitalisation projects</t>
+        </is>
+      </c>
+      <c r="I86" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J86" s="19" t="inlineStr">
+        <is>
           <t>DG3</t>
         </is>
       </c>
-      <c r="K70" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L70" s="15" t="inlineStr"/>
+      <c r="K86" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L86" s="20" t="inlineStr">
+        <is>
+          <t>Source states 'knap 7.000' (just under 7,000).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="13" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>DK.SME.SMVD.INV</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="inlineStr">
+        <is>
+          <t>Participants who invested further during the project</t>
+        </is>
+      </c>
+      <c r="D87" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E87" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F87" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="G87" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H87" s="15" t="inlineStr">
+        <is>
+          <t>% of participating enterprises</t>
+        </is>
+      </c>
+      <c r="I87" s="13" t="inlineStr"/>
+      <c r="J87" s="14" t="inlineStr">
+        <is>
+          <t>DG3</t>
+        </is>
+      </c>
+      <c r="K87" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L87" s="15" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>DK.SME.SMVD.NOINV</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="inlineStr">
+        <is>
+          <t>Participants with no further investment plans</t>
+        </is>
+      </c>
+      <c r="D88" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E88" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F88" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G88" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H88" s="15" t="inlineStr">
+        <is>
+          <t>% of participating enterprises</t>
+        </is>
+      </c>
+      <c r="I88" s="13" t="inlineStr"/>
+      <c r="J88" s="14" t="inlineStr">
+        <is>
+          <t>DG3</t>
+        </is>
+      </c>
+      <c r="K88" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L88" s="15" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L70"/>
+  <autoFilter ref="A1:L88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6409,7 +8167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6745,27 +8503,27 @@
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>EC1</t>
+          <t>ES6</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>European Commission</t>
+          <t>Eurostat</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Digital Decade 2026 country report: Denmark, SWD(2026) 155 final, Part 7/27, 17 June 2026</t>
+          <t>Share of enterprises' turnover on e-commerce, by country (country-level values retrieved via search of the Eurostat indicator)</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>DESI 2026</t>
+          <t>tin00110</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>https://digital-strategy.ec.europa.eu/en/policies/desi</t>
+          <t>https://ec.europa.eu/eurostat/databrowser/view/tin00110/default/table?lang=en</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -6775,30 +8533,34 @@
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>European Commission 2026, Digital Decade 2026 country report: Denmark, SWD(2026) 155 final, Part 7/27, European Commission, Brussels.</t>
+          <t>Eurostat 2025, Share of enterprises' turnover on e-commerce (tin00110), European Commission, Luxembourg, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>DG1</t>
+          <t>EC1</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen (Danish Agency for Digital Government)</t>
+          <t>European Commission</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>Statistik om Digital Post</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr"/>
+          <t>Digital Decade 2026 country report: Denmark, SWD(2026) 155 final, Part 7/27, 17 June 2026</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>DESI 2026</t>
+        </is>
+      </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>https://digst.dk/tal-og-statistik/</t>
+          <t>https://digital-strategy.ec.europa.eu/en/policies/desi</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
@@ -6808,14 +8570,14 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen 2026, Statistik om Digital Post, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
+          <t>European Commission 2026, Digital Decade 2026 country report: Denmark, SWD(2026) 155 final, Part 7/27, European Commission, Brussels.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="23" t="inlineStr">
         <is>
-          <t>DG2</t>
+          <t>DG1</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
@@ -6825,13 +8587,13 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Hvem oplever udfordringer ved det digitale?</t>
+          <t>Statistik om Digital Post</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr"/>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>https://digst.dk/digital-inklusion/viden-om-digital-inklusion/hvem-oplever-udfordringer-ved-det-digitale/</t>
+          <t>https://digst.dk/tal-og-statistik/</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
@@ -6841,30 +8603,30 @@
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen 2025, Hvem oplever udfordringer ved det digitale?, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
+          <t>Digitaliseringsstyrelsen 2026, Statistik om Digital Post, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>DG3</t>
+          <t>DG2</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen / Danmarks Statistik</t>
+          <t>Digitaliseringsstyrelsen (Danish Agency for Digital Government)</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>Effektmaaling af SMV:Digital, June 2025</t>
+          <t>Hvem oplever udfordringer ved det digitale?</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr"/>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>https://digst.dk/media/yz2ouzzz/effektmaaling-af-smvdigital-2025.pdf</t>
+          <t>https://digst.dk/digital-inklusion/viden-om-digital-inklusion/hvem-oplever-udfordringer-ved-det-digitale/</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
@@ -6874,34 +8636,30 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen 2025, Effektmaaling af SMV:Digital, prepared by Danmarks Statistik, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
+          <t>Digitaliseringsstyrelsen 2025, Hvem oplever udfordringer ved det digitale?, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
         <is>
-          <t>JU1</t>
+          <t>DG3</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Justitia (independent Danish legal think tank)</t>
+          <t>Digitaliseringsstyrelsen / Danmarks Statistik</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Retssikkerhed for digitalt udsatte borgere, July 2022</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>Folketinget DIU Alm.del bilag 32</t>
-        </is>
-      </c>
+          <t>Effektmaaling af SMV:Digital, June 2025</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr"/>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>https://justitia-int.org/wp-content/uploads/2022/09/Rapport_Retssikkerhed-for-digitalt-udsatte-borgere-1.pdf</t>
+          <t>https://digst.dk/media/yz2ouzzz/effektmaaling-af-smvdigital-2025.pdf</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
@@ -6911,30 +8669,34 @@
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>Justitia 2022, Retssikkerhed for digitalt udsatte borgere, Justitia, Copenhagen, accessed 12 September 2026.</t>
+          <t>Digitaliseringsstyrelsen 2025, Effektmaaling af SMV:Digital, prepared by Danmarks Statistik, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>IMR1</t>
+          <t>JU1</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Institut for Menneskerettigheder (Danish Institute for Human Rights)</t>
+          <t>Justitia (independent Danish legal think tank)</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>Rettigheder i den digitale velfaerdsstat, December 2023</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr"/>
+          <t>Retssikkerhed for digitalt udsatte borgere, July 2022</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Folketinget DIU Alm.del bilag 32</t>
+        </is>
+      </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>https://menneskeret.dk/sites/menneskeret.dk/files/media/document/Rettigheder%20i%20den%20digitale%20velf%C3%A6rdsstat.%20Analyse,%20Institut%20for%20Menneskerettigheder,%20december%202023.PDF</t>
+          <t>https://justitia-int.org/wp-content/uploads/2022/09/Rapport_Retssikkerhed-for-digitalt-udsatte-borgere-1.pdf</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
@@ -6944,34 +8706,30 @@
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>Institut for Menneskerettigheder 2023, Rettigheder i den digitale velfaerdsstat, Danish Institute for Human Rights, Copenhagen, accessed 12 September 2026.</t>
+          <t>Justitia 2022, Retssikkerhed for digitalt udsatte borgere, Justitia, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="23" t="inlineStr">
         <is>
-          <t>RI1</t>
+          <t>IMR1</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Retsinformation (Danish official legal information portal)</t>
+          <t>Institut for Menneskerettigheder (Danish Institute for Human Rights)</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Lov om Offentlig Digital Post, LOV nr 528 af 11/06/2012</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>ELI: lta/2012/528</t>
-        </is>
-      </c>
+          <t>Rettigheder i den digitale velfaerdsstat, December 2023</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr"/>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>https://www.retsinformation.dk/eli/lta/2012/528</t>
+          <t>https://menneskeret.dk/sites/menneskeret.dk/files/media/document/Rettigheder%20i%20den%20digitale%20velf%C3%A6rdsstat.%20Analyse,%20Institut%20for%20Menneskerettigheder,%20december%202023.PDF</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
@@ -6981,42 +8739,79 @@
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>Denmark 2012, Lov om Offentlig Digital Post (LOV nr 528 af 11/06/2012), Retsinformation, Copenhagen, accessed 12 September 2026.</t>
+          <t>Institut for Menneskerettigheder 2023, Rettigheder i den digitale velfaerdsstat, Danish Institute for Human Rights, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
         <is>
+          <t>RI1</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Retsinformation (Danish official legal information portal)</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Lov om Offentlig Digital Post, LOV nr 528 af 11/06/2012</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>ELI: lta/2012/528</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>https://www.retsinformation.dk/eli/lta/2012/528</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>Denmark 2012, Lov om Offentlig Digital Post (LOV nr 528 af 11/06/2012), Retsinformation, Copenhagen, accessed 12 September 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
           <t>DST1</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>Danmarks Statistik</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>Detailomsaetningsindeks (retail trade turnover index)</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>StatBank; base year rebased 2015 -&gt; 2021</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>https://www.dst.dk/da/Statistik/dokumentation/statistikdokumentation/detailomsaetningsindeks</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="G17" s="15" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
         <is>
           <t>Danmarks Statistik 2025, Detailomsaetningsindeks, Statistics Denmark, Copenhagen, accessed 12 September 2026.</t>
         </is>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -19,12 +19,15 @@
     <sheet name="F4_EXCLUSION" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="F5_EU8" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="F6_ADOPT_BENEFIT" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="06_RETAIL_GAP" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="07_LIMITATIONS" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="08_AI_LOG" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="F7_QUALITY" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="F8_SMVDIGITAL" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="09_POLICY" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="06_RETAIL_GAP" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="07_LIMITATIONS" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="08_AI_LOG" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_MASTER'!$A$1:$L$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_MASTER'!$A$1:$L$93</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -150,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -221,6 +224,10 @@
     <xf numFmtId="1" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -1011,7 +1018,7 @@
           </marker>
           <trendline>
             <trendlineType val="linear"/>
-            <dispRSqr val="1"/>
+            <dispRSqr val="0"/>
             <dispEq val="1"/>
           </trendline>
           <xVal>
@@ -1079,6 +1086,223 @@
             </rich>
           </tx>
         </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Denmark vs EU-27 average</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'F7_QUALITY'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'F7_QUALITY'!$A$5:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'F7_QUALITY'!$B$5:$B$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'F7_QUALITY'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'F7_QUALITY'!$A$5:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'F7_QUALITY'!$C$5:$C$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% or benchmark score</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SMV:Digital participant outcomes</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'F8_SMVDIGITAL'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'F8_SMVDIGITAL'!$A$5:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'F8_SMVDIGITAL'!$B$5:$B$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% of participating enterprises / count</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -1257,6 +1481,60 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1563,7 +1841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1664,7 +1942,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>92</t>
         </is>
       </c>
     </row>
@@ -1866,34 +2144,70 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>06_RETAIL_GAP</t>
+          <t>F7_QUALITY</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Documented gap - retail volume index not retrieved</t>
+          <t>Figure 7 - DK vs EU: leads on adoption, trails on service quality</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>07_LIMITATIONS</t>
+          <t>F8_SMVDIGITAL</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Data quality statement - read before citing</t>
+          <t>Figure 8 - SMV:Digital, the one policy with a control group</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
+          <t>09_POLICY</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Policy events - dated instruments with legal citations</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>06_RETAIL_GAP</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Documented gap - retail volume index not retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>07_LIMITATIONS</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Data quality statement - read before citing</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t>08_AI_LOG</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>AI use and validation log</t>
         </is>
@@ -1910,13 +2224,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -2123,7 +2438,199 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>HEADCOUNTS, NOT SHARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>persons</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>Citizens formally exempt, Q1 2026</t>
+        </is>
+      </c>
+      <c r="B19" s="27">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026))</f>
+        <v/>
+      </c>
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>Reported directly by the Agency for Digital Government (DG1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>Citizens formally exempt, April 2025</t>
+        </is>
+      </c>
+      <c r="B20" s="27">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C20" s="29" t="inlineStr">
+        <is>
+          <t>Reported as approximately 256,000 (DG1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>Implied population aged 15+</t>
+        </is>
+      </c>
+      <c r="B21" s="27">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026))/(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026))/100)</f>
+        <v/>
+      </c>
+      <c r="C21" s="29" t="inlineStr">
+        <is>
+          <t>DERIVED, not retrieved: the exempt headcount divided by the exemption rate. Used only to convert the capability shares below into orders of magnitude. A published 15+ population figure was not verifiable in this session; see 06_RETAIL_GAP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>Implied persons who do not use digital public services at all</t>
+        </is>
+      </c>
+      <c r="B22" s="27">
+        <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.NOUSE",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.NOUSE",'02_MASTER'!$E:$E,2026))/100)*(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026))/(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026))/100))</f>
+        <v/>
+      </c>
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>ORDER OF MAGNITUDE ONLY. Applies a share measured on 'the population' to a 15+ base; the denominators are not identical.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>Implied persons facing difficulty with digital public services</t>
+        </is>
+      </c>
+      <c r="B23" s="27">
+        <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.DIFF",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.DIFF",'02_MASTER'!$E:$E,2026))/100)*(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026))/(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026))/100))</f>
+        <v/>
+      </c>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>ORDER OF MAGNITUDE ONLY, same caveat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>POLICY EVENTS ON THIS SERIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>instrument</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Lov om Offentlig Digital Post adopted</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>LOV nr 528 af 11/06/2012</t>
+        </is>
+      </c>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>RI1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>2014-11-01</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Digital Post becomes mandatory for citizens aged 15+</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>Lov om Offentlig Digital Post</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>DG4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>Sources: DG1, DG2, EC1, JU1. Reading: the measures are nested rather than contradictory. Formal exemption (4.7%) is an administrative status; the capability measures are three to five times larger. The statutory exemption regime therefore reaches only a minority of the citizens the state's own agency counts as struggling. Which measure is chosen determines the conclusion - so the choice must be argued, not assumed.</t>
         </is>
@@ -2327,7 +2834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2592,7 +3099,7 @@
       </c>
       <c r="C18" s="29" t="inlineStr">
         <is>
-          <t>Share of cross-country variation in Y that moves with X.</t>
+          <t>Share of cross-country variation in Y that moves with X. READ THE SELECTION WARNING BELOW BEFORE QUOTING THIS NUMBER: it is inflated by how the sample was drawn and overstates the fit.</t>
         </is>
       </c>
     </row>
@@ -2647,286 +3154,560 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>SELECTION WARNING - read before quoting the fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="46" customHeight="1">
+      <c r="A24" s="40" t="inlineStr">
+        <is>
+          <t>HOW THE SAMPLE WAS DRAWN: the X column (consumer adoption) was not available as a complete Eurostat table in this session. The values come from a Eurostat press release, which names the three highest countries, the three lowest, and three large movers - a sample concentrated in the TAILS of the adoption distribution.</t>
+        </is>
+      </c>
+      <c r="B24" s="41" t="n"/>
+      <c r="C24" s="41" t="n"/>
+      <c r="D24" s="41" t="n"/>
+    </row>
+    <row r="25" ht="46" customHeight="1">
+      <c r="A25" s="40" t="inlineStr">
+        <is>
+          <t>CONSEQUENCE: of the 6 countries plotted, 5 come from the top or bottom of the EU ranking. Selecting on the extremes of X and dropping the middle inflates the correlation coefficient and R-squared by construction, because it widens the spread in X relative to the scatter around the line.</t>
+        </is>
+      </c>
+      <c r="B25" s="41" t="n"/>
+      <c r="C25" s="41" t="n"/>
+      <c r="D25" s="41" t="n"/>
+    </row>
+    <row r="26" ht="46" customHeight="1">
+      <c r="A26" s="40" t="inlineStr">
+        <is>
+          <t>HOW TO USE THIS FIGURE HONESTLY: report the SLOPE, which is far less sensitive to this kind of selection, and report n. Treat the R-squared as an upper bound. Do not describe the fit as 'strong' or 'tight', and do not compute a p-value or confidence interval from these points.</t>
+        </is>
+      </c>
+      <c r="B26" s="41" t="n"/>
+      <c r="C26" s="41" t="n"/>
+      <c r="D26" s="41" t="n"/>
+    </row>
+    <row r="27" ht="46" customHeight="1">
+      <c r="A27" s="40" t="inlineStr">
+        <is>
+          <t>HOW TO FIX IT: retrieve Eurostat isoc_ec_ib20 for 2024 for all 27 member states from the databrowser and add the rows to dataset.py. That removes the selection entirely and roughly triples n. The register below names every country still missing and the exact series code for each.</t>
+        </is>
+      </c>
+      <c r="B27" s="41" t="n"/>
+      <c r="C27" s="41" t="n"/>
+      <c r="D27" s="41" t="n"/>
+    </row>
+    <row r="28" ht="46" customHeight="1">
+      <c r="A28" s="40" t="inlineStr">
+        <is>
+          <t>DIRECTION OF CAUSATION IS NOT ESTABLISHED AND CANNOT BE. X measures consumers; Y measures enterprises, including business-to-business sales that no consumer touches. Both plausibly rise with national income, which is in neither axis. This figure shows that digital commerce runs deep in the same economies where consumers buy online. It does not show that the one produces the other.</t>
+        </is>
+      </c>
+      <c r="B28" s="41" t="n"/>
+      <c r="C28" s="41" t="n"/>
+      <c r="D28" s="41" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t>AWAITING DATA - not plotted</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="26" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="B25" s="36" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="C25" s="40" t="inlineStr">
-        <is>
-          <t>X - add AT.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="26" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="B26" s="36" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C26" s="40" t="inlineStr">
-        <is>
-          <t>X - add BE.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="26" t="inlineStr">
-        <is>
-          <t>Cyprus</t>
-        </is>
-      </c>
-      <c r="B27" s="36" t="inlineStr">
-        <is>
-          <t>CY</t>
-        </is>
-      </c>
-      <c r="C27" s="40" t="inlineStr">
-        <is>
-          <t>X - add CY.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="26" t="inlineStr">
-        <is>
-          <t>Czechia</t>
-        </is>
-      </c>
-      <c r="B28" s="36" t="inlineStr">
-        <is>
-          <t>CZ</t>
-        </is>
-      </c>
-      <c r="C28" s="40" t="inlineStr">
-        <is>
-          <t>X - add CZ.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="26" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B29" s="36" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="C29" s="40" t="inlineStr">
-        <is>
-          <t>X - add ES.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="26" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B30" s="36" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="C30" s="40" t="inlineStr">
-        <is>
-          <t>X - add FR.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="26" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="B31" s="36" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="C31" s="40" t="inlineStr">
-        <is>
-          <t>X - add HR.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B32" s="36" t="inlineStr">
         <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="C32" s="40" t="inlineStr">
-        <is>
-          <t>X - add LU.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="C32" s="42" t="inlineStr">
+        <is>
+          <t>X - add AT.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="26" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B33" s="36" t="inlineStr">
         <is>
-          <t>MT</t>
-        </is>
-      </c>
-      <c r="C33" s="40" t="inlineStr">
-        <is>
-          <t>X - add MT.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C33" s="42" t="inlineStr">
+        <is>
+          <t>X - add BE.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="26" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="B34" s="36" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="C34" s="40" t="inlineStr">
-        <is>
-          <t>X - add PL.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="C34" s="42" t="inlineStr">
+        <is>
+          <t>X - add CY.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="26" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B35" s="36" t="inlineStr">
         <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="C35" s="40" t="inlineStr">
-        <is>
-          <t>X - add SE.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+          <t>CZ</t>
+        </is>
+      </c>
+      <c r="C35" s="42" t="inlineStr">
+        <is>
+          <t>X - add CZ.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B36" s="36" t="inlineStr">
         <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="C36" s="40" t="inlineStr">
-        <is>
-          <t>X - add SI.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C36" s="42" t="inlineStr">
+        <is>
+          <t>X - add ES.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B37" s="36" t="inlineStr">
         <is>
-          <t>LT</t>
-        </is>
-      </c>
-      <c r="C37" s="40" t="inlineStr">
-        <is>
-          <t>Y - add LT.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="C37" s="42" t="inlineStr">
+        <is>
+          <t>X - add FR.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B38" s="36" t="inlineStr">
         <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="C38" s="40" t="inlineStr">
-        <is>
-          <t>Y - add NL.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C38" s="42" t="inlineStr">
+        <is>
+          <t>X - add HR.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="26" t="inlineStr">
         <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="B39" s="36" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="C39" s="42" t="inlineStr">
+        <is>
+          <t>X - add LU.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="B40" s="36" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="C40" s="42" t="inlineStr">
+        <is>
+          <t>X - add MT.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B41" s="36" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C41" s="42" t="inlineStr">
+        <is>
+          <t>X - add PL.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B42" s="36" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C42" s="42" t="inlineStr">
+        <is>
+          <t>X - add SE.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="B43" s="36" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C43" s="42" t="inlineStr">
+        <is>
+          <t>X - add SI.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B44" s="36" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C44" s="42" t="inlineStr">
+        <is>
+          <t>Y - add LT.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B45" s="36" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C45" s="42" t="inlineStr">
+        <is>
+          <t>Y - add NL.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
           <t>Romania</t>
         </is>
       </c>
-      <c r="B39" s="36" t="inlineStr">
+      <c r="B46" s="36" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="C39" s="40" t="inlineStr">
+      <c r="C46" s="42" t="inlineStr">
         <is>
           <t>Y - add RO.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="32" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="32" t="inlineStr">
         <is>
           <t>Sources: Eurostat isoc_ec_ib20 (ES4) for X; Eurostat tin00110 (ES5, ES6) for Y. WHY A CROSS-SECTION: the Danish adoption and outcome series share almost no observation years - the best time-series pairing in this dataset is n=2 - so a within-Denmark scatter of adoption against outcome cannot be drawn from verified data. SAMPLE: n=6 of 27 member states. This is a small sample; report the association descriptively and do not quote a p-value. Adding the missing values listed above raises n automatically on the next rebuild. WHAT Y MEASURES: tin00110 covers all enterprises with 10+ employees outside the financial sector, so it includes B2B and EDI ordering across every industry, not retail alone. X is a consumer measure. The two sit on different sides of the market, so a positive association is evidence that digital commerce is deep in an economy - not evidence that consumers buying online causes enterprise turnover.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A28:D28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Figure 7 - Denmark vs the EU: adoption and capability, then quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Leads on every capability measure. Below average on citizen service quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>indicator</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>SMEs with at least basic digital intensity</t>
+        </is>
+      </c>
+      <c r="B5" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENT.DII",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENT.DII",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C5" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.ENT.DII",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.ENT.DII",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>% of SMEs</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>Enterprises adopting AI</t>
+        </is>
+      </c>
+      <c r="B6" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENT.AI",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENT.AI",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C6" s="41" t="n"/>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>% of enterprises (EU avg 19.95)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>Digital public services for citizens</t>
+        </is>
+      </c>
+      <c r="B7" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C7" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>eGovernment Benchmark score 0-100</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>Cross-border digital public services</t>
+        </is>
+      </c>
+      <c r="B8" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DPS.XB",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DPS.XB",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C8" s="41" t="n"/>
+      <c r="D8" s="28" t="inlineStr">
+        <is>
+          <t>score 0-100 (EU avg 75.28)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>THE GAP THAT MATTERS - service quality, not capability</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>reading</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>Digital public services, DK minus EU average</t>
+        </is>
+      </c>
+      <c r="B12" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"EU.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C12" s="29" t="inlineStr">
+        <is>
+          <t>Negative. The most digitalised population in the EU receives below-average digital public services.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>Digital skills gap within Denmark, 16-24 minus 55-74</t>
+        </is>
+      </c>
+      <c r="B13" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>The within-country spread. Note that Denmark's WEAKEST age group (67.81%) still beats the EU average (42.60%) by 25pp, so Danish exclusion is not a skills deficit relative to Europe - it is a mandate calibrated above the bottom of its own distribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>AI adoption gap within Denmark, large firms minus SMEs</t>
+        </is>
+      </c>
+      <c r="B14" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENT.AI.LRG",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENT.AI.LRG",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENT.AI.SME",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENT.AI.SME",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>Breadth without depth, restated for AI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>Source: European Commission, Digital Decade 2026 country report for Denmark (EC1). CAUTION: the eGovernment Benchmark is a scored assessment, not a survey proportion, and a 2.4-point difference between two scores should not be read as a precisely measured gap. The direction is the finding; the magnitude is not.</t>
         </is>
       </c>
     </row>
@@ -2936,7 +3717,702 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Figure 8 - SMV:Digital, the one policy with a control group</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Danmarks Statistik matched-comparison evaluation, June 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>Digitalisation projects supported since 2018</t>
+        </is>
+      </c>
+      <c r="B5" s="27">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SME.SMVD.PROJ",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SME.SMVD.PROJ",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>Participants investing further during the project</t>
+        </is>
+      </c>
+      <c r="B6" s="33">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SME.SMVD.INV",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SME.SMVD.INV",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C6" s="28" t="inlineStr">
+        <is>
+          <t>% of participants</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>Participants with no further investment plans</t>
+        </is>
+      </c>
+      <c r="B7" s="33">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SME.SMVD.NOINV",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SME.SMVD.NOINV",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>% of participants</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>WHY THIS IS THE STRONGEST EVIDENCE IN THE WORKBOOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>The evaluation was carried out by Danmarks Statistik, which compared participating firms against comparable firms that did not participate. Participants showed higher revenue AND higher employment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>That is a comparison group. Nothing else in this workbook has one. Figure 6's cross-section can show that adoption and commercial activity move together across countries; it cannot rule out that richer countries simply do more of both. A matched comparison can.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>LIMIT: the effect sizes are not reproduced here because they were not verified against the evaluation itself. The direction of the finding is sourced; the magnitude is not, and must not be invented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>LIMIT: participation is voluntary, so selection into the programme by more capable or more ambitious firms is not excluded by matching alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>POLICY EVENTS ON THIS SERIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>instrument</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>SMV:Digital launched</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Danish digital growth plan for SMEs</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>DG3</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>SMV:Digital grant pools continue</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Tilskudspuljer i 2026</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>SMV1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>Source: Effektmaaling af SMV:Digital, Danmarks Statistik for the Agency for Digital Government, June 2025 (DG3); scheme status from SMV:Digital's 2026 grant-pool page (SMV1).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="74" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Policy events</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Dated instruments, with the series each one bears on. Rendered as event tables beneath the figures they affect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>instrument</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>legal citation</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>what it does</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>series affected</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Lov om Offentlig Digital Post adopted</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>LOV nr 528 af 11/06/2012</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>RI1</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Creates the statutory basis for mandatory public digital post. Section 10 deems delivery effective on availability, not on the message being read.</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>DK.DGP.EXMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Digital Post becomes mandatory for businesses</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Lov om Offentlig Digital Post</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>DG4</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>Businesses are enrolled a year ahead of citizens.</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>DK.ECM.ENT.TRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>2014-11-01</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Digital Post becomes mandatory for citizens aged 15+</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Lov om Offentlig Digital Post</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>DG4</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Citizens are enrolled automatically whether or not they registered themselves. Exemption is available only against statutory criteria. This is the single most consequential date in this workbook.</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>DK.DGP.EXMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Rigsrevisionen reports on the Digital Post business case</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Beretning, January 2016</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>RR1</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Of an approx. DKK 1bn projected annual saving, only DKK 450m - postage, paper and envelopes - could be verified.</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>DK.GOV.DGP.SAVE.PLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>SMV:Digital launched</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>Danish digital growth plan for SMEs</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>DG3</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Grant scheme subsidising SME digitalisation projects.</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>DK.SME.SMVD.PROJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>MitID rollout begins</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>National electronic ID replacement programme</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>DG4</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Begins the migration of the whole population off NemID.</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>DK.TRU.DPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Kontantreglen amended</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Lov om betalinger, ss 81</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>RI2</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Businesses may refuse cash from other businesses; temporary events are exempted; the notification duty for 06:00-20:00 acceptance is removed. The obligation on shops to accept cash from consumers remains.</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>DK.PAY.CASH.POS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>MitID required for public digital services</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>National electronic ID replacement programme</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>DG4</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>From this date citizens need MitID for borger.dk, skat.dk and sundhed.dk.</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>DK.TRU.DPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>NemID fully phased out</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>National electronic ID replacement programme</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>DG4</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>The predecessor credential can no longer be obtained or used.</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>DK.TRU.DPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>SMV:Digital grant pools continue</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Tilskudspuljer i 2026</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>SMV1</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>The scheme is still operating and still awarding grants in 2026; a further pool opens on 26 October 2026. Recorded because an earlier draft of this workbook asserted the scheme was being defunded. It was not verifiable and the opposite is documented.</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>DK.SME.SMVD.PROJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>Reading: the mandate date of 1 November 2014 is the hinge of this workbook. Digital Post was not adopted by citizens choosing it; citizens were enrolled automatically, and exemption is available only against statutory criteria. Adoption rates after that date therefore measure compliance with a legal obligation, not revealed preference, and no figure in this workbook should be read as though they measured preference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>CORRECTION RECORDED: an earlier draft of this workbook stated that SMV:Digital was being defunded. That claim could not be verified, and the scheme's own 2026 grant-pool page (SMV1) documents pools still open, with a further pool opening on 26 October 2026. The claim has been withdrawn from the dataset and from the report's argument. See 07_LIMITATIONS and 08_AI_LOG.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2969,7 +4445,7 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="B4" s="41" t="inlineStr">
+      <c r="B4" s="43" t="inlineStr">
         <is>
           <t>NOT RETRIEVED</t>
         </is>
@@ -2981,7 +4457,7 @@
           <t>Indicator</t>
         </is>
       </c>
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>Retail trade turnover, volume index (mangdeindeks)</t>
         </is>
@@ -2993,7 +4469,7 @@
           <t>Authority</t>
         </is>
       </c>
-      <c r="B6" s="41" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>Danmarks Statistik; also available via Eurostat sts_trtu_a</t>
         </is>
@@ -3005,7 +4481,7 @@
           <t>Filters required</t>
         </is>
       </c>
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>geo=DK; nace_r2=G47; indic_bt=VOL; s_adj=SCA; unit=I21 (2021=100)</t>
         </is>
@@ -3017,7 +4493,7 @@
           <t>Why not retrieved</t>
         </is>
       </c>
-      <c r="B8" s="41" t="inlineStr">
+      <c r="B8" s="43" t="inlineStr">
         <is>
           <t>Values are published through StatBank and the Eurostat databrowser. This session's network policy blocked direct access to both, and the figure could not be verified by search. A value that cannot be traced is not entered.</t>
         </is>
@@ -3029,7 +4505,7 @@
           <t>Base year caution</t>
         </is>
       </c>
-      <c r="B9" s="41" t="inlineStr">
+      <c r="B9" s="43" t="inlineStr">
         <is>
           <t>Danmarks Statistik rebased the index from 2015=100 to 2021=100. Series retrieved on different bases must not be joined.</t>
         </is>
@@ -3041,7 +4517,7 @@
           <t>Effect on the analysis</t>
         </is>
       </c>
-      <c r="B10" s="41" t="inlineStr">
+      <c r="B10" s="43" t="inlineStr">
         <is>
           <t>The e-commerce section rests on the enterprise e-sales evidence in F3_ESALES instead, which is better sourced. No conclusion in the report depends on this series.</t>
         </is>
@@ -3053,7 +4529,7 @@
           <t>To fill</t>
         </is>
       </c>
-      <c r="B11" s="41" t="inlineStr">
+      <c r="B11" s="43" t="inlineStr">
         <is>
           <t>Retrieve from statistikbanken.dk, add rows to dataset.py under series_code DK.RET.VOL with unit 'index 2021=100', and re-run build_workbook.py.</t>
         </is>
@@ -3064,13 +4540,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3106,130 +4582,202 @@
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Unbalanced panel</t>
+          <t>Figure 6 sample is selected on the tails</t>
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>Observation years differ by series because the underlying sources publish on different cycles - payment habits roughly biennially, Eurostat annually, branch counts irregularly. Gaps are genuine and are not filled.</t>
+          <t>The adoption column in Figure 6 was assembled from a Eurostat press release naming the highest three countries, the lowest three, and three large movers. Most of the plotted points therefore come from the ends of the EU distribution. Selecting on the extremes of X inflates the correlation coefficient and R-squared regardless of the underlying relationship. The R-squared is an upper bound, not an estimate; the slope is the statistic to quote, alongside n. The chart deliberately does not display R-squared on its face. Fixing this requires the full 27-country isoc_ec_ib20 column.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="62" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Denominator break</t>
+          <t>No price deflator on the turnover series</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Danish online-purchasing figures change base between 2019 (% of individuals) and 2020 onward (% of internet users). The 2019 observation carries flag 'b' and is never plotted with later years.</t>
+          <t>E-sales as a share of enterprise turnover runs 2014 to 2024, spanning the pandemic and the 2022 inflation episode. Turnover is nominal, and online and physical retail did not face the same price path. Part of the measured rise in the e-sales share is therefore relative price movement rather than real reallocation of activity. No deflator was available in this session and none has been applied, so the doubling of intensity should be read as nominal.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="62" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Verbal quantities</t>
+          <t>Banking series use different base years</t>
         </is>
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>Values flagged 'e' were published as words, not figures - 'nearly one in five', 'just under 36,000'. They are recorded as the stated approximation with the original wording in the notes column.</t>
+          <t>Branch counts begin in 2004; institution counts and employment begin in 1991. A 2004-2024 branch change and a 1991-2024 employment change are not comparable, and placing the two percentages side by side in prose would misrepresent both. 05_CALC labels every window explicitly. Either state both windows or do not draw the comparison.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="62" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Confounded outcome</t>
+          <t>No sampling error is reported anywhere</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Branch closures reflect both digitalisation and sectoral consolidation (219 institutions in 1991, 51 in 2024). The branch series alone cannot separate these, and the report should not claim that it does.</t>
+          <t>The Eurostat, Nationalbank and Agency for Digital Government figures are survey estimates and carry sampling error that the issuing authorities publish but this workbook does not reproduce. Small differences should not be treated as established: a 2-3 point gap between two survey proportions, or between two eGovernment Benchmark scores, may not be distinguishable from zero. Directions are more robust than magnitudes throughout.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="62" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Definitional spread in exclusion measures</t>
+          <t>Headcount conversions rest on an implied denominator</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>The five exclusion measures range from 4.7% to 25% because they define the population differently. They are not competing estimates of one quantity and must not be averaged or presented as a range.</t>
+          <t>A published figure for the Danish population aged 15 and over could not be verified in this session. F4 therefore derives an implied 15+ base by dividing the exempt headcount by the exemption rate, both from the same source. Persons-affected figures built on it are orders of magnitude, not counts, and the capability shares they scale are measured on 'the population' rather than on the 15+ base - the denominators are not identical. Every such cell is marked in place.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="62" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Cross-section incomplete</t>
+          <t>A withdrawn claim about SMV:Digital</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>F5 covers 8 of 27 member states. It supports a ranking, not a regression.</t>
+          <t>An earlier draft of this workbook asserted that SMV:Digital was being defunded, and an argument was built on the contrast between a programme that works and a programme being cut. The claim could not be verified. The scheme's own 2026 grant-pool page documents pools still open and a further pool opening on 26 October 2026. The claim has been removed from the dataset and from the report's argument, and the correction is recorded in 09_POLICY and 08_AI_LOG rather than silently erased.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="62" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Figure 6 sample size</t>
+          <t>Unbalanced panel</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>The adoption-to-outcome scatter rests on 6 complete country pairs. The association is strong and positive, but 6 points cannot support a p-value, a confidence interval, or a claim about causal direction. Report the slope and R-squared descriptively and say n explicitly. Adding the missing values listed on that sheet raises n automatically.</t>
+          <t>Observation years differ by series because the underlying sources publish on different cycles - payment habits roughly biennially, Eurostat annually, branch counts irregularly. Gaps are genuine and are not filled.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="62" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Figure 6 measures two sides of the market</t>
+          <t>Denominator break</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>X is a consumer measure (individuals buying online); Y is an all-enterprise, all-sector measure that includes B2B and EDI ordering. A positive association indicates that digital commerce runs deep in an economy. It is not evidence that consumer purchasing causes enterprise turnover, and must not be written as though it were.</t>
+          <t>Danish online-purchasing figures change base between 2019 (% of individuals) and 2020 onward (% of internet users). The 2019 observation carries flag 'b' and is never plotted with later years.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="62" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Mirror-sourced column</t>
+          <t>Verbal quantities</t>
         </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>The 16 country-level e-sales turnover values flagged 'u' were retrieved via search of Eurostat tin00110 rather than from the databrowser directly. Two values in the same column (EU27 19.49 and Ireland 38.25) are independently corroborated by source ES5, which supports the column, but each value should be spot-checked against the databrowser before final submission.</t>
+          <t>Values flagged 'e' were published as words, not figures - 'nearly one in five', 'just under 36,000'. They are recorded as the stated approximation with the original wording in the notes column.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="62" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Search-based verification</t>
+          <t>Confounded outcome</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Direct access to statistical portals was blocked in the build environment. Values were verified against the issuing authority through search results reporting those publications. This is weaker than downloading the dataset: before final submission, spot-check high-stakes figures against the source pages directly.</t>
+          <t>Branch closures reflect both digitalisation and sectoral consolidation (219 institutions in 1991, 51 in 2024). The branch series alone cannot separate these, and the report should not claim that it does.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="62" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Definitional spread in exclusion measures</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>The five exclusion measures range from 4.7% to 25% because they define the population differently. They are not competing estimates of one quantity and must not be averaged or presented as a range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="62" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Cross-section incomplete</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>F5 covers 8 of 27 member states. It supports a ranking, not a regression.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="62" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Figure 6 sample size</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>The adoption-to-outcome scatter rests on 6 complete country pairs. The association is strong and positive, but 6 points cannot support a p-value, a confidence interval, or a claim about causal direction. Report the slope and R-squared descriptively and say n explicitly. Adding the missing values listed on that sheet raises n automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="62" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Figure 6 measures two sides of the market</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>X is a consumer measure (individuals buying online); Y is an all-enterprise, all-sector measure that includes B2B and EDI ordering. A positive association indicates that digital commerce runs deep in an economy. It is not evidence that consumer purchasing causes enterprise turnover, and must not be written as though it were.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="62" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Mirror-sourced column</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>The 16 country-level e-sales turnover values flagged 'u' were retrieved via search of Eurostat tin00110 rather than from the databrowser directly. Two values in the same column (EU27 19.49 and Ireland 38.25) are independently corroborated by source ES5, which supports the column, but each value should be spot-checked against the databrowser before final submission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="62" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Search-based verification</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>Direct access to statistical portals was blocked in the build environment. Values were verified against the issuing authority through search results reporting those publications. This is weaker than downloading the dataset: before final submission, spot-check high-stakes figures against the source pages directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="62" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
           <t>Discarded material</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>An earlier candidate dataset was rejected in full after verification found fabricated values carrying authentic dataset codes and extraction dates - including a Eurostat cross-section that inverted the true EU country ranking. None of it survives in this workbook.</t>
         </is>
@@ -3240,13 +4788,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3331,7 +4879,7 @@
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>69 observations retained.</t>
+          <t>Every retained observation carries a source_id.</t>
         </is>
       </c>
     </row>
@@ -3360,71 +4908,115 @@
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>Workbook construction</t>
+          <t>Withdrawal of an AI-suggested claim</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>AI wrote the Python build script that generates this workbook.</t>
+          <t>An AI-assisted draft asserted that the SMV:Digital grant scheme was being defunded, and an argument was built on the contrast between a programme with measured positive effects and a programme being cut.</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Structural assertions run at build time: source_ids resolve, units and denominators present, no duplicate observations, break flags set.</t>
+          <t>Searched for the scheme's funding status. The scheme's own 2026 grant-pool page documents pools still open and a further pool opening 26 October 2026. No source supported the defunding claim.</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>build_workbook.py, re-runnable.</t>
+          <t>Claim withdrawn from the dataset and the argument; the withdrawal is recorded in 09_POLICY and 07_LIMITATIONS rather than erased.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="52" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>Analytical framing</t>
+          <t>Statistical self-audit</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>AI used to interpret patterns and suggest framings.</t>
+          <t>AI was asked to audit its own workbook as a macroeconomic policy reviewer would.</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>Author reviewed each interpretation against the underlying values.</t>
+          <t>The audit found that Figure 6's adoption column had been assembled from a press release naming only the top three, bottom three and three large movers - a sample drawn from the tails, which inflates R-squared by construction.</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>Interpretations appear in the report, attributed to the author.</t>
+          <t>R-squared removed from the chart face; a SELECTION WARNING added to F6; the limitation recorded in 07_LIMITATIONS.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
+          <t>Workbook construction</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>AI wrote the Python build script that generates this workbook.</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Structural assertions run at build time: source_ids resolve, units and denominators present, no duplicate observations, break flags set.</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>build_workbook.py, re-runnable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Analytical framing</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>AI used to interpret patterns and suggest framings.</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Author reviewed each interpretation against the underlying values.</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Interpretations appear in the report, attributed to the author.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
           <t>Not delegated to AI</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Selection of the research question, country, industries, SDG and policy comparator; the argument; the conclusions.</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>Author's own work.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>This log records assistance during data assembly. Complete it with any further AI use during drafting before submission. The assessment requires that AI-assisted content be verified and acknowledged.</t>
         </is>
@@ -3656,7 +5248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8155,8 +9747,280 @@
       </c>
       <c r="L88" s="15" t="inlineStr"/>
     </row>
+    <row r="89">
+      <c r="A89" s="13" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>DK.POP.TOT</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="inlineStr">
+        <is>
+          <t>Resident population</t>
+        </is>
+      </c>
+      <c r="D89" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E89" s="13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F89" s="17" t="n">
+        <v>6025603</v>
+      </c>
+      <c r="G89" s="13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H89" s="15" t="inlineStr">
+        <is>
+          <t>persons resident in Denmark</t>
+        </is>
+      </c>
+      <c r="I89" s="13" t="inlineStr"/>
+      <c r="J89" s="14" t="inlineStr">
+        <is>
+          <t>DST2</t>
+        </is>
+      </c>
+      <c r="K89" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L89" s="15" t="inlineStr">
+        <is>
+          <t>As at 1 January 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="18" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="19" t="inlineStr">
+        <is>
+          <t>DK.DGP.EXMP.N</t>
+        </is>
+      </c>
+      <c r="C90" s="20" t="inlineStr">
+        <is>
+          <t>Citizens formally exempt from Digital Post</t>
+        </is>
+      </c>
+      <c r="D90" s="18" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F90" s="21" t="n">
+        <v>256000</v>
+      </c>
+      <c r="G90" s="18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H90" s="20" t="inlineStr">
+        <is>
+          <t>citizens aged 15+ resident in Denmark</t>
+        </is>
+      </c>
+      <c r="I90" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J90" s="19" t="inlineStr">
+        <is>
+          <t>DG1</t>
+        </is>
+      </c>
+      <c r="K90" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L90" s="20" t="inlineStr">
+        <is>
+          <t>April 2025; source states approx. 256,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="14" t="inlineStr">
+        <is>
+          <t>DK.DGP.EXMP.N</t>
+        </is>
+      </c>
+      <c r="C91" s="15" t="inlineStr">
+        <is>
+          <t>Citizens formally exempt from Digital Post</t>
+        </is>
+      </c>
+      <c r="D91" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E91" s="13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F91" s="17" t="n">
+        <v>238479</v>
+      </c>
+      <c r="G91" s="13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H91" s="15" t="inlineStr">
+        <is>
+          <t>citizens aged 15+ resident in Denmark</t>
+        </is>
+      </c>
+      <c r="I91" s="13" t="inlineStr"/>
+      <c r="J91" s="14" t="inlineStr">
+        <is>
+          <t>DG1</t>
+        </is>
+      </c>
+      <c r="K91" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L91" s="15" t="inlineStr">
+        <is>
+          <t>Q1 2026. Paired with the 4.7% rate, implies a 15+ base of about 5.07m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="18" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="19" t="inlineStr">
+        <is>
+          <t>DK.GOV.DGP.SAVE.PLAN</t>
+        </is>
+      </c>
+      <c r="C92" s="20" t="inlineStr">
+        <is>
+          <t>Digital Post: projected annual public saving</t>
+        </is>
+      </c>
+      <c r="D92" s="18" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E92" s="18" t="n">
+        <v>2016</v>
+      </c>
+      <c r="F92" s="22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G92" s="18" t="inlineStr">
+        <is>
+          <t>million DKK per year</t>
+        </is>
+      </c>
+      <c r="H92" s="20" t="inlineStr">
+        <is>
+          <t>projected annual saving, whole public sector</t>
+        </is>
+      </c>
+      <c r="I92" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J92" s="19" t="inlineStr">
+        <is>
+          <t>RR1</t>
+        </is>
+      </c>
+      <c r="K92" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L92" s="20" t="inlineStr">
+        <is>
+          <t>Ministry of Finance business case; Rigsrevisionen reports it as 'approx. 1bn'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="18" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="19" t="inlineStr">
+        <is>
+          <t>DK.GOV.DGP.SAVE.VERIF</t>
+        </is>
+      </c>
+      <c r="C93" s="20" t="inlineStr">
+        <is>
+          <t>Digital Post: annual saving verifiable by audit</t>
+        </is>
+      </c>
+      <c r="D93" s="18" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E93" s="18" t="n">
+        <v>2016</v>
+      </c>
+      <c r="F93" s="22" t="n">
+        <v>450</v>
+      </c>
+      <c r="G93" s="18" t="inlineStr">
+        <is>
+          <t>million DKK per year</t>
+        </is>
+      </c>
+      <c r="H93" s="20" t="inlineStr">
+        <is>
+          <t>verified annual saving, whole public sector</t>
+        </is>
+      </c>
+      <c r="I93" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J93" s="19" t="inlineStr">
+        <is>
+          <t>RR1</t>
+        </is>
+      </c>
+      <c r="K93" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L93" s="20" t="inlineStr">
+        <is>
+          <t>Postage, paper and envelopes only. The wage and overhead component was never verified: the cross-government study was abandoned after KL declined to take part.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L88"/>
+  <autoFilter ref="A1:L93"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8167,7 +10031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8783,35 +10647,208 @@
     <row r="18" ht="46" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
         <is>
+          <t>RR1</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Rigsrevisionen (Danish National Audit Office)</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Beretning om besparelsespotentialet ved obligatorisk Digital Post paa ca. 1 mia. kr. om aaret, January 2016</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr"/>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>https://www.rigsrevisionen.dk/revisionssager-arkiv/2016/jan/beretning-om-besparelsespotentialet-ved-obligatorisk-digital-post-paa-ca-1-mia-kr-om-aaret</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>Rigsrevisionen 2016, Beretning om besparelsespotentialet ved obligatorisk Digital Post paa ca. 1 mia. kr. om aaret, National Audit Office of Denmark, Copenhagen, accessed 12 September 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>RI2</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Finanstilsynet (Danish Financial Supervisory Authority)</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Kontantreglen - lov om betalinger section 81</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Lov om betalinger, ss 81</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>https://www.finanstilsynet.dk/finansielle-temaer/betalingstjenester-og-e-penge/kontantreglen</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>Finanstilsynet 2025, Kontantreglen, Danish Financial Supervisory Authority, Copenhagen, accessed 12 September 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>DG4</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Digitaliseringsstyrelsen (Danish Agency for Digital Government)</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Digital Post - lovgivning, and the MitID transition news archive</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr"/>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>https://digst.dk/it-loesninger/digital-post/lovgivning/</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>Digitaliseringsstyrelsen 2025, Digital Post - lovgivning, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>SMV1</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>SMV:Digital (Danish SME digitalisation grant scheme)</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Tilskudspuljer i 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>https://smvdigital.dk/content/ydelser/tilskudspuljer-i-2026/8efa07f4-5032-47f4-b7fa-bab57412b762/</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>SMV:Digital 2026, Tilskudspuljer i 2026, SMV:Digital, Copenhagen, accessed 12 September 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="46" customHeight="1">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>DST2</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Danmarks Statistik</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Befolkningstal (population figures)</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>StatBank FOLK1A</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>https://www.dst.dk/da/Statistik/emner/borgere/befolkning/befolkningstal</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>Danmarks Statistik 2026, Befolkningstal, Statistics Denmark, Copenhagen, accessed 12 September 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="46" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
           <t>DST1</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>Danmarks Statistik</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>Detailomsaetningsindeks (retail trade turnover index)</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>StatBank; base year rebased 2015 -&gt; 2021</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>https://www.dst.dk/da/Statistik/dokumentation/statistikdokumentation/detailomsaetningsindeks</t>
         </is>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G18" s="15" t="inlineStr">
+      <c r="G23" s="15" t="inlineStr">
         <is>
           <t>Danmarks Statistik 2025, Detailomsaetningsindeks, Statistics Denmark, Copenhagen, accessed 12 September 2026.</t>
         </is>
@@ -9085,7 +11122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -9463,6 +11500,153 @@
       <c r="D20" s="29" t="inlineStr">
         <is>
           <t>Trust in the mandated system over the mandate period (CLO4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>Digital Post: projected annual saving</t>
+        </is>
+      </c>
+      <c r="B21" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.PLAN",'02_MASTER'!$E:$E,2016)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.PLAN",'02_MASTER'!$E:$E,2016))</f>
+        <v/>
+      </c>
+      <c r="C21" s="28" t="inlineStr">
+        <is>
+          <t>mDKK/yr</t>
+        </is>
+      </c>
+      <c r="D21" s="29" t="inlineStr">
+        <is>
+          <t>Ministry of Finance business case for the mandate (RR1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>Digital Post: saving verifiable by audit</t>
+        </is>
+      </c>
+      <c r="B22" s="31">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.VERIF",'02_MASTER'!$E:$E,2016)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.VERIF",'02_MASTER'!$E:$E,2016))</f>
+        <v/>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>mDKK/yr</t>
+        </is>
+      </c>
+      <c r="D22" s="29" t="inlineStr">
+        <is>
+          <t>Postage, paper and envelopes only (RR1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>Digital Post: unverified share of the business case</t>
+        </is>
+      </c>
+      <c r="B23" s="30">
+        <f>1-(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.VERIF",'02_MASTER'!$E:$E,2016)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.VERIF",'02_MASTER'!$E:$E,2016))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.PLAN",'02_MASTER'!$E:$E,2016)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.PLAN",'02_MASTER'!$E:$E,2016)))</f>
+        <v/>
+      </c>
+      <c r="C23" s="28" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D23" s="29" t="inlineStr">
+        <is>
+          <t>Over half the projected saving - the wage and overhead component - was never substantiated. The cross-government study intended to test it was abandoned. The strongest cost-side finding in this workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>Digital Post: cost per formally exempt citizen, if the shortfall is real</t>
+        </is>
+      </c>
+      <c r="B24" s="31">
+        <f>((IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.PLAN",'02_MASTER'!$E:$E,2016)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.PLAN",'02_MASTER'!$E:$E,2016))-IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.VERIF",'02_MASTER'!$E:$E,2016)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.VERIF",'02_MASTER'!$E:$E,2016)))*1000000)/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026))</f>
+        <v/>
+      </c>
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>DKK</t>
+        </is>
+      </c>
+      <c r="D24" s="29" t="inlineStr">
+        <is>
+          <t>ILLUSTRATIVE ONLY, and not a real unit cost: it divides an unverified saving shortfall by an unrelated headcount. Included because the comparison of magnitudes is informative; it must not be quoted as a cost per person.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>Resident population, 1 January 2026</t>
+        </is>
+      </c>
+      <c r="B25" s="27">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.POP.TOT",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.POP.TOT",'02_MASTER'!$E:$E,2026))</f>
+        <v/>
+      </c>
+      <c r="C25" s="28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="D25" s="29" t="inlineStr">
+        <is>
+          <t>Direct lookup. The only population level in the workbook (DST2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>Citizens formally exempt from Digital Post, Q1 2026</t>
+        </is>
+      </c>
+      <c r="B26" s="27">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026))</f>
+        <v/>
+      </c>
+      <c r="C26" s="28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="D26" s="29" t="inlineStr">
+        <is>
+          <t>Headcount behind the 4.7% rate (DG1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>Change in exempt headcount, 2025 to 2026</t>
+        </is>
+      </c>
+      <c r="B27" s="27">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026))-IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C27" s="28" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="D27" s="29" t="inlineStr">
+        <is>
+          <t>Falling. Note the 2025 figure is an 'approximately' value, so this difference is not precise.</t>
         </is>
       </c>
     </row>
@@ -9583,11 +11767,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -9748,8 +11935,69 @@
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="32" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>POLICY EVENTS ON THIS SERIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>instrument</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Kontantreglen amended</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Lov om betalinger, ss 81</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>RI2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="32" t="inlineStr">
         <is>
           <t>Source: Danmarks Nationalbank, Danskernes betalingsvaner (NB1). Panel B sums to 95%, not 100%: the residual is other digital instruments (chiefly account transfers and non-card mobile payments). Wallet payments ARE card payments settled through a phone, so the wallet and physical-card rows must not be added to produce a 'card' total. The memo series is excluded from both panels because its denominator is % of citizens, not % of payments. Physical card and wallet shares are observed in 2025 only, so no time series is drawn for them - a two-point line through an unobserved middle would assert a path the data does not contain.</t>
         </is>
@@ -9767,12 +12015,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -9900,8 +12150,69 @@
       </c>
       <c r="C13" s="28" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="32" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>POLICY EVENTS ON THIS SERIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>instrument</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Digital Post becomes mandatory for businesses</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Lov om Offentlig Digital Post</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>DG4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t>Source: Eurostat (ES5). Reading: Denmark's e-sales share of turnover rose from 17.05% to 33.31% while the EU average moved from 16.43% to 19.49%. Breadth of adoption is flat at roughly 38% of enterprises; intensity nearly doubled. The growth came from incumbents selling more online, not from new firms entering.</t>
         </is>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -35,11 +35,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="+0.00;-0.00"/>
+    <numFmt numFmtId="165" formatCode="_(#,##0_);\(#,##0\);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
+    <numFmt numFmtId="166" formatCode="_(#,##0.0_);\(#,##0.0\);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
+    <numFmt numFmtId="167" formatCode="_(#,##0.00_);\(#,##0.00\);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
+    <numFmt numFmtId="168" formatCode="_(#,##0.000_);\(#,##0.000\);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
+    <numFmt numFmtId="169" formatCode="_(+#,##0.00_);_(-#,##0.00_);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -94,7 +96,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -126,6 +128,11 @@
         <fgColor rgb="FFF7E4E4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F2FF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -153,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -214,16 +221,20 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -310,23 +321,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Bank branches in Denmark, 2004-2024</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
     <plotArea>
       <scatterChart>
         <ser>
@@ -339,6 +334,9 @@
           </tx>
           <spPr>
             <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="2E6DB4"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -346,7 +344,11 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E6DB4"/>
+              </a:solidFill>
               <a:ln>
+                <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -373,7 +375,6 @@
           <min val="2002"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -391,6 +392,12 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="20"/>
       </valAx>
       <valAx>
@@ -400,7 +407,6 @@
           <min val="0"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -418,12 +424,15 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -432,23 +441,7 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Cash share of in-store payments, 2017-2025</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
     <plotArea>
       <scatterChart>
         <ser>
@@ -461,6 +454,9 @@
           </tx>
           <spPr>
             <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="2E6DB4"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -468,7 +464,11 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E6DB4"/>
+              </a:solidFill>
               <a:ln>
+                <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -495,7 +495,6 @@
           <min val="2016"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -513,6 +512,12 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="20"/>
       </valAx>
       <valAx>
@@ -523,7 +528,6 @@
           <min val="0"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -541,6 +545,12 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
@@ -552,23 +562,7 @@
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Composition of in-store payments, 2025</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
     <plotArea>
       <barChart>
         <barDir val="bar"/>
@@ -582,10 +576,50 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="A3A3A3"/>
+            </a:solidFill>
             <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E6DB4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
               <f>'F2_PAYMENTS'!$A$12:$A$14</f>
@@ -597,7 +631,7 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <gapWidth val="80"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -624,6 +658,12 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -633,9 +673,14 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
@@ -647,23 +692,7 @@
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>E-sales as % of enterprise turnover</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
     <plotArea>
       <barChart>
         <barDir val="col"/>
@@ -677,7 +706,11 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2E6DB4"/>
+            </a:solidFill>
             <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -701,7 +734,11 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="A3A3A3"/>
+            </a:solidFill>
             <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -716,7 +753,8 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <gapWidth val="80"/>
+        <overlap val="-27"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -743,6 +781,12 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -752,7 +796,6 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -770,11 +813,18 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -784,23 +834,7 @@
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Measures of digital exclusion, Denmark</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
     <plotArea>
       <barChart>
         <barDir val="bar"/>
@@ -814,7 +848,11 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2E6DB4"/>
+            </a:solidFill>
             <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -829,7 +867,7 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <gapWidth val="80"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -856,6 +894,12 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -865,9 +909,14 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
@@ -879,23 +928,7 @@
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Individuals who bought online in last 12 months, 2024</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
     <plotArea>
       <barChart>
         <barDir val="bar"/>
@@ -909,10 +942,110 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="A3A3A3"/>
+            </a:solidFill>
             <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E6DB4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F3A5F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="6"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
               <f>'F5_EU8'!$A$5:$A$12</f>
@@ -924,7 +1057,7 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <gapWidth val="80"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -951,6 +1084,12 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -960,9 +1099,14 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
@@ -974,23 +1118,7 @@
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Digital adoption and e-commerce turnover, EU 2024</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
     <plotArea>
       <scatterChart>
         <ser>
@@ -1011,12 +1139,24 @@
             <symbol val="circle"/>
             <size val="9"/>
             <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E6DB4"/>
+              </a:solidFill>
               <a:ln>
+                <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <trendline>
+            <spPr>
+              <a:ln w="16000">
+                <a:solidFill>
+                  <a:srgbClr val="A3A3A3"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
             <trendlineType val="linear"/>
             <dispRSqr val="0"/>
             <dispEq val="1"/>
@@ -1043,7 +1183,6 @@
           <min val="50"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -1061,6 +1200,12 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="20"/>
       </valAx>
       <valAx>
@@ -1070,7 +1215,6 @@
           <min val="0"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <title>
           <tx>
             <rich>
@@ -1088,6 +1232,12 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
@@ -1099,23 +1249,7 @@
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Denmark vs EU-27 average</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
     <plotArea>
       <barChart>
         <barDir val="bar"/>
@@ -1129,7 +1263,11 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2E6DB4"/>
+            </a:solidFill>
             <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1153,7 +1291,11 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="A3A3A3"/>
+            </a:solidFill>
             <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1168,7 +1310,8 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <gapWidth val="80"/>
+        <overlap val="-27"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -1195,6 +1338,12 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1204,14 +1353,20 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1221,23 +1376,7 @@
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>SMV:Digital participant outcomes</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
     <plotArea>
       <barChart>
         <barDir val="bar"/>
@@ -1251,7 +1390,11 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2E6DB4"/>
+            </a:solidFill>
             <a:ln>
+              <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1266,7 +1409,7 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <gapWidth val="80"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -1293,6 +1436,12 @@
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1302,9 +1451,14 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
@@ -2224,7 +2378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2402,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="F3" s="32" t="inlineStr">
+        <is>
+          <t>Measures of digital exclusion, Denmark</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2269,6 +2430,11 @@
           <t>source</t>
         </is>
       </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>Five definitions of the same phenomenon; they are nested, not contradictory.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
@@ -2276,7 +2442,7 @@
           <t>Formally exempt from Digital Post (Q1 2026)</t>
         </is>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026))</f>
         <v/>
       </c>
@@ -2285,7 +2451,7 @@
           <t>administrative status</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="39" t="inlineStr">
         <is>
           <t>DG1</t>
         </is>
@@ -2297,7 +2463,7 @@
           <t>Do not use digital public services at all</t>
         </is>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.NOUSE",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.NOUSE",'02_MASTER'!$E:$E,2026))</f>
         <v/>
       </c>
@@ -2306,7 +2472,7 @@
           <t>self-reported non-use</t>
         </is>
       </c>
-      <c r="D6" s="36" t="inlineStr">
+      <c r="D6" s="39" t="inlineStr">
         <is>
           <t>EC1</t>
         </is>
@@ -2318,7 +2484,7 @@
           <t>Face difficulties using digital public services</t>
         </is>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.DIFF",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.DIFF",'02_MASTER'!$E:$E,2026))</f>
         <v/>
       </c>
@@ -2327,7 +2493,7 @@
           <t>capability estimate</t>
         </is>
       </c>
-      <c r="D7" s="36" t="inlineStr">
+      <c r="D7" s="39" t="inlineStr">
         <is>
           <t>EC1</t>
         </is>
@@ -2339,7 +2505,7 @@
           <t>'Digitally disadvantaged' - lower bound</t>
         </is>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.DISADV.LO",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.DISADV.LO",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
@@ -2348,7 +2514,7 @@
           <t>capability estimate (range)</t>
         </is>
       </c>
-      <c r="D8" s="36" t="inlineStr">
+      <c r="D8" s="39" t="inlineStr">
         <is>
           <t>DG2</t>
         </is>
@@ -2360,7 +2526,7 @@
           <t>'Digitally disadvantaged' - upper bound</t>
         </is>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.DISADV.HI",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.DISADV.HI",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
@@ -2369,7 +2535,7 @@
           <t>capability estimate (range)</t>
         </is>
       </c>
-      <c r="D9" s="36" t="inlineStr">
+      <c r="D9" s="39" t="inlineStr">
         <is>
           <t>DG2</t>
         </is>
@@ -2381,7 +2547,7 @@
           <t>'Digitally disadvantaged' - Justitia</t>
         </is>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.JUST",'02_MASTER'!$E:$E,2022)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.JUST",'02_MASTER'!$E:$E,2022))</f>
         <v/>
       </c>
@@ -2390,7 +2556,7 @@
           <t>broadest definition</t>
         </is>
       </c>
-      <c r="D10" s="36" t="inlineStr">
+      <c r="D10" s="39" t="inlineStr">
         <is>
           <t>JU1</t>
         </is>
@@ -2421,7 +2587,7 @@
           <t>Age 75-84</t>
         </is>
       </c>
-      <c r="B14" s="34">
+      <c r="B14" s="36">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.7584",'02_MASTER'!$E:$E,2022)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.7584",'02_MASTER'!$E:$E,2022))</f>
         <v/>
       </c>
@@ -2432,7 +2598,7 @@
           <t>Age 85+</t>
         </is>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="36">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.85P",'02_MASTER'!$E:$E,2022)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.85P",'02_MASTER'!$E:$E,2022))</f>
         <v/>
       </c>
@@ -2467,7 +2633,7 @@
           <t>Citizens formally exempt, Q1 2026</t>
         </is>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="33">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026))</f>
         <v/>
       </c>
@@ -2483,7 +2649,7 @@
           <t>Citizens formally exempt, April 2025</t>
         </is>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="33">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
@@ -2499,7 +2665,7 @@
           <t>Implied population aged 15+</t>
         </is>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="33">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026))/(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026))/100)</f>
         <v/>
       </c>
@@ -2515,7 +2681,7 @@
           <t>Implied persons who do not use digital public services at all</t>
         </is>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="33">
         <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.NOUSE",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.NOUSE",'02_MASTER'!$E:$E,2026))/100)*(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026))/(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026))/100))</f>
         <v/>
       </c>
@@ -2531,7 +2697,7 @@
           <t>Implied persons facing difficulty with digital public services</t>
         </is>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="33">
         <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.DIFF",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.DIFF",'02_MASTER'!$E:$E,2026))/100)*(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026))/(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026))/100))</f>
         <v/>
       </c>
@@ -2630,7 +2796,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="inlineStr">
+      <c r="A30" s="34" t="inlineStr">
         <is>
           <t>Sources: DG1, DG2, EC1, JU1. Reading: the measures are nested rather than contradictory. Formal exemption (4.7%) is an administrative status; the capability measures are three to five times larger. The statutory exemption regime therefore reaches only a minority of the citizens the state's own agency counts as struggling. Which measure is chosen determines the conclusion - so the choice must be argued, not assumed.</t>
         </is>
@@ -2648,7 +2814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2670,6 +2836,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="E3" s="32" t="inlineStr">
+        <is>
+          <t>Individuals who bought online, 2024</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2686,6 +2859,11 @@
           <t>series_code</t>
         </is>
       </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>Denmark in blue, EU-27 average in navy, other members in grey.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
@@ -2693,11 +2871,11 @@
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>IE.ECM.IND.BUY</t>
         </is>
@@ -2709,11 +2887,11 @@
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"NL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"NL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="39" t="inlineStr">
         <is>
           <t>NL.ECM.IND.BUY</t>
         </is>
@@ -2725,11 +2903,11 @@
           <t>Denmark</t>
         </is>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="C7" s="39" t="inlineStr">
         <is>
           <t>DK.ECM.IND.BUY</t>
         </is>
@@ -2741,11 +2919,11 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C8" s="36" t="inlineStr">
+      <c r="C8" s="39" t="inlineStr">
         <is>
           <t>DE.ECM.IND.BUY</t>
         </is>
@@ -2757,11 +2935,11 @@
           <t>EU-27 average</t>
         </is>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C9" s="36" t="inlineStr">
+      <c r="C9" s="39" t="inlineStr">
         <is>
           <t>EU.ECM.IND.BUY</t>
         </is>
@@ -2773,11 +2951,11 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C10" s="36" t="inlineStr">
+      <c r="C10" s="39" t="inlineStr">
         <is>
           <t>IT.ECM.IND.BUY</t>
         </is>
@@ -2789,11 +2967,11 @@
           <t>Romania</t>
         </is>
       </c>
-      <c r="B11" s="33">
+      <c r="B11" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"RO.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"RO.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C11" s="36" t="inlineStr">
+      <c r="C11" s="39" t="inlineStr">
         <is>
           <t>RO.ECM.IND.BUY</t>
         </is>
@@ -2805,18 +2983,18 @@
           <t>Bulgaria</t>
         </is>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"BG.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"BG.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="C12" s="39" t="inlineStr">
         <is>
           <t>BG.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>Source: Eurostat (ES4). SCOPE LIMIT: 8 of 27 member states were verified, so this sheet presents a ranking and makes no regression claim. To extend it, add the remaining member states to dataset.py using the series_code pattern XX.ECM.IND.BUY and re-run the build; this sheet and its chart will expand automatically. Denominator is % of internet users, not % of individuals.</t>
         </is>
@@ -2834,7 +3012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2857,6 +3035,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="F3" s="32" t="inlineStr">
+        <is>
+          <t>Digital adoption and e-commerce turnover, EU 2024</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -2878,6 +3063,11 @@
           <t>Y: e-sales share of turnover (%)</t>
         </is>
       </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>One point per country. Read the SELECTION WARNING below before quoting the fit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
@@ -2885,16 +3075,16 @@
           <t>Bulgaria</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>BG</t>
         </is>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"BG.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"BG.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"BG.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"BG.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
@@ -2905,16 +3095,16 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
@@ -2925,16 +3115,16 @@
           <t>Denmark</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
@@ -2945,16 +3135,16 @@
           <t>Hungary</t>
         </is>
       </c>
-      <c r="B8" s="36" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"HU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"HU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"HU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"HU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
@@ -2965,16 +3155,16 @@
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B9" s="36" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
@@ -2985,16 +3175,16 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="B10" s="36" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IT.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IT.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
@@ -3029,7 +3219,7 @@
           <t>n (countries)</t>
         </is>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="33">
         <f>COUNT($C$5:$C$10)</f>
         <v/>
       </c>
@@ -3045,7 +3235,7 @@
           <t>Slope</t>
         </is>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="40">
         <f>SLOPE($D$5:$D$10,$C$5:$C$10)</f>
         <v/>
       </c>
@@ -3061,7 +3251,7 @@
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="38">
         <f>INTERCEPT($D$5:$D$10,$C$5:$C$10)</f>
         <v/>
       </c>
@@ -3077,7 +3267,7 @@
           <t>Correlation (r)</t>
         </is>
       </c>
-      <c r="B17" s="38">
+      <c r="B17" s="40">
         <f>CORREL($C$5:$C$10,$D$5:$D$10)</f>
         <v/>
       </c>
@@ -3093,7 +3283,7 @@
           <t>R-squared</t>
         </is>
       </c>
-      <c r="B18" s="38">
+      <c r="B18" s="40">
         <f>RSQ($D$5:$D$10,$C$5:$C$10)</f>
         <v/>
       </c>
@@ -3109,7 +3299,7 @@
           <t>Denmark: actual Y</t>
         </is>
       </c>
-      <c r="B19" s="31">
+      <c r="B19" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
@@ -3125,7 +3315,7 @@
           <t>Denmark: fitted Y</t>
         </is>
       </c>
-      <c r="B20" s="31">
+      <c r="B20" s="38">
         <f>INTERCEPT($D$5:$D$10,$C$5:$C$10)+SLOPE($D$5:$D$10,$C$5:$C$10)*IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
@@ -3141,7 +3331,7 @@
           <t>Denmark: residual</t>
         </is>
       </c>
-      <c r="B21" s="39">
+      <c r="B21" s="41">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))-(INTERCEPT($D$5:$D$10,$C$5:$C$10)+SLOPE($D$5:$D$10,$C$5:$C$10)*IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)))</f>
         <v/>
       </c>
@@ -3159,54 +3349,54 @@
       </c>
     </row>
     <row r="24" ht="46" customHeight="1">
-      <c r="A24" s="40" t="inlineStr">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>HOW THE SAMPLE WAS DRAWN: the X column (consumer adoption) was not available as a complete Eurostat table in this session. The values come from a Eurostat press release, which names the three highest countries, the three lowest, and three large movers - a sample concentrated in the TAILS of the adoption distribution.</t>
         </is>
       </c>
-      <c r="B24" s="41" t="n"/>
-      <c r="C24" s="41" t="n"/>
-      <c r="D24" s="41" t="n"/>
+      <c r="B24" s="43" t="n"/>
+      <c r="C24" s="43" t="n"/>
+      <c r="D24" s="43" t="n"/>
     </row>
     <row r="25" ht="46" customHeight="1">
-      <c r="A25" s="40" t="inlineStr">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>CONSEQUENCE: of the 6 countries plotted, 5 come from the top or bottom of the EU ranking. Selecting on the extremes of X and dropping the middle inflates the correlation coefficient and R-squared by construction, because it widens the spread in X relative to the scatter around the line.</t>
         </is>
       </c>
-      <c r="B25" s="41" t="n"/>
-      <c r="C25" s="41" t="n"/>
-      <c r="D25" s="41" t="n"/>
+      <c r="B25" s="43" t="n"/>
+      <c r="C25" s="43" t="n"/>
+      <c r="D25" s="43" t="n"/>
     </row>
     <row r="26" ht="46" customHeight="1">
-      <c r="A26" s="40" t="inlineStr">
+      <c r="A26" s="42" t="inlineStr">
         <is>
           <t>HOW TO USE THIS FIGURE HONESTLY: report the SLOPE, which is far less sensitive to this kind of selection, and report n. Treat the R-squared as an upper bound. Do not describe the fit as 'strong' or 'tight', and do not compute a p-value or confidence interval from these points.</t>
         </is>
       </c>
-      <c r="B26" s="41" t="n"/>
-      <c r="C26" s="41" t="n"/>
-      <c r="D26" s="41" t="n"/>
+      <c r="B26" s="43" t="n"/>
+      <c r="C26" s="43" t="n"/>
+      <c r="D26" s="43" t="n"/>
     </row>
     <row r="27" ht="46" customHeight="1">
-      <c r="A27" s="40" t="inlineStr">
+      <c r="A27" s="42" t="inlineStr">
         <is>
           <t>HOW TO FIX IT: retrieve Eurostat isoc_ec_ib20 for 2024 for all 27 member states from the databrowser and add the rows to dataset.py. That removes the selection entirely and roughly triples n. The register below names every country still missing and the exact series code for each.</t>
         </is>
       </c>
-      <c r="B27" s="41" t="n"/>
-      <c r="C27" s="41" t="n"/>
-      <c r="D27" s="41" t="n"/>
+      <c r="B27" s="43" t="n"/>
+      <c r="C27" s="43" t="n"/>
+      <c r="D27" s="43" t="n"/>
     </row>
     <row r="28" ht="46" customHeight="1">
-      <c r="A28" s="40" t="inlineStr">
+      <c r="A28" s="42" t="inlineStr">
         <is>
           <t>DIRECTION OF CAUSATION IS NOT ESTABLISHED AND CANNOT BE. X measures consumers; Y measures enterprises, including business-to-business sales that no consumer touches. Both plausibly rise with national income, which is in neither axis. This figure shows that digital commerce runs deep in the same economies where consumers buy online. It does not show that the one produces the other.</t>
         </is>
       </c>
-      <c r="B28" s="41" t="n"/>
-      <c r="C28" s="41" t="n"/>
-      <c r="D28" s="41" t="n"/>
+      <c r="B28" s="43" t="n"/>
+      <c r="C28" s="43" t="n"/>
+      <c r="D28" s="43" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -3238,12 +3428,12 @@
           <t>Austria</t>
         </is>
       </c>
-      <c r="B32" s="36" t="inlineStr">
+      <c r="B32" s="39" t="inlineStr">
         <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="C32" s="42" t="inlineStr">
+      <c r="C32" s="44" t="inlineStr">
         <is>
           <t>X - add AT.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
@@ -3255,12 +3445,12 @@
           <t>Belgium</t>
         </is>
       </c>
-      <c r="B33" s="36" t="inlineStr">
+      <c r="B33" s="39" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="C33" s="42" t="inlineStr">
+      <c r="C33" s="44" t="inlineStr">
         <is>
           <t>X - add BE.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
@@ -3272,12 +3462,12 @@
           <t>Cyprus</t>
         </is>
       </c>
-      <c r="B34" s="36" t="inlineStr">
+      <c r="B34" s="39" t="inlineStr">
         <is>
           <t>CY</t>
         </is>
       </c>
-      <c r="C34" s="42" t="inlineStr">
+      <c r="C34" s="44" t="inlineStr">
         <is>
           <t>X - add CY.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
@@ -3289,12 +3479,12 @@
           <t>Czechia</t>
         </is>
       </c>
-      <c r="B35" s="36" t="inlineStr">
+      <c r="B35" s="39" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="C35" s="42" t="inlineStr">
+      <c r="C35" s="44" t="inlineStr">
         <is>
           <t>X - add CZ.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
@@ -3306,12 +3496,12 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="B36" s="36" t="inlineStr">
+      <c r="B36" s="39" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="C36" s="42" t="inlineStr">
+      <c r="C36" s="44" t="inlineStr">
         <is>
           <t>X - add ES.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
@@ -3323,12 +3513,12 @@
           <t>France</t>
         </is>
       </c>
-      <c r="B37" s="36" t="inlineStr">
+      <c r="B37" s="39" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C37" s="42" t="inlineStr">
+      <c r="C37" s="44" t="inlineStr">
         <is>
           <t>X - add FR.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
@@ -3340,12 +3530,12 @@
           <t>Croatia</t>
         </is>
       </c>
-      <c r="B38" s="36" t="inlineStr">
+      <c r="B38" s="39" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="C38" s="42" t="inlineStr">
+      <c r="C38" s="44" t="inlineStr">
         <is>
           <t>X - add HR.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
@@ -3357,12 +3547,12 @@
           <t>Luxembourg</t>
         </is>
       </c>
-      <c r="B39" s="36" t="inlineStr">
+      <c r="B39" s="39" t="inlineStr">
         <is>
           <t>LU</t>
         </is>
       </c>
-      <c r="C39" s="42" t="inlineStr">
+      <c r="C39" s="44" t="inlineStr">
         <is>
           <t>X - add LU.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
@@ -3374,12 +3564,12 @@
           <t>Malta</t>
         </is>
       </c>
-      <c r="B40" s="36" t="inlineStr">
+      <c r="B40" s="39" t="inlineStr">
         <is>
           <t>MT</t>
         </is>
       </c>
-      <c r="C40" s="42" t="inlineStr">
+      <c r="C40" s="44" t="inlineStr">
         <is>
           <t>X - add MT.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
@@ -3391,12 +3581,12 @@
           <t>Poland</t>
         </is>
       </c>
-      <c r="B41" s="36" t="inlineStr">
+      <c r="B41" s="39" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="C41" s="42" t="inlineStr">
+      <c r="C41" s="44" t="inlineStr">
         <is>
           <t>X - add PL.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
@@ -3408,12 +3598,12 @@
           <t>Sweden</t>
         </is>
       </c>
-      <c r="B42" s="36" t="inlineStr">
+      <c r="B42" s="39" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="C42" s="42" t="inlineStr">
+      <c r="C42" s="44" t="inlineStr">
         <is>
           <t>X - add SE.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
@@ -3425,12 +3615,12 @@
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="B43" s="36" t="inlineStr">
+      <c r="B43" s="39" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="C43" s="42" t="inlineStr">
+      <c r="C43" s="44" t="inlineStr">
         <is>
           <t>X - add SI.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
         </is>
@@ -3442,12 +3632,12 @@
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B44" s="36" t="inlineStr">
+      <c r="B44" s="39" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
       </c>
-      <c r="C44" s="42" t="inlineStr">
+      <c r="C44" s="44" t="inlineStr">
         <is>
           <t>Y - add LT.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
         </is>
@@ -3459,12 +3649,12 @@
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="B45" s="36" t="inlineStr">
+      <c r="B45" s="39" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="C45" s="42" t="inlineStr">
+      <c r="C45" s="44" t="inlineStr">
         <is>
           <t>Y - add NL.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
         </is>
@@ -3476,19 +3666,19 @@
           <t>Romania</t>
         </is>
       </c>
-      <c r="B46" s="36" t="inlineStr">
+      <c r="B46" s="39" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="C46" s="42" t="inlineStr">
+      <c r="C46" s="44" t="inlineStr">
         <is>
           <t>Y - add RO.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="32" t="inlineStr">
+      <c r="A48" s="34" t="inlineStr">
         <is>
           <t>Sources: Eurostat isoc_ec_ib20 (ES4) for X; Eurostat tin00110 (ES5, ES6) for Y. WHY A CROSS-SECTION: the Danish adoption and outcome series share almost no observation years - the best time-series pairing in this dataset is n=2 - so a within-Denmark scatter of adoption against outcome cannot be drawn from verified data. SAMPLE: n=6 of 27 member states. This is a small sample; report the association descriptively and do not quote a p-value. Adding the missing values listed above raises n automatically on the next rebuild. WHAT Y MEASURES: tin00110 covers all enterprises with 10+ employees outside the financial sector, so it includes B2B and EDI ordering across every industry, not retail alone. X is a consumer measure. The two sit on different sides of the market, so a positive association is evidence that digital commerce is deep in an economy - not evidence that consumers buying online causes enterprise turnover.</t>
         </is>
@@ -3513,7 +3703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3536,6 +3726,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="F3" s="32" t="inlineStr">
+        <is>
+          <t>Denmark vs EU-27 average</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -3557,6 +3754,11 @@
           <t>unit</t>
         </is>
       </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>Denmark in blue, EU average in grey. Note the direction reverses on the bottom two rows.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
@@ -3564,11 +3766,11 @@
           <t>SMEs with at least basic digital intensity</t>
         </is>
       </c>
-      <c r="B5" s="31">
+      <c r="B5" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENT.DII",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENT.DII",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.ENT.DII",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.ENT.DII",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
@@ -3584,11 +3786,11 @@
           <t>Enterprises adopting AI</t>
         </is>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENT.AI",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENT.AI",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C6" s="41" t="n"/>
+      <c r="C6" s="43" t="n"/>
       <c r="D6" s="28" t="inlineStr">
         <is>
           <t>% of enterprises (EU avg 19.95)</t>
@@ -3601,11 +3803,11 @@
           <t>Digital public services for citizens</t>
         </is>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
@@ -3621,11 +3823,11 @@
           <t>Cross-border digital public services</t>
         </is>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DPS.XB",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DPS.XB",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C8" s="41" t="n"/>
+      <c r="C8" s="43" t="n"/>
       <c r="D8" s="28" t="inlineStr">
         <is>
           <t>score 0-100 (EU avg 75.28)</t>
@@ -3662,7 +3864,7 @@
           <t>Digital public services, DK minus EU average</t>
         </is>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"EU.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
@@ -3678,7 +3880,7 @@
           <t>Digital skills gap within Denmark, 16-24 minus 55-74</t>
         </is>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
@@ -3694,7 +3896,7 @@
           <t>AI adoption gap within Denmark, large firms minus SMEs</t>
         </is>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENT.AI.LRG",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENT.AI.LRG",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENT.AI.SME",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENT.AI.SME",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
@@ -3705,7 +3907,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Source: European Commission, Digital Decade 2026 country report for Denmark (EC1). CAUTION: the eGovernment Benchmark is a scored assessment, not a survey proportion, and a 2.4-point difference between two scores should not be read as a precisely measured gap. The direction is the finding; the magnitude is not.</t>
         </is>
@@ -3747,6 +3949,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="E3" s="32" t="inlineStr">
+        <is>
+          <t>SMV:Digital participant outcomes</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -3763,6 +3972,11 @@
           <t>unit</t>
         </is>
       </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>Participation measures only. No effect size is plotted because none was verified.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
@@ -3770,7 +3984,7 @@
           <t>Digitalisation projects supported since 2018</t>
         </is>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="33">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SME.SMVD.PROJ",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SME.SMVD.PROJ",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
@@ -3786,7 +4000,7 @@
           <t>Participants investing further during the project</t>
         </is>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SME.SMVD.INV",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SME.SMVD.INV",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
@@ -3802,7 +4016,7 @@
           <t>Participants with no further investment plans</t>
         </is>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SME.SMVD.NOINV",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SME.SMVD.NOINV",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
@@ -3820,28 +4034,28 @@
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>The evaluation was carried out by Danmarks Statistik, which compared participating firms against comparable firms that did not participate. Participants showed higher revenue AND higher employment.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="32" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>That is a comparison group. Nothing else in this workbook has one. Figure 6's cross-section can show that adoption and commercial activity move together across countries; it cannot rule out that richer countries simply do more of both. A matched comparison can.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>LIMIT: the effect sizes are not reproduced here because they were not verified against the evaluation itself. The direction of the finding is sourced; the magnitude is not, and must not be invented.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>LIMIT: participation is voluntary, so selection into the programme by more capable or more ambitious firms is not excluded by matching alone.</t>
         </is>
@@ -3936,7 +4150,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>Source: Effektmaaling af SMV:Digital, Danmarks Statistik for the Agency for Digital Government, June 2025 (DG3); scheme status from SMV:Digital's 2026 grant-pool page (SMV1).</t>
         </is>
@@ -4394,14 +4608,14 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>Reading: the mandate date of 1 November 2014 is the hinge of this workbook. Digital Post was not adopted by citizens choosing it; citizens were enrolled automatically, and exemption is available only against statutory criteria. Adoption rates after that date therefore measure compliance with a legal obligation, not revealed preference, and no figure in this workbook should be read as though they measured preference.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>CORRECTION RECORDED: an earlier draft of this workbook stated that SMV:Digital was being defunded. That claim could not be verified, and the scheme's own 2026 grant-pool page (SMV1) documents pools still open, with a further pool opening on 26 October 2026. The claim has been withdrawn from the dataset and from the report's argument. See 07_LIMITATIONS and 08_AI_LOG.</t>
         </is>
@@ -4445,7 +4659,7 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="45" t="inlineStr">
         <is>
           <t>NOT RETRIEVED</t>
         </is>
@@ -4457,7 +4671,7 @@
           <t>Indicator</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="45" t="inlineStr">
         <is>
           <t>Retail trade turnover, volume index (mangdeindeks)</t>
         </is>
@@ -4469,7 +4683,7 @@
           <t>Authority</t>
         </is>
       </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="45" t="inlineStr">
         <is>
           <t>Danmarks Statistik; also available via Eurostat sts_trtu_a</t>
         </is>
@@ -4481,7 +4695,7 @@
           <t>Filters required</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="45" t="inlineStr">
         <is>
           <t>geo=DK; nace_r2=G47; indic_bt=VOL; s_adj=SCA; unit=I21 (2021=100)</t>
         </is>
@@ -4493,7 +4707,7 @@
           <t>Why not retrieved</t>
         </is>
       </c>
-      <c r="B8" s="43" t="inlineStr">
+      <c r="B8" s="45" t="inlineStr">
         <is>
           <t>Values are published through StatBank and the Eurostat databrowser. This session's network policy blocked direct access to both, and the figure could not be verified by search. A value that cannot be traced is not entered.</t>
         </is>
@@ -4505,7 +4719,7 @@
           <t>Base year caution</t>
         </is>
       </c>
-      <c r="B9" s="43" t="inlineStr">
+      <c r="B9" s="45" t="inlineStr">
         <is>
           <t>Danmarks Statistik rebased the index from 2015=100 to 2021=100. Series retrieved on different bases must not be joined.</t>
         </is>
@@ -4517,7 +4731,7 @@
           <t>Effect on the analysis</t>
         </is>
       </c>
-      <c r="B10" s="43" t="inlineStr">
+      <c r="B10" s="45" t="inlineStr">
         <is>
           <t>The e-commerce section rests on the enterprise e-sales evidence in F3_ESALES instead, which is better sourced. No conclusion in the report depends on this series.</t>
         </is>
@@ -4529,7 +4743,7 @@
           <t>To fill</t>
         </is>
       </c>
-      <c r="B11" s="43" t="inlineStr">
+      <c r="B11" s="45" t="inlineStr">
         <is>
           <t>Retrieve from statistikbanken.dk, add rows to dataset.py under series_code DK.RET.VOL with unit 'index 2021=100', and re-run build_workbook.py.</t>
         </is>
@@ -5016,7 +5230,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>This log records assistance during data assembly. Complete it with any further AI use during drafting before submission. The assessment requires that AI-assisted content be verified and acknowledged.</t>
         </is>
@@ -11661,7 +11875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11682,6 +11896,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="D3" s="32" t="inlineStr">
+        <is>
+          <t>Bank branches in Denmark, 2004-2024</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -11691,6 +11912,11 @@
       <c r="B4" s="8" t="inlineStr">
         <is>
           <t>bank branches</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>Count of retail branches. Uneven year spacing, numeric X axis.</t>
         </is>
       </c>
     </row>
@@ -11698,7 +11924,7 @@
       <c r="A5" s="26" t="n">
         <v>2004</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="33">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004))</f>
         <v/>
       </c>
@@ -11707,7 +11933,7 @@
       <c r="A6" s="26" t="n">
         <v>2006</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="33">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2006)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2006))</f>
         <v/>
       </c>
@@ -11716,7 +11942,7 @@
       <c r="A7" s="26" t="n">
         <v>2010</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="33">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2010)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2010))</f>
         <v/>
       </c>
@@ -11725,7 +11951,7 @@
       <c r="A8" s="26" t="n">
         <v>2016</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="33">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2016)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2016))</f>
         <v/>
       </c>
@@ -11734,7 +11960,7 @@
       <c r="A9" s="26" t="n">
         <v>2021</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="33">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2021)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2021))</f>
         <v/>
       </c>
@@ -11743,13 +11969,13 @@
       <c r="A10" s="26" t="n">
         <v>2024</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="33">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Source: Finans Danmark, Institutter, filialer &amp; ansatte (FD1). Note: years are unevenly spaced, so the chart uses a numeric X axis - a category axis would imply a constant rate of decline that the data does not show.</t>
         </is>
@@ -11797,6 +12023,11 @@
           <t>Panel A - Cash share of in-store payments</t>
         </is>
       </c>
+      <c r="D4" s="32" t="inlineStr">
+        <is>
+          <t>Cash share of in-store payments, 2017-2025</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
@@ -11807,6 +12038,11 @@
       <c r="B5" s="8" t="inlineStr">
         <is>
           <t>cash (%)</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>% of the number of payments made in physical retail.</t>
         </is>
       </c>
     </row>
@@ -11814,7 +12050,7 @@
       <c r="A6" s="26" t="n">
         <v>2017</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.PAY.CASH.POS",'02_MASTER'!$E:$E,2017)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.PAY.CASH.POS",'02_MASTER'!$E:$E,2017))</f>
         <v/>
       </c>
@@ -11823,7 +12059,7 @@
       <c r="A7" s="26" t="n">
         <v>2023</v>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.PAY.CASH.POS",'02_MASTER'!$E:$E,2023)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.PAY.CASH.POS",'02_MASTER'!$E:$E,2023))</f>
         <v/>
       </c>
@@ -11832,7 +12068,7 @@
       <c r="A8" s="26" t="n">
         <v>2025</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.PAY.CASH.POS",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.PAY.CASH.POS",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
@@ -11843,6 +12079,11 @@
           <t>Panel B - Composition of in-store payments, 2025</t>
         </is>
       </c>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>Composition of in-store payments, 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
@@ -11855,6 +12096,11 @@
           <t>share of payments (%)</t>
         </is>
       </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>Sums to 95%; the residual is other digital instruments.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
@@ -11862,7 +12108,7 @@
           <t>Physical payment card</t>
         </is>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.PAY.CRD.PHYS",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.PAY.CRD.PHYS",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
@@ -11873,7 +12119,7 @@
           <t>Mobile wallet (card-based)</t>
         </is>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.PAY.WLT.SHR",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.PAY.WLT.SHR",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
@@ -11884,7 +12130,7 @@
           <t>Cash</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="35">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.PAY.CASH.POS",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.PAY.CASH.POS",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
@@ -11912,7 +12158,7 @@
       <c r="A18" s="26" t="n">
         <v>2019</v>
       </c>
-      <c r="B18" s="34">
+      <c r="B18" s="36">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.PAY.WLT.OWN",'02_MASTER'!$E:$E,2019)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.PAY.WLT.OWN",'02_MASTER'!$E:$E,2019))</f>
         <v/>
       </c>
@@ -11921,7 +12167,7 @@
       <c r="A19" s="26" t="n">
         <v>2023</v>
       </c>
-      <c r="B19" s="34">
+      <c r="B19" s="36">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.PAY.WLT.OWN",'02_MASTER'!$E:$E,2023)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.PAY.WLT.OWN",'02_MASTER'!$E:$E,2023))</f>
         <v/>
       </c>
@@ -11930,7 +12176,7 @@
       <c r="A20" s="26" t="n">
         <v>2025</v>
       </c>
-      <c r="B20" s="34">
+      <c r="B20" s="36">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.PAY.WLT.OWN",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.PAY.WLT.OWN",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
@@ -11997,7 +12243,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="inlineStr">
+      <c r="A27" s="34" t="inlineStr">
         <is>
           <t>Source: Danmarks Nationalbank, Danskernes betalingsvaner (NB1). Panel B sums to 95%, not 100%: the residual is other digital instruments (chiefly account transfers and non-card mobile payments). Wallet payments ARE card payments settled through a phone, so the wallet and physical-card rows must not be added to produce a 'card' total. The memo series is excluded from both panels because its denominator is % of citizens, not % of payments. Physical card and wallet shares are observed in 2025 only, so no time series is drawn for them - a two-point line through an unobserved middle would assert a path the data does not contain.</t>
         </is>
@@ -12039,6 +12285,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="E3" s="32" t="inlineStr">
+        <is>
+          <t>E-sales as % of enterprise turnover, DK vs EU-27</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -12053,6 +12306,11 @@
       <c r="C4" s="8" t="inlineStr">
         <is>
           <t>EU-27</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>Denmark in blue; the EU average in grey.</t>
         </is>
       </c>
     </row>
@@ -12060,11 +12318,11 @@
       <c r="A5" s="26" t="n">
         <v>2014</v>
       </c>
-      <c r="B5" s="35">
+      <c r="B5" s="37">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2014)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2014))</f>
         <v/>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="37">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2014)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2014))</f>
         <v/>
       </c>
@@ -12073,11 +12331,11 @@
       <c r="A6" s="26" t="n">
         <v>2024</v>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="37">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="37">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
@@ -12112,7 +12370,7 @@
           <t>Enterprises making e-sales (%)</t>
         </is>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.SHR",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.SHR",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
@@ -12128,7 +12386,7 @@
           <t>E-sales share of turnover (%)</t>
         </is>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
@@ -12144,7 +12402,7 @@
           <t>EU average, e-sales share of turnover (%)</t>
         </is>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
@@ -12212,7 +12470,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t>Source: Eurostat (ES5). Reading: Denmark's e-sales share of turnover rose from 17.05% to 33.31% while the EU average moved from 16.43% to 19.49%. Breadth of adoption is flat at roughly 38% of enterprises; intensity nearly doubled. The growth came from incumbents selling more online, not from new firms entering.</t>
         </is>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -17,7 +17,7 @@
     <sheet name="F2_PAYMENTS" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="F3_ESALES" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="F4_EXCLUSION" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="F5_EU8" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="F5_EU27" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="F6_ADOPT_BENEFIT" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="F7_QUALITY" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="F8_SMVDIGITAL" sheetId="14" state="visible" r:id="rId14"/>
@@ -27,7 +27,7 @@
     <sheet name="08_AI_LOG" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_MASTER'!$A$1:$L$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_MASTER'!$A$1:$L$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -938,7 +938,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'F5_EU8'!B4</f>
+              <f>'F5_EU27'!B4</f>
             </strRef>
           </tx>
           <spPr>
@@ -1002,7 +1002,7 @@
             <idx val="4"/>
             <spPr>
               <a:solidFill>
-                <a:srgbClr val="1F3A5F"/>
+                <a:srgbClr val="A3A3A3"/>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -1046,14 +1046,254 @@
               </a:ln>
             </spPr>
           </dPt>
+          <dPt>
+            <idx val="8"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="9"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="10"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="11"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="12"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="13"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F3A5F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="14"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="15"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="16"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="17"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="18"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="19"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="20"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="21"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="22"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="23"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="24"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="25"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="26"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="27"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="A3A3A3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'F5_EU8'!$A$5:$A$12</f>
+              <f>'F5_EU27'!$A$5:$A$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'F5_EU8'!$B$5:$B$12</f>
+              <f>'F5_EU27'!$B$5:$B$32</f>
             </numRef>
           </val>
         </ser>
@@ -1152,23 +1392,23 @@
             <spPr>
               <a:ln w="16000">
                 <a:solidFill>
-                  <a:srgbClr val="A3A3A3"/>
+                  <a:srgbClr val="1F3A5F"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <trendlineType val="linear"/>
-            <dispRSqr val="0"/>
+            <dispRSqr val="1"/>
             <dispEq val="1"/>
           </trendline>
           <xVal>
             <numRef>
-              <f>'F6_ADOPT_BENEFIT'!$C$5:$C$10</f>
+              <f>'F6_ADOPT_BENEFIT'!$C$5:$C$22</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'F6_ADOPT_BENEFIT'!$D$5:$D$10</f>
+              <f>'F6_ADOPT_BENEFIT'!$D$5:$D$22</f>
             </numRef>
           </yVal>
         </ser>
@@ -1607,7 +1847,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6120000" cy="3600000"/>
+    <ext cx="6120000" cy="6480000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -2096,7 +2336,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>110</t>
         </is>
       </c>
     </row>
@@ -2274,12 +2514,12 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>F5_EU8</t>
+          <t>F5_EU27</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Figure 5 - online purchasing, verified EU countries, 2024</t>
+          <t>Figure 5 - online purchasing, all 27 member states, 2024</t>
         </is>
       </c>
     </row>
@@ -2814,7 +3054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2832,7 +3072,7 @@
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Verified EU countries only (8 of 27). Ranked, not a regression.</t>
+          <t>All 27 member states and the EU-27 aggregate, ranked. Denominator: % of internet users.</t>
         </is>
       </c>
     </row>
@@ -2861,7 +3101,7 @@
       </c>
       <c r="E4" s="25" t="inlineStr">
         <is>
-          <t>Denmark in blue, EU-27 average in navy, other members in grey.</t>
+          <t>Denmark in blue, EU-27 aggregate in navy, member states in grey. Ranked descending.</t>
         </is>
       </c>
     </row>
@@ -2871,7 +3111,7 @@
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B5" s="35">
+      <c r="B5" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
@@ -2887,7 +3127,7 @@
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"NL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"NL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
@@ -2903,7 +3143,7 @@
           <t>Denmark</t>
         </is>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
@@ -2916,87 +3156,407 @@
     <row r="8">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="B8" s="35">
-        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B8" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"SE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"SE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
       <c r="C8" s="39" t="inlineStr">
         <is>
-          <t>DE.ECM.IND.BUY</t>
+          <t>SE.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>EU-27 average</t>
-        </is>
-      </c>
-      <c r="B9" s="35">
-        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+          <t>Czechia</t>
+        </is>
+      </c>
+      <c r="B9" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"CZ.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"CZ.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
       <c r="C9" s="39" t="inlineStr">
         <is>
-          <t>EU.ECM.IND.BUY</t>
+          <t>CZ.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="26" t="inlineStr">
         <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="B10" s="35">
-        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="B10" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"SK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"SK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
       <c r="C10" s="39" t="inlineStr">
         <is>
-          <t>IT.ECM.IND.BUY</t>
+          <t>SK.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="26" t="inlineStr">
         <is>
-          <t>Romania</t>
-        </is>
-      </c>
-      <c r="B11" s="35">
-        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"RO.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"RO.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B11" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"FR.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"FR.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
       <c r="C11" s="39" t="inlineStr">
         <is>
-          <t>RO.ECM.IND.BUY</t>
+          <t>FR.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="26" t="inlineStr">
         <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B12" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C12" s="39" t="inlineStr">
+        <is>
+          <t>DE.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="B13" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"LU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"LU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C13" s="39" t="inlineStr">
+        <is>
+          <t>LU.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="B14" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"FI.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"FI.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C14" s="39" t="inlineStr">
+        <is>
+          <t>FI.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="B15" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"BE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"BE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C15" s="39" t="inlineStr">
+        <is>
+          <t>BE.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="B16" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"HU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"HU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C16" s="39" t="inlineStr">
+        <is>
+          <t>HU.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="B17" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C17" s="39" t="inlineStr">
+        <is>
+          <t>EE.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>EU-27 average</t>
+        </is>
+      </c>
+      <c r="B18" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C18" s="39" t="inlineStr">
+        <is>
+          <t>EU.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B19" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"PL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"PL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C19" s="39" t="inlineStr">
+        <is>
+          <t>PL.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="B20" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C20" s="39" t="inlineStr">
+        <is>
+          <t>EL.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="B21" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"AT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"AT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C21" s="39" t="inlineStr">
+        <is>
+          <t>AT.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="B22" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"MT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"MT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>MT.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="B23" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"SI.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"SI.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C23" s="39" t="inlineStr">
+        <is>
+          <t>SI.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B24" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"LT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"LT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C24" s="39" t="inlineStr">
+        <is>
+          <t>LT.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B25" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"ES.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"ES.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C25" s="39" t="inlineStr">
+        <is>
+          <t>ES.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="B26" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"HR.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"HR.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C26" s="39" t="inlineStr">
+        <is>
+          <t>HR.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B27" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"LV.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"LV.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C27" s="39" t="inlineStr">
+        <is>
+          <t>LV.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="B28" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"CY.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"CY.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C28" s="39" t="inlineStr">
+        <is>
+          <t>CY.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B29" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"PT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"PT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C29" s="39" t="inlineStr">
+        <is>
+          <t>PT.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="B30" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"RO.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"RO.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C30" s="39" t="inlineStr">
+        <is>
+          <t>RO.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B31" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C31" s="39" t="inlineStr">
+        <is>
+          <t>IT.ECM.IND.BUY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="26" t="inlineStr">
+        <is>
           <t>Bulgaria</t>
         </is>
       </c>
-      <c r="B12" s="35">
+      <c r="B32" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"BG.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"BG.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C12" s="39" t="inlineStr">
+      <c r="C32" s="39" t="inlineStr">
         <is>
           <t>BG.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="34" t="inlineStr">
-        <is>
-          <t>Source: Eurostat (ES4). SCOPE LIMIT: 8 of 27 member states were verified, so this sheet presents a ranking and makes no regression claim. To extend it, add the remaining member states to dataset.py using the series_code pattern XX.ECM.IND.BUY and re-run the build; this sheet and its chart will expand automatically. Denominator is % of internet users, not % of individuals.</t>
+    <row r="34">
+      <c r="A34" s="34" t="inlineStr">
+        <is>
+          <t>Source: Eurostat isoc_ec_ib20, complete databrowser extract for 2024 (ES7), unrounded. This replaces an earlier 8-country version built from rounded press-release figures; on those the Italian and Romanian values both read 60% and appeared tied, while unrounded Italy is second lowest at 59.60 and Romania is above it at 59.73. Bulgaria remains the lowest of the 27 at 57.18. The ranking above is computed from the data at build time, so it cannot fall out of step with 02_MASTER. Denominator is % of internet users, not % of individuals - see 04_DEFINITIONS.</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3065,632 +3625,802 @@
       </c>
       <c r="F4" s="25" t="inlineStr">
         <is>
-          <t>One point per country. Read the SELECTION WARNING below before quoting the fit.</t>
+          <t>One point per member state with both measures. Fitted by ordinary least squares; see the statistics below.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="C5" s="38">
-        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"BG.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"BG.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"AT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"AT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
       <c r="D5" s="38">
-        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"BG.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"BG.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"AT.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"AT.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B6" s="39" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="C6" s="38">
-        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"BE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"BE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
       <c r="D6" s="38">
-        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"BE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"BE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="26" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="B7" s="39" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="C7" s="38">
-        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"BG.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"BG.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
       <c r="D7" s="38">
-        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"BG.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"BG.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="B8" s="39" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="C8" s="38">
-        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"HU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"HU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"CY.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"CY.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
       <c r="D8" s="38">
-        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"HU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"HU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"CY.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"CY.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B9" s="39" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="C9" s="38">
-        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"CZ.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"CZ.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
       <c r="D9" s="38">
-        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"CZ.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"CZ.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="26" t="inlineStr">
         <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B10" s="39" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C10" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="D10" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="C11" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="D11" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B12" s="39" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C12" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"ES.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"ES.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="D12" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"ES.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"ES.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B13" s="39" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="C13" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"FR.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"FR.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="D13" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"FR.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"FR.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="C14" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"HR.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"HR.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="D14" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"HR.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"HR.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="B15" s="39" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C15" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"HU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"HU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="D15" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"HU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"HU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B16" s="39" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="C16" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="D16" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="B10" s="39" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="C10" s="38">
+      <c r="C17" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D10" s="38">
+      <c r="D17" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IT.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IT.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="B18" s="39" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="C18" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"LU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"LU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="D18" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"LU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"LU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="B19" s="39" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="C19" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"MT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"MT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="D19" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"MT.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"MT.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B20" s="39" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C20" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"PL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"PL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="D20" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"PL.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"PL.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C21" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"SE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"SE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="D21" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"SE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"SE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="C22" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"SI.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"SI.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="D22" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"SI.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"SI.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>FITTED LINE (ordinary least squares)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>statistic</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>reading</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>n (countries)</t>
         </is>
       </c>
-      <c r="B14" s="33">
-        <f>COUNT($C$5:$C$10)</f>
-        <v/>
-      </c>
-      <c r="C14" s="29" t="inlineStr">
+      <c r="B26" s="33">
+        <f>COUNT($C$5:$C$22)</f>
+        <v/>
+      </c>
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>Number of complete X-Y pairs. Expands automatically as data is added.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>Slope</t>
         </is>
       </c>
-      <c r="B15" s="40">
-        <f>SLOPE($D$5:$D$10,$C$5:$C$10)</f>
-        <v/>
-      </c>
-      <c r="C15" s="29" t="inlineStr">
+      <c r="B27" s="40">
+        <f>SLOPE($D$5:$D$22,$C$5:$C$22)</f>
+        <v/>
+      </c>
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>Percentage points of enterprise turnover per percentage point of consumer adoption.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="26" t="inlineStr">
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B16" s="38">
-        <f>INTERCEPT($D$5:$D$10,$C$5:$C$10)</f>
-        <v/>
-      </c>
-      <c r="C16" s="29" t="inlineStr">
+      <c r="B28" s="38">
+        <f>INTERCEPT($D$5:$D$22,$C$5:$C$22)</f>
+        <v/>
+      </c>
+      <c r="C28" s="29" t="inlineStr">
         <is>
           <t>Not interpretable - no country has zero adoption, so this is far outside the observed range.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="26" t="inlineStr">
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>Correlation (r)</t>
         </is>
       </c>
-      <c r="B17" s="40">
-        <f>CORREL($C$5:$C$10,$D$5:$D$10)</f>
-        <v/>
-      </c>
-      <c r="C17" s="29" t="inlineStr">
+      <c r="B29" s="40">
+        <f>CORREL($C$5:$C$22,$D$5:$D$22)</f>
+        <v/>
+      </c>
+      <c r="C29" s="29" t="inlineStr">
         <is>
           <t>Strength and direction of the linear association.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="26" t="inlineStr">
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>R-squared</t>
         </is>
       </c>
-      <c r="B18" s="40">
-        <f>RSQ($D$5:$D$10,$C$5:$C$10)</f>
-        <v/>
-      </c>
-      <c r="C18" s="29" t="inlineStr">
-        <is>
-          <t>Share of cross-country variation in Y that moves with X. READ THE SELECTION WARNING BELOW BEFORE QUOTING THIS NUMBER: it is inflated by how the sample was drawn and overstates the fit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="B30" s="40">
+        <f>RSQ($D$5:$D$22,$C$5:$C$22)</f>
+        <v/>
+      </c>
+      <c r="C30" s="29" t="inlineStr">
+        <is>
+          <t>Share of cross-country variation in Y that moves with X. Estimated on the complete set of paired member states, so it is quotable - see the SAMPLE block below for what the earlier tail-selected sample claimed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t>Slope standard error</t>
+        </is>
+      </c>
+      <c r="B31" s="40">
+        <f>STEYX($D$5:$D$22,$C$5:$C$22)/SQRT(DEVSQ($C$5:$C$22))</f>
+        <v/>
+      </c>
+      <c r="C31" s="29" t="inlineStr">
+        <is>
+          <t>Precision of the slope estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="26" t="inlineStr">
+        <is>
+          <t>Slope t-statistic</t>
+        </is>
+      </c>
+      <c r="B32" s="38">
+        <f>SLOPE($D$5:$D$22,$C$5:$C$22)/(STEYX($D$5:$D$22,$C$5:$C$22)/SQRT(DEVSQ($C$5:$C$22)))</f>
+        <v/>
+      </c>
+      <c r="C32" s="29" t="inlineStr">
+        <is>
+          <t>Slope divided by its standard error, on n-2 degrees of freedom. Above about 2.1 the slope is distinguishable from zero at the 5% level on this sample size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t>Denmark: actual Y</t>
         </is>
       </c>
-      <c r="B19" s="38">
+      <c r="B33" s="38">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C19" s="29" t="inlineStr">
+      <c r="C33" s="29" t="inlineStr">
         <is>
           <t>Denmark's observed value.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="26" t="inlineStr">
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t>Denmark: fitted Y</t>
         </is>
       </c>
-      <c r="B20" s="38">
-        <f>INTERCEPT($D$5:$D$10,$C$5:$C$10)+SLOPE($D$5:$D$10,$C$5:$C$10)*IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
-        <v/>
-      </c>
-      <c r="C20" s="29" t="inlineStr">
+      <c r="B34" s="38">
+        <f>INTERCEPT($D$5:$D$22,$C$5:$C$22)+SLOPE($D$5:$D$22,$C$5:$C$22)*IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C34" s="29" t="inlineStr">
         <is>
           <t>What the line predicts for Denmark's adoption level.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="26" t="inlineStr">
         <is>
           <t>Denmark: residual</t>
         </is>
       </c>
-      <c r="B21" s="41">
-        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))-(INTERCEPT($D$5:$D$10,$C$5:$C$10)+SLOPE($D$5:$D$10,$C$5:$C$10)*IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)))</f>
-        <v/>
-      </c>
-      <c r="C21" s="29" t="inlineStr">
+      <c r="B35" s="41">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))-(INTERCEPT($D$5:$D$22,$C$5:$C$22)+SLOPE($D$5:$D$22,$C$5:$C$22)*IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)))</f>
+        <v/>
+      </c>
+      <c r="C35" s="29" t="inlineStr">
         <is>
           <t>Positive: Denmark converts adoption into commercial activity better than the EU pattern predicts. Negative: worse.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>SELECTION WARNING - read before quoting the fit</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="46" customHeight="1">
-      <c r="A24" s="42" t="inlineStr">
-        <is>
-          <t>HOW THE SAMPLE WAS DRAWN: the X column (consumer adoption) was not available as a complete Eurostat table in this session. The values come from a Eurostat press release, which names the three highest countries, the three lowest, and three large movers - a sample concentrated in the TAILS of the adoption distribution.</t>
-        </is>
-      </c>
-      <c r="B24" s="43" t="n"/>
-      <c r="C24" s="43" t="n"/>
-      <c r="D24" s="43" t="n"/>
-    </row>
-    <row r="25" ht="46" customHeight="1">
-      <c r="A25" s="42" t="inlineStr">
-        <is>
-          <t>CONSEQUENCE: of the 6 countries plotted, 5 come from the top or bottom of the EU ranking. Selecting on the extremes of X and dropping the middle inflates the correlation coefficient and R-squared by construction, because it widens the spread in X relative to the scatter around the line.</t>
-        </is>
-      </c>
-      <c r="B25" s="43" t="n"/>
-      <c r="C25" s="43" t="n"/>
-      <c r="D25" s="43" t="n"/>
-    </row>
-    <row r="26" ht="46" customHeight="1">
-      <c r="A26" s="42" t="inlineStr">
-        <is>
-          <t>HOW TO USE THIS FIGURE HONESTLY: report the SLOPE, which is far less sensitive to this kind of selection, and report n. Treat the R-squared as an upper bound. Do not describe the fit as 'strong' or 'tight', and do not compute a p-value or confidence interval from these points.</t>
-        </is>
-      </c>
-      <c r="B26" s="43" t="n"/>
-      <c r="C26" s="43" t="n"/>
-      <c r="D26" s="43" t="n"/>
-    </row>
-    <row r="27" ht="46" customHeight="1">
-      <c r="A27" s="42" t="inlineStr">
-        <is>
-          <t>HOW TO FIX IT: retrieve Eurostat isoc_ec_ib20 for 2024 for all 27 member states from the databrowser and add the rows to dataset.py. That removes the selection entirely and roughly triples n. The register below names every country still missing and the exact series code for each.</t>
-        </is>
-      </c>
-      <c r="B27" s="43" t="n"/>
-      <c r="C27" s="43" t="n"/>
-      <c r="D27" s="43" t="n"/>
-    </row>
-    <row r="28" ht="46" customHeight="1">
-      <c r="A28" s="42" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>SAMPLE - how these points were obtained</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="46" customHeight="1">
+      <c r="A38" s="42" t="inlineStr">
+        <is>
+          <t>COMPLETE FOR 2024: the X column is the full Eurostat isoc_ec_ib20 extract for all 27 member states, unrounded, taken from the databrowser. Every member state holding both measures is plotted - 18 of them. No country with both values is excluded, so the fit is no longer conditioned on where a country sits in the ranking.</t>
+        </is>
+      </c>
+      <c r="B38" s="43" t="n"/>
+      <c r="C38" s="43" t="n"/>
+      <c r="D38" s="43" t="n"/>
+    </row>
+    <row r="39" ht="46" customHeight="1">
+      <c r="A39" s="42" t="inlineStr">
+        <is>
+          <t>WHAT THE EARLIER SAMPLE CLAIMED: an earlier version of this figure drew X from a Eurostat press release, which named only the three highest countries, the three lowest and two large movers. On those 6 tail countries the fit was R-squared 0.853 with a slope of +0.655. On the complete cross-section it is R-squared 0.674 with a slope of +0.602.</t>
+        </is>
+      </c>
+      <c r="B39" s="43" t="n"/>
+      <c r="C39" s="43" t="n"/>
+      <c r="D39" s="43" t="n"/>
+    </row>
+    <row r="40" ht="46" customHeight="1">
+      <c r="A40" s="42" t="inlineStr">
+        <is>
+          <t>READING THAT COMPARISON: the slope moved by about 8% while R-squared fell by 0.18. This is the signature of selection on the tails - it widens the spread in X relative to the scatter around the line, which flatters the fit while leaving the estimated relationship roughly intact. The earlier R-squared was an upper bound, as the warning it replaced said; this one is an estimate.</t>
+        </is>
+      </c>
+      <c r="B40" s="43" t="n"/>
+      <c r="C40" s="43" t="n"/>
+      <c r="D40" s="43" t="n"/>
+    </row>
+    <row r="41" ht="46" customHeight="1">
+      <c r="A41" s="42" t="inlineStr">
+        <is>
+          <t>STILL NOT A COMPLETE CROSS-SECTION OF THE EU: nine member states hold the adoption measure but not the enterprise turnover measure and are listed below. The sample is complete with respect to X and incomplete with respect to Y, so it is 18 countries rather than 27 - but the countries dropped are dropped by data availability, not by their position on either axis.</t>
+        </is>
+      </c>
+      <c r="B41" s="43" t="n"/>
+      <c r="C41" s="43" t="n"/>
+      <c r="D41" s="43" t="n"/>
+    </row>
+    <row r="42" ht="46" customHeight="1">
+      <c r="A42" s="42" t="inlineStr">
         <is>
           <t>DIRECTION OF CAUSATION IS NOT ESTABLISHED AND CANNOT BE. X measures consumers; Y measures enterprises, including business-to-business sales that no consumer touches. Both plausibly rise with national income, which is in neither axis. This figure shows that digital commerce runs deep in the same economies where consumers buy online. It does not show that the one produces the other.</t>
         </is>
       </c>
-      <c r="B28" s="43" t="n"/>
-      <c r="C28" s="43" t="n"/>
-      <c r="D28" s="43" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="B42" s="43" t="n"/>
+      <c r="C42" s="43" t="n"/>
+      <c r="D42" s="43" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>AWAITING DATA - not plotted</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="26" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="B32" s="39" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="C32" s="44" t="inlineStr">
-        <is>
-          <t>X - add AT.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="26" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="B33" s="39" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="C33" s="44" t="inlineStr">
-        <is>
-          <t>X - add BE.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="26" t="inlineStr">
-        <is>
-          <t>Cyprus</t>
-        </is>
-      </c>
-      <c r="B34" s="39" t="inlineStr">
-        <is>
-          <t>CY</t>
-        </is>
-      </c>
-      <c r="C34" s="44" t="inlineStr">
-        <is>
-          <t>X - add CY.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="26" t="inlineStr">
-        <is>
-          <t>Czechia</t>
-        </is>
-      </c>
-      <c r="B35" s="39" t="inlineStr">
-        <is>
-          <t>CZ</t>
-        </is>
-      </c>
-      <c r="C35" s="44" t="inlineStr">
-        <is>
-          <t>X - add CZ.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="26" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="B36" s="39" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="C36" s="44" t="inlineStr">
-        <is>
-          <t>X - add ES.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="26" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B37" s="39" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="C37" s="44" t="inlineStr">
-        <is>
-          <t>X - add FR.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="26" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="B38" s="39" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="C38" s="44" t="inlineStr">
-        <is>
-          <t>X - add HR.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="26" t="inlineStr">
-        <is>
-          <t>Luxembourg</t>
-        </is>
-      </c>
-      <c r="B39" s="39" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="C39" s="44" t="inlineStr">
-        <is>
-          <t>X - add LU.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="26" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-      <c r="B40" s="39" t="inlineStr">
-        <is>
-          <t>MT</t>
-        </is>
-      </c>
-      <c r="C40" s="44" t="inlineStr">
-        <is>
-          <t>X - add MT.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="26" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B41" s="39" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="C41" s="44" t="inlineStr">
-        <is>
-          <t>X - add PL.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="26" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-      <c r="B42" s="39" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="C42" s="44" t="inlineStr">
-        <is>
-          <t>X - add SE.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="26" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="B43" s="39" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="C43" s="44" t="inlineStr">
-        <is>
-          <t>X - add SI.ECM.IND.BUY for 2024 (Eurostat isoc_ec_ib20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="26" t="inlineStr">
-        <is>
-          <t>Lithuania</t>
-        </is>
-      </c>
-      <c r="B44" s="39" t="inlineStr">
-        <is>
-          <t>LT</t>
-        </is>
-      </c>
-      <c r="C44" s="44" t="inlineStr">
-        <is>
-          <t>Y - add LT.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="26" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="B45" s="39" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="C45" s="44" t="inlineStr">
-        <is>
-          <t>Y - add NL.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="26" t="inlineStr">
         <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="B46" s="39" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="C46" s="44" t="inlineStr">
+        <is>
+          <t>Y - add EE.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="B47" s="39" t="inlineStr">
+        <is>
+          <t>EL</t>
+        </is>
+      </c>
+      <c r="C47" s="44" t="inlineStr">
+        <is>
+          <t>Y - add EL.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="B48" s="39" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="C48" s="44" t="inlineStr">
+        <is>
+          <t>Y - add FI.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="B49" s="39" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="C49" s="44" t="inlineStr">
+        <is>
+          <t>Y - add LT.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="26" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B50" s="39" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="C50" s="44" t="inlineStr">
+        <is>
+          <t>Y - add LV.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B51" s="39" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C51" s="44" t="inlineStr">
+        <is>
+          <t>Y - add NL.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="26" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B52" s="39" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="C52" s="44" t="inlineStr">
+        <is>
+          <t>Y - add PT.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="26" t="inlineStr">
+        <is>
           <t>Romania</t>
         </is>
       </c>
-      <c r="B46" s="39" t="inlineStr">
+      <c r="B53" s="39" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="C46" s="44" t="inlineStr">
+      <c r="C53" s="44" t="inlineStr">
         <is>
           <t>Y - add RO.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="34" t="inlineStr">
-        <is>
-          <t>Sources: Eurostat isoc_ec_ib20 (ES4) for X; Eurostat tin00110 (ES5, ES6) for Y. WHY A CROSS-SECTION: the Danish adoption and outcome series share almost no observation years - the best time-series pairing in this dataset is n=2 - so a within-Denmark scatter of adoption against outcome cannot be drawn from verified data. SAMPLE: n=6 of 27 member states. This is a small sample; report the association descriptively and do not quote a p-value. Adding the missing values listed above raises n automatically on the next rebuild. WHAT Y MEASURES: tin00110 covers all enterprises with 10+ employees outside the financial sector, so it includes B2B and EDI ordering across every industry, not retail alone. X is a consumer measure. The two sit on different sides of the market, so a positive association is evidence that digital commerce is deep in an economy - not evidence that consumers buying online causes enterprise turnover.</t>
+    <row r="54">
+      <c r="A54" s="26" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="B54" s="39" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C54" s="44" t="inlineStr">
+        <is>
+          <t>Y - add SK.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="34" t="inlineStr">
+        <is>
+          <t>Sources: Eurostat isoc_ec_ib20 (ES4) for X; Eurostat tin00110 (ES5, ES6) for Y. WHY A CROSS-SECTION: the Danish adoption and outcome series share almost no observation years - the best time-series pairing in this dataset is n=2 - so a within-Denmark scatter of adoption against outcome cannot be drawn from verified data. SAMPLE: n=18 of 27 member states. This is a small sample; report the association descriptively and do not quote a p-value. Adding the missing values listed above raises n automatically on the next rebuild. WHAT Y MEASURES: tin00110 covers all enterprises with 10+ employees outside the financial sector, so it includes B2B and EDI ordering across every industry, not retail alone. X is a consumer measure. The two sit on different sides of the market, so a positive association is evidence that digital commerce is deep in an economy - not evidence that consumers buying online causes enterprise turnover.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -4796,12 +5526,12 @@
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Figure 6 sample is selected on the tails</t>
+          <t>Figure 6 tail selection - RESOLVED, and what it cost</t>
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>The adoption column in Figure 6 was assembled from a Eurostat press release naming the highest three countries, the lowest three, and three large movers. Most of the plotted points therefore come from the ends of the EU distribution. Selecting on the extremes of X inflates the correlation coefficient and R-squared regardless of the underlying relationship. The R-squared is an upper bound, not an estimate; the slope is the statistic to quote, alongside n. The chart deliberately does not display R-squared on its face. Fixing this requires the full 27-country isoc_ec_ib20 column.</t>
+          <t>The adoption column in Figure 6 was originally assembled from a Eurostat press release naming the highest three countries, the lowest three and two large movers, so most plotted points came from the ends of the EU distribution. Selecting on the extremes of X inflates the correlation coefficient regardless of the underlying relationship, and R-squared was withheld from the chart face for that reason. The column is now the complete isoc_ec_ib20 databrowser extract for all 27 member states, unrounded, so the selection is gone and R-squared is displayed. The measured cost of the bias is retained on F6 because it is informative: on the 6 tail countries the fit was R-squared 0.853 with a slope of +0.655; on the complete cross-section it is R-squared 0.674 with a slope of +0.602. Tail selection barely moved the slope and flattered the fit by 0.18.</t>
         </is>
       </c>
     </row>
@@ -4928,12 +5658,12 @@
     <row r="16" ht="62" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Cross-section incomplete</t>
+          <t>Cross-section complete on adoption, incomplete on outcome</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>F5 covers 8 of 27 member states. It supports a ranking, not a regression.</t>
+          <t>The adoption measure now covers all 27 member states for 2024, so F5 is a complete EU ranking. The enterprise-turnover measure does not: nine member states hold adoption but not turnover and cannot enter Figure 6. Those nine are dropped by data availability rather than by their position on either axis, which is why the remaining 18 are treated as a usable cross-section.</t>
         </is>
       </c>
     </row>
@@ -4945,7 +5675,7 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>The adoption-to-outcome scatter rests on 6 complete country pairs. The association is strong and positive, but 6 points cannot support a p-value, a confidence interval, or a claim about causal direction. Report the slope and R-squared descriptively and say n explicitly. Adding the missing values listed on that sheet raises n automatically.</t>
+          <t>The adoption-to-outcome scatter rests on 18 complete country pairs, up from 6. That is enough to report a slope with a standard error and a t-statistic, all three of which are on the sheet as live formulas. It is not enough, and no sample size would be enough here, to support a claim about causal direction: this is one year of cross-sectional data with no control for national income. Say n explicitly, report the slope with its standard error, and keep the language associational.</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5159,78 +5889,122 @@
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>R-squared removed from the chart face; a SELECTION WARNING added to F6; the limitation recorded in 07_LIMITATIONS.</t>
+          <t>R-squared removed from the chart face; a selection warning added to F6; the limitation recorded in 07_LIMITATIONS. Later resolved - see the two rows below.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>Workbook construction</t>
+          <t>Failed verification attempt</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>AI wrote the Python build script that generates this workbook.</t>
+          <t>AI was asked to retrieve Eurostat isoc_ec_ib20 for 2024 for the twelve member states missing from Figure 6, so the tail selection could be removed.</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Structural assertions run at build time: source_ids resolve, units and denominators present, no duplicate observations, break flags set.</t>
+          <t>Eurostat and the national statistical offices are unreachable from the build environment. Web search returned only the press release naming the same tails, two country values with no attributable source, and one answer mixing the '% of internet users' and '% of individuals' denominators in a single paragraph.</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>build_workbook.py, re-runnable.</t>
+          <t>No values accepted. Recorded because the honest outcome of a verification attempt is sometimes that it failed.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>Analytical framing</t>
+          <t>Author-supplied authoritative extract</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>AI used to interpret patterns and suggest framings.</t>
+          <t>The author retrieved the complete isoc_ec_ib20 table from the Eurostat databrowser and supplied it as a spreadsheet; AI parsed it into the dataset.</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>Author reviewed each interpretation against the underlying values.</t>
+          <t>The extract carries its own provenance header - dataset code, extraction timestamp, last-update date, and an explicit unit of 'percentage of individuals who used internet within the last year'. The ten values it overlapped with were compared against the rounded press-release figures already held; all ten agreed to rounding.</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>Interpretations appear in the report, attributed to the author.</t>
+          <t>All 27 member states plus the EU-27 aggregate added under source ES7. Figure 6 went from n=6 to n=18 and R-squared was restored to the chart face. The superseded rounded values are recorded in each row's note.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
+          <t>Workbook construction</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>AI wrote the Python build script that generates this workbook.</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Structural assertions run at build time: source_ids resolve, units and denominators present, no duplicate observations, break flags set.</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>build_workbook.py, re-runnable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Analytical framing</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>AI used to interpret patterns and suggest framings.</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Author reviewed each interpretation against the underlying values.</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Interpretations appear in the report, attributed to the author.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
           <t>Not delegated to AI</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Selection of the research question, country, industries, SDG and policy comparator; the argument; the conclusions.</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>Author's own work.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>This log records assistance during data assembly. Complete it with any further AI use during drafting before submission. The assessment requires that AI-assisted content be verified and acknowledged.</t>
         </is>
@@ -5462,7 +6236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6687,7 +7461,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L24" s="15" t="inlineStr"/>
+      <c r="L24" s="15" t="inlineStr">
+        <is>
+          <t>Rounded, from a Eurostat news release. Only the 2024 cross-section is available here unrounded, so this series mixes precisions across years.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="n">
@@ -6735,7 +7513,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L25" s="15" t="inlineStr"/>
+      <c r="L25" s="15" t="inlineStr">
+        <is>
+          <t>Rounded, from a Eurostat news release. See the 2020 note on mixed precision.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="n">
@@ -6743,7 +7525,7 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>DK.ECM.IND.BUY</t>
+          <t>EU.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -6753,14 +7535,14 @@
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>EU27</t>
         </is>
       </c>
       <c r="E26" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>91</v>
+        <v>76.58</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
@@ -6775,7 +7557,7 @@
       <c r="I26" s="13" t="inlineStr"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>ES4</t>
+          <t>ES7</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
@@ -6791,7 +7573,7 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>EU.ECM.IND.BUY</t>
+          <t>AT.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
@@ -6801,14 +7583,14 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>EU27</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="E27" s="13" t="n">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>59</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
@@ -6823,7 +7605,7 @@
       <c r="I27" s="13" t="inlineStr"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>ES4</t>
+          <t>ES7</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
@@ -6839,7 +7621,7 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>EU.ECM.IND.BUY</t>
+          <t>BE.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
@@ -6849,14 +7631,14 @@
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>EU27</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E28" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>77</v>
+        <v>78.98</v>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
@@ -6871,7 +7653,7 @@
       <c r="I28" s="13" t="inlineStr"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>ES4</t>
+          <t>ES7</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
@@ -6887,7 +7669,7 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>IE.ECM.IND.BUY</t>
+          <t>BG.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
@@ -6897,14 +7679,14 @@
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="E29" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>96</v>
+        <v>57.18</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
@@ -6919,7 +7701,7 @@
       <c r="I29" s="13" t="inlineStr"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>ES4</t>
+          <t>ES7</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -6929,7 +7711,7 @@
       </c>
       <c r="L29" s="15" t="inlineStr">
         <is>
-          <t>Highest in EU.</t>
+          <t>Lowest of the 27, as the press release reported. Supersedes the rounded 57%.</t>
         </is>
       </c>
     </row>
@@ -6939,7 +7721,7 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>NL.ECM.IND.BUY</t>
+          <t>CY.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
@@ -6949,14 +7731,14 @@
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="E30" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>94</v>
+        <v>68.16</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
@@ -6971,7 +7753,7 @@
       <c r="I30" s="13" t="inlineStr"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>ES4</t>
+          <t>ES7</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
@@ -6987,7 +7769,7 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>DE.ECM.IND.BUY</t>
+          <t>CZ.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
@@ -6997,14 +7779,14 @@
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="E31" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F31" s="16" t="n">
-        <v>83</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
@@ -7019,7 +7801,7 @@
       <c r="I31" s="13" t="inlineStr"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>ES4</t>
+          <t>ES7</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
@@ -7027,11 +7809,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L31" s="15" t="inlineStr">
-        <is>
-          <t>Ranked 8th in EU.</t>
-        </is>
-      </c>
+      <c r="L31" s="15" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="13" t="n">
@@ -7039,7 +7817,7 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>IT.ECM.IND.BUY</t>
+          <t>DE.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
@@ -7049,14 +7827,14 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E32" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F32" s="16" t="n">
-        <v>60</v>
+        <v>82.53</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
@@ -7071,7 +7849,7 @@
       <c r="I32" s="13" t="inlineStr"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>ES4</t>
+          <t>ES7</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
@@ -7079,7 +7857,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L32" s="15" t="inlineStr"/>
+      <c r="L32" s="15" t="inlineStr">
+        <is>
+          <t>Supersedes the rounded 83%.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="n">
@@ -7087,7 +7869,7 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>RO.ECM.IND.BUY</t>
+          <t>DK.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
@@ -7097,14 +7879,14 @@
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="E33" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F33" s="16" t="n">
-        <v>60</v>
+        <v>90.86</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
@@ -7119,7 +7901,7 @@
       <c r="I33" s="13" t="inlineStr"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>ES4</t>
+          <t>ES7</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
@@ -7127,7 +7909,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L33" s="15" t="inlineStr"/>
+      <c r="L33" s="15" t="inlineStr">
+        <is>
+          <t>Supersedes the rounded 91% taken from the Eurostat press release.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="n">
@@ -7135,7 +7921,7 @@
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>BG.ECM.IND.BUY</t>
+          <t>EE.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
@@ -7145,14 +7931,14 @@
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="E34" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F34" s="16" t="n">
-        <v>57</v>
+        <v>78.72</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -7167,7 +7953,7 @@
       <c r="I34" s="13" t="inlineStr"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>ES4</t>
+          <t>ES7</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
@@ -7175,11 +7961,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L34" s="15" t="inlineStr">
-        <is>
-          <t>Lowest in EU.</t>
-        </is>
-      </c>
+      <c r="L34" s="15" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="13" t="n">
@@ -7187,24 +7969,24 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>DK.ECM.ENT.TRN</t>
+          <t>EL.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
-          <t>E-sales as share of enterprise turnover</t>
+          <t>Individuals who bought online in last 12 months</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="E35" s="13" t="n">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>17.05</v>
+        <v>74.66</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
@@ -7213,13 +7995,13 @@
       </c>
       <c r="H35" s="15" t="inlineStr">
         <is>
-          <t>% of total enterprise turnover</t>
+          <t>% of internet users</t>
         </is>
       </c>
       <c r="I35" s="13" t="inlineStr"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>ES5</t>
+          <t>ES7</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
@@ -7235,24 +8017,24 @@
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>DK.ECM.ENT.TRN</t>
+          <t>ES.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>E-sales as share of enterprise turnover</t>
+          <t>Individuals who bought online in last 12 months</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E36" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F36" s="16" t="n">
-        <v>33.31</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
@@ -7261,13 +8043,13 @@
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>% of total enterprise turnover</t>
+          <t>% of internet users</t>
         </is>
       </c>
       <c r="I36" s="13" t="inlineStr"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>ES5</t>
+          <t>ES7</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
@@ -7275,11 +8057,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L36" s="15" t="inlineStr">
-        <is>
-          <t>2nd in EU after Ireland.</t>
-        </is>
-      </c>
+      <c r="L36" s="15" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="13" t="n">
@@ -7287,24 +8065,24 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>EU.ECM.ENT.TRN</t>
+          <t>FI.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>E-sales as share of enterprise turnover</t>
+          <t>Individuals who bought online in last 12 months</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>EU27</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E37" s="13" t="n">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>16.43</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
@@ -7313,13 +8091,13 @@
       </c>
       <c r="H37" s="15" t="inlineStr">
         <is>
-          <t>% of total enterprise turnover</t>
+          <t>% of internet users</t>
         </is>
       </c>
       <c r="I37" s="13" t="inlineStr"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>ES5</t>
+          <t>ES7</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
@@ -7335,24 +8113,24 @@
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>EU.ECM.ENT.TRN</t>
+          <t>FR.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>E-sales as share of enterprise turnover</t>
+          <t>Individuals who bought online in last 12 months</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>EU27</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E38" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F38" s="16" t="n">
-        <v>19.49</v>
+        <v>84.37</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -7361,13 +8139,13 @@
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>% of total enterprise turnover</t>
+          <t>% of internet users</t>
         </is>
       </c>
       <c r="I38" s="13" t="inlineStr"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>ES5</t>
+          <t>ES7</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
@@ -7383,24 +8161,24 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>IE.ECM.ENT.TRN</t>
+          <t>HR.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>E-sales as share of enterprise turnover</t>
+          <t>Individuals who bought online in last 12 months</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E39" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F39" s="16" t="n">
-        <v>38.25</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
@@ -7409,13 +8187,13 @@
       </c>
       <c r="H39" s="15" t="inlineStr">
         <is>
-          <t>% of total enterprise turnover</t>
+          <t>% of internet users</t>
         </is>
       </c>
       <c r="I39" s="13" t="inlineStr"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>ES5</t>
+          <t>ES7</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -7423,11 +8201,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L39" s="15" t="inlineStr">
-        <is>
-          <t>Highest in EU.</t>
-        </is>
-      </c>
+      <c r="L39" s="15" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="13" t="n">
@@ -7452,7 +8226,7 @@
         <v>2024</v>
       </c>
       <c r="F40" s="16" t="n">
-        <v>79</v>
+        <v>78.87</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -7467,7 +8241,7 @@
       <c r="I40" s="13" t="inlineStr"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>ES4</t>
+          <t>ES7</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
@@ -7477,7 +8251,7 @@
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
-          <t>Rose 37pp from 42% in 2014.</t>
+          <t>Supersedes the rounded 79%.</t>
         </is>
       </c>
     </row>
@@ -7487,7 +8261,7 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>LT.ECM.IND.BUY</t>
+          <t>IE.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
@@ -7497,14 +8271,14 @@
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="E41" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F41" s="16" t="n">
-        <v>72</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -7519,851 +8293,807 @@
       <c r="I41" s="13" t="inlineStr"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
+          <t>ES7</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L41" s="15" t="inlineStr">
+        <is>
+          <t>Highest in EU. Supersedes the rounded 96%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>IT.ECM.IND.BUY</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Individuals who bought online in last 12 months</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F42" s="16" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="inlineStr">
+        <is>
+          <t>% of internet users</t>
+        </is>
+      </c>
+      <c r="I42" s="13" t="inlineStr"/>
+      <c r="J42" s="14" t="inlineStr">
+        <is>
+          <t>ES7</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L42" s="15" t="inlineStr">
+        <is>
+          <t>Second lowest of the 27. Supersedes the rounded 60%, which tied Italy with Romania; unrounded Italy is below Romania, so they are not tied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>LT.ECM.IND.BUY</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>Individuals who bought online in last 12 months</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F43" s="16" t="n">
+        <v>71.95999999999999</v>
+      </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="inlineStr">
+        <is>
+          <t>% of internet users</t>
+        </is>
+      </c>
+      <c r="I43" s="13" t="inlineStr"/>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
+          <t>ES7</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L43" s="15" t="inlineStr">
+        <is>
+          <t>Supersedes the rounded 72%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>LU.ECM.IND.BUY</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Individuals who bought online in last 12 months</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F44" s="16" t="n">
+        <v>81.34</v>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="inlineStr">
+        <is>
+          <t>% of internet users</t>
+        </is>
+      </c>
+      <c r="I44" s="13" t="inlineStr"/>
+      <c r="J44" s="14" t="inlineStr">
+        <is>
+          <t>ES7</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L44" s="15" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>LV.ECM.IND.BUY</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>Individuals who bought online in last 12 months</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F45" s="16" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="inlineStr">
+        <is>
+          <t>% of internet users</t>
+        </is>
+      </c>
+      <c r="I45" s="13" t="inlineStr"/>
+      <c r="J45" s="14" t="inlineStr">
+        <is>
+          <t>ES7</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L45" s="15" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>MT.ECM.IND.BUY</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>Individuals who bought online in last 12 months</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F46" s="16" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="inlineStr">
+        <is>
+          <t>% of internet users</t>
+        </is>
+      </c>
+      <c r="I46" s="13" t="inlineStr"/>
+      <c r="J46" s="14" t="inlineStr">
+        <is>
+          <t>ES7</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L46" s="15" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>NL.ECM.IND.BUY</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>Individuals who bought online in last 12 months</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F47" s="16" t="n">
+        <v>94.42</v>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="inlineStr">
+        <is>
+          <t>% of internet users</t>
+        </is>
+      </c>
+      <c r="I47" s="13" t="inlineStr"/>
+      <c r="J47" s="14" t="inlineStr">
+        <is>
+          <t>ES7</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L47" s="15" t="inlineStr">
+        <is>
+          <t>Supersedes the rounded 94%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>PL.ECM.IND.BUY</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>Individuals who bought online in last 12 months</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F48" s="16" t="n">
+        <v>75.06999999999999</v>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="inlineStr">
+        <is>
+          <t>% of internet users</t>
+        </is>
+      </c>
+      <c r="I48" s="13" t="inlineStr"/>
+      <c r="J48" s="14" t="inlineStr">
+        <is>
+          <t>ES7</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L48" s="15" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>PT.ECM.IND.BUY</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>Individuals who bought online in last 12 months</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F49" s="16" t="n">
+        <v>66.64</v>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="inlineStr">
+        <is>
+          <t>% of internet users</t>
+        </is>
+      </c>
+      <c r="I49" s="13" t="inlineStr"/>
+      <c r="J49" s="14" t="inlineStr">
+        <is>
+          <t>ES7</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L49" s="15" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>RO.ECM.IND.BUY</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>Individuals who bought online in last 12 months</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F50" s="16" t="n">
+        <v>59.73</v>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="inlineStr">
+        <is>
+          <t>% of internet users</t>
+        </is>
+      </c>
+      <c r="I50" s="13" t="inlineStr"/>
+      <c r="J50" s="14" t="inlineStr">
+        <is>
+          <t>ES7</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L50" s="15" t="inlineStr">
+        <is>
+          <t>Supersedes the rounded 60%. See the Italy note on the tie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>SE.ECM.IND.BUY</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>Individuals who bought online in last 12 months</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F51" s="16" t="n">
+        <v>89.89</v>
+      </c>
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="inlineStr">
+        <is>
+          <t>% of internet users</t>
+        </is>
+      </c>
+      <c r="I51" s="13" t="inlineStr"/>
+      <c r="J51" s="14" t="inlineStr">
+        <is>
+          <t>ES7</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L51" s="15" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>SI.ECM.IND.BUY</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>Individuals who bought online in last 12 months</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F52" s="16" t="n">
+        <v>72.39</v>
+      </c>
+      <c r="G52" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="inlineStr">
+        <is>
+          <t>% of internet users</t>
+        </is>
+      </c>
+      <c r="I52" s="13" t="inlineStr"/>
+      <c r="J52" s="14" t="inlineStr">
+        <is>
+          <t>ES7</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L52" s="15" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>SK.ECM.IND.BUY</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>Individuals who bought online in last 12 months</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F53" s="16" t="n">
+        <v>85.13</v>
+      </c>
+      <c r="G53" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="inlineStr">
+        <is>
+          <t>% of internet users</t>
+        </is>
+      </c>
+      <c r="I53" s="13" t="inlineStr"/>
+      <c r="J53" s="14" t="inlineStr">
+        <is>
+          <t>ES7</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L53" s="15" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>EU.ECM.IND.BUY</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>Individuals who bought online in last 12 months</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>EU27</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F54" s="16" t="n">
+        <v>59</v>
+      </c>
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="inlineStr">
+        <is>
+          <t>% of internet users</t>
+        </is>
+      </c>
+      <c r="I54" s="13" t="inlineStr"/>
+      <c r="J54" s="14" t="inlineStr">
+        <is>
           <t>ES4</t>
         </is>
       </c>
-      <c r="K41" s="13" t="inlineStr">
+      <c r="K54" s="13" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L41" s="15" t="inlineStr">
-        <is>
-          <t>Rose 36pp from 36% in 2014.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="18" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="19" t="inlineStr">
-        <is>
-          <t>BE.ECM.ENT.TRN</t>
-        </is>
-      </c>
-      <c r="C42" s="20" t="inlineStr">
+      <c r="L54" s="15" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>DK.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="inlineStr">
         <is>
           <t>E-sales as share of enterprise turnover</t>
         </is>
       </c>
-      <c r="D42" s="18" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="E42" s="18" t="n">
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F55" s="16" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="G55" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I55" s="13" t="inlineStr"/>
+      <c r="J55" s="14" t="inlineStr">
+        <is>
+          <t>ES5</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L55" s="15" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>DK.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="F42" s="22" t="n">
-        <v>29.51</v>
-      </c>
-      <c r="G42" s="18" t="inlineStr">
+      <c r="F56" s="16" t="n">
+        <v>33.31</v>
+      </c>
+      <c r="G56" s="13" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H42" s="20" t="inlineStr">
+      <c r="H56" s="15" t="inlineStr">
         <is>
           <t>% of total enterprise turnover</t>
         </is>
       </c>
-      <c r="I42" s="18" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="J42" s="19" t="inlineStr">
-        <is>
-          <t>ES6</t>
-        </is>
-      </c>
-      <c r="K42" s="18" t="inlineStr">
+      <c r="I56" s="13" t="inlineStr"/>
+      <c r="J56" s="14" t="inlineStr">
+        <is>
+          <t>ES5</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L42" s="20" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="18" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="19" t="inlineStr">
-        <is>
-          <t>SE.ECM.ENT.TRN</t>
-        </is>
-      </c>
-      <c r="C43" s="20" t="inlineStr">
+      <c r="L56" s="15" t="inlineStr">
+        <is>
+          <t>2nd in EU after Ireland.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>EU.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="inlineStr">
         <is>
           <t>E-sales as share of enterprise turnover</t>
         </is>
       </c>
-      <c r="D43" s="18" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="E43" s="18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F43" s="22" t="n">
-        <v>26.32</v>
-      </c>
-      <c r="G43" s="18" t="inlineStr">
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>EU27</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F57" s="16" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="G57" s="13" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H43" s="20" t="inlineStr">
+      <c r="H57" s="15" t="inlineStr">
         <is>
           <t>% of total enterprise turnover</t>
         </is>
       </c>
-      <c r="I43" s="18" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="J43" s="19" t="inlineStr">
-        <is>
-          <t>ES6</t>
-        </is>
-      </c>
-      <c r="K43" s="18" t="inlineStr">
+      <c r="I57" s="13" t="inlineStr"/>
+      <c r="J57" s="14" t="inlineStr">
+        <is>
+          <t>ES5</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L43" s="20" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="18" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="19" t="inlineStr">
-        <is>
-          <t>CZ.ECM.ENT.TRN</t>
-        </is>
-      </c>
-      <c r="C44" s="20" t="inlineStr">
-        <is>
-          <t>E-sales as share of enterprise turnover</t>
-        </is>
-      </c>
-      <c r="D44" s="18" t="inlineStr">
-        <is>
-          <t>CZ</t>
-        </is>
-      </c>
-      <c r="E44" s="18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F44" s="22" t="n">
-        <v>25.65</v>
-      </c>
-      <c r="G44" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H44" s="20" t="inlineStr">
-        <is>
-          <t>% of total enterprise turnover</t>
-        </is>
-      </c>
-      <c r="I44" s="18" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="J44" s="19" t="inlineStr">
-        <is>
-          <t>ES6</t>
-        </is>
-      </c>
-      <c r="K44" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L44" s="20" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="18" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="19" t="inlineStr">
-        <is>
-          <t>LU.ECM.ENT.TRN</t>
-        </is>
-      </c>
-      <c r="C45" s="20" t="inlineStr">
-        <is>
-          <t>E-sales as share of enterprise turnover</t>
-        </is>
-      </c>
-      <c r="D45" s="18" t="inlineStr">
-        <is>
-          <t>LU</t>
-        </is>
-      </c>
-      <c r="E45" s="18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F45" s="22" t="n">
-        <v>23.86</v>
-      </c>
-      <c r="G45" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H45" s="20" t="inlineStr">
-        <is>
-          <t>% of total enterprise turnover</t>
-        </is>
-      </c>
-      <c r="I45" s="18" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="J45" s="19" t="inlineStr">
-        <is>
-          <t>ES6</t>
-        </is>
-      </c>
-      <c r="K45" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L45" s="20" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="18" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="19" t="inlineStr">
-        <is>
-          <t>HU.ECM.ENT.TRN</t>
-        </is>
-      </c>
-      <c r="C46" s="20" t="inlineStr">
-        <is>
-          <t>E-sales as share of enterprise turnover</t>
-        </is>
-      </c>
-      <c r="D46" s="18" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="E46" s="18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F46" s="22" t="n">
-        <v>21.35</v>
-      </c>
-      <c r="G46" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H46" s="20" t="inlineStr">
-        <is>
-          <t>% of total enterprise turnover</t>
-        </is>
-      </c>
-      <c r="I46" s="18" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="J46" s="19" t="inlineStr">
-        <is>
-          <t>ES6</t>
-        </is>
-      </c>
-      <c r="K46" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L46" s="20" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="18" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="19" t="inlineStr">
-        <is>
-          <t>DE.ECM.ENT.TRN</t>
-        </is>
-      </c>
-      <c r="C47" s="20" t="inlineStr">
-        <is>
-          <t>E-sales as share of enterprise turnover</t>
-        </is>
-      </c>
-      <c r="D47" s="18" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="E47" s="18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F47" s="22" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="G47" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H47" s="20" t="inlineStr">
-        <is>
-          <t>% of total enterprise turnover</t>
-        </is>
-      </c>
-      <c r="I47" s="18" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="J47" s="19" t="inlineStr">
-        <is>
-          <t>ES6</t>
-        </is>
-      </c>
-      <c r="K47" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L47" s="20" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="18" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="19" t="inlineStr">
-        <is>
-          <t>AT.ECM.ENT.TRN</t>
-        </is>
-      </c>
-      <c r="C48" s="20" t="inlineStr">
-        <is>
-          <t>E-sales as share of enterprise turnover</t>
-        </is>
-      </c>
-      <c r="D48" s="18" t="inlineStr">
-        <is>
-          <t>AT</t>
-        </is>
-      </c>
-      <c r="E48" s="18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F48" s="22" t="n">
-        <v>18.96</v>
-      </c>
-      <c r="G48" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H48" s="20" t="inlineStr">
-        <is>
-          <t>% of total enterprise turnover</t>
-        </is>
-      </c>
-      <c r="I48" s="18" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="J48" s="19" t="inlineStr">
-        <is>
-          <t>ES6</t>
-        </is>
-      </c>
-      <c r="K48" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L48" s="20" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="18" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="19" t="inlineStr">
-        <is>
-          <t>HR.ECM.ENT.TRN</t>
-        </is>
-      </c>
-      <c r="C49" s="20" t="inlineStr">
-        <is>
-          <t>E-sales as share of enterprise turnover</t>
-        </is>
-      </c>
-      <c r="D49" s="18" t="inlineStr">
-        <is>
-          <t>HR</t>
-        </is>
-      </c>
-      <c r="E49" s="18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F49" s="22" t="n">
-        <v>18.48</v>
-      </c>
-      <c r="G49" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H49" s="20" t="inlineStr">
-        <is>
-          <t>% of total enterprise turnover</t>
-        </is>
-      </c>
-      <c r="I49" s="18" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="J49" s="19" t="inlineStr">
-        <is>
-          <t>ES6</t>
-        </is>
-      </c>
-      <c r="K49" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L49" s="20" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="18" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="19" t="inlineStr">
-        <is>
-          <t>ES.ECM.ENT.TRN</t>
-        </is>
-      </c>
-      <c r="C50" s="20" t="inlineStr">
-        <is>
-          <t>E-sales as share of enterprise turnover</t>
-        </is>
-      </c>
-      <c r="D50" s="18" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="E50" s="18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F50" s="22" t="n">
-        <v>18.27</v>
-      </c>
-      <c r="G50" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H50" s="20" t="inlineStr">
-        <is>
-          <t>% of total enterprise turnover</t>
-        </is>
-      </c>
-      <c r="I50" s="18" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="J50" s="19" t="inlineStr">
-        <is>
-          <t>ES6</t>
-        </is>
-      </c>
-      <c r="K50" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L50" s="20" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="18" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="19" t="inlineStr">
-        <is>
-          <t>PL.ECM.ENT.TRN</t>
-        </is>
-      </c>
-      <c r="C51" s="20" t="inlineStr">
-        <is>
-          <t>E-sales as share of enterprise turnover</t>
-        </is>
-      </c>
-      <c r="D51" s="18" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E51" s="18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F51" s="22" t="n">
-        <v>17.66</v>
-      </c>
-      <c r="G51" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H51" s="20" t="inlineStr">
-        <is>
-          <t>% of total enterprise turnover</t>
-        </is>
-      </c>
-      <c r="I51" s="18" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="J51" s="19" t="inlineStr">
-        <is>
-          <t>ES6</t>
-        </is>
-      </c>
-      <c r="K51" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L51" s="20" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="18" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="19" t="inlineStr">
-        <is>
-          <t>SI.ECM.ENT.TRN</t>
-        </is>
-      </c>
-      <c r="C52" s="20" t="inlineStr">
-        <is>
-          <t>E-sales as share of enterprise turnover</t>
-        </is>
-      </c>
-      <c r="D52" s="18" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="E52" s="18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F52" s="22" t="n">
-        <v>16.78</v>
-      </c>
-      <c r="G52" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H52" s="20" t="inlineStr">
-        <is>
-          <t>% of total enterprise turnover</t>
-        </is>
-      </c>
-      <c r="I52" s="18" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="J52" s="19" t="inlineStr">
-        <is>
-          <t>ES6</t>
-        </is>
-      </c>
-      <c r="K52" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L52" s="20" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="18" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="19" t="inlineStr">
-        <is>
-          <t>IT.ECM.ENT.TRN</t>
-        </is>
-      </c>
-      <c r="C53" s="20" t="inlineStr">
-        <is>
-          <t>E-sales as share of enterprise turnover</t>
-        </is>
-      </c>
-      <c r="D53" s="18" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="E53" s="18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F53" s="22" t="n">
-        <v>15.66</v>
-      </c>
-      <c r="G53" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H53" s="20" t="inlineStr">
-        <is>
-          <t>% of total enterprise turnover</t>
-        </is>
-      </c>
-      <c r="I53" s="18" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="J53" s="19" t="inlineStr">
-        <is>
-          <t>ES6</t>
-        </is>
-      </c>
-      <c r="K53" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L53" s="20" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="18" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="19" t="inlineStr">
-        <is>
-          <t>MT.ECM.ENT.TRN</t>
-        </is>
-      </c>
-      <c r="C54" s="20" t="inlineStr">
-        <is>
-          <t>E-sales as share of enterprise turnover</t>
-        </is>
-      </c>
-      <c r="D54" s="18" t="inlineStr">
-        <is>
-          <t>MT</t>
-        </is>
-      </c>
-      <c r="E54" s="18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F54" s="22" t="n">
-        <v>15.46</v>
-      </c>
-      <c r="G54" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H54" s="20" t="inlineStr">
-        <is>
-          <t>% of total enterprise turnover</t>
-        </is>
-      </c>
-      <c r="I54" s="18" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="J54" s="19" t="inlineStr">
-        <is>
-          <t>ES6</t>
-        </is>
-      </c>
-      <c r="K54" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L54" s="20" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="18" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="19" t="inlineStr">
-        <is>
-          <t>FR.ECM.ENT.TRN</t>
-        </is>
-      </c>
-      <c r="C55" s="20" t="inlineStr">
-        <is>
-          <t>E-sales as share of enterprise turnover</t>
-        </is>
-      </c>
-      <c r="D55" s="18" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E55" s="18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F55" s="22" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="G55" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H55" s="20" t="inlineStr">
-        <is>
-          <t>% of total enterprise turnover</t>
-        </is>
-      </c>
-      <c r="I55" s="18" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="J55" s="19" t="inlineStr">
-        <is>
-          <t>ES6</t>
-        </is>
-      </c>
-      <c r="K55" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L55" s="20" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="18" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="19" t="inlineStr">
-        <is>
-          <t>CY.ECM.ENT.TRN</t>
-        </is>
-      </c>
-      <c r="C56" s="20" t="inlineStr">
-        <is>
-          <t>E-sales as share of enterprise turnover</t>
-        </is>
-      </c>
-      <c r="D56" s="18" t="inlineStr">
-        <is>
-          <t>CY</t>
-        </is>
-      </c>
-      <c r="E56" s="18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F56" s="22" t="n">
-        <v>13.36</v>
-      </c>
-      <c r="G56" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H56" s="20" t="inlineStr">
-        <is>
-          <t>% of total enterprise turnover</t>
-        </is>
-      </c>
-      <c r="I56" s="18" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="J56" s="19" t="inlineStr">
-        <is>
-          <t>ES6</t>
-        </is>
-      </c>
-      <c r="K56" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L56" s="20" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="18" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="19" t="inlineStr">
-        <is>
-          <t>BG.ECM.ENT.TRN</t>
-        </is>
-      </c>
-      <c r="C57" s="20" t="inlineStr">
-        <is>
-          <t>E-sales as share of enterprise turnover</t>
-        </is>
-      </c>
-      <c r="D57" s="18" t="inlineStr">
-        <is>
-          <t>BG</t>
-        </is>
-      </c>
-      <c r="E57" s="18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F57" s="22" t="n">
-        <v>7.63</v>
-      </c>
-      <c r="G57" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H57" s="20" t="inlineStr">
-        <is>
-          <t>% of total enterprise turnover</t>
-        </is>
-      </c>
-      <c r="I57" s="18" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="J57" s="19" t="inlineStr">
-        <is>
-          <t>ES6</t>
-        </is>
-      </c>
-      <c r="K57" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L57" s="20" t="inlineStr"/>
+      <c r="L57" s="15" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="13" t="n">
@@ -8371,24 +9101,24 @@
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>DK.ECM.ENT.SHR</t>
+          <t>EU.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
         <is>
-          <t>Enterprises making e-sales</t>
+          <t>E-sales as share of enterprise turnover</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>EU27</t>
         </is>
       </c>
       <c r="E58" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F58" s="16" t="n">
-        <v>38.78</v>
+        <v>19.49</v>
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
@@ -8397,7 +9127,7 @@
       </c>
       <c r="H58" s="15" t="inlineStr">
         <is>
-          <t>% of enterprises</t>
+          <t>% of total enterprise turnover</t>
         </is>
       </c>
       <c r="I58" s="13" t="inlineStr"/>
@@ -8411,11 +9141,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L58" s="15" t="inlineStr">
-        <is>
-          <t>2nd in EU after Lithuania.</t>
-        </is>
-      </c>
+      <c r="L58" s="15" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="13" t="n">
@@ -8423,24 +9149,24 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>LT.ECM.ENT.SHR</t>
+          <t>IE.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C59" s="15" t="inlineStr">
         <is>
-          <t>Enterprises making e-sales</t>
+          <t>E-sales as share of enterprise turnover</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="E59" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F59" s="16" t="n">
-        <v>43.03</v>
+        <v>38.25</v>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
@@ -8449,7 +9175,7 @@
       </c>
       <c r="H59" s="15" t="inlineStr">
         <is>
-          <t>% of enterprises</t>
+          <t>% of total enterprise turnover</t>
         </is>
       </c>
       <c r="I59" s="13" t="inlineStr"/>
@@ -8470,108 +9196,108 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="13" t="n">
+      <c r="A60" s="18" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="14" t="inlineStr">
-        <is>
-          <t>DK.DGP.EXMP</t>
-        </is>
-      </c>
-      <c r="C60" s="15" t="inlineStr">
-        <is>
-          <t>Citizens formally exempt from Digital Post</t>
-        </is>
-      </c>
-      <c r="D60" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E60" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F60" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="G60" s="13" t="inlineStr">
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t>BE.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="E60" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F60" s="22" t="n">
+        <v>29.51</v>
+      </c>
+      <c r="G60" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H60" s="15" t="inlineStr">
-        <is>
-          <t>% of citizens aged 15+ resident in Denmark</t>
-        </is>
-      </c>
-      <c r="I60" s="13" t="inlineStr"/>
-      <c r="J60" s="14" t="inlineStr">
-        <is>
-          <t>DG1</t>
-        </is>
-      </c>
-      <c r="K60" s="13" t="inlineStr">
+      <c r="H60" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I60" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J60" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K60" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L60" s="15" t="inlineStr">
-        <is>
-          <t>April 2025; approx. 256,000 citizens.</t>
-        </is>
-      </c>
+      <c r="L60" s="20" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="13" t="n">
+      <c r="A61" s="18" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="14" t="inlineStr">
-        <is>
-          <t>DK.DGP.EXMP</t>
-        </is>
-      </c>
-      <c r="C61" s="15" t="inlineStr">
-        <is>
-          <t>Citizens formally exempt from Digital Post</t>
-        </is>
-      </c>
-      <c r="D61" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E61" s="13" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F61" s="16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G61" s="13" t="inlineStr">
+      <c r="B61" s="19" t="inlineStr">
+        <is>
+          <t>SE.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C61" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D61" s="18" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="E61" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F61" s="22" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="G61" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H61" s="15" t="inlineStr">
-        <is>
-          <t>% of citizens aged 15+ resident in Denmark</t>
-        </is>
-      </c>
-      <c r="I61" s="13" t="inlineStr"/>
-      <c r="J61" s="14" t="inlineStr">
-        <is>
-          <t>DG1</t>
-        </is>
-      </c>
-      <c r="K61" s="13" t="inlineStr">
+      <c r="H61" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I61" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J61" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K61" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L61" s="15" t="inlineStr">
-        <is>
-          <t>Q1 2026; 238,479 citizens. 95.2% enrolled.</t>
-        </is>
-      </c>
+      <c r="L61" s="20" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="18" t="n">
@@ -8579,24 +9305,24 @@
       </c>
       <c r="B62" s="19" t="inlineStr">
         <is>
-          <t>DK.DGP.EXMP.7584</t>
+          <t>CZ.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>Exemption rate, age 75-84</t>
+          <t>E-sales as share of enterprise turnover</t>
         </is>
       </c>
       <c r="D62" s="18" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="E62" s="18" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F62" s="22" t="n">
-        <v>20</v>
+        <v>25.65</v>
       </c>
       <c r="G62" s="18" t="inlineStr">
         <is>
@@ -8605,17 +9331,17 @@
       </c>
       <c r="H62" s="20" t="inlineStr">
         <is>
-          <t>% of age group</t>
+          <t>% of total enterprise turnover</t>
         </is>
       </c>
       <c r="I62" s="18" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>u</t>
         </is>
       </c>
       <c r="J62" s="19" t="inlineStr">
         <is>
-          <t>DG1</t>
+          <t>ES6</t>
         </is>
       </c>
       <c r="K62" s="18" t="inlineStr">
@@ -8623,11 +9349,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L62" s="20" t="inlineStr">
-        <is>
-          <t>Source states 'nearly one in five'.</t>
-        </is>
-      </c>
+      <c r="L62" s="20" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="18" t="n">
@@ -8635,24 +9357,24 @@
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
-          <t>DK.DGP.EXMP.85P</t>
+          <t>LU.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C63" s="20" t="inlineStr">
         <is>
-          <t>Exemption rate, age 85+</t>
+          <t>E-sales as share of enterprise turnover</t>
         </is>
       </c>
       <c r="D63" s="18" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E63" s="18" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F63" s="22" t="n">
-        <v>33</v>
+        <v>23.86</v>
       </c>
       <c r="G63" s="18" t="inlineStr">
         <is>
@@ -8661,17 +9383,17 @@
       </c>
       <c r="H63" s="20" t="inlineStr">
         <is>
-          <t>% of age group</t>
+          <t>% of total enterprise turnover</t>
         </is>
       </c>
       <c r="I63" s="18" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>u</t>
         </is>
       </c>
       <c r="J63" s="19" t="inlineStr">
         <is>
-          <t>DG1</t>
+          <t>ES6</t>
         </is>
       </c>
       <c r="K63" s="18" t="inlineStr">
@@ -8679,115 +9401,111 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L63" s="20" t="inlineStr">
-        <is>
-          <t>Source states 'roughly one in three'.</t>
-        </is>
-      </c>
+      <c r="L63" s="20" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="13" t="n">
+      <c r="A64" s="18" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="14" t="inlineStr">
-        <is>
-          <t>DK.DGX.NOUSE</t>
-        </is>
-      </c>
-      <c r="C64" s="15" t="inlineStr">
-        <is>
-          <t>Do not use digital public services at all</t>
-        </is>
-      </c>
-      <c r="D64" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E64" s="13" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F64" s="16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G64" s="13" t="inlineStr">
+      <c r="B64" s="19" t="inlineStr">
+        <is>
+          <t>HU.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C64" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D64" s="18" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="E64" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F64" s="22" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="G64" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H64" s="15" t="inlineStr">
-        <is>
-          <t>% of population</t>
-        </is>
-      </c>
-      <c r="I64" s="13" t="inlineStr"/>
-      <c r="J64" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K64" s="13" t="inlineStr">
+      <c r="H64" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I64" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J64" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K64" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L64" s="15" t="inlineStr">
-        <is>
-          <t>Agency for Digital Government estimate.</t>
-        </is>
-      </c>
+      <c r="L64" s="20" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="13" t="n">
+      <c r="A65" s="18" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="14" t="inlineStr">
-        <is>
-          <t>DK.DGX.DIFF</t>
-        </is>
-      </c>
-      <c r="C65" s="15" t="inlineStr">
-        <is>
-          <t>Face difficulties using digital public services</t>
-        </is>
-      </c>
-      <c r="D65" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E65" s="13" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F65" s="16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G65" s="13" t="inlineStr">
+      <c r="B65" s="19" t="inlineStr">
+        <is>
+          <t>DE.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C65" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D65" s="18" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E65" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F65" s="22" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="G65" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H65" s="15" t="inlineStr">
-        <is>
-          <t>% of population</t>
-        </is>
-      </c>
-      <c r="I65" s="13" t="inlineStr"/>
-      <c r="J65" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K65" s="13" t="inlineStr">
+      <c r="H65" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I65" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J65" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K65" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L65" s="15" t="inlineStr">
-        <is>
-          <t>Agency for Digital Government estimate.</t>
-        </is>
-      </c>
+      <c r="L65" s="20" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="18" t="n">
@@ -8795,24 +9513,24 @@
       </c>
       <c r="B66" s="19" t="inlineStr">
         <is>
-          <t>DK.DGX.DISADV.LO</t>
+          <t>AT.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>'Digitally disadvantaged' - lower bound</t>
+          <t>E-sales as share of enterprise turnover</t>
         </is>
       </c>
       <c r="D66" s="18" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="E66" s="18" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F66" s="22" t="n">
-        <v>17</v>
+        <v>18.96</v>
       </c>
       <c r="G66" s="18" t="inlineStr">
         <is>
@@ -8821,17 +9539,17 @@
       </c>
       <c r="H66" s="20" t="inlineStr">
         <is>
-          <t>% of adult population</t>
+          <t>% of total enterprise turnover</t>
         </is>
       </c>
       <c r="I66" s="18" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>u</t>
         </is>
       </c>
       <c r="J66" s="19" t="inlineStr">
         <is>
-          <t>DG2</t>
+          <t>ES6</t>
         </is>
       </c>
       <c r="K66" s="18" t="inlineStr">
@@ -8839,11 +9557,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L66" s="20" t="inlineStr">
-        <is>
-          <t>Published as a 17-22% range.</t>
-        </is>
-      </c>
+      <c r="L66" s="20" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="18" t="n">
@@ -8851,24 +9565,24 @@
       </c>
       <c r="B67" s="19" t="inlineStr">
         <is>
-          <t>DK.DGX.DISADV.HI</t>
+          <t>HR.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C67" s="20" t="inlineStr">
         <is>
-          <t>'Digitally disadvantaged' - upper bound</t>
+          <t>E-sales as share of enterprise turnover</t>
         </is>
       </c>
       <c r="D67" s="18" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E67" s="18" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F67" s="22" t="n">
-        <v>22</v>
+        <v>18.48</v>
       </c>
       <c r="G67" s="18" t="inlineStr">
         <is>
@@ -8877,17 +9591,17 @@
       </c>
       <c r="H67" s="20" t="inlineStr">
         <is>
-          <t>% of adult population</t>
+          <t>% of total enterprise turnover</t>
         </is>
       </c>
       <c r="I67" s="18" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>u</t>
         </is>
       </c>
       <c r="J67" s="19" t="inlineStr">
         <is>
-          <t>DG2</t>
+          <t>ES6</t>
         </is>
       </c>
       <c r="K67" s="18" t="inlineStr">
@@ -8895,11 +9609,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L67" s="20" t="inlineStr">
-        <is>
-          <t>Published as a 17-22% range.</t>
-        </is>
-      </c>
+      <c r="L67" s="20" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="18" t="n">
@@ -8907,24 +9617,24 @@
       </c>
       <c r="B68" s="19" t="inlineStr">
         <is>
-          <t>DK.DGX.JUST</t>
+          <t>ES.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>'Digitally disadvantaged' - Justitia estimate</t>
+          <t>E-sales as share of enterprise turnover</t>
         </is>
       </c>
       <c r="D68" s="18" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E68" s="18" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F68" s="22" t="n">
-        <v>25</v>
+        <v>18.27</v>
       </c>
       <c r="G68" s="18" t="inlineStr">
         <is>
@@ -8933,17 +9643,17 @@
       </c>
       <c r="H68" s="20" t="inlineStr">
         <is>
-          <t>% of adult population</t>
+          <t>% of total enterprise turnover</t>
         </is>
       </c>
       <c r="I68" s="18" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>u</t>
         </is>
       </c>
       <c r="J68" s="19" t="inlineStr">
         <is>
-          <t>JU1</t>
+          <t>ES6</t>
         </is>
       </c>
       <c r="K68" s="18" t="inlineStr">
@@ -8951,363 +9661,371 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L68" s="20" t="inlineStr">
-        <is>
-          <t>Report states 'up to a quarter of the adult population'.</t>
-        </is>
-      </c>
+      <c r="L68" s="20" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="13" t="n">
+      <c r="A69" s="18" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="14" t="inlineStr">
-        <is>
-          <t>DK.TRU.DPS</t>
-        </is>
-      </c>
-      <c r="C69" s="15" t="inlineStr">
-        <is>
-          <t>Trust in digital public solutions</t>
-        </is>
-      </c>
-      <c r="D69" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E69" s="13" t="n">
+      <c r="B69" s="19" t="inlineStr">
+        <is>
+          <t>PL.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C69" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D69" s="18" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="n">
         <v>2024</v>
       </c>
-      <c r="F69" s="16" t="n">
-        <v>82</v>
-      </c>
-      <c r="G69" s="13" t="inlineStr">
+      <c r="F69" s="22" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="G69" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H69" s="15" t="inlineStr">
-        <is>
-          <t>% of population</t>
-        </is>
-      </c>
-      <c r="I69" s="13" t="inlineStr"/>
-      <c r="J69" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K69" s="13" t="inlineStr">
+      <c r="H69" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I69" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J69" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K69" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L69" s="15" t="inlineStr"/>
+      <c r="L69" s="20" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="13" t="n">
+      <c r="A70" s="18" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="14" t="inlineStr">
-        <is>
-          <t>DK.TRU.DPS</t>
-        </is>
-      </c>
-      <c r="C70" s="15" t="inlineStr">
-        <is>
-          <t>Trust in digital public solutions</t>
-        </is>
-      </c>
-      <c r="D70" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E70" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F70" s="16" t="n">
-        <v>84</v>
-      </c>
-      <c r="G70" s="13" t="inlineStr">
+      <c r="B70" s="19" t="inlineStr">
+        <is>
+          <t>SI.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C70" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D70" s="18" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="E70" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F70" s="22" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="G70" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H70" s="15" t="inlineStr">
-        <is>
-          <t>% of population</t>
-        </is>
-      </c>
-      <c r="I70" s="13" t="inlineStr"/>
-      <c r="J70" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K70" s="13" t="inlineStr">
+      <c r="H70" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I70" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J70" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K70" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L70" s="15" t="inlineStr">
-        <is>
-          <t>Record high.</t>
-        </is>
-      </c>
+      <c r="L70" s="20" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="13" t="n">
+      <c r="A71" s="18" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="14" t="inlineStr">
-        <is>
-          <t>DK.TRU.DGP.SEC</t>
-        </is>
-      </c>
-      <c r="C71" s="15" t="inlineStr">
-        <is>
-          <t>Perceived security of Digital Post</t>
-        </is>
-      </c>
-      <c r="D71" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E71" s="13" t="n">
-        <v>2017</v>
-      </c>
-      <c r="F71" s="16" t="n">
-        <v>77</v>
-      </c>
-      <c r="G71" s="13" t="inlineStr">
+      <c r="B71" s="19" t="inlineStr">
+        <is>
+          <t>IT.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C71" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E71" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F71" s="22" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="G71" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H71" s="15" t="inlineStr">
-        <is>
-          <t>% of population</t>
-        </is>
-      </c>
-      <c r="I71" s="13" t="inlineStr"/>
-      <c r="J71" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K71" s="13" t="inlineStr">
+      <c r="H71" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I71" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J71" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K71" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L71" s="15" t="inlineStr"/>
+      <c r="L71" s="20" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="13" t="n">
+      <c r="A72" s="18" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="14" t="inlineStr">
-        <is>
-          <t>DK.TRU.DGP.SEC</t>
-        </is>
-      </c>
-      <c r="C72" s="15" t="inlineStr">
-        <is>
-          <t>Perceived security of Digital Post</t>
-        </is>
-      </c>
-      <c r="D72" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E72" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F72" s="16" t="n">
-        <v>89</v>
-      </c>
-      <c r="G72" s="13" t="inlineStr">
+      <c r="B72" s="19" t="inlineStr">
+        <is>
+          <t>MT.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C72" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D72" s="18" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="E72" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F72" s="22" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="G72" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H72" s="15" t="inlineStr">
-        <is>
-          <t>% of population</t>
-        </is>
-      </c>
-      <c r="I72" s="13" t="inlineStr"/>
-      <c r="J72" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K72" s="13" t="inlineStr">
+      <c r="H72" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I72" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J72" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K72" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L72" s="15" t="inlineStr"/>
+      <c r="L72" s="20" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="13" t="n">
+      <c r="A73" s="18" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="14" t="inlineStr">
-        <is>
-          <t>DK.SKL.1624</t>
-        </is>
-      </c>
-      <c r="C73" s="15" t="inlineStr">
-        <is>
-          <t>At least basic digital skills, age 16-24</t>
-        </is>
-      </c>
-      <c r="D73" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E73" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F73" s="16" t="n">
-        <v>92.06</v>
-      </c>
-      <c r="G73" s="13" t="inlineStr">
+      <c r="B73" s="19" t="inlineStr">
+        <is>
+          <t>FR.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C73" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D73" s="18" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E73" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F73" s="22" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="G73" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H73" s="15" t="inlineStr">
-        <is>
-          <t>% of age group</t>
-        </is>
-      </c>
-      <c r="I73" s="13" t="inlineStr"/>
-      <c r="J73" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K73" s="13" t="inlineStr">
+      <c r="H73" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I73" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J73" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K73" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L73" s="15" t="inlineStr">
-        <is>
-          <t>EU average 74.55%.</t>
-        </is>
-      </c>
+      <c r="L73" s="20" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="13" t="n">
+      <c r="A74" s="18" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="14" t="inlineStr">
-        <is>
-          <t>DK.SKL.2554</t>
-        </is>
-      </c>
-      <c r="C74" s="15" t="inlineStr">
-        <is>
-          <t>At least basic digital skills, age 25-54</t>
-        </is>
-      </c>
-      <c r="D74" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E74" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F74" s="16" t="n">
-        <v>86.89</v>
-      </c>
-      <c r="G74" s="13" t="inlineStr">
+      <c r="B74" s="19" t="inlineStr">
+        <is>
+          <t>CY.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C74" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="E74" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F74" s="22" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="G74" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H74" s="15" t="inlineStr">
-        <is>
-          <t>% of age group</t>
-        </is>
-      </c>
-      <c r="I74" s="13" t="inlineStr"/>
-      <c r="J74" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K74" s="13" t="inlineStr">
+      <c r="H74" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I74" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J74" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K74" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L74" s="15" t="inlineStr">
-        <is>
-          <t>EU average 68.57%.</t>
-        </is>
-      </c>
+      <c r="L74" s="20" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="13" t="n">
+      <c r="A75" s="18" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="14" t="inlineStr">
-        <is>
-          <t>DK.SKL.5574</t>
-        </is>
-      </c>
-      <c r="C75" s="15" t="inlineStr">
-        <is>
-          <t>At least basic digital skills, age 55-74</t>
-        </is>
-      </c>
-      <c r="D75" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E75" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F75" s="16" t="n">
-        <v>67.81</v>
-      </c>
-      <c r="G75" s="13" t="inlineStr">
+      <c r="B75" s="19" t="inlineStr">
+        <is>
+          <t>BG.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C75" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D75" s="18" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F75" s="22" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="G75" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H75" s="15" t="inlineStr">
-        <is>
-          <t>% of age group</t>
-        </is>
-      </c>
-      <c r="I75" s="13" t="inlineStr"/>
-      <c r="J75" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K75" s="13" t="inlineStr">
+      <c r="H75" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I75" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J75" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K75" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L75" s="15" t="inlineStr">
-        <is>
-          <t>EU average 42.60%.</t>
-        </is>
-      </c>
+      <c r="L75" s="20" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="13" t="n">
@@ -9315,12 +10033,12 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>DK.ENT.DII</t>
+          <t>DK.ECM.ENT.SHR</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>SMEs with at least basic digital intensity</t>
+          <t>Enterprises making e-sales</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr">
@@ -9329,10 +10047,10 @@
         </is>
       </c>
       <c r="E76" s="13" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F76" s="16" t="n">
-        <v>92.45</v>
+        <v>38.78</v>
       </c>
       <c r="G76" s="13" t="inlineStr">
         <is>
@@ -9341,13 +10059,13 @@
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>% of SMEs</t>
+          <t>% of enterprises</t>
         </is>
       </c>
       <c r="I76" s="13" t="inlineStr"/>
       <c r="J76" s="14" t="inlineStr">
         <is>
-          <t>EC1</t>
+          <t>ES5</t>
         </is>
       </c>
       <c r="K76" s="13" t="inlineStr">
@@ -9357,7 +10075,7 @@
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>EU average 71.39%.</t>
+          <t>2nd in EU after Lithuania.</t>
         </is>
       </c>
     </row>
@@ -9367,24 +10085,24 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>EU.ENT.DII</t>
+          <t>LT.ECM.ENT.SHR</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>SMEs with at least basic digital intensity</t>
+          <t>Enterprises making e-sales</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>EU27</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="E77" s="13" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F77" s="16" t="n">
-        <v>71.39</v>
+        <v>43.03</v>
       </c>
       <c r="G77" s="13" t="inlineStr">
         <is>
@@ -9393,13 +10111,13 @@
       </c>
       <c r="H77" s="15" t="inlineStr">
         <is>
-          <t>% of SMEs</t>
+          <t>% of enterprises</t>
         </is>
       </c>
       <c r="I77" s="13" t="inlineStr"/>
       <c r="J77" s="14" t="inlineStr">
         <is>
-          <t>EC1</t>
+          <t>ES5</t>
         </is>
       </c>
       <c r="K77" s="13" t="inlineStr">
@@ -9407,7 +10125,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L77" s="15" t="inlineStr"/>
+      <c r="L77" s="15" t="inlineStr">
+        <is>
+          <t>Highest in EU.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="13" t="n">
@@ -9415,12 +10137,12 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>DK.ENT.AI</t>
+          <t>DK.DGP.EXMP</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Enterprises adopting AI</t>
+          <t>Citizens formally exempt from Digital Post</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr">
@@ -9432,7 +10154,7 @@
         <v>2025</v>
       </c>
       <c r="F78" s="16" t="n">
-        <v>42.03</v>
+        <v>5</v>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
@@ -9441,13 +10163,13 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>% of enterprises</t>
+          <t>% of citizens aged 15+ resident in Denmark</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr"/>
       <c r="J78" s="14" t="inlineStr">
         <is>
-          <t>EC1</t>
+          <t>DG1</t>
         </is>
       </c>
       <c r="K78" s="13" t="inlineStr">
@@ -9457,7 +10179,7 @@
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>EU average 19.95%.</t>
+          <t>April 2025; approx. 256,000 citizens.</t>
         </is>
       </c>
     </row>
@@ -9467,12 +10189,12 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>DK.ENT.AI.LRG</t>
+          <t>DK.DGP.EXMP</t>
         </is>
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>Large enterprises adopting AI</t>
+          <t>Citizens formally exempt from Digital Post</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr">
@@ -9481,10 +10203,10 @@
         </is>
       </c>
       <c r="E79" s="13" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F79" s="16" t="n">
-        <v>74.52</v>
+        <v>4.7</v>
       </c>
       <c r="G79" s="13" t="inlineStr">
         <is>
@@ -9493,13 +10215,13 @@
       </c>
       <c r="H79" s="15" t="inlineStr">
         <is>
-          <t>% of large enterprises (250+)</t>
+          <t>% of citizens aged 15+ resident in Denmark</t>
         </is>
       </c>
       <c r="I79" s="13" t="inlineStr"/>
       <c r="J79" s="14" t="inlineStr">
         <is>
-          <t>EC1</t>
+          <t>DG1</t>
         </is>
       </c>
       <c r="K79" s="13" t="inlineStr">
@@ -9507,105 +10229,121 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L79" s="15" t="inlineStr"/>
+      <c r="L79" s="15" t="inlineStr">
+        <is>
+          <t>Q1 2026; 238,479 citizens. 95.2% enrolled.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="13" t="n">
+      <c r="A80" s="18" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="14" t="inlineStr">
-        <is>
-          <t>DK.ENT.AI.SME</t>
-        </is>
-      </c>
-      <c r="C80" s="15" t="inlineStr">
-        <is>
-          <t>SMEs adopting AI</t>
-        </is>
-      </c>
-      <c r="D80" s="13" t="inlineStr">
+      <c r="B80" s="19" t="inlineStr">
+        <is>
+          <t>DK.DGP.EXMP.7584</t>
+        </is>
+      </c>
+      <c r="C80" s="20" t="inlineStr">
+        <is>
+          <t>Exemption rate, age 75-84</t>
+        </is>
+      </c>
+      <c r="D80" s="18" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E80" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F80" s="16" t="n">
-        <v>40.99</v>
-      </c>
-      <c r="G80" s="13" t="inlineStr">
+      <c r="E80" s="18" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F80" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="G80" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H80" s="15" t="inlineStr">
-        <is>
-          <t>% of SMEs (10-249)</t>
-        </is>
-      </c>
-      <c r="I80" s="13" t="inlineStr"/>
-      <c r="J80" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K80" s="13" t="inlineStr">
+      <c r="H80" s="20" t="inlineStr">
+        <is>
+          <t>% of age group</t>
+        </is>
+      </c>
+      <c r="I80" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J80" s="19" t="inlineStr">
+        <is>
+          <t>DG1</t>
+        </is>
+      </c>
+      <c r="K80" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L80" s="15" t="inlineStr"/>
+      <c r="L80" s="20" t="inlineStr">
+        <is>
+          <t>Source states 'nearly one in five'.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="13" t="n">
+      <c r="A81" s="18" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="14" t="inlineStr">
-        <is>
-          <t>DK.GOV.DPS.CIT</t>
-        </is>
-      </c>
-      <c r="C81" s="15" t="inlineStr">
-        <is>
-          <t>Digital public services for citizens (score)</t>
-        </is>
-      </c>
-      <c r="D81" s="13" t="inlineStr">
+      <c r="B81" s="19" t="inlineStr">
+        <is>
+          <t>DK.DGP.EXMP.85P</t>
+        </is>
+      </c>
+      <c r="C81" s="20" t="inlineStr">
+        <is>
+          <t>Exemption rate, age 85+</t>
+        </is>
+      </c>
+      <c r="D81" s="18" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E81" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F81" s="16" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="G81" s="13" t="inlineStr">
-        <is>
-          <t>score 0-100</t>
-        </is>
-      </c>
-      <c r="H81" s="15" t="inlineStr">
-        <is>
-          <t>eGovernment Benchmark score</t>
-        </is>
-      </c>
-      <c r="I81" s="13" t="inlineStr"/>
-      <c r="J81" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K81" s="13" t="inlineStr">
+      <c r="E81" s="18" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F81" s="22" t="n">
+        <v>33</v>
+      </c>
+      <c r="G81" s="18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H81" s="20" t="inlineStr">
+        <is>
+          <t>% of age group</t>
+        </is>
+      </c>
+      <c r="I81" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J81" s="19" t="inlineStr">
+        <is>
+          <t>DG1</t>
+        </is>
+      </c>
+      <c r="K81" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L81" s="15" t="inlineStr">
-        <is>
-          <t>BELOW the EU average of 84.64.</t>
+      <c r="L81" s="20" t="inlineStr">
+        <is>
+          <t>Source states 'roughly one in three'.</t>
         </is>
       </c>
     </row>
@@ -9615,33 +10353,33 @@
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>EU.GOV.DPS.CIT</t>
+          <t>DK.DGX.NOUSE</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Digital public services for citizens (score)</t>
+          <t>Do not use digital public services at all</t>
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr">
         <is>
-          <t>EU27</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="E82" s="13" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F82" s="16" t="n">
-        <v>84.64</v>
+        <v>6.5</v>
       </c>
       <c r="G82" s="13" t="inlineStr">
         <is>
-          <t>score 0-100</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H82" s="15" t="inlineStr">
         <is>
-          <t>eGovernment Benchmark score</t>
+          <t>% of population</t>
         </is>
       </c>
       <c r="I82" s="13" t="inlineStr"/>
@@ -9655,7 +10393,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L82" s="15" t="inlineStr"/>
+      <c r="L82" s="15" t="inlineStr">
+        <is>
+          <t>Agency for Digital Government estimate.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="13" t="n">
@@ -9663,12 +10405,12 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>DK.GOV.DPS.XB</t>
+          <t>DK.DGX.DIFF</t>
         </is>
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>Cross-border digital public services, citizens (score)</t>
+          <t>Face difficulties using digital public services</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr">
@@ -9677,19 +10419,19 @@
         </is>
       </c>
       <c r="E83" s="13" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F83" s="16" t="n">
-        <v>64.40000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="G83" s="13" t="inlineStr">
         <is>
-          <t>score 0-100</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H83" s="15" t="inlineStr">
         <is>
-          <t>eGovernment Benchmark score</t>
+          <t>% of population</t>
         </is>
       </c>
       <c r="I83" s="13" t="inlineStr"/>
@@ -9705,109 +10447,121 @@
       </c>
       <c r="L83" s="15" t="inlineStr">
         <is>
-          <t>EU average 75.28.</t>
+          <t>Agency for Digital Government estimate.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="13" t="n">
+      <c r="A84" s="18" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="14" t="inlineStr">
-        <is>
-          <t>DK.ENV.WEEE</t>
-        </is>
-      </c>
-      <c r="C84" s="15" t="inlineStr">
-        <is>
-          <t>ICT waste recycled or prepared for reuse</t>
-        </is>
-      </c>
-      <c r="D84" s="13" t="inlineStr">
+      <c r="B84" s="19" t="inlineStr">
+        <is>
+          <t>DK.DGX.DISADV.LO</t>
+        </is>
+      </c>
+      <c r="C84" s="20" t="inlineStr">
+        <is>
+          <t>'Digitally disadvantaged' - lower bound</t>
+        </is>
+      </c>
+      <c r="D84" s="18" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E84" s="13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F84" s="16" t="n">
-        <v>15.37</v>
-      </c>
-      <c r="G84" s="13" t="inlineStr">
+      <c r="E84" s="18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F84" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="G84" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H84" s="15" t="inlineStr">
-        <is>
-          <t>% of ICT-related WEEE collected</t>
-        </is>
-      </c>
-      <c r="I84" s="13" t="inlineStr"/>
-      <c r="J84" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K84" s="13" t="inlineStr">
+      <c r="H84" s="20" t="inlineStr">
+        <is>
+          <t>% of adult population</t>
+        </is>
+      </c>
+      <c r="I84" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J84" s="19" t="inlineStr">
+        <is>
+          <t>DG2</t>
+        </is>
+      </c>
+      <c r="K84" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L84" s="15" t="inlineStr">
-        <is>
-          <t>Among the lowest in the EU; EU average 80.23%.</t>
+      <c r="L84" s="20" t="inlineStr">
+        <is>
+          <t>Published as a 17-22% range.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="13" t="n">
+      <c r="A85" s="18" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="14" t="inlineStr">
-        <is>
-          <t>EU.ENV.WEEE</t>
-        </is>
-      </c>
-      <c r="C85" s="15" t="inlineStr">
-        <is>
-          <t>ICT waste recycled or prepared for reuse</t>
-        </is>
-      </c>
-      <c r="D85" s="13" t="inlineStr">
-        <is>
-          <t>EU27</t>
-        </is>
-      </c>
-      <c r="E85" s="13" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F85" s="16" t="n">
-        <v>80.23</v>
-      </c>
-      <c r="G85" s="13" t="inlineStr">
+      <c r="B85" s="19" t="inlineStr">
+        <is>
+          <t>DK.DGX.DISADV.HI</t>
+        </is>
+      </c>
+      <c r="C85" s="20" t="inlineStr">
+        <is>
+          <t>'Digitally disadvantaged' - upper bound</t>
+        </is>
+      </c>
+      <c r="D85" s="18" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E85" s="18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F85" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="G85" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H85" s="15" t="inlineStr">
-        <is>
-          <t>% of ICT-related WEEE collected</t>
-        </is>
-      </c>
-      <c r="I85" s="13" t="inlineStr"/>
-      <c r="J85" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K85" s="13" t="inlineStr">
+      <c r="H85" s="20" t="inlineStr">
+        <is>
+          <t>% of adult population</t>
+        </is>
+      </c>
+      <c r="I85" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J85" s="19" t="inlineStr">
+        <is>
+          <t>DG2</t>
+        </is>
+      </c>
+      <c r="K85" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L85" s="15" t="inlineStr"/>
+      <c r="L85" s="20" t="inlineStr">
+        <is>
+          <t>Published as a 17-22% range.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="18" t="n">
@@ -9815,12 +10569,12 @@
       </c>
       <c r="B86" s="19" t="inlineStr">
         <is>
-          <t>DK.SME.SMVD.PROJ</t>
+          <t>DK.DGX.JUST</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
         <is>
-          <t>SMV:Digital projects supported since 2018</t>
+          <t>'Digitally disadvantaged' - Justitia estimate</t>
         </is>
       </c>
       <c r="D86" s="18" t="inlineStr">
@@ -9829,19 +10583,19 @@
         </is>
       </c>
       <c r="E86" s="18" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F86" s="21" t="n">
-        <v>7000</v>
+        <v>2022</v>
+      </c>
+      <c r="F86" s="22" t="n">
+        <v>25</v>
       </c>
       <c r="G86" s="18" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H86" s="20" t="inlineStr">
         <is>
-          <t>digitalisation projects</t>
+          <t>% of adult population</t>
         </is>
       </c>
       <c r="I86" s="18" t="inlineStr">
@@ -9851,7 +10605,7 @@
       </c>
       <c r="J86" s="19" t="inlineStr">
         <is>
-          <t>DG3</t>
+          <t>JU1</t>
         </is>
       </c>
       <c r="K86" s="18" t="inlineStr">
@@ -9861,7 +10615,7 @@
       </c>
       <c r="L86" s="20" t="inlineStr">
         <is>
-          <t>Source states 'knap 7.000' (just under 7,000).</t>
+          <t>Report states 'up to a quarter of the adult population'.</t>
         </is>
       </c>
     </row>
@@ -9871,12 +10625,12 @@
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>DK.SME.SMVD.INV</t>
+          <t>DK.TRU.DPS</t>
         </is>
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>Participants who invested further during the project</t>
+          <t>Trust in digital public solutions</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr">
@@ -9885,10 +10639,10 @@
         </is>
       </c>
       <c r="E87" s="13" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F87" s="16" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="G87" s="13" t="inlineStr">
         <is>
@@ -9897,13 +10651,13 @@
       </c>
       <c r="H87" s="15" t="inlineStr">
         <is>
-          <t>% of participating enterprises</t>
+          <t>% of population</t>
         </is>
       </c>
       <c r="I87" s="13" t="inlineStr"/>
       <c r="J87" s="14" t="inlineStr">
         <is>
-          <t>DG3</t>
+          <t>EC1</t>
         </is>
       </c>
       <c r="K87" s="13" t="inlineStr">
@@ -9919,12 +10673,12 @@
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>DK.SME.SMVD.NOINV</t>
+          <t>DK.TRU.DPS</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Participants with no further investment plans</t>
+          <t>Trust in digital public solutions</t>
         </is>
       </c>
       <c r="D88" s="13" t="inlineStr">
@@ -9936,7 +10690,7 @@
         <v>2025</v>
       </c>
       <c r="F88" s="16" t="n">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="G88" s="13" t="inlineStr">
         <is>
@@ -9945,13 +10699,13 @@
       </c>
       <c r="H88" s="15" t="inlineStr">
         <is>
-          <t>% of participating enterprises</t>
+          <t>% of population</t>
         </is>
       </c>
       <c r="I88" s="13" t="inlineStr"/>
       <c r="J88" s="14" t="inlineStr">
         <is>
-          <t>DG3</t>
+          <t>EC1</t>
         </is>
       </c>
       <c r="K88" s="13" t="inlineStr">
@@ -9959,7 +10713,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L88" s="15" t="inlineStr"/>
+      <c r="L88" s="15" t="inlineStr">
+        <is>
+          <t>Record high.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="13" t="n">
@@ -9967,12 +10725,12 @@
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>DK.POP.TOT</t>
+          <t>DK.TRU.DGP.SEC</t>
         </is>
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>Resident population</t>
+          <t>Perceived security of Digital Post</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr">
@@ -9981,25 +10739,25 @@
         </is>
       </c>
       <c r="E89" s="13" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F89" s="17" t="n">
-        <v>6025603</v>
+        <v>2017</v>
+      </c>
+      <c r="F89" s="16" t="n">
+        <v>77</v>
       </c>
       <c r="G89" s="13" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H89" s="15" t="inlineStr">
         <is>
-          <t>persons resident in Denmark</t>
+          <t>% of population</t>
         </is>
       </c>
       <c r="I89" s="13" t="inlineStr"/>
       <c r="J89" s="14" t="inlineStr">
         <is>
-          <t>DST2</t>
+          <t>EC1</t>
         </is>
       </c>
       <c r="K89" s="13" t="inlineStr">
@@ -10007,67 +10765,55 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L89" s="15" t="inlineStr">
-        <is>
-          <t>As at 1 January 2026.</t>
-        </is>
-      </c>
+      <c r="L89" s="15" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="18" t="n">
+      <c r="A90" s="13" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="19" t="inlineStr">
-        <is>
-          <t>DK.DGP.EXMP.N</t>
-        </is>
-      </c>
-      <c r="C90" s="20" t="inlineStr">
-        <is>
-          <t>Citizens formally exempt from Digital Post</t>
-        </is>
-      </c>
-      <c r="D90" s="18" t="inlineStr">
+      <c r="B90" s="14" t="inlineStr">
+        <is>
+          <t>DK.TRU.DGP.SEC</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="inlineStr">
+        <is>
+          <t>Perceived security of Digital Post</t>
+        </is>
+      </c>
+      <c r="D90" s="13" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E90" s="18" t="n">
+      <c r="E90" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="F90" s="21" t="n">
-        <v>256000</v>
-      </c>
-      <c r="G90" s="18" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H90" s="20" t="inlineStr">
-        <is>
-          <t>citizens aged 15+ resident in Denmark</t>
-        </is>
-      </c>
-      <c r="I90" s="18" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J90" s="19" t="inlineStr">
-        <is>
-          <t>DG1</t>
-        </is>
-      </c>
-      <c r="K90" s="18" t="inlineStr">
+      <c r="F90" s="16" t="n">
+        <v>89</v>
+      </c>
+      <c r="G90" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H90" s="15" t="inlineStr">
+        <is>
+          <t>% of population</t>
+        </is>
+      </c>
+      <c r="I90" s="13" t="inlineStr"/>
+      <c r="J90" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K90" s="13" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L90" s="20" t="inlineStr">
-        <is>
-          <t>April 2025; source states approx. 256,000.</t>
-        </is>
-      </c>
+      <c r="L90" s="15" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="13" t="n">
@@ -10075,12 +10821,12 @@
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>DK.DGP.EXMP.N</t>
+          <t>DK.SKL.1624</t>
         </is>
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>Citizens formally exempt from Digital Post</t>
+          <t>At least basic digital skills, age 16-24</t>
         </is>
       </c>
       <c r="D91" s="13" t="inlineStr">
@@ -10089,152 +10835,1068 @@
         </is>
       </c>
       <c r="E91" s="13" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F91" s="17" t="n">
-        <v>238479</v>
+        <v>2025</v>
+      </c>
+      <c r="F91" s="16" t="n">
+        <v>92.06</v>
       </c>
       <c r="G91" s="13" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H91" s="15" t="inlineStr">
         <is>
-          <t>citizens aged 15+ resident in Denmark</t>
+          <t>% of age group</t>
         </is>
       </c>
       <c r="I91" s="13" t="inlineStr"/>
       <c r="J91" s="14" t="inlineStr">
         <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K91" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L91" s="15" t="inlineStr">
+        <is>
+          <t>EU average 74.55%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="14" t="inlineStr">
+        <is>
+          <t>DK.SKL.2554</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="inlineStr">
+        <is>
+          <t>At least basic digital skills, age 25-54</t>
+        </is>
+      </c>
+      <c r="D92" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E92" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F92" s="16" t="n">
+        <v>86.89</v>
+      </c>
+      <c r="G92" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H92" s="15" t="inlineStr">
+        <is>
+          <t>% of age group</t>
+        </is>
+      </c>
+      <c r="I92" s="13" t="inlineStr"/>
+      <c r="J92" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K92" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L92" s="15" t="inlineStr">
+        <is>
+          <t>EU average 68.57%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="13" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="14" t="inlineStr">
+        <is>
+          <t>DK.SKL.5574</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="inlineStr">
+        <is>
+          <t>At least basic digital skills, age 55-74</t>
+        </is>
+      </c>
+      <c r="D93" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E93" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F93" s="16" t="n">
+        <v>67.81</v>
+      </c>
+      <c r="G93" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H93" s="15" t="inlineStr">
+        <is>
+          <t>% of age group</t>
+        </is>
+      </c>
+      <c r="I93" s="13" t="inlineStr"/>
+      <c r="J93" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K93" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L93" s="15" t="inlineStr">
+        <is>
+          <t>EU average 42.60%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="14" t="inlineStr">
+        <is>
+          <t>DK.ENT.DII</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="inlineStr">
+        <is>
+          <t>SMEs with at least basic digital intensity</t>
+        </is>
+      </c>
+      <c r="D94" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E94" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F94" s="16" t="n">
+        <v>92.45</v>
+      </c>
+      <c r="G94" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H94" s="15" t="inlineStr">
+        <is>
+          <t>% of SMEs</t>
+        </is>
+      </c>
+      <c r="I94" s="13" t="inlineStr"/>
+      <c r="J94" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K94" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L94" s="15" t="inlineStr">
+        <is>
+          <t>EU average 71.39%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="13" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="14" t="inlineStr">
+        <is>
+          <t>EU.ENT.DII</t>
+        </is>
+      </c>
+      <c r="C95" s="15" t="inlineStr">
+        <is>
+          <t>SMEs with at least basic digital intensity</t>
+        </is>
+      </c>
+      <c r="D95" s="13" t="inlineStr">
+        <is>
+          <t>EU27</t>
+        </is>
+      </c>
+      <c r="E95" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F95" s="16" t="n">
+        <v>71.39</v>
+      </c>
+      <c r="G95" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H95" s="15" t="inlineStr">
+        <is>
+          <t>% of SMEs</t>
+        </is>
+      </c>
+      <c r="I95" s="13" t="inlineStr"/>
+      <c r="J95" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K95" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L95" s="15" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="14" t="inlineStr">
+        <is>
+          <t>DK.ENT.AI</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="inlineStr">
+        <is>
+          <t>Enterprises adopting AI</t>
+        </is>
+      </c>
+      <c r="D96" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E96" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F96" s="16" t="n">
+        <v>42.03</v>
+      </c>
+      <c r="G96" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H96" s="15" t="inlineStr">
+        <is>
+          <t>% of enterprises</t>
+        </is>
+      </c>
+      <c r="I96" s="13" t="inlineStr"/>
+      <c r="J96" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K96" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L96" s="15" t="inlineStr">
+        <is>
+          <t>EU average 19.95%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="13" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>DK.ENT.AI.LRG</t>
+        </is>
+      </c>
+      <c r="C97" s="15" t="inlineStr">
+        <is>
+          <t>Large enterprises adopting AI</t>
+        </is>
+      </c>
+      <c r="D97" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E97" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F97" s="16" t="n">
+        <v>74.52</v>
+      </c>
+      <c r="G97" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H97" s="15" t="inlineStr">
+        <is>
+          <t>% of large enterprises (250+)</t>
+        </is>
+      </c>
+      <c r="I97" s="13" t="inlineStr"/>
+      <c r="J97" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K97" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L97" s="15" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="13" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="14" t="inlineStr">
+        <is>
+          <t>DK.ENT.AI.SME</t>
+        </is>
+      </c>
+      <c r="C98" s="15" t="inlineStr">
+        <is>
+          <t>SMEs adopting AI</t>
+        </is>
+      </c>
+      <c r="D98" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E98" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F98" s="16" t="n">
+        <v>40.99</v>
+      </c>
+      <c r="G98" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H98" s="15" t="inlineStr">
+        <is>
+          <t>% of SMEs (10-249)</t>
+        </is>
+      </c>
+      <c r="I98" s="13" t="inlineStr"/>
+      <c r="J98" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K98" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L98" s="15" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="13" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="14" t="inlineStr">
+        <is>
+          <t>DK.GOV.DPS.CIT</t>
+        </is>
+      </c>
+      <c r="C99" s="15" t="inlineStr">
+        <is>
+          <t>Digital public services for citizens (score)</t>
+        </is>
+      </c>
+      <c r="D99" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E99" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F99" s="16" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="G99" s="13" t="inlineStr">
+        <is>
+          <t>score 0-100</t>
+        </is>
+      </c>
+      <c r="H99" s="15" t="inlineStr">
+        <is>
+          <t>eGovernment Benchmark score</t>
+        </is>
+      </c>
+      <c r="I99" s="13" t="inlineStr"/>
+      <c r="J99" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K99" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L99" s="15" t="inlineStr">
+        <is>
+          <t>BELOW the EU average of 84.64.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="13" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="14" t="inlineStr">
+        <is>
+          <t>EU.GOV.DPS.CIT</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="inlineStr">
+        <is>
+          <t>Digital public services for citizens (score)</t>
+        </is>
+      </c>
+      <c r="D100" s="13" t="inlineStr">
+        <is>
+          <t>EU27</t>
+        </is>
+      </c>
+      <c r="E100" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F100" s="16" t="n">
+        <v>84.64</v>
+      </c>
+      <c r="G100" s="13" t="inlineStr">
+        <is>
+          <t>score 0-100</t>
+        </is>
+      </c>
+      <c r="H100" s="15" t="inlineStr">
+        <is>
+          <t>eGovernment Benchmark score</t>
+        </is>
+      </c>
+      <c r="I100" s="13" t="inlineStr"/>
+      <c r="J100" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K100" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L100" s="15" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="14" t="inlineStr">
+        <is>
+          <t>DK.GOV.DPS.XB</t>
+        </is>
+      </c>
+      <c r="C101" s="15" t="inlineStr">
+        <is>
+          <t>Cross-border digital public services, citizens (score)</t>
+        </is>
+      </c>
+      <c r="D101" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E101" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F101" s="16" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="G101" s="13" t="inlineStr">
+        <is>
+          <t>score 0-100</t>
+        </is>
+      </c>
+      <c r="H101" s="15" t="inlineStr">
+        <is>
+          <t>eGovernment Benchmark score</t>
+        </is>
+      </c>
+      <c r="I101" s="13" t="inlineStr"/>
+      <c r="J101" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K101" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L101" s="15" t="inlineStr">
+        <is>
+          <t>EU average 75.28.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="13" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="14" t="inlineStr">
+        <is>
+          <t>DK.ENV.WEEE</t>
+        </is>
+      </c>
+      <c r="C102" s="15" t="inlineStr">
+        <is>
+          <t>ICT waste recycled or prepared for reuse</t>
+        </is>
+      </c>
+      <c r="D102" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E102" s="13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F102" s="16" t="n">
+        <v>15.37</v>
+      </c>
+      <c r="G102" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H102" s="15" t="inlineStr">
+        <is>
+          <t>% of ICT-related WEEE collected</t>
+        </is>
+      </c>
+      <c r="I102" s="13" t="inlineStr"/>
+      <c r="J102" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K102" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L102" s="15" t="inlineStr">
+        <is>
+          <t>Among the lowest in the EU; EU average 80.23%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="13" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="14" t="inlineStr">
+        <is>
+          <t>EU.ENV.WEEE</t>
+        </is>
+      </c>
+      <c r="C103" s="15" t="inlineStr">
+        <is>
+          <t>ICT waste recycled or prepared for reuse</t>
+        </is>
+      </c>
+      <c r="D103" s="13" t="inlineStr">
+        <is>
+          <t>EU27</t>
+        </is>
+      </c>
+      <c r="E103" s="13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F103" s="16" t="n">
+        <v>80.23</v>
+      </c>
+      <c r="G103" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H103" s="15" t="inlineStr">
+        <is>
+          <t>% of ICT-related WEEE collected</t>
+        </is>
+      </c>
+      <c r="I103" s="13" t="inlineStr"/>
+      <c r="J103" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K103" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L103" s="15" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="18" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="19" t="inlineStr">
+        <is>
+          <t>DK.SME.SMVD.PROJ</t>
+        </is>
+      </c>
+      <c r="C104" s="20" t="inlineStr">
+        <is>
+          <t>SMV:Digital projects supported since 2018</t>
+        </is>
+      </c>
+      <c r="D104" s="18" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F104" s="21" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G104" s="18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H104" s="20" t="inlineStr">
+        <is>
+          <t>digitalisation projects</t>
+        </is>
+      </c>
+      <c r="I104" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J104" s="19" t="inlineStr">
+        <is>
+          <t>DG3</t>
+        </is>
+      </c>
+      <c r="K104" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L104" s="20" t="inlineStr">
+        <is>
+          <t>Source states 'knap 7.000' (just under 7,000).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="13" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="14" t="inlineStr">
+        <is>
+          <t>DK.SME.SMVD.INV</t>
+        </is>
+      </c>
+      <c r="C105" s="15" t="inlineStr">
+        <is>
+          <t>Participants who invested further during the project</t>
+        </is>
+      </c>
+      <c r="D105" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E105" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F105" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="G105" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H105" s="15" t="inlineStr">
+        <is>
+          <t>% of participating enterprises</t>
+        </is>
+      </c>
+      <c r="I105" s="13" t="inlineStr"/>
+      <c r="J105" s="14" t="inlineStr">
+        <is>
+          <t>DG3</t>
+        </is>
+      </c>
+      <c r="K105" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L105" s="15" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="13" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="14" t="inlineStr">
+        <is>
+          <t>DK.SME.SMVD.NOINV</t>
+        </is>
+      </c>
+      <c r="C106" s="15" t="inlineStr">
+        <is>
+          <t>Participants with no further investment plans</t>
+        </is>
+      </c>
+      <c r="D106" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E106" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F106" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G106" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H106" s="15" t="inlineStr">
+        <is>
+          <t>% of participating enterprises</t>
+        </is>
+      </c>
+      <c r="I106" s="13" t="inlineStr"/>
+      <c r="J106" s="14" t="inlineStr">
+        <is>
+          <t>DG3</t>
+        </is>
+      </c>
+      <c r="K106" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L106" s="15" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="13" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="14" t="inlineStr">
+        <is>
+          <t>DK.POP.TOT</t>
+        </is>
+      </c>
+      <c r="C107" s="15" t="inlineStr">
+        <is>
+          <t>Resident population</t>
+        </is>
+      </c>
+      <c r="D107" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E107" s="13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F107" s="17" t="n">
+        <v>6025603</v>
+      </c>
+      <c r="G107" s="13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H107" s="15" t="inlineStr">
+        <is>
+          <t>persons resident in Denmark</t>
+        </is>
+      </c>
+      <c r="I107" s="13" t="inlineStr"/>
+      <c r="J107" s="14" t="inlineStr">
+        <is>
+          <t>DST2</t>
+        </is>
+      </c>
+      <c r="K107" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L107" s="15" t="inlineStr">
+        <is>
+          <t>As at 1 January 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="18" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="19" t="inlineStr">
+        <is>
+          <t>DK.DGP.EXMP.N</t>
+        </is>
+      </c>
+      <c r="C108" s="20" t="inlineStr">
+        <is>
+          <t>Citizens formally exempt from Digital Post</t>
+        </is>
+      </c>
+      <c r="D108" s="18" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E108" s="18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F108" s="21" t="n">
+        <v>256000</v>
+      </c>
+      <c r="G108" s="18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H108" s="20" t="inlineStr">
+        <is>
+          <t>citizens aged 15+ resident in Denmark</t>
+        </is>
+      </c>
+      <c r="I108" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J108" s="19" t="inlineStr">
+        <is>
           <t>DG1</t>
         </is>
       </c>
-      <c r="K91" s="13" t="inlineStr">
+      <c r="K108" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L91" s="15" t="inlineStr">
+      <c r="L108" s="20" t="inlineStr">
+        <is>
+          <t>April 2025; source states approx. 256,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="13" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="14" t="inlineStr">
+        <is>
+          <t>DK.DGP.EXMP.N</t>
+        </is>
+      </c>
+      <c r="C109" s="15" t="inlineStr">
+        <is>
+          <t>Citizens formally exempt from Digital Post</t>
+        </is>
+      </c>
+      <c r="D109" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E109" s="13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F109" s="17" t="n">
+        <v>238479</v>
+      </c>
+      <c r="G109" s="13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H109" s="15" t="inlineStr">
+        <is>
+          <t>citizens aged 15+ resident in Denmark</t>
+        </is>
+      </c>
+      <c r="I109" s="13" t="inlineStr"/>
+      <c r="J109" s="14" t="inlineStr">
+        <is>
+          <t>DG1</t>
+        </is>
+      </c>
+      <c r="K109" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L109" s="15" t="inlineStr">
         <is>
           <t>Q1 2026. Paired with the 4.7% rate, implies a 15+ base of about 5.07m.</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="18" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="19" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="18" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="19" t="inlineStr">
         <is>
           <t>DK.GOV.DGP.SAVE.PLAN</t>
         </is>
       </c>
-      <c r="C92" s="20" t="inlineStr">
+      <c r="C110" s="20" t="inlineStr">
         <is>
           <t>Digital Post: projected annual public saving</t>
         </is>
       </c>
-      <c r="D92" s="18" t="inlineStr">
+      <c r="D110" s="18" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E92" s="18" t="n">
+      <c r="E110" s="18" t="n">
         <v>2016</v>
       </c>
-      <c r="F92" s="22" t="n">
+      <c r="F110" s="22" t="n">
         <v>1000</v>
       </c>
-      <c r="G92" s="18" t="inlineStr">
+      <c r="G110" s="18" t="inlineStr">
         <is>
           <t>million DKK per year</t>
         </is>
       </c>
-      <c r="H92" s="20" t="inlineStr">
+      <c r="H110" s="20" t="inlineStr">
         <is>
           <t>projected annual saving, whole public sector</t>
         </is>
       </c>
-      <c r="I92" s="18" t="inlineStr">
+      <c r="I110" s="18" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="J92" s="19" t="inlineStr">
+      <c r="J110" s="19" t="inlineStr">
         <is>
           <t>RR1</t>
         </is>
       </c>
-      <c r="K92" s="18" t="inlineStr">
+      <c r="K110" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L92" s="20" t="inlineStr">
+      <c r="L110" s="20" t="inlineStr">
         <is>
           <t>Ministry of Finance business case; Rigsrevisionen reports it as 'approx. 1bn'.</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="18" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="19" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="18" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="19" t="inlineStr">
         <is>
           <t>DK.GOV.DGP.SAVE.VERIF</t>
         </is>
       </c>
-      <c r="C93" s="20" t="inlineStr">
+      <c r="C111" s="20" t="inlineStr">
         <is>
           <t>Digital Post: annual saving verifiable by audit</t>
         </is>
       </c>
-      <c r="D93" s="18" t="inlineStr">
+      <c r="D111" s="18" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E93" s="18" t="n">
+      <c r="E111" s="18" t="n">
         <v>2016</v>
       </c>
-      <c r="F93" s="22" t="n">
+      <c r="F111" s="22" t="n">
         <v>450</v>
       </c>
-      <c r="G93" s="18" t="inlineStr">
+      <c r="G111" s="18" t="inlineStr">
         <is>
           <t>million DKK per year</t>
         </is>
       </c>
-      <c r="H93" s="20" t="inlineStr">
+      <c r="H111" s="20" t="inlineStr">
         <is>
           <t>verified annual saving, whole public sector</t>
         </is>
       </c>
-      <c r="I93" s="18" t="inlineStr">
+      <c r="I111" s="18" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="J93" s="19" t="inlineStr">
+      <c r="J111" s="19" t="inlineStr">
         <is>
           <t>RR1</t>
         </is>
       </c>
-      <c r="K93" s="18" t="inlineStr">
+      <c r="K111" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L93" s="20" t="inlineStr">
+      <c r="L111" s="20" t="inlineStr">
         <is>
           <t>Postage, paper and envelopes only. The wage and overhead component was never verified: the cross-government study was abandoned after KL declined to take part.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L93"/>
+  <autoFilter ref="A1:L111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10245,7 +11907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11034,35 +12696,72 @@
     <row r="23" ht="46" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
         <is>
+          <t>ES7</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Eurostat</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Internet purchases by individuals (2020 onwards) - custom extraction, all individuals, last online purchase in the 12 months, percentage of individuals who used internet within the last year, 2024</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>isoc_ec_ib20</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/databrowser/view/isoc_ec_ib20/default/table?lang=en</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>Eurostat 2026, Internet purchases by individuals (2020 onwards), dataset isoc_ec_ib20, Statistical Office of the European Union, Luxembourg, data last updated 17 April 2026, accessed 12 September 2026, &lt;https://ec.europa.eu/eurostat/databrowser/view/isoc_ec_ib20/default/table?lang=en&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="46" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
           <t>DST1</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>Danmarks Statistik</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Detailomsaetningsindeks (retail trade turnover index)</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>StatBank; base year rebased 2015 -&gt; 2021</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>https://www.dst.dk/da/Statistik/dokumentation/statistikdokumentation/detailomsaetningsindeks</t>
         </is>
       </c>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="F24" s="15" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="G23" s="15" t="inlineStr">
+      <c r="G24" s="15" t="inlineStr">
         <is>
           <t>Danmarks Statistik 2025, Detailomsaetningsindeks, Statistics Denmark, Copenhagen, accessed 12 September 2026.</t>
         </is>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -21,13 +21,15 @@
     <sheet name="F6_ADOPT_BENEFIT" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="F7_QUALITY" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="F8_SMVDIGITAL" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="09_POLICY" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="06_RETAIL_GAP" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="07_LIMITATIONS" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="08_AI_LOG" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="F9_CONSOLIDATION" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="F10_SKILLS" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="09_POLICY" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="06_RETAIL_GAP" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="07_LIMITATIONS" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="08_AI_LOG" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_MASTER'!$A$1:$L$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_MASTER'!$A$1:$L$114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,13 +37,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="_(#,##0_);\(#,##0\);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
     <numFmt numFmtId="166" formatCode="_(#,##0.0_);\(#,##0.0\);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
     <numFmt numFmtId="167" formatCode="_(#,##0.00_);\(#,##0.00\);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
     <numFmt numFmtId="168" formatCode="_(#,##0.000_);\(#,##0.000\);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
     <numFmt numFmtId="169" formatCode="_(+#,##0.00_);_(-#,##0.00_);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
+    <numFmt numFmtId="170" formatCode="_(0.0%_);\(0.0%\);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -160,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -240,6 +243,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -433,6 +438,279 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'F9_CONSOLIDATION'!H4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F3A5F"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F3A5F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F3A5F"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2E6DB4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <cat>
+            <numRef>
+              <f>'F9_CONSOLIDATION'!$G$5:$G$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'F9_CONSOLIDATION'!$H$5:$H$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="80"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Change over the stated period</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'F10_SKILLS'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2E6DB4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'F10_SKILLS'!$A$5:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'F10_SKILLS'!$B$5:$B$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'F10_SKILLS'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="A3A3A3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'F10_SKILLS'!$A$5:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'F10_SKILLS'!$C$5:$C$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="80"/>
+        <overlap val="-27"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Age band</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="100"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% of age group</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln>
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -1735,6 +2013,33 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -1929,6 +2234,33 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -2235,7 +2567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2336,7 +2668,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>113</t>
         </is>
       </c>
     </row>
@@ -2562,46 +2894,70 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>09_POLICY</t>
+          <t>F9_CONSOLIDATION</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Policy events - dated instruments with legal citations</t>
+          <t>Figure 9 - banking consolidation on three measures, and the asymmetry between them</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>06_RETAIL_GAP</t>
+          <t>F10_SKILLS</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Documented gap - retail volume index not retrieved</t>
+          <t>Figure 10 - digital skills by age band, DK vs EU-27</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>07_LIMITATIONS</t>
+          <t>09_POLICY</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Data quality statement - read before citing</t>
+          <t>Policy events - dated instruments with legal citations</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
+          <t>06_RETAIL_GAP</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Documented gap - retail volume index not retrieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>07_LIMITATIONS</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Data quality statement - read before citing</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
           <t>08_AI_LOG</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>AI use and validation log</t>
         </is>
@@ -4904,6 +5260,485 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Figure 9 - Consolidation of Danish retail banking</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Three measures of the same structural shift. Note the different start years: the periods are NOT comparable to one another.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="J3" s="32" t="inlineStr">
+        <is>
+          <t>Banking consolidation, by measure</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>period</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>first</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>last</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t>chart label (helper)</t>
+        </is>
+      </c>
+      <c r="H4" s="25" t="inlineStr">
+        <is>
+          <t>change</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="inlineStr">
+        <is>
+          <t>Employment in blue - it fell least. Periods differ by measure; read each bar against its own label.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>Financial institutions</t>
+        </is>
+      </c>
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>1991-2024</t>
+        </is>
+      </c>
+      <c r="C5" s="33">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991))</f>
+        <v/>
+      </c>
+      <c r="D5" s="33">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="E5" s="45">
+        <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991)))-1</f>
+        <v/>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Financial institutions (1991-2024)</t>
+        </is>
+      </c>
+      <c r="H5" s="46">
+        <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991)))-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>Bank branches</t>
+        </is>
+      </c>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>2004-2024</t>
+        </is>
+      </c>
+      <c r="C6" s="33">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004))</f>
+        <v/>
+      </c>
+      <c r="D6" s="33">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="E6" s="45">
+        <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004)))-1</f>
+        <v/>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Bank branches (2004-2024)</t>
+        </is>
+      </c>
+      <c r="H6" s="46">
+        <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004)))-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>Bank employees</t>
+        </is>
+      </c>
+      <c r="B7" s="39" t="inlineStr">
+        <is>
+          <t>1991-2024</t>
+        </is>
+      </c>
+      <c r="C7" s="33">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991))</f>
+        <v/>
+      </c>
+      <c r="D7" s="33">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="E7" s="45">
+        <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991)))-1</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Bank employees (1991-2024)</t>
+        </is>
+      </c>
+      <c r="H7" s="46">
+        <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991)))-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>THE ASYMMETRY - staff per institution</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>statistic</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>reading</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>Employees per institution</t>
+        </is>
+      </c>
+      <c r="B11" s="33">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991))</f>
+        <v/>
+      </c>
+      <c r="C11" s="33">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>Denmark did not shed banking labour in proportion to its institutions. It concentrated it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>Change in staff per institution</t>
+        </is>
+      </c>
+      <c r="B12" s="45">
+        <f>((IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024)))/(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991))))-1</f>
+        <v/>
+      </c>
+      <c r="C12" s="43" t="inlineStr"/>
+      <c r="D12" s="29" t="inlineStr">
+        <is>
+          <t>The measure that rose. Every other line on this sheet falls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>Employees per branch, 2024</t>
+        </is>
+      </c>
+      <c r="B13" s="35">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C13" s="43" t="inlineStr"/>
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>Branch counts begin in 2004, so no 1991 comparison is available for this ratio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>Sources: Finans Danmark (FD1) for institutions, branches and employment. CAUTION ON THE PERIODS: institutions and employment run 1991-2024; branches only 2004-2024. The three percentage changes above are therefore NOT measured over a common window and must not be subtracted from one another. What is comparable is institutions against employment, both 1991-2024: institutions fell by roughly three quarters while employment fell by under a third. Reading: consolidation removed institutions and branches far faster than it removed jobs, so the surviving institutions are much larger. This is a concentration and scale effect, not a labour-shedding one, and it is the economic consequence of digital payment adoption that the branch count alone does not show. Employment figures are rounded by the source - it states 'around 51,000' and 'just under 36,000' - and carry flag e.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Figure 10 - At least basic digital skills, by age band, 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Denmark against the EU-27 average. Same publication, same definition, same year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="F3" s="32" t="inlineStr">
+        <is>
+          <t>At least basic digital skills by age, DK vs EU-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>age band</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>DK lead</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
+        <is>
+          <t>Denmark in blue; the EU-27 average in grey. Note that the Danish 55-74 bar still clears the EU average for its own band.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="39" t="inlineStr">
+        <is>
+          <t>16-24</t>
+        </is>
+      </c>
+      <c r="B5" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C5" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.SKL.1624",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.SKL.1624",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="D5" s="41">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"EU.SKL.1624",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.SKL.1624",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="39" t="inlineStr">
+        <is>
+          <t>25-54</t>
+        </is>
+      </c>
+      <c r="B6" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.2554",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.2554",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C6" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.SKL.2554",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.SKL.2554",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="D6" s="41">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.2554",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.2554",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"EU.SKL.2554",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.SKL.2554",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="39" t="inlineStr">
+        <is>
+          <t>55-74</t>
+        </is>
+      </c>
+      <c r="B7" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C7" s="38">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.SKL.5574",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="D7" s="41">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"EU.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.SKL.5574",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>WHY THIS MATTERS FOR THE EXCLUSION ARGUMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>statistic</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>reading</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>Danish gradient, 16-24 less 55-74</t>
+        </is>
+      </c>
+      <c r="B11" s="41">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>The internal spread across Danish age bands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>EU gradient, 16-24 less 55-74</t>
+        </is>
+      </c>
+      <c r="B12" s="41">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.SKL.1624",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.SKL.1624",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"EU.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.SKL.5574",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C12" s="29" t="inlineStr">
+        <is>
+          <t>The same spread for the EU as a whole. Denmark's is the narrower of the two, so its age gradient is comparatively mild.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>Danish 55-74 less the EU average for 55-74</t>
+        </is>
+      </c>
+      <c r="B13" s="41">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"EU.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.SKL.5574",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>Denmark's weakest band against the EU's same band - NOT against the EU all-ages average. Positive and large.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>Source: European Commission, Digital Decade 2026 country report for Denmark (EC1). The three EU-27 values were previously held only in the note field of the Danish rows; they are now observations in 02_MASTER under EU.SKL.*, because a figure in a note cannot be looked up, charted or traced. READING: Denmark leads the EU average in every age band, and its weakest band (55-74) clears the EU average for that same band by a wide margin. The Danish population excluded from digital public services is therefore not explained by low skills relative to Europe - the mandate is calibrated above the bottom of its own distribution. Compare the exclusion measures on F4: 4.7% are formally exempt while 16.5% report difficulty. That gap is administrative, not a capability deficit. Do not compare the 55-74 figure against an EU all-ages average; the comparison is band against the same band.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5356,7 +6191,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5389,7 +6224,7 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="B4" s="45" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>NOT RETRIEVED</t>
         </is>
@@ -5401,7 +6236,7 @@
           <t>Indicator</t>
         </is>
       </c>
-      <c r="B5" s="45" t="inlineStr">
+      <c r="B5" s="47" t="inlineStr">
         <is>
           <t>Retail trade turnover, volume index (mangdeindeks)</t>
         </is>
@@ -5413,7 +6248,7 @@
           <t>Authority</t>
         </is>
       </c>
-      <c r="B6" s="45" t="inlineStr">
+      <c r="B6" s="47" t="inlineStr">
         <is>
           <t>Danmarks Statistik; also available via Eurostat sts_trtu_a</t>
         </is>
@@ -5425,7 +6260,7 @@
           <t>Filters required</t>
         </is>
       </c>
-      <c r="B7" s="45" t="inlineStr">
+      <c r="B7" s="47" t="inlineStr">
         <is>
           <t>geo=DK; nace_r2=G47; indic_bt=VOL; s_adj=SCA; unit=I21 (2021=100)</t>
         </is>
@@ -5437,7 +6272,7 @@
           <t>Why not retrieved</t>
         </is>
       </c>
-      <c r="B8" s="45" t="inlineStr">
+      <c r="B8" s="47" t="inlineStr">
         <is>
           <t>Values are published through StatBank and the Eurostat databrowser. This session's network policy blocked direct access to both, and the figure could not be verified by search. A value that cannot be traced is not entered.</t>
         </is>
@@ -5449,7 +6284,7 @@
           <t>Base year caution</t>
         </is>
       </c>
-      <c r="B9" s="45" t="inlineStr">
+      <c r="B9" s="47" t="inlineStr">
         <is>
           <t>Danmarks Statistik rebased the index from 2015=100 to 2021=100. Series retrieved on different bases must not be joined.</t>
         </is>
@@ -5461,7 +6296,7 @@
           <t>Effect on the analysis</t>
         </is>
       </c>
-      <c r="B10" s="45" t="inlineStr">
+      <c r="B10" s="47" t="inlineStr">
         <is>
           <t>The e-commerce section rests on the enterprise e-sales evidence in F3_ESALES instead, which is better sourced. No conclusion in the report depends on this series.</t>
         </is>
@@ -5473,7 +6308,7 @@
           <t>To fill</t>
         </is>
       </c>
-      <c r="B11" s="45" t="inlineStr">
+      <c r="B11" s="47" t="inlineStr">
         <is>
           <t>Retrieve from statistikbanken.dk, add rows to dataset.py under series_code DK.RET.VOL with unit 'index 2021=100', and re-run build_workbook.py.</t>
         </is>
@@ -5484,7 +6319,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5555,7 +6390,7 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>Branch counts begin in 2004; institution counts and employment begin in 1991. A 2004-2024 branch change and a 1991-2024 employment change are not comparable, and placing the two percentages side by side in prose would misrepresent both. 05_CALC labels every window explicitly. Either state both windows or do not draw the comparison.</t>
+          <t>This constrains F9_CONSOLIDATION directly: the three percentage changes on that sheet are not measured over a common window, so they must not be differenced against one another. Institutions and employment are comparable to each other, both 1991-2024. Branch counts begin in 2004; institution counts and employment begin in 1991. A 2004-2024 branch change and a 1991-2024 employment change are not comparable, and placing the two percentages side by side in prose would misrepresent both. 05_CALC labels every window explicitly. Either state both windows or do not draw the comparison.</t>
         </is>
       </c>
     </row>
@@ -5724,289 +6559,6 @@
       <c r="B21" s="20" t="inlineStr">
         <is>
           <t>An earlier candidate dataset was rejected in full after verification found fabricated values carrying authentic dataset codes and extraction dates - including a Eurostat cross-section that inverted the true EU country ranking. None of it survives in this workbook.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>AI use and validation log</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Raw material for the AI Use and Validation Appendix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>AI assistance used</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>how it was validated</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>outcome</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>Source identification</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>AI used to identify candidate statistical sources and dataset codes.</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>Each source opened or search-verified against the issuing authority.</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>Source register in 03_SOURCES.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Value retrieval</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>AI used to search for published values by authority and indicator.</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>Each value checked against a result reporting the issuing authority's own publication.</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>Every retained observation carries a source_id.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Rejection of a prior dataset</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>A candidate dataset produced with AI assistance was reviewed.</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Cross-checked against Eurostat's published country ranking; the values inverted the true ranking and contained duplicated and interpolated cells.</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Dataset rejected in full and excluded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>Withdrawal of an AI-suggested claim</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>An AI-assisted draft asserted that the SMV:Digital grant scheme was being defunded, and an argument was built on the contrast between a programme with measured positive effects and a programme being cut.</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Searched for the scheme's funding status. The scheme's own 2026 grant-pool page documents pools still open and a further pool opening 26 October 2026. No source supported the defunding claim.</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>Claim withdrawn from the dataset and the argument; the withdrawal is recorded in 09_POLICY and 07_LIMITATIONS rather than erased.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>Statistical self-audit</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>AI was asked to audit its own workbook as a macroeconomic policy reviewer would.</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>The audit found that Figure 6's adoption column had been assembled from a press release naming only the top three, bottom three and three large movers - a sample drawn from the tails, which inflates R-squared by construction.</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>R-squared removed from the chart face; a selection warning added to F6; the limitation recorded in 07_LIMITATIONS. Later resolved - see the two rows below.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Failed verification attempt</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>AI was asked to retrieve Eurostat isoc_ec_ib20 for 2024 for the twelve member states missing from Figure 6, so the tail selection could be removed.</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Eurostat and the national statistical offices are unreachable from the build environment. Web search returned only the press release naming the same tails, two country values with no attributable source, and one answer mixing the '% of internet users' and '% of individuals' denominators in a single paragraph.</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>No values accepted. Recorded because the honest outcome of a verification attempt is sometimes that it failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Author-supplied authoritative extract</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>The author retrieved the complete isoc_ec_ib20 table from the Eurostat databrowser and supplied it as a spreadsheet; AI parsed it into the dataset.</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>The extract carries its own provenance header - dataset code, extraction timestamp, last-update date, and an explicit unit of 'percentage of individuals who used internet within the last year'. The ten values it overlapped with were compared against the rounded press-release figures already held; all ten agreed to rounding.</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>All 27 member states plus the EU-27 aggregate added under source ES7. Figure 6 went from n=6 to n=18 and R-squared was restored to the chart face. The superseded rounded values are recorded in each row's note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Workbook construction</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>AI wrote the Python build script that generates this workbook.</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Structural assertions run at build time: source_ids resolve, units and denominators present, no duplicate observations, break flags set.</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>build_workbook.py, re-runnable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Analytical framing</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>AI used to interpret patterns and suggest framings.</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Author reviewed each interpretation against the underlying values.</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>Interpretations appear in the report, attributed to the author.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Not delegated to AI</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>Selection of the research question, country, industries, SDG and policy comparator; the argument; the conclusions.</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>Author's own work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="34" t="inlineStr">
-        <is>
-          <t>This log records assistance during data assembly. Complete it with any further AI use during drafting before submission. The assessment requires that AI-assisted content be verified and acknowledged.</t>
         </is>
       </c>
     </row>
@@ -6230,13 +6782,296 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>AI use and validation log</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Raw material for the AI Use and Validation Appendix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>AI assistance used</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>how it was validated</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Source identification</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>AI used to identify candidate statistical sources and dataset codes.</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Each source opened or search-verified against the issuing authority.</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Source register in 03_SOURCES.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Value retrieval</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>AI used to search for published values by authority and indicator.</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Each value checked against a result reporting the issuing authority's own publication.</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Every retained observation carries a source_id.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Rejection of a prior dataset</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>A candidate dataset produced with AI assistance was reviewed.</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Cross-checked against Eurostat's published country ranking; the values inverted the true ranking and contained duplicated and interpolated cells.</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Dataset rejected in full and excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Withdrawal of an AI-suggested claim</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>An AI-assisted draft asserted that the SMV:Digital grant scheme was being defunded, and an argument was built on the contrast between a programme with measured positive effects and a programme being cut.</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Searched for the scheme's funding status. The scheme's own 2026 grant-pool page documents pools still open and a further pool opening 26 October 2026. No source supported the defunding claim.</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Claim withdrawn from the dataset and the argument; the withdrawal is recorded in 09_POLICY and 07_LIMITATIONS rather than erased.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Statistical self-audit</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>AI was asked to audit its own workbook as a macroeconomic policy reviewer would.</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>The audit found that Figure 6's adoption column had been assembled from a press release naming only the top three, bottom three and three large movers - a sample drawn from the tails, which inflates R-squared by construction.</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>R-squared removed from the chart face; a selection warning added to F6; the limitation recorded in 07_LIMITATIONS. Later resolved - see the two rows below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Failed verification attempt</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>AI was asked to retrieve Eurostat isoc_ec_ib20 for 2024 for the twelve member states missing from Figure 6, so the tail selection could be removed.</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Eurostat and the national statistical offices are unreachable from the build environment. Web search returned only the press release naming the same tails, two country values with no attributable source, and one answer mixing the '% of internet users' and '% of individuals' denominators in a single paragraph.</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>No values accepted. Recorded because the honest outcome of a verification attempt is sometimes that it failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Author-supplied authoritative extract</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>The author retrieved the complete isoc_ec_ib20 table from the Eurostat databrowser and supplied it as a spreadsheet; AI parsed it into the dataset.</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>The extract carries its own provenance header - dataset code, extraction timestamp, last-update date, and an explicit unit of 'percentage of individuals who used internet within the last year'. The ten values it overlapped with were compared against the rounded press-release figures already held; all ten agreed to rounding.</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>All 27 member states plus the EU-27 aggregate added under source ES7. Figure 6 went from n=6 to n=18 and R-squared was restored to the chart face. The superseded rounded values are recorded in each row's note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Workbook construction</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>AI wrote the Python build script that generates this workbook.</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Structural assertions run at build time: source_ids resolve, units and denominators present, no duplicate observations, break flags set.</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>build_workbook.py, re-runnable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Analytical framing</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>AI used to interpret patterns and suggest framings.</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Author reviewed each interpretation against the underlying values.</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Interpretations appear in the report, attributed to the author.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Not delegated to AI</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Selection of the research question, country, industries, SDG and policy comparator; the argument; the conclusions.</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Author's own work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>This log records assistance during data assembly. Complete it with any further AI use during drafting before submission. The assessment requires that AI-assisted content be verified and acknowledged.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:L114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10863,7 +11698,7 @@
       </c>
       <c r="L91" s="15" t="inlineStr">
         <is>
-          <t>EU average 74.55%.</t>
+          <t>EU average carried as EU.SKL.1624.</t>
         </is>
       </c>
     </row>
@@ -10915,7 +11750,7 @@
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>EU average 68.57%.</t>
+          <t>EU average carried as EU.SKL.2554.</t>
         </is>
       </c>
     </row>
@@ -10967,7 +11802,7 @@
       </c>
       <c r="L93" s="15" t="inlineStr">
         <is>
-          <t>EU average 42.60%.</t>
+          <t>EU average carried as EU.SKL.5574.</t>
         </is>
       </c>
     </row>
@@ -10977,24 +11812,24 @@
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>DK.ENT.DII</t>
+          <t>EU.SKL.1624</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>SMEs with at least basic digital intensity</t>
+          <t>At least basic digital skills, age 16-24</t>
         </is>
       </c>
       <c r="D94" s="13" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>EU27</t>
         </is>
       </c>
       <c r="E94" s="13" t="n">
         <v>2025</v>
       </c>
       <c r="F94" s="16" t="n">
-        <v>92.45</v>
+        <v>74.55</v>
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
@@ -11003,7 +11838,7 @@
       </c>
       <c r="H94" s="15" t="inlineStr">
         <is>
-          <t>% of SMEs</t>
+          <t>% of age group</t>
         </is>
       </c>
       <c r="I94" s="13" t="inlineStr"/>
@@ -11019,7 +11854,7 @@
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>EU average 71.39%.</t>
+          <t>Comparator for DK.SKL.1624.</t>
         </is>
       </c>
     </row>
@@ -11029,12 +11864,12 @@
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>EU.ENT.DII</t>
+          <t>EU.SKL.2554</t>
         </is>
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>SMEs with at least basic digital intensity</t>
+          <t>At least basic digital skills, age 25-54</t>
         </is>
       </c>
       <c r="D95" s="13" t="inlineStr">
@@ -11046,7 +11881,7 @@
         <v>2025</v>
       </c>
       <c r="F95" s="16" t="n">
-        <v>71.39</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="G95" s="13" t="inlineStr">
         <is>
@@ -11055,7 +11890,7 @@
       </c>
       <c r="H95" s="15" t="inlineStr">
         <is>
-          <t>% of SMEs</t>
+          <t>% of age group</t>
         </is>
       </c>
       <c r="I95" s="13" t="inlineStr"/>
@@ -11069,7 +11904,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L95" s="15" t="inlineStr"/>
+      <c r="L95" s="15" t="inlineStr">
+        <is>
+          <t>Comparator for DK.SKL.2554.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="13" t="n">
@@ -11077,24 +11916,24 @@
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>DK.ENT.AI</t>
+          <t>EU.SKL.5574</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>Enterprises adopting AI</t>
+          <t>At least basic digital skills, age 55-74</t>
         </is>
       </c>
       <c r="D96" s="13" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>EU27</t>
         </is>
       </c>
       <c r="E96" s="13" t="n">
         <v>2025</v>
       </c>
       <c r="F96" s="16" t="n">
-        <v>42.03</v>
+        <v>42.6</v>
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
@@ -11103,7 +11942,7 @@
       </c>
       <c r="H96" s="15" t="inlineStr">
         <is>
-          <t>% of enterprises</t>
+          <t>% of age group</t>
         </is>
       </c>
       <c r="I96" s="13" t="inlineStr"/>
@@ -11119,7 +11958,7 @@
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>EU average 19.95%.</t>
+          <t>Comparator for DK.SKL.5574.</t>
         </is>
       </c>
     </row>
@@ -11129,12 +11968,12 @@
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>DK.ENT.AI.LRG</t>
+          <t>DK.ENT.DII</t>
         </is>
       </c>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>Large enterprises adopting AI</t>
+          <t>SMEs with at least basic digital intensity</t>
         </is>
       </c>
       <c r="D97" s="13" t="inlineStr">
@@ -11146,7 +11985,7 @@
         <v>2025</v>
       </c>
       <c r="F97" s="16" t="n">
-        <v>74.52</v>
+        <v>92.45</v>
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
@@ -11155,7 +11994,7 @@
       </c>
       <c r="H97" s="15" t="inlineStr">
         <is>
-          <t>% of large enterprises (250+)</t>
+          <t>% of SMEs</t>
         </is>
       </c>
       <c r="I97" s="13" t="inlineStr"/>
@@ -11169,7 +12008,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L97" s="15" t="inlineStr"/>
+      <c r="L97" s="15" t="inlineStr">
+        <is>
+          <t>EU average 71.39%.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="13" t="n">
@@ -11177,24 +12020,24 @@
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>DK.ENT.AI.SME</t>
+          <t>EU.ENT.DII</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>SMEs adopting AI</t>
+          <t>SMEs with at least basic digital intensity</t>
         </is>
       </c>
       <c r="D98" s="13" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>EU27</t>
         </is>
       </c>
       <c r="E98" s="13" t="n">
         <v>2025</v>
       </c>
       <c r="F98" s="16" t="n">
-        <v>40.99</v>
+        <v>71.39</v>
       </c>
       <c r="G98" s="13" t="inlineStr">
         <is>
@@ -11203,7 +12046,7 @@
       </c>
       <c r="H98" s="15" t="inlineStr">
         <is>
-          <t>% of SMEs (10-249)</t>
+          <t>% of SMEs</t>
         </is>
       </c>
       <c r="I98" s="13" t="inlineStr"/>
@@ -11225,12 +12068,12 @@
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>DK.GOV.DPS.CIT</t>
+          <t>DK.ENT.AI</t>
         </is>
       </c>
       <c r="C99" s="15" t="inlineStr">
         <is>
-          <t>Digital public services for citizens (score)</t>
+          <t>Enterprises adopting AI</t>
         </is>
       </c>
       <c r="D99" s="13" t="inlineStr">
@@ -11242,16 +12085,16 @@
         <v>2025</v>
       </c>
       <c r="F99" s="16" t="n">
-        <v>82.2</v>
+        <v>42.03</v>
       </c>
       <c r="G99" s="13" t="inlineStr">
         <is>
-          <t>score 0-100</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H99" s="15" t="inlineStr">
         <is>
-          <t>eGovernment Benchmark score</t>
+          <t>% of enterprises</t>
         </is>
       </c>
       <c r="I99" s="13" t="inlineStr"/>
@@ -11267,7 +12110,7 @@
       </c>
       <c r="L99" s="15" t="inlineStr">
         <is>
-          <t>BELOW the EU average of 84.64.</t>
+          <t>EU average 19.95%.</t>
         </is>
       </c>
     </row>
@@ -11277,33 +12120,33 @@
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>EU.GOV.DPS.CIT</t>
+          <t>DK.ENT.AI.LRG</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Digital public services for citizens (score)</t>
+          <t>Large enterprises adopting AI</t>
         </is>
       </c>
       <c r="D100" s="13" t="inlineStr">
         <is>
-          <t>EU27</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="E100" s="13" t="n">
         <v>2025</v>
       </c>
       <c r="F100" s="16" t="n">
-        <v>84.64</v>
+        <v>74.52</v>
       </c>
       <c r="G100" s="13" t="inlineStr">
         <is>
-          <t>score 0-100</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H100" s="15" t="inlineStr">
         <is>
-          <t>eGovernment Benchmark score</t>
+          <t>% of large enterprises (250+)</t>
         </is>
       </c>
       <c r="I100" s="13" t="inlineStr"/>
@@ -11325,12 +12168,12 @@
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>DK.GOV.DPS.XB</t>
+          <t>DK.ENT.AI.SME</t>
         </is>
       </c>
       <c r="C101" s="15" t="inlineStr">
         <is>
-          <t>Cross-border digital public services, citizens (score)</t>
+          <t>SMEs adopting AI</t>
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr">
@@ -11342,16 +12185,16 @@
         <v>2025</v>
       </c>
       <c r="F101" s="16" t="n">
-        <v>64.40000000000001</v>
+        <v>40.99</v>
       </c>
       <c r="G101" s="13" t="inlineStr">
         <is>
-          <t>score 0-100</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H101" s="15" t="inlineStr">
         <is>
-          <t>eGovernment Benchmark score</t>
+          <t>% of SMEs (10-249)</t>
         </is>
       </c>
       <c r="I101" s="13" t="inlineStr"/>
@@ -11365,11 +12208,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L101" s="15" t="inlineStr">
-        <is>
-          <t>EU average 75.28.</t>
-        </is>
-      </c>
+      <c r="L101" s="15" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="13" t="n">
@@ -11377,12 +12216,12 @@
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>DK.ENV.WEEE</t>
+          <t>DK.GOV.DPS.CIT</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>ICT waste recycled or prepared for reuse</t>
+          <t>Digital public services for citizens (score)</t>
         </is>
       </c>
       <c r="D102" s="13" t="inlineStr">
@@ -11391,19 +12230,19 @@
         </is>
       </c>
       <c r="E102" s="13" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="F102" s="16" t="n">
-        <v>15.37</v>
+        <v>82.2</v>
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>score 0-100</t>
         </is>
       </c>
       <c r="H102" s="15" t="inlineStr">
         <is>
-          <t>% of ICT-related WEEE collected</t>
+          <t>eGovernment Benchmark score</t>
         </is>
       </c>
       <c r="I102" s="13" t="inlineStr"/>
@@ -11419,7 +12258,7 @@
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>Among the lowest in the EU; EU average 80.23%.</t>
+          <t>BELOW the EU average of 84.64.</t>
         </is>
       </c>
     </row>
@@ -11429,12 +12268,12 @@
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>EU.ENV.WEEE</t>
+          <t>EU.GOV.DPS.CIT</t>
         </is>
       </c>
       <c r="C103" s="15" t="inlineStr">
         <is>
-          <t>ICT waste recycled or prepared for reuse</t>
+          <t>Digital public services for citizens (score)</t>
         </is>
       </c>
       <c r="D103" s="13" t="inlineStr">
@@ -11443,19 +12282,19 @@
         </is>
       </c>
       <c r="E103" s="13" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="F103" s="16" t="n">
-        <v>80.23</v>
+        <v>84.64</v>
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>score 0-100</t>
         </is>
       </c>
       <c r="H103" s="15" t="inlineStr">
         <is>
-          <t>% of ICT-related WEEE collected</t>
+          <t>eGovernment Benchmark score</t>
         </is>
       </c>
       <c r="I103" s="13" t="inlineStr"/>
@@ -11472,58 +12311,54 @@
       <c r="L103" s="15" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="18" t="n">
+      <c r="A104" s="13" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="19" t="inlineStr">
-        <is>
-          <t>DK.SME.SMVD.PROJ</t>
-        </is>
-      </c>
-      <c r="C104" s="20" t="inlineStr">
-        <is>
-          <t>SMV:Digital projects supported since 2018</t>
-        </is>
-      </c>
-      <c r="D104" s="18" t="inlineStr">
+      <c r="B104" s="14" t="inlineStr">
+        <is>
+          <t>DK.GOV.DPS.XB</t>
+        </is>
+      </c>
+      <c r="C104" s="15" t="inlineStr">
+        <is>
+          <t>Cross-border digital public services, citizens (score)</t>
+        </is>
+      </c>
+      <c r="D104" s="13" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E104" s="18" t="n">
+      <c r="E104" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="F104" s="21" t="n">
-        <v>7000</v>
-      </c>
-      <c r="G104" s="18" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H104" s="20" t="inlineStr">
-        <is>
-          <t>digitalisation projects</t>
-        </is>
-      </c>
-      <c r="I104" s="18" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J104" s="19" t="inlineStr">
-        <is>
-          <t>DG3</t>
-        </is>
-      </c>
-      <c r="K104" s="18" t="inlineStr">
+      <c r="F104" s="16" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="G104" s="13" t="inlineStr">
+        <is>
+          <t>score 0-100</t>
+        </is>
+      </c>
+      <c r="H104" s="15" t="inlineStr">
+        <is>
+          <t>eGovernment Benchmark score</t>
+        </is>
+      </c>
+      <c r="I104" s="13" t="inlineStr"/>
+      <c r="J104" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K104" s="13" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L104" s="20" t="inlineStr">
-        <is>
-          <t>Source states 'knap 7.000' (just under 7,000).</t>
+      <c r="L104" s="15" t="inlineStr">
+        <is>
+          <t>EU average 75.28.</t>
         </is>
       </c>
     </row>
@@ -11533,12 +12368,12 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>DK.SME.SMVD.INV</t>
+          <t>DK.ENV.WEEE</t>
         </is>
       </c>
       <c r="C105" s="15" t="inlineStr">
         <is>
-          <t>Participants who invested further during the project</t>
+          <t>ICT waste recycled or prepared for reuse</t>
         </is>
       </c>
       <c r="D105" s="13" t="inlineStr">
@@ -11547,10 +12382,10 @@
         </is>
       </c>
       <c r="E105" s="13" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="F105" s="16" t="n">
-        <v>65</v>
+        <v>15.37</v>
       </c>
       <c r="G105" s="13" t="inlineStr">
         <is>
@@ -11559,13 +12394,13 @@
       </c>
       <c r="H105" s="15" t="inlineStr">
         <is>
-          <t>% of participating enterprises</t>
+          <t>% of ICT-related WEEE collected</t>
         </is>
       </c>
       <c r="I105" s="13" t="inlineStr"/>
       <c r="J105" s="14" t="inlineStr">
         <is>
-          <t>DG3</t>
+          <t>EC1</t>
         </is>
       </c>
       <c r="K105" s="13" t="inlineStr">
@@ -11573,7 +12408,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L105" s="15" t="inlineStr"/>
+      <c r="L105" s="15" t="inlineStr">
+        <is>
+          <t>Among the lowest in the EU; EU average 80.23%.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="13" t="n">
@@ -11581,24 +12420,24 @@
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>DK.SME.SMVD.NOINV</t>
+          <t>EU.ENV.WEEE</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Participants with no further investment plans</t>
+          <t>ICT waste recycled or prepared for reuse</t>
         </is>
       </c>
       <c r="D106" s="13" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>EU27</t>
         </is>
       </c>
       <c r="E106" s="13" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="F106" s="16" t="n">
-        <v>2</v>
+        <v>80.23</v>
       </c>
       <c r="G106" s="13" t="inlineStr">
         <is>
@@ -11607,129 +12446,125 @@
       </c>
       <c r="H106" s="15" t="inlineStr">
         <is>
-          <t>% of participating enterprises</t>
+          <t>% of ICT-related WEEE collected</t>
         </is>
       </c>
       <c r="I106" s="13" t="inlineStr"/>
       <c r="J106" s="14" t="inlineStr">
         <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K106" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L106" s="15" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="18" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="19" t="inlineStr">
+        <is>
+          <t>DK.SME.SMVD.PROJ</t>
+        </is>
+      </c>
+      <c r="C107" s="20" t="inlineStr">
+        <is>
+          <t>SMV:Digital projects supported since 2018</t>
+        </is>
+      </c>
+      <c r="D107" s="18" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E107" s="18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F107" s="21" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G107" s="18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H107" s="20" t="inlineStr">
+        <is>
+          <t>digitalisation projects</t>
+        </is>
+      </c>
+      <c r="I107" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J107" s="19" t="inlineStr">
+        <is>
           <t>DG3</t>
         </is>
       </c>
-      <c r="K106" s="13" t="inlineStr">
+      <c r="K107" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L106" s="15" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="13" t="n">
-        <v>106</v>
-      </c>
-      <c r="B107" s="14" t="inlineStr">
-        <is>
-          <t>DK.POP.TOT</t>
-        </is>
-      </c>
-      <c r="C107" s="15" t="inlineStr">
-        <is>
-          <t>Resident population</t>
-        </is>
-      </c>
-      <c r="D107" s="13" t="inlineStr">
+      <c r="L107" s="20" t="inlineStr">
+        <is>
+          <t>Source states 'knap 7.000' (just under 7,000).</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="13" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="14" t="inlineStr">
+        <is>
+          <t>DK.SME.SMVD.INV</t>
+        </is>
+      </c>
+      <c r="C108" s="15" t="inlineStr">
+        <is>
+          <t>Participants who invested further during the project</t>
+        </is>
+      </c>
+      <c r="D108" s="13" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E107" s="13" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F107" s="17" t="n">
-        <v>6025603</v>
-      </c>
-      <c r="G107" s="13" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H107" s="15" t="inlineStr">
-        <is>
-          <t>persons resident in Denmark</t>
-        </is>
-      </c>
-      <c r="I107" s="13" t="inlineStr"/>
-      <c r="J107" s="14" t="inlineStr">
-        <is>
-          <t>DST2</t>
-        </is>
-      </c>
-      <c r="K107" s="13" t="inlineStr">
+      <c r="E108" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F108" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="G108" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H108" s="15" t="inlineStr">
+        <is>
+          <t>% of participating enterprises</t>
+        </is>
+      </c>
+      <c r="I108" s="13" t="inlineStr"/>
+      <c r="J108" s="14" t="inlineStr">
+        <is>
+          <t>DG3</t>
+        </is>
+      </c>
+      <c r="K108" s="13" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L107" s="15" t="inlineStr">
-        <is>
-          <t>As at 1 January 2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="18" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" s="19" t="inlineStr">
-        <is>
-          <t>DK.DGP.EXMP.N</t>
-        </is>
-      </c>
-      <c r="C108" s="20" t="inlineStr">
-        <is>
-          <t>Citizens formally exempt from Digital Post</t>
-        </is>
-      </c>
-      <c r="D108" s="18" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E108" s="18" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F108" s="21" t="n">
-        <v>256000</v>
-      </c>
-      <c r="G108" s="18" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H108" s="20" t="inlineStr">
-        <is>
-          <t>citizens aged 15+ resident in Denmark</t>
-        </is>
-      </c>
-      <c r="I108" s="18" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J108" s="19" t="inlineStr">
-        <is>
-          <t>DG1</t>
-        </is>
-      </c>
-      <c r="K108" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L108" s="20" t="inlineStr">
-        <is>
-          <t>April 2025; source states approx. 256,000.</t>
-        </is>
-      </c>
+      <c r="L108" s="15" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="13" t="n">
@@ -11737,12 +12572,12 @@
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t>DK.DGP.EXMP.N</t>
+          <t>DK.SME.SMVD.NOINV</t>
         </is>
       </c>
       <c r="C109" s="15" t="inlineStr">
         <is>
-          <t>Citizens formally exempt from Digital Post</t>
+          <t>Participants with no further investment plans</t>
         </is>
       </c>
       <c r="D109" s="13" t="inlineStr">
@@ -11751,25 +12586,25 @@
         </is>
       </c>
       <c r="E109" s="13" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F109" s="17" t="n">
-        <v>238479</v>
+        <v>2025</v>
+      </c>
+      <c r="F109" s="16" t="n">
+        <v>2</v>
       </c>
       <c r="G109" s="13" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H109" s="15" t="inlineStr">
         <is>
-          <t>citizens aged 15+ resident in Denmark</t>
+          <t>% of participating enterprises</t>
         </is>
       </c>
       <c r="I109" s="13" t="inlineStr"/>
       <c r="J109" s="14" t="inlineStr">
         <is>
-          <t>DG1</t>
+          <t>DG3</t>
         </is>
       </c>
       <c r="K109" s="13" t="inlineStr">
@@ -11777,65 +12612,57 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L109" s="15" t="inlineStr">
-        <is>
-          <t>Q1 2026. Paired with the 4.7% rate, implies a 15+ base of about 5.07m.</t>
-        </is>
-      </c>
+      <c r="L109" s="15" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="18" t="n">
+      <c r="A110" s="13" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="19" t="inlineStr">
-        <is>
-          <t>DK.GOV.DGP.SAVE.PLAN</t>
-        </is>
-      </c>
-      <c r="C110" s="20" t="inlineStr">
-        <is>
-          <t>Digital Post: projected annual public saving</t>
-        </is>
-      </c>
-      <c r="D110" s="18" t="inlineStr">
+      <c r="B110" s="14" t="inlineStr">
+        <is>
+          <t>DK.POP.TOT</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="inlineStr">
+        <is>
+          <t>Resident population</t>
+        </is>
+      </c>
+      <c r="D110" s="13" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E110" s="18" t="n">
-        <v>2016</v>
-      </c>
-      <c r="F110" s="22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G110" s="18" t="inlineStr">
-        <is>
-          <t>million DKK per year</t>
-        </is>
-      </c>
-      <c r="H110" s="20" t="inlineStr">
-        <is>
-          <t>projected annual saving, whole public sector</t>
-        </is>
-      </c>
-      <c r="I110" s="18" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J110" s="19" t="inlineStr">
-        <is>
-          <t>RR1</t>
-        </is>
-      </c>
-      <c r="K110" s="18" t="inlineStr">
+      <c r="E110" s="13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F110" s="17" t="n">
+        <v>6025603</v>
+      </c>
+      <c r="G110" s="13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H110" s="15" t="inlineStr">
+        <is>
+          <t>persons resident in Denmark</t>
+        </is>
+      </c>
+      <c r="I110" s="13" t="inlineStr"/>
+      <c r="J110" s="14" t="inlineStr">
+        <is>
+          <t>DST2</t>
+        </is>
+      </c>
+      <c r="K110" s="13" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L110" s="20" t="inlineStr">
-        <is>
-          <t>Ministry of Finance business case; Rigsrevisionen reports it as 'approx. 1bn'.</t>
+      <c r="L110" s="15" t="inlineStr">
+        <is>
+          <t>As at 1 January 2026.</t>
         </is>
       </c>
     </row>
@@ -11845,58 +12672,222 @@
       </c>
       <c r="B111" s="19" t="inlineStr">
         <is>
+          <t>DK.DGP.EXMP.N</t>
+        </is>
+      </c>
+      <c r="C111" s="20" t="inlineStr">
+        <is>
+          <t>Citizens formally exempt from Digital Post</t>
+        </is>
+      </c>
+      <c r="D111" s="18" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E111" s="18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F111" s="21" t="n">
+        <v>256000</v>
+      </c>
+      <c r="G111" s="18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H111" s="20" t="inlineStr">
+        <is>
+          <t>citizens aged 15+ resident in Denmark</t>
+        </is>
+      </c>
+      <c r="I111" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J111" s="19" t="inlineStr">
+        <is>
+          <t>DG1</t>
+        </is>
+      </c>
+      <c r="K111" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L111" s="20" t="inlineStr">
+        <is>
+          <t>April 2025; source states approx. 256,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="13" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="14" t="inlineStr">
+        <is>
+          <t>DK.DGP.EXMP.N</t>
+        </is>
+      </c>
+      <c r="C112" s="15" t="inlineStr">
+        <is>
+          <t>Citizens formally exempt from Digital Post</t>
+        </is>
+      </c>
+      <c r="D112" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E112" s="13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F112" s="17" t="n">
+        <v>238479</v>
+      </c>
+      <c r="G112" s="13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H112" s="15" t="inlineStr">
+        <is>
+          <t>citizens aged 15+ resident in Denmark</t>
+        </is>
+      </c>
+      <c r="I112" s="13" t="inlineStr"/>
+      <c r="J112" s="14" t="inlineStr">
+        <is>
+          <t>DG1</t>
+        </is>
+      </c>
+      <c r="K112" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L112" s="15" t="inlineStr">
+        <is>
+          <t>Q1 2026. Paired with the 4.7% rate, implies a 15+ base of about 5.07m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="18" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="19" t="inlineStr">
+        <is>
+          <t>DK.GOV.DGP.SAVE.PLAN</t>
+        </is>
+      </c>
+      <c r="C113" s="20" t="inlineStr">
+        <is>
+          <t>Digital Post: projected annual public saving</t>
+        </is>
+      </c>
+      <c r="D113" s="18" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E113" s="18" t="n">
+        <v>2016</v>
+      </c>
+      <c r="F113" s="22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G113" s="18" t="inlineStr">
+        <is>
+          <t>million DKK per year</t>
+        </is>
+      </c>
+      <c r="H113" s="20" t="inlineStr">
+        <is>
+          <t>projected annual saving, whole public sector</t>
+        </is>
+      </c>
+      <c r="I113" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J113" s="19" t="inlineStr">
+        <is>
+          <t>RR1</t>
+        </is>
+      </c>
+      <c r="K113" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L113" s="20" t="inlineStr">
+        <is>
+          <t>Ministry of Finance business case; Rigsrevisionen reports it as 'approx. 1bn'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="18" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="19" t="inlineStr">
+        <is>
           <t>DK.GOV.DGP.SAVE.VERIF</t>
         </is>
       </c>
-      <c r="C111" s="20" t="inlineStr">
+      <c r="C114" s="20" t="inlineStr">
         <is>
           <t>Digital Post: annual saving verifiable by audit</t>
         </is>
       </c>
-      <c r="D111" s="18" t="inlineStr">
+      <c r="D114" s="18" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E111" s="18" t="n">
+      <c r="E114" s="18" t="n">
         <v>2016</v>
       </c>
-      <c r="F111" s="22" t="n">
+      <c r="F114" s="22" t="n">
         <v>450</v>
       </c>
-      <c r="G111" s="18" t="inlineStr">
+      <c r="G114" s="18" t="inlineStr">
         <is>
           <t>million DKK per year</t>
         </is>
       </c>
-      <c r="H111" s="20" t="inlineStr">
+      <c r="H114" s="20" t="inlineStr">
         <is>
           <t>verified annual saving, whole public sector</t>
         </is>
       </c>
-      <c r="I111" s="18" t="inlineStr">
+      <c r="I114" s="18" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="J111" s="19" t="inlineStr">
+      <c r="J114" s="19" t="inlineStr">
         <is>
           <t>RR1</t>
         </is>
       </c>
-      <c r="K111" s="18" t="inlineStr">
+      <c r="K114" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L111" s="20" t="inlineStr">
+      <c r="L114" s="20" t="inlineStr">
         <is>
           <t>Postage, paper and envelopes only. The wage and overhead component was never verified: the cross-government study was abandoned after KL declined to take part.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L111"/>
+  <autoFilter ref="A1:L114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -23,10 +23,10 @@
     <sheet name="F8_SMVDIGITAL" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="F9_CONSOLIDATION" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="F10_SKILLS" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="09_POLICY" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="06_RETAIL_GAP" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="07_LIMITATIONS" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="08_AI_LOG" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="06_RETAIL_GAP" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="07_LIMITATIONS" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="08_AI_LOG" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="09_POLICY" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_MASTER'!$A$1:$L$114</definedName>
@@ -37,14 +37,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="_(#,##0_);\(#,##0\);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
-    <numFmt numFmtId="166" formatCode="_(#,##0.0_);\(#,##0.0\);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
-    <numFmt numFmtId="167" formatCode="_(#,##0.00_);\(#,##0.00\);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
+  <numFmts count="6">
+    <numFmt numFmtId="164" formatCode="_(#,##0_);\(#,##0\);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
+    <numFmt numFmtId="165" formatCode="_(0.0%_);\(0.0%\);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
+    <numFmt numFmtId="166" formatCode="_(#,##0.00_);\(#,##0.00\);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
+    <numFmt numFmtId="167" formatCode="_(#,##0.0_);\(#,##0.0\);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
     <numFmt numFmtId="168" formatCode="_(#,##0.000_);\(#,##0.000\);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
     <numFmt numFmtId="169" formatCode="_(+#,##0.00_);_(-#,##0.00_);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
-    <numFmt numFmtId="170" formatCode="_(0.0%_);\(0.0%\);_(&quot;–&quot;_);_(&quot;–&quot;_)"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -163,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -214,27 +213,28 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -243,8 +243,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2992,14 +2991,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Same phenomenon, five definitions. The spread is the finding.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="F3" s="32" t="inlineStr">
+      <c r="F3" s="33" t="inlineStr">
         <is>
           <t>Measures of digital exclusion, Denmark</t>
         </is>
@@ -3026,14 +3025,14 @@
           <t>source</t>
         </is>
       </c>
-      <c r="F4" s="25" t="inlineStr">
+      <c r="F4" s="26" t="inlineStr">
         <is>
           <t>Five definitions of the same phenomenon; they are nested, not contradictory.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Formally exempt from Digital Post (Q1 2026)</t>
         </is>
@@ -3042,19 +3041,19 @@
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026))</f>
         <v/>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>administrative status</t>
         </is>
       </c>
-      <c r="D5" s="39" t="inlineStr">
+      <c r="D5" s="38" t="inlineStr">
         <is>
           <t>DG1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Do not use digital public services at all</t>
         </is>
@@ -3063,19 +3062,19 @@
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.NOUSE",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.NOUSE",'02_MASTER'!$E:$E,2026))</f>
         <v/>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>self-reported non-use</t>
         </is>
       </c>
-      <c r="D6" s="39" t="inlineStr">
+      <c r="D6" s="38" t="inlineStr">
         <is>
           <t>EC1</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Face difficulties using digital public services</t>
         </is>
@@ -3084,19 +3083,19 @@
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.DIFF",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.DIFF",'02_MASTER'!$E:$E,2026))</f>
         <v/>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>capability estimate</t>
         </is>
       </c>
-      <c r="D7" s="39" t="inlineStr">
+      <c r="D7" s="38" t="inlineStr">
         <is>
           <t>EC1</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>'Digitally disadvantaged' - lower bound</t>
         </is>
@@ -3105,19 +3104,19 @@
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.DISADV.LO",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.DISADV.LO",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>capability estimate (range)</t>
         </is>
       </c>
-      <c r="D8" s="39" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>DG2</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>'Digitally disadvantaged' - upper bound</t>
         </is>
@@ -3126,19 +3125,19 @@
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.DISADV.HI",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.DISADV.HI",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>capability estimate (range)</t>
         </is>
       </c>
-      <c r="D9" s="39" t="inlineStr">
+      <c r="D9" s="38" t="inlineStr">
         <is>
           <t>DG2</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>'Digitally disadvantaged' - Justitia</t>
         </is>
@@ -3147,12 +3146,12 @@
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.JUST",'02_MASTER'!$E:$E,2022)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.JUST",'02_MASTER'!$E:$E,2022))</f>
         <v/>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>broadest definition</t>
         </is>
       </c>
-      <c r="D10" s="39" t="inlineStr">
+      <c r="D10" s="38" t="inlineStr">
         <is>
           <t>JU1</t>
         </is>
@@ -3178,7 +3177,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Age 75-84</t>
         </is>
@@ -3189,7 +3188,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>Age 85+</t>
         </is>
@@ -3224,80 +3223,80 @@
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>Citizens formally exempt, Q1 2026</t>
         </is>
       </c>
-      <c r="B19" s="33">
+      <c r="B19" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026))</f>
         <v/>
       </c>
-      <c r="C19" s="29" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <t>Reported directly by the Agency for Digital Government (DG1).</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Citizens formally exempt, April 2025</t>
         </is>
       </c>
-      <c r="B20" s="33">
+      <c r="B20" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C20" s="29" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
         <is>
           <t>Reported as approximately 256,000 (DG1).</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>Implied population aged 15+</t>
         </is>
       </c>
-      <c r="B21" s="33">
+      <c r="B21" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026))/(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026))/100)</f>
         <v/>
       </c>
-      <c r="C21" s="29" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
         <is>
           <t>DERIVED, not retrieved: the exempt headcount divided by the exemption rate. Used only to convert the capability shares below into orders of magnitude. A published 15+ population figure was not verifiable in this session; see 06_RETAIL_GAP.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>Implied persons who do not use digital public services at all</t>
         </is>
       </c>
-      <c r="B22" s="33">
+      <c r="B22" s="28">
         <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.NOUSE",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.NOUSE",'02_MASTER'!$E:$E,2026))/100)*(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026))/(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026))/100))</f>
         <v/>
       </c>
-      <c r="C22" s="29" t="inlineStr">
+      <c r="C22" s="30" t="inlineStr">
         <is>
           <t>ORDER OF MAGNITUDE ONLY. Applies a share measured on 'the population' to a 15+ base; the denominators are not identical.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>Implied persons facing difficulty with digital public services</t>
         </is>
       </c>
-      <c r="B23" s="33">
+      <c r="B23" s="28">
         <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.DIFF",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.DIFF",'02_MASTER'!$E:$E,2026))/100)*(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026))/(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026))/100))</f>
         <v/>
       </c>
-      <c r="C23" s="29" t="inlineStr">
+      <c r="C23" s="30" t="inlineStr">
         <is>
           <t>ORDER OF MAGNITUDE ONLY, same caveat.</t>
         </is>
@@ -3426,14 +3425,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>All 27 member states and the EU-27 aggregate, ranked. Denominator: % of internet users.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="E3" s="32" t="inlineStr">
+      <c r="E3" s="33" t="inlineStr">
         <is>
           <t>Individuals who bought online, 2024</t>
         </is>
@@ -3455,455 +3454,455 @@
           <t>series_code</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t>Denmark in blue, EU-27 aggregate in navy, member states in grey. Ranked descending.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" s="38" t="inlineStr">
         <is>
           <t>IE.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"NL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"NL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C6" s="39" t="inlineStr">
+      <c r="C6" s="38" t="inlineStr">
         <is>
           <t>NL.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="B7" s="38">
+      <c r="B7" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C7" s="39" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>DK.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="B8" s="38">
+      <c r="B8" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"SE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"SE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>SE.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Czechia</t>
         </is>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"CZ.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"CZ.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C9" s="39" t="inlineStr">
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>CZ.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Slovakia</t>
         </is>
       </c>
-      <c r="B10" s="38">
+      <c r="B10" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"SK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"SK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C10" s="39" t="inlineStr">
+      <c r="C10" s="38" t="inlineStr">
         <is>
           <t>SK.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="B11" s="38">
+      <c r="B11" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"FR.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"FR.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C11" s="39" t="inlineStr">
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t>FR.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B12" s="38">
+      <c r="B12" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C12" s="39" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>DE.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Luxembourg</t>
         </is>
       </c>
-      <c r="B13" s="38">
+      <c r="B13" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"LU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"LU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C13" s="39" t="inlineStr">
+      <c r="C13" s="38" t="inlineStr">
         <is>
           <t>LU.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="B14" s="38">
+      <c r="B14" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"FI.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"FI.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C14" s="39" t="inlineStr">
+      <c r="C14" s="38" t="inlineStr">
         <is>
           <t>FI.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="B15" s="38">
+      <c r="B15" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"BE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"BE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C15" s="39" t="inlineStr">
+      <c r="C15" s="38" t="inlineStr">
         <is>
           <t>BE.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>Hungary</t>
         </is>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"HU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"HU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C16" s="39" t="inlineStr">
+      <c r="C16" s="38" t="inlineStr">
         <is>
           <t>HU.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>Estonia</t>
         </is>
       </c>
-      <c r="B17" s="38">
+      <c r="B17" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C17" s="39" t="inlineStr">
+      <c r="C17" s="38" t="inlineStr">
         <is>
           <t>EE.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>EU-27 average</t>
         </is>
       </c>
-      <c r="B18" s="38">
+      <c r="B18" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C18" s="39" t="inlineStr">
+      <c r="C18" s="38" t="inlineStr">
         <is>
           <t>EU.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="B19" s="38">
+      <c r="B19" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"PL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"PL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C19" s="39" t="inlineStr">
+      <c r="C19" s="38" t="inlineStr">
         <is>
           <t>PL.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Greece</t>
         </is>
       </c>
-      <c r="B20" s="38">
+      <c r="B20" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C20" s="39" t="inlineStr">
+      <c r="C20" s="38" t="inlineStr">
         <is>
           <t>EL.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
       </c>
-      <c r="B21" s="38">
+      <c r="B21" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"AT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"AT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C21" s="39" t="inlineStr">
+      <c r="C21" s="38" t="inlineStr">
         <is>
           <t>AT.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>Malta</t>
         </is>
       </c>
-      <c r="B22" s="38">
+      <c r="B22" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"MT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"MT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C22" s="39" t="inlineStr">
+      <c r="C22" s="38" t="inlineStr">
         <is>
           <t>MT.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="B23" s="38">
+      <c r="B23" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"SI.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"SI.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C23" s="39" t="inlineStr">
+      <c r="C23" s="38" t="inlineStr">
         <is>
           <t>SI.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B24" s="38">
+      <c r="B24" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"LT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"LT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C24" s="39" t="inlineStr">
+      <c r="C24" s="38" t="inlineStr">
         <is>
           <t>LT.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B25" s="38">
+      <c r="B25" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"ES.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"ES.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C25" s="39" t="inlineStr">
+      <c r="C25" s="38" t="inlineStr">
         <is>
           <t>ES.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="B26" s="38">
+      <c r="B26" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"HR.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"HR.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C26" s="39" t="inlineStr">
+      <c r="C26" s="38" t="inlineStr">
         <is>
           <t>HR.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>Latvia</t>
         </is>
       </c>
-      <c r="B27" s="38">
+      <c r="B27" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"LV.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"LV.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C27" s="39" t="inlineStr">
+      <c r="C27" s="38" t="inlineStr">
         <is>
           <t>LV.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>Cyprus</t>
         </is>
       </c>
-      <c r="B28" s="38">
+      <c r="B28" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"CY.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"CY.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C28" s="39" t="inlineStr">
+      <c r="C28" s="38" t="inlineStr">
         <is>
           <t>CY.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="B29" s="38">
+      <c r="B29" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"PT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"PT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C29" s="39" t="inlineStr">
+      <c r="C29" s="38" t="inlineStr">
         <is>
           <t>PT.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>Romania</t>
         </is>
       </c>
-      <c r="B30" s="38">
+      <c r="B30" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"RO.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"RO.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C30" s="39" t="inlineStr">
+      <c r="C30" s="38" t="inlineStr">
         <is>
           <t>RO.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="B31" s="38">
+      <c r="B31" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C31" s="39" t="inlineStr">
+      <c r="C31" s="38" t="inlineStr">
         <is>
           <t>IT.ECM.IND.BUY</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>Bulgaria</t>
         </is>
       </c>
-      <c r="B32" s="38">
+      <c r="B32" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"BG.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"BG.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C32" s="39" t="inlineStr">
+      <c r="C32" s="38" t="inlineStr">
         <is>
           <t>BG.ECM.IND.BUY</t>
         </is>
@@ -3945,14 +3944,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>EU cross-section, 2024. X = consumer adoption. Y = share of enterprise turnover from e-sales.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="F3" s="32" t="inlineStr">
+      <c r="F3" s="33" t="inlineStr">
         <is>
           <t>Digital adoption and e-commerce turnover, EU 2024</t>
         </is>
@@ -3979,368 +3978,368 @@
           <t>Y: e-sales share of turnover (%)</t>
         </is>
       </c>
-      <c r="F4" s="25" t="inlineStr">
+      <c r="F4" s="26" t="inlineStr">
         <is>
           <t>One point per member state with both measures. Fitted by ordinary least squares; see the statistics below.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="C5" s="38">
+      <c r="C5" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"AT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"AT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"AT.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"AT.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Belgium</t>
         </is>
       </c>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="38" t="inlineStr">
         <is>
           <t>BE</t>
         </is>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"BE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"BE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"BE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"BE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Bulgaria</t>
         </is>
       </c>
-      <c r="B7" s="39" t="inlineStr">
+      <c r="B7" s="38" t="inlineStr">
         <is>
           <t>BG</t>
         </is>
       </c>
-      <c r="C7" s="38">
+      <c r="C7" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"BG.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"BG.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"BG.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"BG.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Cyprus</t>
         </is>
       </c>
-      <c r="B8" s="39" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>CY</t>
         </is>
       </c>
-      <c r="C8" s="38">
+      <c r="C8" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"CY.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"CY.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D8" s="38">
+      <c r="D8" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"CY.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"CY.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Czechia</t>
         </is>
       </c>
-      <c r="B9" s="39" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>CZ</t>
         </is>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"CZ.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"CZ.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"CZ.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"CZ.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="B10" s="39" t="inlineStr">
+      <c r="B10" s="38" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="C10" s="38">
+      <c r="C10" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D10" s="38">
+      <c r="D10" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="B11" s="39" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="C11" s="38">
+      <c r="C11" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D11" s="38">
+      <c r="D11" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="B12" s="39" t="inlineStr">
+      <c r="B12" s="38" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="C12" s="38">
+      <c r="C12" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"ES.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"ES.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D12" s="38">
+      <c r="D12" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"ES.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"ES.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="B13" s="39" t="inlineStr">
+      <c r="B13" s="38" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="C13" s="38">
+      <c r="C13" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"FR.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"FR.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D13" s="38">
+      <c r="D13" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"FR.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"FR.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="B14" s="39" t="inlineStr">
+      <c r="B14" s="38" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="C14" s="38">
+      <c r="C14" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"HR.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"HR.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"HR.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"HR.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>Hungary</t>
         </is>
       </c>
-      <c r="B15" s="39" t="inlineStr">
+      <c r="B15" s="38" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"HU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"HU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D15" s="38">
+      <c r="D15" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"HU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"HU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="B16" s="39" t="inlineStr">
+      <c r="B16" s="38" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D16" s="38">
+      <c r="D16" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="B17" s="39" t="inlineStr">
+      <c r="B17" s="38" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="C17" s="38">
+      <c r="C17" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D17" s="38">
+      <c r="D17" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"IT.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"IT.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>Luxembourg</t>
         </is>
       </c>
-      <c r="B18" s="39" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>LU</t>
         </is>
       </c>
-      <c r="C18" s="38">
+      <c r="C18" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"LU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"LU.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D18" s="38">
+      <c r="D18" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"LU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"LU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>Malta</t>
         </is>
       </c>
-      <c r="B19" s="39" t="inlineStr">
+      <c r="B19" s="38" t="inlineStr">
         <is>
           <t>MT</t>
         </is>
       </c>
-      <c r="C19" s="38">
+      <c r="C19" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"MT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"MT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D19" s="38">
+      <c r="D19" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"MT.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"MT.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="B20" s="39" t="inlineStr">
+      <c r="B20" s="38" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="C20" s="38">
+      <c r="C20" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"PL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"PL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D20" s="38">
+      <c r="D20" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"PL.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"PL.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="B21" s="39" t="inlineStr">
+      <c r="B21" s="38" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="C21" s="38">
+      <c r="C21" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"SE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"SE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D21" s="38">
+      <c r="D21" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"SE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"SE.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="B22" s="39" t="inlineStr">
+      <c r="B22" s="38" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="C22" s="38">
+      <c r="C22" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"SI.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"SI.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D22" s="38">
+      <c r="D22" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"SI.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"SI.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
@@ -4370,160 +4369,160 @@
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>n (countries)</t>
         </is>
       </c>
-      <c r="B26" s="33">
+      <c r="B26" s="28">
         <f>COUNT($C$5:$C$22)</f>
         <v/>
       </c>
-      <c r="C26" s="29" t="inlineStr">
+      <c r="C26" s="30" t="inlineStr">
         <is>
           <t>Number of complete X-Y pairs. Expands automatically as data is added.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>Slope</t>
         </is>
       </c>
-      <c r="B27" s="40">
+      <c r="B27" s="39">
         <f>SLOPE($D$5:$D$22,$C$5:$C$22)</f>
         <v/>
       </c>
-      <c r="C27" s="29" t="inlineStr">
+      <c r="C27" s="30" t="inlineStr">
         <is>
           <t>Percentage points of enterprise turnover per percentage point of consumer adoption.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B28" s="38">
+      <c r="B28" s="32">
         <f>INTERCEPT($D$5:$D$22,$C$5:$C$22)</f>
         <v/>
       </c>
-      <c r="C28" s="29" t="inlineStr">
+      <c r="C28" s="30" t="inlineStr">
         <is>
           <t>Not interpretable - no country has zero adoption, so this is far outside the observed range.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>Correlation (r)</t>
         </is>
       </c>
-      <c r="B29" s="40">
+      <c r="B29" s="39">
         <f>CORREL($C$5:$C$22,$D$5:$D$22)</f>
         <v/>
       </c>
-      <c r="C29" s="29" t="inlineStr">
+      <c r="C29" s="30" t="inlineStr">
         <is>
           <t>Strength and direction of the linear association.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>R-squared</t>
         </is>
       </c>
-      <c r="B30" s="40">
+      <c r="B30" s="39">
         <f>RSQ($D$5:$D$22,$C$5:$C$22)</f>
         <v/>
       </c>
-      <c r="C30" s="29" t="inlineStr">
+      <c r="C30" s="30" t="inlineStr">
         <is>
           <t>Share of cross-country variation in Y that moves with X. Estimated on the complete set of paired member states, so it is quotable - see the SAMPLE block below for what the earlier tail-selected sample claimed.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>Slope standard error</t>
         </is>
       </c>
-      <c r="B31" s="40">
+      <c r="B31" s="39">
         <f>STEYX($D$5:$D$22,$C$5:$C$22)/SQRT(DEVSQ($C$5:$C$22))</f>
         <v/>
       </c>
-      <c r="C31" s="29" t="inlineStr">
+      <c r="C31" s="30" t="inlineStr">
         <is>
           <t>Precision of the slope estimate.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>Slope t-statistic</t>
         </is>
       </c>
-      <c r="B32" s="38">
+      <c r="B32" s="32">
         <f>SLOPE($D$5:$D$22,$C$5:$C$22)/(STEYX($D$5:$D$22,$C$5:$C$22)/SQRT(DEVSQ($C$5:$C$22)))</f>
         <v/>
       </c>
-      <c r="C32" s="29" t="inlineStr">
+      <c r="C32" s="30" t="inlineStr">
         <is>
           <t>Slope divided by its standard error, on n-2 degrees of freedom. Above about 2.1 the slope is distinguishable from zero at the 5% level on this sample size.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>Denmark: actual Y</t>
         </is>
       </c>
-      <c r="B33" s="38">
+      <c r="B33" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C33" s="29" t="inlineStr">
+      <c r="C33" s="30" t="inlineStr">
         <is>
           <t>Denmark's observed value.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="27" t="inlineStr">
         <is>
           <t>Denmark: fitted Y</t>
         </is>
       </c>
-      <c r="B34" s="38">
+      <c r="B34" s="32">
         <f>INTERCEPT($D$5:$D$22,$C$5:$C$22)+SLOPE($D$5:$D$22,$C$5:$C$22)*IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C34" s="29" t="inlineStr">
+      <c r="C34" s="30" t="inlineStr">
         <is>
           <t>What the line predicts for Denmark's adoption level.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="26" t="inlineStr">
+      <c r="A35" s="27" t="inlineStr">
         <is>
           <t>Denmark: residual</t>
         </is>
       </c>
-      <c r="B35" s="41">
+      <c r="B35" s="40">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))-(INTERCEPT($D$5:$D$22,$C$5:$C$22)+SLOPE($D$5:$D$22,$C$5:$C$22)*IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)))</f>
         <v/>
       </c>
-      <c r="C35" s="29" t="inlineStr">
+      <c r="C35" s="30" t="inlineStr">
         <is>
           <t>Positive: Denmark converts adoption into commercial activity better than the EU pattern predicts. Negative: worse.</t>
         </is>
@@ -4537,54 +4536,54 @@
       </c>
     </row>
     <row r="38" ht="46" customHeight="1">
-      <c r="A38" s="42" t="inlineStr">
+      <c r="A38" s="41" t="inlineStr">
         <is>
           <t>COMPLETE FOR 2024: the X column is the full Eurostat isoc_ec_ib20 extract for all 27 member states, unrounded, taken from the databrowser. Every member state holding both measures is plotted - 18 of them. No country with both values is excluded, so the fit is no longer conditioned on where a country sits in the ranking.</t>
         </is>
       </c>
-      <c r="B38" s="43" t="n"/>
-      <c r="C38" s="43" t="n"/>
-      <c r="D38" s="43" t="n"/>
+      <c r="B38" s="42" t="n"/>
+      <c r="C38" s="42" t="n"/>
+      <c r="D38" s="42" t="n"/>
     </row>
     <row r="39" ht="46" customHeight="1">
-      <c r="A39" s="42" t="inlineStr">
+      <c r="A39" s="41" t="inlineStr">
         <is>
           <t>WHAT THE EARLIER SAMPLE CLAIMED: an earlier version of this figure drew X from a Eurostat press release, which named only the three highest countries, the three lowest and two large movers. On those 6 tail countries the fit was R-squared 0.853 with a slope of +0.655. On the complete cross-section it is R-squared 0.674 with a slope of +0.602.</t>
         </is>
       </c>
-      <c r="B39" s="43" t="n"/>
-      <c r="C39" s="43" t="n"/>
-      <c r="D39" s="43" t="n"/>
+      <c r="B39" s="42" t="n"/>
+      <c r="C39" s="42" t="n"/>
+      <c r="D39" s="42" t="n"/>
     </row>
     <row r="40" ht="46" customHeight="1">
-      <c r="A40" s="42" t="inlineStr">
+      <c r="A40" s="41" t="inlineStr">
         <is>
           <t>READING THAT COMPARISON: the slope moved by about 8% while R-squared fell by 0.18. This is the signature of selection on the tails - it widens the spread in X relative to the scatter around the line, which flatters the fit while leaving the estimated relationship roughly intact. The earlier R-squared was an upper bound, as the warning it replaced said; this one is an estimate.</t>
         </is>
       </c>
-      <c r="B40" s="43" t="n"/>
-      <c r="C40" s="43" t="n"/>
-      <c r="D40" s="43" t="n"/>
+      <c r="B40" s="42" t="n"/>
+      <c r="C40" s="42" t="n"/>
+      <c r="D40" s="42" t="n"/>
     </row>
     <row r="41" ht="46" customHeight="1">
-      <c r="A41" s="42" t="inlineStr">
+      <c r="A41" s="41" t="inlineStr">
         <is>
           <t>STILL NOT A COMPLETE CROSS-SECTION OF THE EU: nine member states hold the adoption measure but not the enterprise turnover measure and are listed below. The sample is complete with respect to X and incomplete with respect to Y, so it is 18 countries rather than 27 - but the countries dropped are dropped by data availability, not by their position on either axis.</t>
         </is>
       </c>
-      <c r="B41" s="43" t="n"/>
-      <c r="C41" s="43" t="n"/>
-      <c r="D41" s="43" t="n"/>
+      <c r="B41" s="42" t="n"/>
+      <c r="C41" s="42" t="n"/>
+      <c r="D41" s="42" t="n"/>
     </row>
     <row r="42" ht="46" customHeight="1">
-      <c r="A42" s="42" t="inlineStr">
+      <c r="A42" s="41" t="inlineStr">
         <is>
           <t>DIRECTION OF CAUSATION IS NOT ESTABLISHED AND CANNOT BE. X measures consumers; Y measures enterprises, including business-to-business sales that no consumer touches. Both plausibly rise with national income, which is in neither axis. This figure shows that digital commerce runs deep in the same economies where consumers buy online. It does not show that the one produces the other.</t>
         </is>
       </c>
-      <c r="B42" s="43" t="n"/>
-      <c r="C42" s="43" t="n"/>
-      <c r="D42" s="43" t="n"/>
+      <c r="B42" s="42" t="n"/>
+      <c r="C42" s="42" t="n"/>
+      <c r="D42" s="42" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -4611,153 +4610,153 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="26" t="inlineStr">
+      <c r="A46" s="27" t="inlineStr">
         <is>
           <t>Estonia</t>
         </is>
       </c>
-      <c r="B46" s="39" t="inlineStr">
+      <c r="B46" s="38" t="inlineStr">
         <is>
           <t>EE</t>
         </is>
       </c>
-      <c r="C46" s="44" t="inlineStr">
+      <c r="C46" s="43" t="inlineStr">
         <is>
           <t>Y - add EE.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="26" t="inlineStr">
+      <c r="A47" s="27" t="inlineStr">
         <is>
           <t>Greece</t>
         </is>
       </c>
-      <c r="B47" s="39" t="inlineStr">
+      <c r="B47" s="38" t="inlineStr">
         <is>
           <t>EL</t>
         </is>
       </c>
-      <c r="C47" s="44" t="inlineStr">
+      <c r="C47" s="43" t="inlineStr">
         <is>
           <t>Y - add EL.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="26" t="inlineStr">
+      <c r="A48" s="27" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="B48" s="39" t="inlineStr">
+      <c r="B48" s="38" t="inlineStr">
         <is>
           <t>FI</t>
         </is>
       </c>
-      <c r="C48" s="44" t="inlineStr">
+      <c r="C48" s="43" t="inlineStr">
         <is>
           <t>Y - add FI.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="26" t="inlineStr">
+      <c r="A49" s="27" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="B49" s="39" t="inlineStr">
+      <c r="B49" s="38" t="inlineStr">
         <is>
           <t>LT</t>
         </is>
       </c>
-      <c r="C49" s="44" t="inlineStr">
+      <c r="C49" s="43" t="inlineStr">
         <is>
           <t>Y - add LT.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="26" t="inlineStr">
+      <c r="A50" s="27" t="inlineStr">
         <is>
           <t>Latvia</t>
         </is>
       </c>
-      <c r="B50" s="39" t="inlineStr">
+      <c r="B50" s="38" t="inlineStr">
         <is>
           <t>LV</t>
         </is>
       </c>
-      <c r="C50" s="44" t="inlineStr">
+      <c r="C50" s="43" t="inlineStr">
         <is>
           <t>Y - add LV.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="26" t="inlineStr">
+      <c r="A51" s="27" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="B51" s="39" t="inlineStr">
+      <c r="B51" s="38" t="inlineStr">
         <is>
           <t>NL</t>
         </is>
       </c>
-      <c r="C51" s="44" t="inlineStr">
+      <c r="C51" s="43" t="inlineStr">
         <is>
           <t>Y - add NL.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="26" t="inlineStr">
+      <c r="A52" s="27" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="B52" s="39" t="inlineStr">
+      <c r="B52" s="38" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="C52" s="44" t="inlineStr">
+      <c r="C52" s="43" t="inlineStr">
         <is>
           <t>Y - add PT.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="26" t="inlineStr">
+      <c r="A53" s="27" t="inlineStr">
         <is>
           <t>Romania</t>
         </is>
       </c>
-      <c r="B53" s="39" t="inlineStr">
+      <c r="B53" s="38" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="C53" s="44" t="inlineStr">
+      <c r="C53" s="43" t="inlineStr">
         <is>
           <t>Y - add RO.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="26" t="inlineStr">
+      <c r="A54" s="27" t="inlineStr">
         <is>
           <t>Slovakia</t>
         </is>
       </c>
-      <c r="B54" s="39" t="inlineStr">
+      <c r="B54" s="38" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="C54" s="44" t="inlineStr">
+      <c r="C54" s="43" t="inlineStr">
         <is>
           <t>Y - add SK.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
         </is>
@@ -4766,7 +4765,7 @@
     <row r="56">
       <c r="A56" s="34" t="inlineStr">
         <is>
-          <t>Sources: Eurostat isoc_ec_ib20 (ES4) for X; Eurostat tin00110 (ES5, ES6) for Y. WHY A CROSS-SECTION: the Danish adoption and outcome series share almost no observation years - the best time-series pairing in this dataset is n=2 - so a within-Denmark scatter of adoption against outcome cannot be drawn from verified data. SAMPLE: n=18 of 27 member states. This is a small sample; report the association descriptively and do not quote a p-value. Adding the missing values listed above raises n automatically on the next rebuild. WHAT Y MEASURES: tin00110 covers all enterprises with 10+ employees outside the financial sector, so it includes B2B and EDI ordering across every industry, not retail alone. X is a consumer measure. The two sit on different sides of the market, so a positive association is evidence that digital commerce is deep in an economy - not evidence that consumers buying online causes enterprise turnover.</t>
+          <t>Sources: Eurostat isoc_ec_ib20 (ES7) for X; Eurostat tin00110 (ES5, ES6) for Y. WHY A CROSS-SECTION: the Danish adoption and outcome series share almost no observation years - the best time-series pairing in this dataset is n=2 - so a within-Denmark scatter of adoption against outcome cannot be drawn from verified data. SAMPLE: n=18 of 27 member states. This is a small sample; report the association descriptively and do not quote a p-value. Adding the missing values listed above raises n automatically on the next rebuild. WHAT Y MEASURES: tin00110 covers all enterprises with 10+ employees outside the financial sector, so it includes B2B and EDI ordering across every industry, not retail alone. X is a consumer measure. The two sit on different sides of the market, so a positive association is evidence that digital commerce is deep in an economy - not evidence that consumers buying online causes enterprise turnover.</t>
         </is>
       </c>
     </row>
@@ -4806,14 +4805,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Leads on every capability measure. Below average on citizen service quality.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="F3" s="32" t="inlineStr">
+      <c r="F3" s="33" t="inlineStr">
         <is>
           <t>Denmark vs EU-27 average</t>
         </is>
@@ -4840,81 +4839,81 @@
           <t>unit</t>
         </is>
       </c>
-      <c r="F4" s="25" t="inlineStr">
+      <c r="F4" s="26" t="inlineStr">
         <is>
           <t>Denmark in blue, EU average in grey. Note the direction reverses on the bottom two rows.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>SMEs with at least basic digital intensity</t>
         </is>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENT.DII",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENT.DII",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C5" s="38">
+      <c r="C5" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.ENT.DII",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.ENT.DII",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>% of SMEs</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Enterprises adopting AI</t>
         </is>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENT.AI",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENT.AI",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C6" s="43" t="n"/>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="C6" s="42" t="n"/>
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>% of enterprises (EU avg 19.95)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Digital public services for citizens</t>
         </is>
       </c>
-      <c r="B7" s="38">
+      <c r="B7" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C7" s="38">
+      <c r="C7" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="D7" s="29" t="inlineStr">
         <is>
           <t>eGovernment Benchmark score 0-100</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Cross-border digital public services</t>
         </is>
       </c>
-      <c r="B8" s="38">
+      <c r="B8" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DPS.XB",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DPS.XB",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C8" s="43" t="n"/>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="C8" s="42" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>score 0-100 (EU avg 75.28)</t>
         </is>
@@ -4945,48 +4944,48 @@
       </c>
     </row>
     <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Digital public services, DK minus EU average</t>
         </is>
       </c>
-      <c r="B12" s="38">
+      <c r="B12" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"EU.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>Negative. The most digitalised population in the EU receives below-average digital public services.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Digital skills gap within Denmark, 16-24 minus 55-74</t>
         </is>
       </c>
-      <c r="B13" s="38">
+      <c r="B13" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>The within-country spread. Note that Denmark's WEAKEST age group (67.81%) still beats the EU average (42.60%) by 25pp, so Danish exclusion is not a skills deficit relative to Europe - it is a mandate calibrated above the bottom of its own distribution.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>AI adoption gap within Denmark, large firms minus SMEs</t>
         </is>
       </c>
-      <c r="B14" s="38">
+      <c r="B14" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENT.AI.LRG",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENT.AI.LRG",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENT.AI.SME",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENT.AI.SME",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C14" s="29" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
         <is>
           <t>Breadth without depth, restated for AI.</t>
         </is>
@@ -5029,14 +5028,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Danmarks Statistik matched-comparison evaluation, June 2025.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="E3" s="32" t="inlineStr">
+      <c r="E3" s="33" t="inlineStr">
         <is>
           <t>SMV:Digital participant outcomes</t>
         </is>
@@ -5058,30 +5057,30 @@
           <t>unit</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t>Participation measures only. No effect size is plotted because none was verified.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Digitalisation projects supported since 2018</t>
         </is>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SME.SMVD.PROJ",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SME.SMVD.PROJ",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Participants investing further during the project</t>
         </is>
@@ -5090,14 +5089,14 @@
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SME.SMVD.INV",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SME.SMVD.INV",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>% of participants</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Participants with no further investment plans</t>
         </is>
@@ -5106,7 +5105,7 @@
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SME.SMVD.NOINV",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SME.SMVD.NOINV",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>% of participants</t>
         </is>
@@ -5278,14 +5277,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Three measures of the same structural shift. Note the different start years: the periods are NOT comparable to one another.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="J3" s="32" t="inlineStr">
+      <c r="J3" s="33" t="inlineStr">
         <is>
           <t>Banking consolidation, by measure</t>
         </is>
@@ -5317,42 +5316,42 @@
           <t>change</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="26" t="inlineStr">
         <is>
           <t>chart label (helper)</t>
         </is>
       </c>
-      <c r="H4" s="25" t="inlineStr">
+      <c r="H4" s="26" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="J4" s="25" t="inlineStr">
+      <c r="J4" s="26" t="inlineStr">
         <is>
           <t>Employment in blue - it fell least. Periods differ by measure; read each bar against its own label.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Financial institutions</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>1991-2024</t>
         </is>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991))</f>
         <v/>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="E5" s="45">
+      <c r="E5" s="31">
         <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991)))-1</f>
         <v/>
       </c>
@@ -5361,31 +5360,31 @@
           <t>Financial institutions (1991-2024)</t>
         </is>
       </c>
-      <c r="H5" s="46">
+      <c r="H5" s="44">
         <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991)))-1</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Bank branches</t>
         </is>
       </c>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="38" t="inlineStr">
         <is>
           <t>2004-2024</t>
         </is>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004))</f>
         <v/>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="E6" s="45">
+      <c r="E6" s="31">
         <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004)))-1</f>
         <v/>
       </c>
@@ -5394,31 +5393,31 @@
           <t>Bank branches (2004-2024)</t>
         </is>
       </c>
-      <c r="H6" s="46">
+      <c r="H6" s="44">
         <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004)))-1</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Bank employees</t>
         </is>
       </c>
-      <c r="B7" s="39" t="inlineStr">
+      <c r="B7" s="38" t="inlineStr">
         <is>
           <t>1991-2024</t>
         </is>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991))</f>
         <v/>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="E7" s="45">
+      <c r="E7" s="31">
         <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991)))-1</f>
         <v/>
       </c>
@@ -5427,7 +5426,7 @@
           <t>Bank employees (1991-2024)</t>
         </is>
       </c>
-      <c r="H7" s="46">
+      <c r="H7" s="44">
         <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991)))-1</f>
         <v/>
       </c>
@@ -5462,44 +5461,44 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Employees per institution</t>
         </is>
       </c>
-      <c r="B11" s="33">
+      <c r="B11" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991))</f>
         <v/>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="D11" s="29" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>Denmark did not shed banking labour in proportion to its institutions. It concentrated it.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Change in staff per institution</t>
         </is>
       </c>
-      <c r="B12" s="45">
+      <c r="B12" s="31">
         <f>((IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,2024)))/(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,1991))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.INST",'02_MASTER'!$E:$E,1991))))-1</f>
         <v/>
       </c>
-      <c r="C12" s="43" t="inlineStr"/>
-      <c r="D12" s="29" t="inlineStr">
+      <c r="C12" s="42" t="inlineStr"/>
+      <c r="D12" s="30" t="inlineStr">
         <is>
           <t>The measure that rose. Every other line on this sheet falls.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Employees per branch, 2024</t>
         </is>
@@ -5508,8 +5507,8 @@
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.EMP",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C13" s="43" t="inlineStr"/>
-      <c r="D13" s="29" t="inlineStr">
+      <c r="C13" s="42" t="inlineStr"/>
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>Branch counts begin in 2004, so no 1991 comparison is available for this ratio.</t>
         </is>
@@ -5551,14 +5550,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Denmark against the EU-27 average. Same publication, same definition, same year.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="F3" s="32" t="inlineStr">
+      <c r="F3" s="33" t="inlineStr">
         <is>
           <t>At least basic digital skills by age, DK vs EU-27</t>
         </is>
@@ -5585,65 +5584,65 @@
           <t>DK lead</t>
         </is>
       </c>
-      <c r="F4" s="25" t="inlineStr">
+      <c r="F4" s="26" t="inlineStr">
         <is>
           <t>Denmark in blue; the EU-27 average in grey. Note that the Danish 55-74 bar still clears the EU average for its own band.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>16-24</t>
         </is>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C5" s="38">
+      <c r="C5" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.SKL.1624",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.SKL.1624",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="40">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"EU.SKL.1624",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.SKL.1624",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>25-54</t>
         </is>
       </c>
-      <c r="B6" s="38">
+      <c r="B6" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.2554",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.2554",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.SKL.2554",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.SKL.2554",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="40">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.2554",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.2554",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"EU.SKL.2554",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.SKL.2554",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>55-74</t>
         </is>
       </c>
-      <c r="B7" s="38">
+      <c r="B7" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C7" s="38">
+      <c r="C7" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.SKL.5574",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="D7" s="41">
+      <c r="D7" s="40">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"EU.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.SKL.5574",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
@@ -5673,48 +5672,48 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Danish gradient, 16-24 less 55-74</t>
         </is>
       </c>
-      <c r="B11" s="41">
+      <c r="B11" s="40">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C11" s="29" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>The internal spread across Danish age bands.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>EU gradient, 16-24 less 55-74</t>
         </is>
       </c>
-      <c r="B12" s="41">
+      <c r="B12" s="40">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.SKL.1624",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.SKL.1624",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"EU.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.SKL.5574",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>The same spread for the EU as a whole. Denmark's is the narrower of the two, so its age gradient is comparatively mild.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Danish 55-74 less the EU average for 55-74</t>
         </is>
       </c>
-      <c r="B13" s="41">
+      <c r="B13" s="40">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"EU.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.SKL.5574",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C13" s="29" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>Denmark's weakest band against the EU's same band - NOT against the EU all-ages average. Positive and large.</t>
         </is>
@@ -5734,464 +5733,6 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="74" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>Policy events</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Dated instruments, with the series each one bears on. Rendered as event tables beneath the figures they affect.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>precision</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>instrument</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>legal citation</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>source_id</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>what it does</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>series affected</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>2012-06-11</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>Lov om Offentlig Digital Post adopted</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>LOV nr 528 af 11/06/2012</t>
-        </is>
-      </c>
-      <c r="E5" s="23" t="inlineStr">
-        <is>
-          <t>RI1</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="inlineStr">
-        <is>
-          <t>Creates the statutory basis for mandatory public digital post. Section 10 deems delivery effective on availability, not on the message being read.</t>
-        </is>
-      </c>
-      <c r="G5" s="23" t="inlineStr">
-        <is>
-          <t>DK.DGP.EXMP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
-        <is>
-          <t>2013-01-01</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>Digital Post becomes mandatory for businesses</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>Lov om Offentlig Digital Post</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="inlineStr">
-        <is>
-          <t>DG4</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="inlineStr">
-        <is>
-          <t>Businesses are enrolled a year ahead of citizens.</t>
-        </is>
-      </c>
-      <c r="G6" s="23" t="inlineStr">
-        <is>
-          <t>DK.ECM.ENT.TRN</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>2014-11-01</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Digital Post becomes mandatory for citizens aged 15+</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Lov om Offentlig Digital Post</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>DG4</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>Citizens are enrolled automatically whether or not they registered themselves. Exemption is available only against statutory criteria. This is the single most consequential date in this workbook.</t>
-        </is>
-      </c>
-      <c r="G7" s="23" t="inlineStr">
-        <is>
-          <t>DK.DGP.EXMP</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>2016-01-01</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Rigsrevisionen reports on the Digital Post business case</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>Beretning, January 2016</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="inlineStr">
-        <is>
-          <t>RR1</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>Of an approx. DKK 1bn projected annual saving, only DKK 450m - postage, paper and envelopes - could be verified.</t>
-        </is>
-      </c>
-      <c r="G8" s="23" t="inlineStr">
-        <is>
-          <t>DK.GOV.DGP.SAVE.PLAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="23" t="inlineStr">
-        <is>
-          <t>2018-01-01</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>SMV:Digital launched</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>Danish digital growth plan for SMEs</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="inlineStr">
-        <is>
-          <t>DG3</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>Grant scheme subsidising SME digitalisation projects.</t>
-        </is>
-      </c>
-      <c r="G9" s="23" t="inlineStr">
-        <is>
-          <t>DK.SME.SMVD.PROJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>2021-10-01</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>MitID rollout begins</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>National electronic ID replacement programme</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>DG4</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="inlineStr">
-        <is>
-          <t>Begins the migration of the whole population off NemID.</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>DK.TRU.DPS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>Kontantreglen amended</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>Lov om betalinger, ss 81</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>RI2</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="inlineStr">
-        <is>
-          <t>Businesses may refuse cash from other businesses; temporary events are exempted; the notification duty for 06:00-20:00 acceptance is removed. The obligation on shops to accept cash from consumers remains.</t>
-        </is>
-      </c>
-      <c r="G11" s="23" t="inlineStr">
-        <is>
-          <t>DK.PAY.CASH.POS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>MitID required for public digital services</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>National electronic ID replacement programme</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="inlineStr">
-        <is>
-          <t>DG4</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="inlineStr">
-        <is>
-          <t>From this date citizens need MitID for borger.dk, skat.dk and sundhed.dk.</t>
-        </is>
-      </c>
-      <c r="G12" s="23" t="inlineStr">
-        <is>
-          <t>DK.TRU.DPS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="46" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>2023-10-31</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>NemID fully phased out</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>National electronic ID replacement programme</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>DG4</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="inlineStr">
-        <is>
-          <t>The predecessor credential can no longer be obtained or used.</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="inlineStr">
-        <is>
-          <t>DK.TRU.DPS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="46" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>SMV:Digital grant pools continue</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>Tilskudspuljer i 2026</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>SMV1</t>
-        </is>
-      </c>
-      <c r="F14" s="15" t="inlineStr">
-        <is>
-          <t>The scheme is still operating and still awarding grants in 2026; a further pool opens on 26 October 2026. Recorded because an earlier draft of this workbook asserted the scheme was being defunded. It was not verifiable and the opposite is documented.</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="inlineStr">
-        <is>
-          <t>DK.SME.SMVD.PROJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="34" t="inlineStr">
-        <is>
-          <t>Reading: the mandate date of 1 November 2014 is the hinge of this workbook. Digital Post was not adopted by citizens choosing it; citizens were enrolled automatically, and exemption is available only against statutory criteria. Adoption rates after that date therefore measure compliance with a legal obligation, not revealed preference, and no figure in this workbook should be read as though they measured preference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="34" t="inlineStr">
-        <is>
-          <t>CORRECTION RECORDED: an earlier draft of this workbook stated that SMV:Digital was being defunded. That claim could not be verified, and the scheme's own 2026 grant-pool page (SMV1) documents pools still open, with a further pool opening on 26 October 2026. The claim has been withdrawn from the dataset and from the report's argument. See 07_LIMITATIONS and 08_AI_LOG.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6212,7 +5753,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Recorded rather than silently omitted.</t>
         </is>
@@ -6224,7 +5765,7 @@
           <t>Status</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="45" t="inlineStr">
         <is>
           <t>NOT RETRIEVED</t>
         </is>
@@ -6236,7 +5777,7 @@
           <t>Indicator</t>
         </is>
       </c>
-      <c r="B5" s="47" t="inlineStr">
+      <c r="B5" s="45" t="inlineStr">
         <is>
           <t>Retail trade turnover, volume index (mangdeindeks)</t>
         </is>
@@ -6248,9 +5789,9 @@
           <t>Authority</t>
         </is>
       </c>
-      <c r="B6" s="47" t="inlineStr">
-        <is>
-          <t>Danmarks Statistik; also available via Eurostat sts_trtu_a</t>
+      <c r="B6" s="45" t="inlineStr">
+        <is>
+          <t>Danmarks Statistik (DST1); also available via Eurostat sts_trtu_a</t>
         </is>
       </c>
     </row>
@@ -6260,7 +5801,7 @@
           <t>Filters required</t>
         </is>
       </c>
-      <c r="B7" s="47" t="inlineStr">
+      <c r="B7" s="45" t="inlineStr">
         <is>
           <t>geo=DK; nace_r2=G47; indic_bt=VOL; s_adj=SCA; unit=I21 (2021=100)</t>
         </is>
@@ -6272,7 +5813,7 @@
           <t>Why not retrieved</t>
         </is>
       </c>
-      <c r="B8" s="47" t="inlineStr">
+      <c r="B8" s="45" t="inlineStr">
         <is>
           <t>Values are published through StatBank and the Eurostat databrowser. This session's network policy blocked direct access to both, and the figure could not be verified by search. A value that cannot be traced is not entered.</t>
         </is>
@@ -6284,7 +5825,7 @@
           <t>Base year caution</t>
         </is>
       </c>
-      <c r="B9" s="47" t="inlineStr">
+      <c r="B9" s="45" t="inlineStr">
         <is>
           <t>Danmarks Statistik rebased the index from 2015=100 to 2021=100. Series retrieved on different bases must not be joined.</t>
         </is>
@@ -6296,7 +5837,7 @@
           <t>Effect on the analysis</t>
         </is>
       </c>
-      <c r="B10" s="47" t="inlineStr">
+      <c r="B10" s="45" t="inlineStr">
         <is>
           <t>The e-commerce section rests on the enterprise e-sales evidence in F3_ESALES instead, which is better sourced. No conclusion in the report depends on this series.</t>
         </is>
@@ -6308,7 +5849,7 @@
           <t>To fill</t>
         </is>
       </c>
-      <c r="B11" s="47" t="inlineStr">
+      <c r="B11" s="45" t="inlineStr">
         <is>
           <t>Retrieve from statistikbanken.dk, add rows to dataset.py under series_code DK.RET.VOL with unit 'index 2021=100', and re-run build_workbook.py.</t>
         </is>
@@ -6319,7 +5860,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6340,7 +5881,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Read before citing any value.</t>
         </is>
@@ -6559,6 +6100,289 @@
       <c r="B21" s="20" t="inlineStr">
         <is>
           <t>An earlier candidate dataset was rejected in full after verification found fabricated values carrying authentic dataset codes and extraction dates - including a Eurostat cross-section that inverted the true EU country ranking. None of it survives in this workbook.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>AI use and validation log</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>Raw material for the AI Use and Validation Appendix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>AI assistance used</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>how it was validated</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Source identification</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>AI used to identify candidate statistical sources and dataset codes.</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Each source opened or search-verified against the issuing authority.</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Source register in 03_SOURCES.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Value retrieval</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>AI used to search for published values by authority and indicator.</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Each value checked against a result reporting the issuing authority's own publication.</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Every retained observation carries a source_id.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Rejection of a prior dataset</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>A candidate dataset produced with AI assistance was reviewed.</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Cross-checked against Eurostat's published country ranking; the values inverted the true ranking and contained duplicated and interpolated cells.</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Dataset rejected in full and excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Withdrawal of an AI-suggested claim</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>An AI-assisted draft asserted that the SMV:Digital grant scheme was being defunded, and an argument was built on the contrast between a programme with measured positive effects and a programme being cut.</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Searched for the scheme's funding status. The scheme's own 2026 grant-pool page documents pools still open and a further pool opening 26 October 2026. No source supported the defunding claim.</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Claim withdrawn from the dataset and the argument; the withdrawal is recorded in 09_POLICY and 07_LIMITATIONS rather than erased.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Statistical self-audit</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>AI was asked to audit its own workbook as a macroeconomic policy reviewer would.</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>The audit found that Figure 6's adoption column had been assembled from a press release naming only the top three, bottom three and three large movers - a sample drawn from the tails, which inflates R-squared by construction.</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>R-squared removed from the chart face; a selection warning added to F6; the limitation recorded in 07_LIMITATIONS. Later resolved - see the two rows below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Failed verification attempt</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>AI was asked to retrieve Eurostat isoc_ec_ib20 for 2024 for the twelve member states missing from Figure 6, so the tail selection could be removed.</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Eurostat and the national statistical offices are unreachable from the build environment. Web search returned only the press release naming the same tails, two country values with no attributable source, and one answer mixing the '% of internet users' and '% of individuals' denominators in a single paragraph.</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>No values accepted. Recorded because the honest outcome of a verification attempt is sometimes that it failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Author-supplied authoritative extract</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>The author retrieved the complete isoc_ec_ib20 table from the Eurostat databrowser and supplied it as a spreadsheet; AI parsed it into the dataset.</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>The extract carries its own provenance header - dataset code, extraction timestamp, last-update date, and an explicit unit of 'percentage of individuals who used internet within the last year'. The ten values it overlapped with were compared against the rounded press-release figures already held; all ten agreed to rounding.</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>All 27 member states plus the EU-27 aggregate added under source ES7. Figure 6 went from n=6 to n=18 and R-squared was restored to the chart face. The superseded rounded values are recorded in each row's note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Workbook construction</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>AI wrote the Python build script that generates this workbook.</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Structural assertions run at build time: source_ids resolve, units and denominators present, no duplicate observations, break flags set.</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>build_workbook.py, re-runnable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Analytical framing</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>AI used to interpret patterns and suggest framings.</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Author reviewed each interpretation against the underlying values.</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Interpretations appear in the report, attributed to the author.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Not delegated to AI</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Selection of the research question, country, industries, SDG and policy comparator; the argument; the conclusions.</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Author's own work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>This log records assistance during data assembly. Complete it with any further AI use during drafting before submission. The assessment requires that AI-assisted content be verified and acknowledged.</t>
         </is>
       </c>
     </row>
@@ -6788,275 +6612,450 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="74" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>AI use and validation log</t>
+          <t>Policy events</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
-        <is>
-          <t>Raw material for the AI Use and Validation Appendix.</t>
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>Dated instruments, with the series each one bears on. Rendered as event tables beneath the figures they affect.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>AI assistance used</t>
+          <t>precision</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>how it was validated</t>
+          <t>instrument</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>outcome</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>Source identification</t>
+          <t>legal citation</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>what it does</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>series affected</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>AI used to identify candidate statistical sources and dataset codes.</t>
+          <t>day</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Each source opened or search-verified against the issuing authority.</t>
+          <t>Lov om Offentlig Digital Post adopted</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>Source register in 03_SOURCES.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Value retrieval</t>
+          <t>LOV nr 528 af 11/06/2012</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>RI1</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Creates the statutory basis for mandatory public digital post. Section 10 deems delivery effective on availability, not on the message being read.</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>DK.DGP.EXMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>2013-01-01</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>AI used to search for published values by authority and indicator.</t>
+          <t>year</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Each value checked against a result reporting the issuing authority's own publication.</t>
+          <t>Digital Post becomes mandatory for businesses</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>Every retained observation carries a source_id.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Rejection of a prior dataset</t>
+          <t>Lov om Offentlig Digital Post</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>DG4</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>Businesses are enrolled a year ahead of citizens.</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>DK.ECM.ENT.TRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>2014-11-01</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>A candidate dataset produced with AI assistance was reviewed.</t>
+          <t>day</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Cross-checked against Eurostat's published country ranking; the values inverted the true ranking and contained duplicated and interpolated cells.</t>
+          <t>Digital Post becomes mandatory for citizens aged 15+</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>Dataset rejected in full and excluded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>Withdrawal of an AI-suggested claim</t>
+          <t>Lov om Offentlig Digital Post</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>DG4</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Citizens are enrolled automatically whether or not they registered themselves. Exemption is available only against statutory criteria. This is the single most consequential date in this workbook.</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>DK.DGP.EXMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>An AI-assisted draft asserted that the SMV:Digital grant scheme was being defunded, and an argument was built on the contrast between a programme with measured positive effects and a programme being cut.</t>
+          <t>month</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Searched for the scheme's funding status. The scheme's own 2026 grant-pool page documents pools still open and a further pool opening 26 October 2026. No source supported the defunding claim.</t>
+          <t>Rigsrevisionen reports on the Digital Post business case</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>Claim withdrawn from the dataset and the argument; the withdrawal is recorded in 09_POLICY and 07_LIMITATIONS rather than erased.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>Statistical self-audit</t>
+          <t>Beretning, January 2016</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>RR1</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Of an approx. DKK 1bn projected annual saving, only DKK 450m - postage, paper and envelopes - could be verified.</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>DK.GOV.DGP.SAVE.PLAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>AI was asked to audit its own workbook as a macroeconomic policy reviewer would.</t>
+          <t>year</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>The audit found that Figure 6's adoption column had been assembled from a press release naming only the top three, bottom three and three large movers - a sample drawn from the tails, which inflates R-squared by construction.</t>
+          <t>SMV:Digital launched</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>R-squared removed from the chart face; a selection warning added to F6; the limitation recorded in 07_LIMITATIONS. Later resolved - see the two rows below.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Failed verification attempt</t>
+          <t>Danish digital growth plan for SMEs</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>DG3</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Grant scheme subsidising SME digitalisation projects.</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>DK.SME.SMVD.PROJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>AI was asked to retrieve Eurostat isoc_ec_ib20 for 2024 for the twelve member states missing from Figure 6, so the tail selection could be removed.</t>
+          <t>month</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Eurostat and the national statistical offices are unreachable from the build environment. Web search returned only the press release naming the same tails, two country values with no attributable source, and one answer mixing the '% of internet users' and '% of individuals' denominators in a single paragraph.</t>
+          <t>MitID rollout begins</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>No values accepted. Recorded because the honest outcome of a verification attempt is sometimes that it failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Author-supplied authoritative extract</t>
+          <t>National electronic ID replacement programme</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>DG4</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Begins the migration of the whole population off NemID.</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>DK.TRU.DPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>The author retrieved the complete isoc_ec_ib20 table from the Eurostat databrowser and supplied it as a spreadsheet; AI parsed it into the dataset.</t>
+          <t>day</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>The extract carries its own provenance header - dataset code, extraction timestamp, last-update date, and an explicit unit of 'percentage of individuals who used internet within the last year'. The ten values it overlapped with were compared against the rounded press-release figures already held; all ten agreed to rounding.</t>
+          <t>Kontantreglen amended</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>All 27 member states plus the EU-27 aggregate added under source ES7. Figure 6 went from n=6 to n=18 and R-squared was restored to the chart face. The superseded rounded values are recorded in each row's note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Workbook construction</t>
+          <t>Lov om betalinger, ss 81</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>RI2</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Businesses may refuse cash from other businesses; temporary events are exempted; the notification duty for 06:00-20:00 acceptance is removed. The obligation on shops to accept cash from consumers remains.</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>DK.PAY.CASH.POS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>AI wrote the Python build script that generates this workbook.</t>
+          <t>day</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Structural assertions run at build time: source_ids resolve, units and denominators present, no duplicate observations, break flags set.</t>
+          <t>MitID required for public digital services</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>build_workbook.py, re-runnable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Analytical framing</t>
+          <t>National electronic ID replacement programme</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>DG4</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>From this date citizens need MitID for borger.dk, skat.dk and sundhed.dk.</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>DK.TRU.DPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>AI used to interpret patterns and suggest framings.</t>
+          <t>day</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>Author reviewed each interpretation against the underlying values.</t>
+          <t>NemID fully phased out</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>Interpretations appear in the report, attributed to the author.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Not delegated to AI</t>
+          <t>National electronic ID replacement programme</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>DG4</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>The predecessor credential can no longer be obtained or used.</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>DK.TRU.DPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Selection of the research question, country, industries, SDG and policy comparator; the argument; the conclusions.</t>
+          <t>year</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>SMV:Digital grant pools continue</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>Author's own work.</t>
+          <t>Tilskudspuljer i 2026</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>SMV1</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>The scheme is still operating and still awarding grants in 2026; a further pool opens on 26 October 2026. Recorded because an earlier draft of this workbook asserted the scheme was being defunded. It was not verifiable and the opposite is documented.</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>DK.SME.SMVD.PROJ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="34" t="inlineStr">
         <is>
-          <t>This log records assistance during data assembly. Complete it with any further AI use during drafting before submission. The assessment requires that AI-assisted content be verified and acknowledged.</t>
+          <t>Reading: the mandate date of 1 November 2014 is the hinge of this workbook. Digital Post was not adopted by citizens choosing it; citizens were enrolled automatically, and exemption is available only against statutory criteria. Adoption rates after that date therefore measure compliance with a legal obligation, not revealed preference, and no figure in this workbook should be read as though they measured preference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="34" t="inlineStr">
+        <is>
+          <t>CORRECTION RECORDED: an earlier draft of this workbook stated that SMV:Digital was being defunded. That claim could not be verified, and the scheme's own 2026 grant-pool page (SMV1) documents pools still open, with a further pool opening on 26 October 2026. The claim has been withdrawn from the dataset and from the report's argument. See 07_LIMITATIONS and 08_AI_LOG.</t>
         </is>
       </c>
     </row>
@@ -12993,7 +12992,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>Danskerne betaler mere digitalt - det goer offline-betalinger endnu vigtigere som beredskab (press release, 26 June 2026)</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Danskerne betaler mere digitalt - det goer offline-betalinger endnu vigtigere som beredskab (press release, 26 June 2026)</t>
         </is>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
@@ -13454,7 +13453,7 @@
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Rettigheder i den digitale velfaerdsstat, December 2023</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Rettigheder i den digitale velfaerdsstat, December 2023</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr"/>
@@ -13769,7 +13768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -13794,228 +13793,511 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="44" customHeight="1">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
+          <t>PREFIXES: definitions below are written against the DK.* codes. The same definition applies to the identical indicator for any other geography - EU.*, and the member-state codes AT.* through SE.* used in F5_EU27 and F6_ADOPT_BENEFIT. Only the geography changes; the measure and its denominator do not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
           <t>DK.PAY.CASH.POS</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Cash as a share of the NUMBER of payments made at physical points of sale.</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Not a share of value. Excludes e-commerce entirely.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="44" customHeight="1">
-      <c r="A3" s="24" t="inlineStr">
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>DK.PAY.CRD.PHYS</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Physical payment cards as a share of the number of in-store payments.</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Falls partly because wallets replace the physical card, not because card payment declines.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="44" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>DK.PAY.WLT.SHR</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Card-based mobile wallets as a share of the number of in-store payments.</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Wallet payments are card payments. Do not add to the card share.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>DK.PAY.WLT.OWN</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Share of CITIZENS with a wallet solution on their phone.</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Different denominator from the payment-share series. Memo only - deliberately excluded from Figure 2.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>DK.FIN.BRCH</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Number of retail bank branches operated by Danish credit institutions.</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>Consolidation and digitalisation both reduce this. The series alone cannot separate the two causes.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>DK.ECM.IND.BUY</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Individuals who purchased goods or services online in the last 12 months.</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>DENOMINATOR BREAK at 2020: % of individuals before, % of internet users after. Never plot 2019 with later years.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>DK.ECM.ENT.TRN</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>E-commerce sales as a share of total enterprise turnover.</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Measures INTENSITY of online selling, not how many firms sell online. Pair with DK.ECM.ENT.SHR.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="24" t="inlineStr">
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>DK.ECM.ENT.SHR</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Share of enterprises making any e-sales.</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>Measures BREADTH of adoption. Flat breadth with rising intensity means incumbents deepening, not new entrants.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>DK.DGP.EXMP</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Citizens formally exempt from mandatory Digital Post under the statutory exemption regime.</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>An administrative status, not a measure of capability. A citizen may struggle without being exempt.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>DK.DGX.DIFF</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Population estimated to face difficulties using digital public services.</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>A capability estimate, not an administrative count. Much larger than the exemption rate - that gap is the analytical point.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>DK.DGX.JUST</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>Justitia's estimate of the digitally disadvantaged adult population.</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>Think-tank estimate, broadest definition of the five. Cite as an upper bound, not as an official statistic.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>DK.GOV.DPS.CIT</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>eGovernment Benchmark composite score for citizen-facing digital public services.</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>A composite index, not a usage rate. Denmark scores BELOW the EU average despite near-universal mandated use.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>DK.ENV.WEEE</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>Share of collected ICT-related electrical waste recycled or prepared for reuse.</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Covers two WEEE categories only. Denominator is waste COLLECTED, not waste generated.</t>
         </is>
       </c>
     </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>DK.PAY.DIG.POS.NUM, DK.PAY.DIG.POS.VAL</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>Digital share of physical-retail payments, by NUMBER and by VALUE respectively.</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Two different denominators. The value share exceeds the number share because cash survives in small transactions. Never quote one as the other, and never average them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>DK.FIN.INST</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Number of financial institutions (credit institutions) operating in Denmark.</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Base year 1991. Do NOT difference against DK.FIN.BRCH, which starts in 2004 - see F9_CONSOLIDATION.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>DK.FIN.EMP</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>Number of persons employed by Danish banks.</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Base year 1991, so comparable with DK.FIN.INST but NOT with the branch series. Falls far less than institutions - that asymmetry is the finding in F9_CONSOLIDATION, not a data error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>DK.SKL.1624, DK.SKL.2554, DK.SKL.5574
+(EU.SKL.1624, EU.SKL.2554, EU.SKL.5574)</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Individuals with at least basic overall digital skills, by age band. EU.SKL.* are the matching EU-27 comparators.</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Age bands, not a time series - all three are the same reference year. The DIGCOMP methodology was revised in 2021; do not join to pre-2021 skills figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>DK.DGP.EXMP.N</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Citizens formally exempt from Digital Post, as a HEADCOUNT.</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>A count, not a rate. Converting between this and DK.DGP.EXMP requires DK.POP.TOT and an assumption about the 15+ denominator - see 07_LIMITATIONS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>DK.DGP.EXMP.7584, DK.DGP.EXMP.85P</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Digital Post exemption rate within the 75-84 and 85+ age bands.</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Denominator is the age group, not the population. These are far above the headline 4.7% and must not be compared with it directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>DK.DGX.NOUSE</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Individuals who do not use digital public services at all.</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Non-use, not inability. Includes those with no need to transact as well as those unable to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>DK.DGX.DISADV.LO, DK.DGX.DISADV.HI</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>Lower and upper bound of the 'digitally disadvantaged' adult population.</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>A RANGE published as a range. Quote both bounds; citing either alone misrepresents the source's own uncertainty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>DK.POP.TOT</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Resident population of Denmark.</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Used only as a denominator for converting headcounts to rates. Total residents, not the 15+ base the exemption rate actually uses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="44" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>DK.TRU.DPS</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Share of the population expressing trust in digital public solutions.</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Self-reported attitude, not behaviour. High trust coexists with the exclusion measures in F4 - the two are not in contradiction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="44" customHeight="1">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t>DK.TRU.DGP.SEC</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Share of the population perceiving Digital Post as secure.</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Narrower than DK.TRU.DPS: one service, not the whole system. Do not treat the two as one series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="44" customHeight="1">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>DK.ENT.DII</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>SMEs reaching at least basic digital intensity (DII).</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>A composite threshold count of adopted technologies, not an intensity of use. A firm clears it by adopting breadth cheaply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="44" customHeight="1">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>DK.ENT.AI, DK.ENT.AI.LRG, DK.ENT.AI.SME</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Enterprises adopting AI: all, large (250+) and SMEs (10-249).</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>The headline rate is close to the SME rate because SMEs dominate by count. The large-firm gap is the real dispersion - report the split, not just the average.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>DK.GOV.DPS.XB</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>eGovernment Benchmark score for CROSS-BORDER citizen services.</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Scored against a different service basket from DK.GOV.DPS.CIT. Lower is not evidence of decline; it is a different test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="44" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>DK.GOV.DGP.SAVE.PLAN, DK.GOV.DGP.SAVE.VERIF</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Digital Post annual public saving: as projected, and as verifiable by audit.</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>The pair exists to be compared - the verified figure is well under half the projection. Never cite the projection alone as a realised saving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="44" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>DK.SME.SMVD.PROJ, DK.SME.SMVD.INV, DK.SME.SMVD.NOINV</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>SMV:Digital programme: projects supported, and participants who did or did not invest further.</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Self-reported by participants, with no control group. Cannot support a causal claim about the programme - see the withdrawn claim in 07_LIMITATIONS and 08_AI_LOG.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14043,7 +14325,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Every cell below is a live formula over 02_MASTER. No pasted numbers.</t>
         </is>
@@ -14072,483 +14354,483 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Bank branches, 2004</t>
         </is>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004))</f>
         <v/>
       </c>
-      <c r="C5" s="28" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="D5" s="30" t="inlineStr">
         <is>
           <t>Direct lookup from 02_MASTER.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Bank branches, 2024</t>
         </is>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C6" s="28" t="inlineStr">
+      <c r="C6" s="29" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D6" s="29" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>Direct lookup from 02_MASTER.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Branch network change, 2004-2024</t>
         </is>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004)))-1</f>
         <v/>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D7" s="29" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>Headline structural change for Figure 1.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Cash share change, 2017-2025</t>
         </is>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.PAY.CASH.POS",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.PAY.CASH.POS",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"DK.PAY.CASH.POS",'02_MASTER'!$E:$E,2017)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.PAY.CASH.POS",'02_MASTER'!$E:$E,2017))</f>
         <v/>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>pp</t>
         </is>
       </c>
-      <c r="D8" s="29" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>Percentage-point change, not a growth rate - both terms are shares.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Cash share, proportional decline 2017-2025</t>
         </is>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.PAY.CASH.POS",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.PAY.CASH.POS",'02_MASTER'!$E:$E,2025))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.PAY.CASH.POS",'02_MASTER'!$E:$E,2017)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.PAY.CASH.POS",'02_MASTER'!$E:$E,2017)))-1</f>
         <v/>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D9" s="29" t="inlineStr">
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>Cash fell to roughly a third of its 2017 share.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>DK e-sales turnover share, change 2014-2024</t>
         </is>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2014)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2014)))-1</f>
         <v/>
       </c>
-      <c r="C10" s="28" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D10" s="29" t="inlineStr">
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>Tests the 'enterprise plateau' claim. Intensity nearly doubled.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>EU e-sales turnover share, change 2014-2024</t>
         </is>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"EU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))/IF(COUNTIFS('02_MASTER'!$B:$B,"EU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2014)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2014)))-1</f>
         <v/>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D11" s="29" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>Comparator for the line above.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>DK lead over EU on e-sales turnover, 2024</t>
         </is>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))-IF(COUNTIFS('02_MASTER'!$B:$B,"EU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>pp</t>
         </is>
       </c>
-      <c r="D12" s="29" t="inlineStr">
+      <c r="D12" s="30" t="inlineStr">
         <is>
           <t>Denmark's margin over the EU average.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Exclusion ratio: difficulty vs formal exemption</t>
         </is>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.DIFF",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.DIFF",'02_MASTER'!$E:$E,2026))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026))</f>
         <v/>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="D13" s="29" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>How many times larger the capability measure is than the administrative one. The core Q4 statistic.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Citizens struggling but NOT exempt</t>
         </is>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.DIFF",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.DIFF",'02_MASTER'!$E:$E,2026))-IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026))</f>
         <v/>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" s="29" t="inlineStr">
         <is>
           <t>pp</t>
         </is>
       </c>
-      <c r="D14" s="29" t="inlineStr">
+      <c r="D14" s="30" t="inlineStr">
         <is>
           <t>Population facing difficulty without statutory relief.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>Digital skills gap, 16-24 vs 55-74</t>
         </is>
       </c>
-      <c r="B15" s="31">
+      <c r="B15" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.1624",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SKL.5574",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C15" s="28" t="inlineStr">
+      <c r="C15" s="29" t="inlineStr">
         <is>
           <t>pp</t>
         </is>
       </c>
-      <c r="D15" s="29" t="inlineStr">
+      <c r="D15" s="30" t="inlineStr">
         <is>
           <t>Generational gradient in basic digital skills.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>AI adoption gap, large firms vs SMEs</t>
         </is>
       </c>
-      <c r="B16" s="31">
+      <c r="B16" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENT.AI.LRG",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENT.AI.LRG",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENT.AI.SME",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENT.AI.SME",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C16" s="28" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>pp</t>
         </is>
       </c>
-      <c r="D16" s="29" t="inlineStr">
+      <c r="D16" s="30" t="inlineStr">
         <is>
           <t>Depth-of-adoption gap behind the 'breadth without depth' finding.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>DK shortfall vs EU, citizen digital public services</t>
         </is>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"EU.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.GOV.DPS.CIT",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C17" s="28" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t>points</t>
         </is>
       </c>
-      <c r="D17" s="29" t="inlineStr">
+      <c r="D17" s="30" t="inlineStr">
         <is>
           <t>Negative: Denmark scores below the EU average.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>DK shortfall vs EU, ICT waste recycling</t>
         </is>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENV.WEEE",'02_MASTER'!$E:$E,2023)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENV.WEEE",'02_MASTER'!$E:$E,2023))-IF(COUNTIFS('02_MASTER'!$B:$B,"EU.ENV.WEEE",'02_MASTER'!$E:$E,2023)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.ENV.WEEE",'02_MASTER'!$E:$E,2023))</f>
         <v/>
       </c>
-      <c r="C18" s="28" t="inlineStr">
+      <c r="C18" s="29" t="inlineStr">
         <is>
           <t>pp</t>
         </is>
       </c>
-      <c r="D18" s="29" t="inlineStr">
+      <c r="D18" s="30" t="inlineStr">
         <is>
           <t>Negative and large - candidate SDG evidence.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>Trust in digital public solutions, change 2024-2025</t>
         </is>
       </c>
-      <c r="B19" s="31">
+      <c r="B19" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.TRU.DPS",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.TRU.DPS",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"DK.TRU.DPS",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.TRU.DPS",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C19" s="28" t="inlineStr">
+      <c r="C19" s="29" t="inlineStr">
         <is>
           <t>pp</t>
         </is>
       </c>
-      <c r="D19" s="29" t="inlineStr">
+      <c r="D19" s="30" t="inlineStr">
         <is>
           <t>Trust rising while the mandate is in force.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Perceived security of Digital Post, change 2017-2025</t>
         </is>
       </c>
-      <c r="B20" s="31">
+      <c r="B20" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.TRU.DGP.SEC",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.TRU.DGP.SEC",'02_MASTER'!$E:$E,2025))-IF(COUNTIFS('02_MASTER'!$B:$B,"DK.TRU.DGP.SEC",'02_MASTER'!$E:$E,2017)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.TRU.DGP.SEC",'02_MASTER'!$E:$E,2017))</f>
         <v/>
       </c>
-      <c r="C20" s="28" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>pp</t>
         </is>
       </c>
-      <c r="D20" s="29" t="inlineStr">
+      <c r="D20" s="30" t="inlineStr">
         <is>
           <t>Trust in the mandated system over the mandate period (CLO4).</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>Digital Post: projected annual saving</t>
         </is>
       </c>
-      <c r="B21" s="31">
+      <c r="B21" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.PLAN",'02_MASTER'!$E:$E,2016)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.PLAN",'02_MASTER'!$E:$E,2016))</f>
         <v/>
       </c>
-      <c r="C21" s="28" t="inlineStr">
+      <c r="C21" s="29" t="inlineStr">
         <is>
           <t>mDKK/yr</t>
         </is>
       </c>
-      <c r="D21" s="29" t="inlineStr">
+      <c r="D21" s="30" t="inlineStr">
         <is>
           <t>Ministry of Finance business case for the mandate (RR1).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>Digital Post: saving verifiable by audit</t>
         </is>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.VERIF",'02_MASTER'!$E:$E,2016)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.VERIF",'02_MASTER'!$E:$E,2016))</f>
         <v/>
       </c>
-      <c r="C22" s="28" t="inlineStr">
+      <c r="C22" s="29" t="inlineStr">
         <is>
           <t>mDKK/yr</t>
         </is>
       </c>
-      <c r="D22" s="29" t="inlineStr">
+      <c r="D22" s="30" t="inlineStr">
         <is>
           <t>Postage, paper and envelopes only (RR1).</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>Digital Post: unverified share of the business case</t>
         </is>
       </c>
-      <c r="B23" s="30">
+      <c r="B23" s="31">
         <f>1-(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.VERIF",'02_MASTER'!$E:$E,2016)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.VERIF",'02_MASTER'!$E:$E,2016))/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.PLAN",'02_MASTER'!$E:$E,2016)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.PLAN",'02_MASTER'!$E:$E,2016)))</f>
         <v/>
       </c>
-      <c r="C23" s="28" t="inlineStr">
+      <c r="C23" s="29" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D23" s="29" t="inlineStr">
+      <c r="D23" s="30" t="inlineStr">
         <is>
           <t>Over half the projected saving - the wage and overhead component - was never substantiated. The cross-government study intended to test it was abandoned. The strongest cost-side finding in this workbook.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>Digital Post: cost per formally exempt citizen, if the shortfall is real</t>
         </is>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="32">
         <f>((IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.PLAN",'02_MASTER'!$E:$E,2016)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.PLAN",'02_MASTER'!$E:$E,2016))-IF(COUNTIFS('02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.VERIF",'02_MASTER'!$E:$E,2016)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.GOV.DGP.SAVE.VERIF",'02_MASTER'!$E:$E,2016)))*1000000)/IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026))</f>
         <v/>
       </c>
-      <c r="C24" s="28" t="inlineStr">
+      <c r="C24" s="29" t="inlineStr">
         <is>
           <t>DKK</t>
         </is>
       </c>
-      <c r="D24" s="29" t="inlineStr">
+      <c r="D24" s="30" t="inlineStr">
         <is>
           <t>ILLUSTRATIVE ONLY, and not a real unit cost: it divides an unverified saving shortfall by an unrelated headcount. Included because the comparison of magnitudes is informative; it must not be quoted as a cost per person.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>Resident population, 1 January 2026</t>
         </is>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.POP.TOT",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.POP.TOT",'02_MASTER'!$E:$E,2026))</f>
         <v/>
       </c>
-      <c r="C25" s="28" t="inlineStr">
+      <c r="C25" s="29" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D25" s="29" t="inlineStr">
+      <c r="D25" s="30" t="inlineStr">
         <is>
           <t>Direct lookup. The only population level in the workbook (DST2).</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>Citizens formally exempt from Digital Post, Q1 2026</t>
         </is>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026))</f>
         <v/>
       </c>
-      <c r="C26" s="28" t="inlineStr">
+      <c r="C26" s="29" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D26" s="29" t="inlineStr">
+      <c r="D26" s="30" t="inlineStr">
         <is>
           <t>Headcount behind the 4.7% rate (DG1).</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>Change in exempt headcount, 2025 to 2026</t>
         </is>
       </c>
-      <c r="B27" s="27">
+      <c r="B27" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2026))-IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP.N",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
-      <c r="C27" s="28" t="inlineStr">
+      <c r="C27" s="29" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="D27" s="29" t="inlineStr">
+      <c r="D27" s="30" t="inlineStr">
         <is>
           <t>Falling. Note the 2025 figure is an 'approximately' value, so this difference is not precise.</t>
         </is>
@@ -14580,14 +14862,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Series DK.FIN.BRCH. Values are formula lookups from 02_MASTER.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="D3" s="32" t="inlineStr">
+      <c r="D3" s="33" t="inlineStr">
         <is>
           <t>Bank branches in Denmark, 2004-2024</t>
         </is>
@@ -14604,62 +14886,62 @@
           <t>bank branches</t>
         </is>
       </c>
-      <c r="D4" s="25" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>Count of retail branches. Uneven year spacing, numeric X axis.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="n">
+      <c r="A5" s="27" t="n">
         <v>2004</v>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2004))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="27" t="n">
         <v>2006</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2006)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2006))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="27" t="n">
         <v>2010</v>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2010)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2010))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="27" t="n">
         <v>2016</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2016)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2016))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="27" t="n">
         <v>2021</v>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2021)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2021))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="27" t="n">
         <v>2024</v>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="28">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.FIN.BRCH",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
@@ -14701,7 +14983,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Denominator throughout: share of the NUMBER of in-store payments.</t>
         </is>
@@ -14713,7 +14995,7 @@
           <t>Panel A - Cash share of in-store payments</t>
         </is>
       </c>
-      <c r="D4" s="32" t="inlineStr">
+      <c r="D4" s="33" t="inlineStr">
         <is>
           <t>Cash share of in-store payments, 2017-2025</t>
         </is>
@@ -14730,14 +15012,14 @@
           <t>cash (%)</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>% of the number of payments made in physical retail.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="27" t="n">
         <v>2017</v>
       </c>
       <c r="B6" s="35">
@@ -14746,7 +15028,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="27" t="n">
         <v>2023</v>
       </c>
       <c r="B7" s="35">
@@ -14755,7 +15037,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="27" t="n">
         <v>2025</v>
       </c>
       <c r="B8" s="35">
@@ -14769,7 +15051,7 @@
           <t>Panel B - Composition of in-store payments, 2025</t>
         </is>
       </c>
-      <c r="D10" s="32" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>Composition of in-store payments, 2025</t>
         </is>
@@ -14786,14 +15068,14 @@
           <t>share of payments (%)</t>
         </is>
       </c>
-      <c r="D11" s="25" t="inlineStr">
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>Sums to 95%; the residual is other digital instruments.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Physical payment card</t>
         </is>
@@ -14804,7 +15086,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Mobile wallet (card-based)</t>
         </is>
@@ -14815,7 +15097,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
@@ -14845,7 +15127,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="n">
+      <c r="A18" s="27" t="n">
         <v>2019</v>
       </c>
       <c r="B18" s="36">
@@ -14854,7 +15136,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="n">
+      <c r="A19" s="27" t="n">
         <v>2023</v>
       </c>
       <c r="B19" s="36">
@@ -14863,7 +15145,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="n">
+      <c r="A20" s="27" t="n">
         <v>2025</v>
       </c>
       <c r="B20" s="36">
@@ -14969,14 +15251,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Tests the 'enterprise plateau' claim: intensity nearly doubled.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="E3" s="32" t="inlineStr">
+      <c r="E3" s="33" t="inlineStr">
         <is>
           <t>E-sales as % of enterprise turnover, DK vs EU-27</t>
         </is>
@@ -14998,14 +15280,14 @@
           <t>EU-27</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t>Denmark in blue; the EU average in grey.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="n">
+      <c r="A5" s="27" t="n">
         <v>2014</v>
       </c>
       <c r="B5" s="37">
@@ -15018,7 +15300,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="27" t="n">
         <v>2024</v>
       </c>
       <c r="B6" s="37">
@@ -15055,48 +15337,48 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Enterprises making e-sales (%)</t>
         </is>
       </c>
-      <c r="B11" s="38">
+      <c r="B11" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.SHR",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.SHR",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="29" t="inlineStr">
         <is>
           <t>Lithuania 43.03 (highest)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>E-sales share of turnover (%)</t>
         </is>
       </c>
-      <c r="B12" s="38">
+      <c r="B12" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C12" s="28" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>Ireland 38.25 (highest)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>EU average, e-sales share of turnover (%)</t>
         </is>
       </c>
-      <c r="B13" s="38">
+      <c r="B13" s="32">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
         <v/>
       </c>
-      <c r="C13" s="28" t="inlineStr"/>
+      <c r="C13" s="29" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -3927,13 +3927,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="74" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -4483,287 +4483,463 @@
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="27" t="inlineStr">
         <is>
-          <t>Denmark: actual Y</t>
-        </is>
-      </c>
-      <c r="B33" s="32">
-        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+          <t>Slope 95% confidence interval, lower</t>
+        </is>
+      </c>
+      <c r="B33" s="39">
+        <f>SLOPE($D$5:$D$22,$C$5:$C$22)-TINV(0.05,COUNT($C$5:$C$22)-2)*(STEYX($D$5:$D$22,$C$5:$C$22)/SQRT(DEVSQ($C$5:$C$22)))</f>
         <v/>
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>Denmark's observed value.</t>
+          <t>Lower bound. The interval excludes zero, which is the claim the t-statistic makes in interval form.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="27" t="inlineStr">
         <is>
-          <t>Denmark: fitted Y</t>
-        </is>
-      </c>
-      <c r="B34" s="32">
-        <f>INTERCEPT($D$5:$D$22,$C$5:$C$22)+SLOPE($D$5:$D$22,$C$5:$C$22)*IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+          <t>Slope 95% confidence interval, upper</t>
+        </is>
+      </c>
+      <c r="B34" s="39">
+        <f>SLOPE($D$5:$D$22,$C$5:$C$22)+TINV(0.05,COUNT($C$5:$C$22)-2)*(STEYX($D$5:$D$22,$C$5:$C$22)/SQRT(DEVSQ($C$5:$C$22)))</f>
         <v/>
       </c>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>What the line predicts for Denmark's adoption level.</t>
+          <t>Upper bound. Quote the interval, not just the point estimate - on n=18 the point estimate alone overstates what is known.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="27" t="inlineStr">
         <is>
+          <t>Residual standard error (RMSE)</t>
+        </is>
+      </c>
+      <c r="B35" s="32">
+        <f>STEYX($D$5:$D$22,$C$5:$C$22)</f>
+        <v/>
+      </c>
+      <c r="C35" s="30" t="inlineStr">
+        <is>
+          <t>Typical vertical distance of a country from the line. The yardstick for judging whether any one country's residual is unusual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t>Denmark: actual Y</t>
+        </is>
+      </c>
+      <c r="B36" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C36" s="30" t="inlineStr">
+        <is>
+          <t>Denmark's observed value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>Denmark: fitted Y</t>
+        </is>
+      </c>
+      <c r="B37" s="32">
+        <f>INTERCEPT($D$5:$D$22,$C$5:$C$22)+SLOPE($D$5:$D$22,$C$5:$C$22)*IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C37" s="30" t="inlineStr">
+        <is>
+          <t>What the line predicts for Denmark's adoption level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
           <t>Denmark: residual</t>
         </is>
       </c>
-      <c r="B35" s="40">
+      <c r="B38" s="40">
         <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))-(INTERCEPT($D$5:$D$22,$C$5:$C$22)+SLOPE($D$5:$D$22,$C$5:$C$22)*IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)))</f>
         <v/>
       </c>
-      <c r="C35" s="30" t="inlineStr">
-        <is>
-          <t>Positive: Denmark converts adoption into commercial activity better than the EU pattern predicts. Negative: worse.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="C38" s="30" t="inlineStr">
+        <is>
+          <t>Distance from the line, in percentage points. On its own this says little - read the next row instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>Denmark: residual in standard errors</t>
+        </is>
+      </c>
+      <c r="B39" s="40">
+        <f>(IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.ENT.TRN",'02_MASTER'!$E:$E,2024))-(INTERCEPT($D$5:$D$22,$C$5:$C$22)+SLOPE($D$5:$D$22,$C$5:$C$22)*IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))))/STEYX($D$5:$D$22,$C$5:$C$22)</f>
+        <v/>
+      </c>
+      <c r="C39" s="30" t="inlineStr">
+        <is>
+          <t>THE TEST THAT MATTERS. Denmark sits above the line, but by less than one residual standard error, and three countries sit further above it. Denmark is CONSISTENT WITH the EU pattern, not exceptional to it. Do not claim Denmark converts adoption into commercial activity better than the pattern predicts - this figure does not support it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>SAMPLE - how these points were obtained</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="46" customHeight="1">
-      <c r="A38" s="41" t="inlineStr">
-        <is>
-          <t>COMPLETE FOR 2024: the X column is the full Eurostat isoc_ec_ib20 extract for all 27 member states, unrounded, taken from the databrowser. Every member state holding both measures is plotted - 18 of them. No country with both values is excluded, so the fit is no longer conditioned on where a country sits in the ranking.</t>
-        </is>
-      </c>
-      <c r="B38" s="42" t="n"/>
-      <c r="C38" s="42" t="n"/>
-      <c r="D38" s="42" t="n"/>
-    </row>
-    <row r="39" ht="46" customHeight="1">
-      <c r="A39" s="41" t="inlineStr">
-        <is>
-          <t>WHAT THE EARLIER SAMPLE CLAIMED: an earlier version of this figure drew X from a Eurostat press release, which named only the three highest countries, the three lowest and two large movers. On those 6 tail countries the fit was R-squared 0.853 with a slope of +0.655. On the complete cross-section it is R-squared 0.674 with a slope of +0.602.</t>
-        </is>
-      </c>
-      <c r="B39" s="42" t="n"/>
-      <c r="C39" s="42" t="n"/>
-      <c r="D39" s="42" t="n"/>
-    </row>
-    <row r="40" ht="46" customHeight="1">
-      <c r="A40" s="41" t="inlineStr">
-        <is>
-          <t>READING THAT COMPARISON: the slope moved by about 8% while R-squared fell by 0.18. This is the signature of selection on the tails - it widens the spread in X relative to the scatter around the line, which flatters the fit while leaving the estimated relationship roughly intact. The earlier R-squared was an upper bound, as the warning it replaced said; this one is an estimate.</t>
-        </is>
-      </c>
-      <c r="B40" s="42" t="n"/>
-      <c r="C40" s="42" t="n"/>
-      <c r="D40" s="42" t="n"/>
-    </row>
-    <row r="41" ht="46" customHeight="1">
-      <c r="A41" s="41" t="inlineStr">
-        <is>
-          <t>STILL NOT A COMPLETE CROSS-SECTION OF THE EU: nine member states hold the adoption measure but not the enterprise turnover measure and are listed below. The sample is complete with respect to X and incomplete with respect to Y, so it is 18 countries rather than 27 - but the countries dropped are dropped by data availability, not by their position on either axis.</t>
-        </is>
-      </c>
-      <c r="B41" s="42" t="n"/>
-      <c r="C41" s="42" t="n"/>
-      <c r="D41" s="42" t="n"/>
     </row>
     <row r="42" ht="46" customHeight="1">
       <c r="A42" s="41" t="inlineStr">
         <is>
-          <t>DIRECTION OF CAUSATION IS NOT ESTABLISHED AND CANNOT BE. X measures consumers; Y measures enterprises, including business-to-business sales that no consumer touches. Both plausibly rise with national income, which is in neither axis. This figure shows that digital commerce runs deep in the same economies where consumers buy online. It does not show that the one produces the other.</t>
+          <t>COMPLETE FOR 2024: the X column is the full Eurostat isoc_ec_ib20 extract for all 27 member states, unrounded, taken from the databrowser. Every member state holding both measures is plotted - 18 of them. No country with both values is excluded, so the fit is no longer conditioned on where a country sits in the ranking.</t>
         </is>
       </c>
       <c r="B42" s="42" t="n"/>
       <c r="C42" s="42" t="n"/>
       <c r="D42" s="42" t="n"/>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="43" ht="46" customHeight="1">
+      <c r="A43" s="41" t="inlineStr">
+        <is>
+          <t>WHAT THE EARLIER SAMPLE CLAIMED: an earlier version of this figure drew X from a Eurostat press release, which named only the three highest countries, the three lowest and two large movers. On those 6 tail countries the fit was R-squared 0.853 with a slope of +0.655. On the complete cross-section it is R-squared 0.674 with a slope of +0.602.</t>
+        </is>
+      </c>
+      <c r="B43" s="42" t="n"/>
+      <c r="C43" s="42" t="n"/>
+      <c r="D43" s="42" t="n"/>
+    </row>
+    <row r="44" ht="46" customHeight="1">
+      <c r="A44" s="41" t="inlineStr">
+        <is>
+          <t>READING THAT COMPARISON: the slope moved by about 8% while R-squared fell by 0.18. This is the signature of selection on the tails - it widens the spread in X relative to the scatter around the line, which flatters the fit while leaving the estimated relationship roughly intact. The earlier R-squared was an upper bound, as the warning it replaced said; this one is an estimate.</t>
+        </is>
+      </c>
+      <c r="B44" s="42" t="n"/>
+      <c r="C44" s="42" t="n"/>
+      <c r="D44" s="42" t="n"/>
+    </row>
+    <row r="45" ht="46" customHeight="1">
+      <c r="A45" s="41" t="inlineStr">
+        <is>
+          <t>STILL NOT A COMPLETE CROSS-SECTION OF THE EU: nine member states hold the adoption measure but not the enterprise turnover measure and are listed below. The sample is complete with respect to X and incomplete with respect to Y, so it is 18 countries rather than 27 - but the countries dropped are dropped by data availability, not by their position on either axis.</t>
+        </is>
+      </c>
+      <c r="B45" s="42" t="n"/>
+      <c r="C45" s="42" t="n"/>
+      <c r="D45" s="42" t="n"/>
+    </row>
+    <row r="46" ht="46" customHeight="1">
+      <c r="A46" s="41" t="inlineStr">
+        <is>
+          <t>DIRECTION OF CAUSATION IS NOT ESTABLISHED AND CANNOT BE. X measures consumers; Y measures enterprises, including business-to-business sales that no consumer touches. Both plausibly rise with national income, which is in neither axis. This figure shows that digital commerce runs deep in the same economies where consumers buy online. It does not show that the one produces the other.</t>
+        </is>
+      </c>
+      <c r="B46" s="42" t="n"/>
+      <c r="C46" s="42" t="n"/>
+      <c r="D46" s="42" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>AWAITING DATA - not plotted</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>missing</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="27" t="inlineStr">
-        <is>
-          <t>Estonia</t>
-        </is>
-      </c>
-      <c r="B46" s="38" t="inlineStr">
-        <is>
-          <t>EE</t>
-        </is>
-      </c>
-      <c r="C46" s="43" t="inlineStr">
-        <is>
-          <t>Y - add EE.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="27" t="inlineStr">
-        <is>
-          <t>Greece</t>
-        </is>
-      </c>
-      <c r="B47" s="38" t="inlineStr">
-        <is>
-          <t>EL</t>
-        </is>
-      </c>
-      <c r="C47" s="43" t="inlineStr">
-        <is>
-          <t>Y - add EL.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="27" t="inlineStr">
-        <is>
-          <t>Finland</t>
-        </is>
-      </c>
-      <c r="B48" s="38" t="inlineStr">
-        <is>
-          <t>FI</t>
-        </is>
-      </c>
-      <c r="C48" s="43" t="inlineStr">
-        <is>
-          <t>Y - add FI.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="27" t="inlineStr">
-        <is>
-          <t>Lithuania</t>
-        </is>
-      </c>
-      <c r="B49" s="38" t="inlineStr">
-        <is>
-          <t>LT</t>
-        </is>
-      </c>
-      <c r="C49" s="43" t="inlineStr">
-        <is>
-          <t>Y - add LT.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>X: adoption (%)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="27" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B50" s="38" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="C50" s="43" t="inlineStr">
         <is>
-          <t>Y - add LV.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
-        </is>
+          <t>Y - add EE.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+      <c r="D50" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EE.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="27" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="B51" s="38" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="C51" s="43" t="inlineStr">
         <is>
-          <t>Y - add NL.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
-        </is>
+          <t>Y - add EL.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+      <c r="D51" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="27" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B52" s="38" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="C52" s="43" t="inlineStr">
         <is>
-          <t>Y - add PT.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
-        </is>
+          <t>Y - add FI.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+      <c r="D52" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"FI.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"FI.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="27" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B53" s="38" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C53" s="43" t="inlineStr">
         <is>
-          <t>Y - add RO.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
-        </is>
+          <t>Y - add LT.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+      <c r="D53" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"LT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"LT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="27" t="inlineStr">
         <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="B54" s="38" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="C54" s="43" t="inlineStr">
+        <is>
+          <t>Y - add LV.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+      <c r="D54" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"LV.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"LV.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B55" s="38" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C55" s="43" t="inlineStr">
+        <is>
+          <t>Y - add NL.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+      <c r="D55" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"NL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"NL.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="27" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B56" s="38" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="C56" s="43" t="inlineStr">
+        <is>
+          <t>Y - add PT.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+      <c r="D56" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"PT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"PT.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="B57" s="38" t="inlineStr">
+        <is>
+          <t>RO</t>
+        </is>
+      </c>
+      <c r="C57" s="43" t="inlineStr">
+        <is>
+          <t>Y - add RO.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
+        </is>
+      </c>
+      <c r="D57" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"RO.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"RO.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="27" t="inlineStr">
+        <is>
           <t>Slovakia</t>
         </is>
       </c>
-      <c r="B54" s="38" t="inlineStr">
+      <c r="B58" s="38" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="C54" s="43" t="inlineStr">
+      <c r="C58" s="43" t="inlineStr">
         <is>
           <t>Y - add SK.ECM.ENT.TRN for 2024 (Eurostat tin00110)</t>
         </is>
       </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="34" t="inlineStr">
+      <c r="D58" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"SK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"SK.ECM.IND.BUY",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>IS THE MISSINGNESS SELECTIVE?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="27" t="inlineStr">
+        <is>
+          <t>Mean adoption, plotted</t>
+        </is>
+      </c>
+      <c r="B61" s="39">
+        <f>AVERAGE($C$5:$C$22)</f>
+        <v/>
+      </c>
+      <c r="C61" s="30" t="inlineStr">
+        <is>
+          <t>Average X across the countries actually in the regression.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="27" t="inlineStr">
+        <is>
+          <t>Mean adoption, awaiting</t>
+        </is>
+      </c>
+      <c r="B62" s="39">
+        <f>AVERAGE($D$50:$D$58)</f>
+        <v/>
+      </c>
+      <c r="C62" s="30" t="inlineStr">
+        <is>
+          <t>Average X across the countries dropped for want of Y.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="27" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="B63" s="39">
+        <f>AVERAGE($D$50:$D$58)-AVERAGE($C$5:$C$22)</f>
+        <v/>
+      </c>
+      <c r="C63" s="30" t="inlineStr">
+        <is>
+          <t>Percentage points. Near zero is the result you want.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="27" t="inlineStr">
+        <is>
+          <t>p-value, two-sample t-test</t>
+        </is>
+      </c>
+      <c r="B64" s="39">
+        <f>TTEST($C$5:$C$22,$D$50:$D$58,2,2)</f>
+        <v/>
+      </c>
+      <c r="C64" s="30" t="inlineStr">
+        <is>
+          <t>THE TEST. A large p-value means the dropped countries are not distinguishable from the plotted ones on adoption, so the sample is missing on Y availability rather than selected on X. This is what separates this figure from the tail-selected version it replaced - there, selection WAS on the axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="34" t="inlineStr">
         <is>
           <t>Sources: Eurostat isoc_ec_ib20 (ES7) for X; Eurostat tin00110 (ES5, ES6) for Y. WHY A CROSS-SECTION: the Danish adoption and outcome series share almost no observation years - the best time-series pairing in this dataset is n=2 - so a within-Denmark scatter of adoption against outcome cannot be drawn from verified data. SAMPLE: n=18 of 27 member states. This is a small sample; report the association descriptively and do not quote a p-value. Adding the missing values listed above raises n automatically on the next rebuild. WHAT Y MEASURES: tin00110 covers all enterprises with 10+ employees outside the financial sector, so it includes B2B and EDI ordering across every industry, not retail alone. X is a consumer measure. The two sit on different sides of the market, so a positive association is evidence that digital commerce is deep in an economy - not evidence that consumers buying online causes enterprise turnover.</t>
         </is>
@@ -4771,11 +4947,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A43:D43"/>
     <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A44:D44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5866,7 +6042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5890,214 +6066,226 @@
     <row r="4" ht="62" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>No inferential statistics</t>
+          <t>Compiled date is not a per-value retrieval date</t>
         </is>
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>The longest series here has six observations. Regression, cointegration and Granger-causality procedures require far more, and any such result on this dataset would be uninterpretable. The workbook supports description and comparison only. Co-movement between digital payment adoption and branch closures is presented as association, never as measured causation.</t>
+          <t>02_MASTER carries a compiled_date column holding a single build-time constant, identical on all 113 rows. It records when this workbook was generated, NOT when each value was retrieved from its authority - those retrievals were made across several working sessions on different days. The column was named extraction_date until an audit of the generated file found that the name claimed per-observation provenance the data does not hold. It is renamed rather than back-filled, because inventing plausible retrieval dates would be precisely the fabrication this workbook exists to avoid. Recording true retrieval dates requires capturing them at retrieval time, in dataset.py, which is the correct fix and is not retrospective.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Figure 6 tail selection - RESOLVED, and what it cost</t>
+          <t>No inferential statistics</t>
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>The adoption column in Figure 6 was originally assembled from a Eurostat press release naming the highest three countries, the lowest three and two large movers, so most plotted points came from the ends of the EU distribution. Selecting on the extremes of X inflates the correlation coefficient regardless of the underlying relationship, and R-squared was withheld from the chart face for that reason. The column is now the complete isoc_ec_ib20 databrowser extract for all 27 member states, unrounded, so the selection is gone and R-squared is displayed. The measured cost of the bias is retained on F6 because it is informative: on the 6 tail countries the fit was R-squared 0.853 with a slope of +0.655; on the complete cross-section it is R-squared 0.674 with a slope of +0.602. Tail selection barely moved the slope and flattered the fit by 0.18.</t>
+          <t>The longest series here has six observations. Regression, cointegration and Granger-causality procedures require far more, and any such result on this dataset would be uninterpretable. The workbook supports description and comparison only. Co-movement between digital payment adoption and branch closures is presented as association, never as measured causation.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="62" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>No price deflator on the turnover series</t>
+          <t>Figure 6 tail selection - RESOLVED, and what it cost</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>E-sales as a share of enterprise turnover runs 2014 to 2024, spanning the pandemic and the 2022 inflation episode. Turnover is nominal, and online and physical retail did not face the same price path. Part of the measured rise in the e-sales share is therefore relative price movement rather than real reallocation of activity. No deflator was available in this session and none has been applied, so the doubling of intensity should be read as nominal.</t>
+          <t>The adoption column in Figure 6 was originally assembled from a Eurostat press release naming the highest three countries, the lowest three and two large movers, so most plotted points came from the ends of the EU distribution. Selecting on the extremes of X inflates the correlation coefficient regardless of the underlying relationship, and R-squared was withheld from the chart face for that reason. The column is now the complete isoc_ec_ib20 databrowser extract for all 27 member states, unrounded, so the selection is gone and R-squared is displayed. The measured cost of the bias is retained on F6 because it is informative: on the 6 tail countries the fit was R-squared 0.853 with a slope of +0.655; on the complete cross-section it is R-squared 0.674 with a slope of +0.602. Tail selection barely moved the slope and flattered the fit by 0.18.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="62" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Banking series use different base years</t>
+          <t>No price deflator on the turnover series</t>
         </is>
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>This constrains F9_CONSOLIDATION directly: the three percentage changes on that sheet are not measured over a common window, so they must not be differenced against one another. Institutions and employment are comparable to each other, both 1991-2024. Branch counts begin in 2004; institution counts and employment begin in 1991. A 2004-2024 branch change and a 1991-2024 employment change are not comparable, and placing the two percentages side by side in prose would misrepresent both. 05_CALC labels every window explicitly. Either state both windows or do not draw the comparison.</t>
+          <t>E-sales as a share of enterprise turnover runs 2014 to 2024, spanning the pandemic and the 2022 inflation episode. Turnover is nominal, and online and physical retail did not face the same price path. Part of the measured rise in the e-sales share is therefore relative price movement rather than real reallocation of activity. No deflator was available in this session and none has been applied, so the doubling of intensity should be read as nominal.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="62" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>No sampling error is reported anywhere</t>
+          <t>Banking series use different base years</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>The Eurostat, Nationalbank and Agency for Digital Government figures are survey estimates and carry sampling error that the issuing authorities publish but this workbook does not reproduce. Small differences should not be treated as established: a 2-3 point gap between two survey proportions, or between two eGovernment Benchmark scores, may not be distinguishable from zero. Directions are more robust than magnitudes throughout.</t>
+          <t>This constrains F9_CONSOLIDATION directly: the three percentage changes on that sheet are not measured over a common window, so they must not be differenced against one another. Institutions and employment are comparable to each other, both 1991-2024. Branch counts begin in 2004; institution counts and employment begin in 1991. A 2004-2024 branch change and a 1991-2024 employment change are not comparable, and placing the two percentages side by side in prose would misrepresent both. 05_CALC labels every window explicitly. Either state both windows or do not draw the comparison.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="62" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Headcount conversions rest on an implied denominator</t>
+          <t>No sampling error is reported anywhere</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>A published figure for the Danish population aged 15 and over could not be verified in this session. F4 therefore derives an implied 15+ base by dividing the exempt headcount by the exemption rate, both from the same source. Persons-affected figures built on it are orders of magnitude, not counts, and the capability shares they scale are measured on 'the population' rather than on the 15+ base - the denominators are not identical. Every such cell is marked in place.</t>
+          <t>The Eurostat, Nationalbank and Agency for Digital Government figures are survey estimates and carry sampling error that the issuing authorities publish but this workbook does not reproduce. Small differences should not be treated as established: a 2-3 point gap between two survey proportions, or between two eGovernment Benchmark scores, may not be distinguishable from zero. Directions are more robust than magnitudes throughout.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="62" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>A withdrawn claim about SMV:Digital</t>
+          <t>Headcount conversions rest on an implied denominator</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>An earlier draft of this workbook asserted that SMV:Digital was being defunded, and an argument was built on the contrast between a programme that works and a programme being cut. The claim could not be verified. The scheme's own 2026 grant-pool page documents pools still open and a further pool opening on 26 October 2026. The claim has been removed from the dataset and from the report's argument, and the correction is recorded in 09_POLICY and 08_AI_LOG rather than silently erased.</t>
+          <t>A published figure for the Danish population aged 15 and over could not be verified in this session. F4 therefore derives an implied 15+ base by dividing the exempt headcount by the exemption rate, both from the same source. Persons-affected figures built on it are orders of magnitude, not counts, and the capability shares they scale are measured on 'the population' rather than on the 15+ base - the denominators are not identical. Every such cell is marked in place.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="62" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Unbalanced panel</t>
+          <t>A withdrawn claim about SMV:Digital</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>Observation years differ by series because the underlying sources publish on different cycles - payment habits roughly biennially, Eurostat annually, branch counts irregularly. Gaps are genuine and are not filled.</t>
+          <t>An earlier draft of this workbook asserted that SMV:Digital was being defunded, and an argument was built on the contrast between a programme that works and a programme being cut. The claim could not be verified. The scheme's own 2026 grant-pool page documents pools still open and a further pool opening on 26 October 2026. The claim has been removed from the dataset and from the report's argument, and the correction is recorded in 09_POLICY and 08_AI_LOG rather than silently erased.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="62" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Denominator break</t>
+          <t>Unbalanced panel</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Danish online-purchasing figures change base between 2019 (% of individuals) and 2020 onward (% of internet users). The 2019 observation carries flag 'b' and is never plotted with later years.</t>
+          <t>Observation years differ by series because the underlying sources publish on different cycles - payment habits roughly biennially, Eurostat annually, branch counts irregularly. Gaps are genuine and are not filled.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="62" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Verbal quantities</t>
+          <t>Denominator break</t>
         </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>Values flagged 'e' were published as words, not figures - 'nearly one in five', 'just under 36,000'. They are recorded as the stated approximation with the original wording in the notes column.</t>
+          <t>Danish online-purchasing figures change base between 2019 (% of individuals) and 2020 onward (% of internet users). The 2019 observation carries flag 'b' and is never plotted with later years.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="62" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Confounded outcome</t>
+          <t>Verbal quantities</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Branch closures reflect both digitalisation and sectoral consolidation (219 institutions in 1991, 51 in 2024). The branch series alone cannot separate these, and the report should not claim that it does.</t>
+          <t>Values flagged 'e' were published as words, not figures - 'nearly one in five', 'just under 36,000'. They are recorded as the stated approximation with the original wording in the notes column.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="62" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Definitional spread in exclusion measures</t>
+          <t>Confounded outcome</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>The five exclusion measures range from 4.7% to 25% because they define the population differently. They are not competing estimates of one quantity and must not be averaged or presented as a range.</t>
+          <t>Branch closures reflect both digitalisation and sectoral consolidation (219 institutions in 1991, 51 in 2024). The branch series alone cannot separate these, and the report should not claim that it does.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="62" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Cross-section complete on adoption, incomplete on outcome</t>
+          <t>Definitional spread in exclusion measures</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>The adoption measure now covers all 27 member states for 2024, so F5 is a complete EU ranking. The enterprise-turnover measure does not: nine member states hold adoption but not turnover and cannot enter Figure 6. Those nine are dropped by data availability rather than by their position on either axis, which is why the remaining 18 are treated as a usable cross-section.</t>
+          <t>The five exclusion measures range from 4.7% to 25% because they define the population differently. They are not competing estimates of one quantity and must not be averaged or presented as a range.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="62" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Figure 6 sample size</t>
+          <t>Cross-section complete on adoption, incomplete on outcome</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>The adoption-to-outcome scatter rests on 18 complete country pairs, up from 6. That is enough to report a slope with a standard error and a t-statistic, all three of which are on the sheet as live formulas. It is not enough, and no sample size would be enough here, to support a claim about causal direction: this is one year of cross-sectional data with no control for national income. Say n explicitly, report the slope with its standard error, and keep the language associational.</t>
+          <t>The adoption measure now covers all 27 member states for 2024, so F5 is a complete EU ranking. The enterprise-turnover measure does not: nine member states hold adoption but not turnover and cannot enter Figure 6. Those nine are dropped by data availability rather than by their position on either axis, which is why the remaining 18 are treated as a usable cross-section.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="62" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Figure 6 measures two sides of the market</t>
+          <t>Figure 6 sample size</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>X is a consumer measure (individuals buying online); Y is an all-enterprise, all-sector measure that includes B2B and EDI ordering. A positive association indicates that digital commerce runs deep in an economy. It is not evidence that consumer purchasing causes enterprise turnover, and must not be written as though it were.</t>
+          <t>The adoption-to-outcome scatter rests on 18 complete country pairs, up from 6. That is enough to report a slope with a standard error and a t-statistic, all three of which are on the sheet as live formulas. It is not enough, and no sample size would be enough here, to support a claim about causal direction: this is one year of cross-sectional data with no control for national income. Say n explicitly, report the slope with its standard error, and keep the language associational.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="62" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Mirror-sourced column</t>
+          <t>Figure 6 measures two sides of the market</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>The 16 country-level e-sales turnover values flagged 'u' were retrieved via search of Eurostat tin00110 rather than from the databrowser directly. Two values in the same column (EU27 19.49 and Ireland 38.25) are independently corroborated by source ES5, which supports the column, but each value should be spot-checked against the databrowser before final submission.</t>
+          <t>X is a consumer measure (individuals buying online); Y is an all-enterprise, all-sector measure that includes B2B and EDI ordering. A positive association indicates that digital commerce runs deep in an economy. It is not evidence that consumer purchasing causes enterprise turnover, and must not be written as though it were.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="62" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Search-based verification</t>
+          <t>Mirror-sourced column</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Direct access to statistical portals was blocked in the build environment. Values were verified against the issuing authority through search results reporting those publications. This is weaker than downloading the dataset: before final submission, spot-check high-stakes figures against the source pages directly.</t>
+          <t>The 16 country-level e-sales turnover values flagged 'u' were retrieved via search of Eurostat tin00110 rather than from the databrowser directly. Two values in the same column (EU27 19.49 and Ireland 38.25) are independently corroborated by source ES5, which supports the column, but each value should be spot-checked against the databrowser before final submission.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="62" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
+          <t>Search-based verification</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Direct access to statistical portals was blocked in the build environment. Values were verified against the issuing authority through search results reporting those publications. This is weaker than downloading the dataset: before final submission, spot-check high-stakes figures against the source pages directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="62" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>Discarded material</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>An earlier candidate dataset was rejected in full after verification found fabricated values carrying authentic dataset codes and extraction dates - including a Eurostat cross-section that inverted the true EU country ranking. None of it survives in this workbook.</t>
         </is>
@@ -7140,7 +7328,7 @@
       </c>
       <c r="K1" s="8" t="inlineStr">
         <is>
-          <t>extraction_date</t>
+          <t>compiled_date</t>
         </is>
       </c>
       <c r="L1" s="8" t="inlineStr">

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -5186,7 +5186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5199,14 +5199,14 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Figure 8 - SMV:Digital, the one policy with a control group</t>
+          <t>Figure 8 - SMV:Digital participation (not the effect estimate)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>Danmarks Statistik matched-comparison evaluation, June 2025.</t>
+          <t>Danmarks Statistik evaluation, June 2025. The evaluation used a matched comparison; the three values below do not come from it.</t>
         </is>
       </c>
     </row>
@@ -5290,138 +5290,146 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>WHY THIS IS THE STRONGEST EVIDENCE IN THE WORKBOOK</t>
+          <t>WHAT THIS FIGURE SHOWS - AND WHAT IT DOES NOT</t>
         </is>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="34" t="inlineStr">
         <is>
-          <t>The evaluation was carried out by Danmarks Statistik, which compared participating firms against comparable firms that did not participate. Participants showed higher revenue AND higher employment.</t>
+          <t>WHAT THE PLOTTED NUMBERS ARE: participation counts and participant self-reports. 'Invested further' is a share OF PARTICIPANTS, with no comparison group behind it. Read alone, these three values cannot support any causal claim about the programme, and 04_DEFINITIONS says so on the same series.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="34" t="inlineStr">
         <is>
-          <t>That is a comparison group. Nothing else in this workbook has one. Figure 6's cross-section can show that adoption and commercial activity move together across countries; it cannot rule out that richer countries simply do more of both. A matched comparison can.</t>
+          <t>WHAT THE EVALUATION SEPARATELY FOUND: Danmarks Statistik compared participating firms against comparable non-participants and reported higher revenue AND higher employment among participants. That matched comparison is the strongest research DESIGN behind any source in this workbook - Figure 6's cross-section cannot rule out that richer countries simply do more of both, and a matched comparison can.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="34" t="inlineStr">
         <is>
-          <t>LIMIT: the effect sizes are not reproduced here because they were not verified against the evaluation itself. The direction of the finding is sourced; the magnitude is not, and must not be invented.</t>
+          <t>WHY THE TWO ARE KEPT APART: the design belongs to the evaluation, not to these three numbers. Citing the figure as 'the one policy with a control group' - as this sheet's title did until an audit caught it - borrows the evaluation's credibility for values that do not carry it. If the report wants the causal claim, it must cite the evaluation's own effect sizes, which means retrieving and verifying them first.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="34" t="inlineStr">
         <is>
+          <t>LIMIT: the effect sizes are not reproduced here because they were not verified against the evaluation itself. The direction of the finding is sourced; the magnitude is not, and must not be invented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
           <t>LIMIT: participation is voluntary, so selection into the programme by more capable or more ambitious firms is not excluded by matching alone.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>POLICY EVENTS ON THIS SERIES</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>instrument</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>citation</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>source</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="inlineStr">
-        <is>
-          <t>2018-01-01</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>SMV:Digital launched</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>Danish digital growth plan for SMEs</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="inlineStr">
-        <is>
-          <t>DG3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="23" t="inlineStr">
         <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>SMV:Digital launched</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Danish digital growth plan for SMEs</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>DG3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>SMV:Digital grant pools continue</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>Tilskudspuljer i 2026</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>SMV1</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="34" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>Source: Effektmaaling af SMV:Digital, Danmarks Statistik for the Agency for Digital Government, June 2025 (DG3); scheme status from SMV:Digital's 2026 grant-pool page (SMV1).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A14:C14"/>
     <mergeCell ref="A12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -2655,7 +2655,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Denmark: Digital Adoption and Policy Outcomes [data workbook], v1.0, 2026-09-12. Compiled from the sources listed in 03_SOURCES.</t>
+          <t>Denmark: Digital Adoption and Policy Outcomes [data workbook], v1.0, 2026-09-13. Compiled from the sources listed in 03_SOURCES.</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>Lov om betalinger, ss 81</t>
+          <t>Lov om betalinger, § 81</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Danskerne betaler mere digitalt - det goer offline-betalinger endnu vigtigere som beredskab (press release, 26 June 2026)</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Danskerne betaler mere digitalt – det gør offline-betalinger endnu vigtigere som beredskab (press release, 26 June 2026)</t>
         </is>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
@@ -13204,7 +13204,7 @@
       </c>
       <c r="G3" s="15" t="inlineStr">
         <is>
-          <t>Danmarks Nationalbank 2026, Danskerne betaler mere digitalt - det goer offline-betalinger endnu vigtigere som beredskab, press release, 26 June, Danmarks Nationalbank, Copenhagen, accessed 12 September 2026.</t>
+          <t>Danmarks Nationalbank 2026, Danskerne betaler mere digitalt – det gør offline-betalinger endnu vigtigere som beredskab, press release, 26 June, Danmarks Nationalbank, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
@@ -13579,7 +13579,7 @@
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Effektmaaling af SMV:Digital, June 2025</t>
+          <t>Effektmåling af SMV:Digital, June 2025</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr"/>
@@ -13595,7 +13595,7 @@
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen 2025, Effektmaaling af SMV:Digital, prepared by Danmarks Statistik, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
+          <t>Digitaliseringsstyrelsen 2025, Effektmåling af SMV:Digital, prepared by Danmarks Statistik, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
@@ -13649,7 +13649,7 @@
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Rettigheder i den digitale velfaerdsstat, December 2023</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Rettigheder i den digitale velfærdsstat, December 2023</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr"/>
@@ -13719,7 +13719,7 @@
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Beretning om besparelsespotentialet ved obligatorisk Digital Post paa ca. 1 mia. kr. om aaret, January 2016</t>
+          <t>Beretning om besparelsespotentialet ved obligatorisk Digital Post på ca. 1 mia. kr. om året, January 2016</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr"/>
@@ -13735,7 +13735,7 @@
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>Rigsrevisionen 2016, Beretning om besparelsespotentialet ved obligatorisk Digital Post paa ca. 1 mia. kr. om aaret, National Audit Office of Denmark, Copenhagen, accessed 12 September 2026.</t>
+          <t>Rigsrevisionen 2016, Beretning om besparelsespotentialet ved obligatorisk Digital Post på ca. 1 mia. kr. om året, National Audit Office of Denmark, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
@@ -13752,12 +13752,12 @@
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>Kontantreglen - lov om betalinger section 81</t>
+          <t>Kontantreglen – lov om betalinger § 81</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>Lov om betalinger, ss 81</t>
+          <t>Lov om betalinger, § 81</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
@@ -13789,7 +13789,7 @@
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Digital Post - lovgivning, and the MitID transition news archive</t>
+          <t>Digital Post – lovgivning, and the MitID transition news archive</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr"/>
@@ -13805,7 +13805,7 @@
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen 2025, Digital Post - lovgivning, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
+          <t>Digitaliseringsstyrelsen 2025, Digital Post – lovgivning, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
@@ -13929,7 +13929,7 @@
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Detailomsaetningsindeks (retail trade turnover index)</t>
+          <t>Detailomsætningsindeks (retail trade turnover index)</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
-          <t>Danmarks Statistik 2025, Detailomsaetningsindeks, Statistics Denmark, Copenhagen, accessed 12 September 2026.</t>
+          <t>Danmarks Statistik 2025, Detailomsætningsindeks, Statistics Denmark, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>Lov om betalinger, ss 81</t>
+          <t>Lov om betalinger, § 81</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -1,32 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="00_COVER" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="01_README" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="02_MASTER" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="03_SOURCES" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="04_DEFINITIONS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="05_CALC" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="F1_BRANCHES" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="F2_PAYMENTS" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="F3_ESALES" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="F4_EXCLUSION" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="F5_EU27" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="F6_ADOPT_BENEFIT" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="F7_QUALITY" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="F8_SMVDIGITAL" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="F9_CONSOLIDATION" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="F10_SKILLS" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="06_RETAIL_GAP" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="07_LIMITATIONS" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="08_AI_LOG" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="09_POLICY" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_COVER" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_README" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_MASTER" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_SOURCES" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_DEFINITIONS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_CALC" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F1_BRANCHES" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F2_PAYMENTS" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F3_ESALES" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F4_EXCLUSION" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F5_EU27" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F6_ADOPT_BENEFIT" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F7_QUALITY" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F8_SMVDIGITAL" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F9_CONSOLIDATION" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F10_SKILLS" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_RETAIL_GAP" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_LIMITATIONS" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_AI_LOG" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_POLICY" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_MASTER'!$A$1:$L$114</definedName>
@@ -324,7 +324,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <plotArea>
       <scatterChart>
@@ -337,7 +337,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="2E6DB4"/>
               </a:solidFill>
@@ -348,10 +348,10 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="2E6DB4"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -382,8 +382,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -397,7 +397,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -414,8 +414,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -429,7 +429,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -444,7 +444,101 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'F8_SMVDIGITAL'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2E6DB4"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'F8_SMVDIGITAL'!$A$5:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'F8_SMVDIGITAL'!$B$5:$B$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="80"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% of participating enterprises</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <plotArea>
       <barChart>
@@ -459,10 +553,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1F3A5F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -470,10 +564,10 @@
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1F3A5F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -482,10 +576,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1F3A5F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -494,10 +588,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="2E6DB4"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -527,8 +621,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -542,7 +636,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -559,7 +653,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -573,8 +667,8 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <plotArea>
       <barChart>
@@ -589,10 +683,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="2E6DB4"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -617,10 +711,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
-              <a:srgbClr val="A3A3A3"/>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="8F8F8F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -650,8 +744,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -665,7 +759,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -683,8 +777,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -698,7 +792,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -717,7 +811,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <plotArea>
       <scatterChart>
@@ -730,7 +824,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
               <a:solidFill>
                 <a:srgbClr val="2E6DB4"/>
               </a:solidFill>
@@ -741,10 +835,10 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="2E6DB4"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -775,8 +869,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -790,7 +884,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -808,8 +902,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -823,7 +917,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -838,7 +932,7 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <plotArea>
       <barChart>
@@ -853,10 +947,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
-              <a:srgbClr val="A3A3A3"/>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="8F8F8F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -864,10 +958,10 @@
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -876,10 +970,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -888,10 +982,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="2E6DB4"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -921,8 +1015,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -936,7 +1030,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -953,7 +1047,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -968,7 +1062,7 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <plotArea>
       <barChart>
@@ -983,10 +1077,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="2E6DB4"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1011,10 +1105,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
-              <a:srgbClr val="A3A3A3"/>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="8F8F8F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1044,8 +1138,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1059,7 +1153,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -1076,8 +1170,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1091,7 +1185,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -1110,7 +1204,7 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <plotArea>
       <barChart>
@@ -1125,10 +1219,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="2E6DB4"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1157,8 +1251,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1172,7 +1266,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -1189,7 +1283,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -1204,7 +1298,7 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <plotArea>
       <barChart>
@@ -1219,10 +1313,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
-              <a:srgbClr val="A3A3A3"/>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="8F8F8F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1230,10 +1324,10 @@
           <dPt>
             <idx val="0"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1242,10 +1336,10 @@
           <dPt>
             <idx val="1"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1254,10 +1348,10 @@
           <dPt>
             <idx val="2"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="2E6DB4"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1266,10 +1360,10 @@
           <dPt>
             <idx val="3"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1278,10 +1372,10 @@
           <dPt>
             <idx val="4"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1290,10 +1384,10 @@
           <dPt>
             <idx val="5"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1302,10 +1396,10 @@
           <dPt>
             <idx val="6"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1314,10 +1408,10 @@
           <dPt>
             <idx val="7"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1326,10 +1420,10 @@
           <dPt>
             <idx val="8"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1338,10 +1432,10 @@
           <dPt>
             <idx val="9"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1350,10 +1444,10 @@
           <dPt>
             <idx val="10"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1362,10 +1456,10 @@
           <dPt>
             <idx val="11"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1374,10 +1468,10 @@
           <dPt>
             <idx val="12"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1386,10 +1480,10 @@
           <dPt>
             <idx val="13"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1F3A5F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1398,10 +1492,10 @@
           <dPt>
             <idx val="14"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1410,10 +1504,10 @@
           <dPt>
             <idx val="15"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1422,10 +1516,10 @@
           <dPt>
             <idx val="16"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1434,10 +1528,10 @@
           <dPt>
             <idx val="17"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1446,10 +1540,10 @@
           <dPt>
             <idx val="18"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1458,10 +1552,10 @@
           <dPt>
             <idx val="19"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1470,10 +1564,10 @@
           <dPt>
             <idx val="20"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1482,10 +1576,10 @@
           <dPt>
             <idx val="21"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1494,10 +1588,10 @@
           <dPt>
             <idx val="22"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1506,10 +1600,10 @@
           <dPt>
             <idx val="23"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1518,10 +1612,10 @@
           <dPt>
             <idx val="24"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1530,10 +1624,10 @@
           <dPt>
             <idx val="25"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1542,10 +1636,10 @@
           <dPt>
             <idx val="26"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1554,10 +1648,10 @@
           <dPt>
             <idx val="27"/>
             <spPr>
-              <a:solidFill>
-                <a:srgbClr val="A3A3A3"/>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1587,8 +1681,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1602,7 +1696,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -1619,7 +1713,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -1634,7 +1728,7 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <plotArea>
       <scatterChart>
@@ -1647,7 +1741,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1656,10 +1750,10 @@
             <symbol val="circle"/>
             <size val="9"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="2E6DB4"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -1667,7 +1761,7 @@
           </marker>
           <trendline>
             <spPr>
-              <a:ln w="16000">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="16000">
                 <a:solidFill>
                   <a:srgbClr val="1F3A5F"/>
                 </a:solidFill>
@@ -1703,8 +1797,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1718,7 +1812,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -1735,8 +1829,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1750,7 +1844,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -1765,7 +1859,7 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <plotArea>
       <barChart>
@@ -1780,10 +1874,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="2E6DB4"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1808,10 +1902,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
-              <a:srgbClr val="A3A3A3"/>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="8F8F8F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1841,8 +1935,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1856,7 +1950,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -1873,7 +1967,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -1892,37 +1986,48 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <plotArea>
       <barChart>
-        <barDir val="bar"/>
+        <barDir val="col"/>
         <grouping val="clustered"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'F8_SMVDIGITAL'!B4</f>
+              <f>'F7_QUALITY'!B17</f>
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="2E6DB4"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="8F8F8F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'F8_SMVDIGITAL'!$A$5:$A$7</f>
+              <f>'F7_QUALITY'!$A$18:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'F8_SMVDIGITAL'!$B$5:$B$7</f>
+              <f>'F7_QUALITY'!$B$18:$B$20</f>
             </numRef>
           </val>
         </ser>
@@ -1936,25 +2041,10 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>% of participating enterprises / count</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -1968,10 +2058,25 @@
           <orientation val="minMax"/>
         </scaling>
         <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% of enterprises</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:ln>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -1979,6 +2084,10 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -1986,7 +2095,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -2001,9 +2110,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2013,7 +2122,7 @@
 </file>
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -2028,9 +2137,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2040,7 +2149,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>3</col>
@@ -2055,9 +2164,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2077,9 +2186,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2089,7 +2198,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -2104,9 +2213,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2116,7 +2225,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -2131,9 +2240,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2143,7 +2252,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -2158,9 +2267,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2170,7 +2279,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -2185,9 +2294,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2197,7 +2306,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -2212,9 +2321,31 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2224,7 +2355,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -2239,9 +2370,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2251,7 +2382,7 @@
 </file>
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>9</col>
@@ -2266,9 +2397,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -4964,7 +5095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5168,9 +5299,95 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>AI ADOPTION BY FIRM SIZE - who could build on the rail</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>firm size</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>% adopting AI</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>reading</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>All enterprises</t>
+        </is>
+      </c>
+      <c r="B18" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENT.AI",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENT.AI",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C18" s="30" t="inlineStr">
+        <is>
+          <t>Denmark's headline AI adoption rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>Large enterprises</t>
+        </is>
+      </c>
+      <c r="B19" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENT.AI.LRG",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENT.AI.LRG",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>Roughly three in four.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>Small and medium enterprises</t>
+        </is>
+      </c>
+      <c r="B20" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENT.AI.SME",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENT.AI.SME",'02_MASTER'!$E:$E,2025))</f>
+        <v/>
+      </c>
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>Two in five, though 92.45% of them clear the basic digital-intensity threshold. The constraint is complementary capital, not connectivity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>Source: European Commission, Digital Decade 2026 country report for Denmark (EC1). CAUTION: the eGovernment Benchmark is a scored assessment, not a survey proportion, and a 2.4-point difference between two scores should not be read as a precisely measured gap. The direction is the finding; the magnitude is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="F26" s="33" t="inlineStr">
+        <is>
+          <t>AI adoption by firm size, Denmark 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="F27" s="26" t="inlineStr">
+        <is>
+          <t>Large firms against SMEs. The aggregate is greyed because it sits between them by construction.</t>
         </is>
       </c>
     </row>
@@ -5235,34 +5452,34 @@
       </c>
       <c r="E4" s="26" t="inlineStr">
         <is>
-          <t>Participation measures only. No effect size is plotted because none was verified.</t>
+          <t>Shares of the ~7,000 supported projects (count in the table, off-axis). Participation only; no effect size is plotted because none was verified.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="27" t="inlineStr">
         <is>
-          <t>Digitalisation projects supported since 2018</t>
-        </is>
-      </c>
-      <c r="B5" s="28">
-        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SME.SMVD.PROJ",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SME.SMVD.PROJ",'02_MASTER'!$E:$E,2025))</f>
+          <t>Participants investing further during the project</t>
+        </is>
+      </c>
+      <c r="B5" s="35">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SME.SMVD.INV",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SME.SMVD.INV",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
       <c r="C5" s="29" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>% of participants</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="27" t="inlineStr">
         <is>
-          <t>Participants investing further during the project</t>
+          <t>Participants with no further investment plans</t>
         </is>
       </c>
       <c r="B6" s="35">
-        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SME.SMVD.INV",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SME.SMVD.INV",'02_MASTER'!$E:$E,2025))</f>
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SME.SMVD.NOINV",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SME.SMVD.NOINV",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
       <c r="C6" s="29" t="inlineStr">
@@ -5274,16 +5491,16 @@
     <row r="7">
       <c r="A7" s="27" t="inlineStr">
         <is>
-          <t>Participants with no further investment plans</t>
-        </is>
-      </c>
-      <c r="B7" s="35">
-        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SME.SMVD.NOINV",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SME.SMVD.NOINV",'02_MASTER'!$E:$E,2025))</f>
+          <t>Digitalisation projects supported since 2018</t>
+        </is>
+      </c>
+      <c r="B7" s="28">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.SME.SMVD.PROJ",'02_MASTER'!$E:$E,2025)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.SME.SMVD.PROJ",'02_MASTER'!$E:$E,2025))</f>
         <v/>
       </c>
       <c r="C7" s="29" t="inlineStr">
         <is>
-          <t>% of participants</t>
+          <t>count</t>
         </is>
       </c>
     </row>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -29,7 +29,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_POLICY" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_MASTER'!$A$1:$L$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_MASTER'!$A$1:$L$135</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>134</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L114"/>
+  <dimension ref="A1:L135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13298,8 +13298,1016 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="13" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C115" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D115" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E115" s="13" t="n">
+        <v>2005</v>
+      </c>
+      <c r="F115" s="16" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="G115" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H115" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I115" s="13" t="inlineStr"/>
+      <c r="J115" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K115" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L115" s="15" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="13" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C116" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D116" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E116" s="13" t="n">
+        <v>2006</v>
+      </c>
+      <c r="F116" s="16" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="G116" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H116" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I116" s="13" t="inlineStr"/>
+      <c r="J116" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K116" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L116" s="15" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="13" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C117" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D117" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E117" s="13" t="n">
+        <v>2007</v>
+      </c>
+      <c r="F117" s="16" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="G117" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H117" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I117" s="13" t="inlineStr"/>
+      <c r="J117" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K117" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L117" s="15" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="13" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C118" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D118" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E118" s="13" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F118" s="16" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="G118" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H118" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I118" s="13" t="inlineStr"/>
+      <c r="J118" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K118" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L118" s="15" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="13" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C119" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D119" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E119" s="13" t="n">
+        <v>2009</v>
+      </c>
+      <c r="F119" s="16" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="G119" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H119" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I119" s="13" t="inlineStr"/>
+      <c r="J119" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K119" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L119" s="15" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="13" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C120" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D120" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E120" s="13" t="n">
+        <v>2010</v>
+      </c>
+      <c r="F120" s="16" t="n">
+        <v>115</v>
+      </c>
+      <c r="G120" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H120" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I120" s="13" t="inlineStr"/>
+      <c r="J120" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K120" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L120" s="15" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C121" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D121" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E121" s="13" t="n">
+        <v>2011</v>
+      </c>
+      <c r="F121" s="16" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="G121" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H121" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I121" s="13" t="inlineStr"/>
+      <c r="J121" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K121" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L121" s="15" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="13" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C122" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D122" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E122" s="13" t="n">
+        <v>2012</v>
+      </c>
+      <c r="F122" s="16" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="G122" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H122" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I122" s="13" t="inlineStr"/>
+      <c r="J122" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K122" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L122" s="15" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="13" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C123" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D123" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E123" s="13" t="n">
+        <v>2013</v>
+      </c>
+      <c r="F123" s="16" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="G123" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H123" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I123" s="13" t="inlineStr"/>
+      <c r="J123" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K123" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L123" s="15" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="13" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C124" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D124" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E124" s="13" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F124" s="16" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="G124" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H124" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I124" s="13" t="inlineStr"/>
+      <c r="J124" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K124" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L124" s="15" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="13" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C125" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D125" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F125" s="16" t="n">
+        <v>113.9</v>
+      </c>
+      <c r="G125" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H125" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I125" s="13" t="inlineStr"/>
+      <c r="J125" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K125" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L125" s="15" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="13" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C126" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D126" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E126" s="13" t="n">
+        <v>2016</v>
+      </c>
+      <c r="F126" s="16" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="G126" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H126" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I126" s="13" t="inlineStr"/>
+      <c r="J126" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K126" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L126" s="15" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="13" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C127" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D127" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E127" s="13" t="n">
+        <v>2017</v>
+      </c>
+      <c r="F127" s="16" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="G127" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H127" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I127" s="13" t="inlineStr"/>
+      <c r="J127" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K127" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L127" s="15" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="13" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C128" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D128" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E128" s="13" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F128" s="16" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="G128" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H128" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I128" s="13" t="inlineStr"/>
+      <c r="J128" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K128" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L128" s="15" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="13" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C129" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D129" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E129" s="13" t="n">
+        <v>2019</v>
+      </c>
+      <c r="F129" s="16" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="G129" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H129" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I129" s="13" t="inlineStr"/>
+      <c r="J129" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K129" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L129" s="15" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="13" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C130" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D130" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E130" s="13" t="n">
+        <v>2020</v>
+      </c>
+      <c r="F130" s="16" t="n">
+        <v>119.6</v>
+      </c>
+      <c r="G130" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H130" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I130" s="13" t="inlineStr"/>
+      <c r="J130" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K130" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L130" s="15" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="13" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C131" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D131" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E131" s="13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="F131" s="16" t="n">
+        <v>121</v>
+      </c>
+      <c r="G131" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H131" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I131" s="13" t="inlineStr"/>
+      <c r="J131" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K131" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L131" s="15" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="13" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C132" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D132" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E132" s="13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="F132" s="16" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="G132" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H132" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I132" s="13" t="inlineStr"/>
+      <c r="J132" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K132" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L132" s="15" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="13" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C133" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D133" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E133" s="13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F133" s="16" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="G133" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H133" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I133" s="13" t="inlineStr"/>
+      <c r="J133" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K133" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L133" s="15" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="13" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C134" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D134" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E134" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F134" s="16" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="G134" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H134" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I134" s="13" t="inlineStr"/>
+      <c r="J134" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K134" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L134" s="15" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="13" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C135" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D135" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E135" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F135" s="16" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="G135" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H135" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I135" s="13" t="inlineStr"/>
+      <c r="J135" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K135" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L135" s="15" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L114"/>
+  <autoFilter ref="A1:L135"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13310,7 +14318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14170,6 +15178,43 @@
         </is>
       </c>
     </row>
+    <row r="25" ht="46" customHeight="1">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>Eurostat</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Labour productivity per person employed and hour worked (EU27_2020=100) - custom extraction, nominal labour productivity per person, Denmark, 2005-2025</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>tesem160</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>https://ec.europa.eu/eurostat/databrowser/view/tesem160/default/table?lang=en</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>13 September 2026</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>Eurostat 2026, Labour productivity per person employed and hour worked (EU27_2020=100), dataset tesem160, last updated 9 September 2026, Eurostat, accessed 13 September 2026, &lt;https://ec.europa.eu/eurostat/databrowser/view/tesem160/default/table?lang=en&gt;.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14181,7 +15226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -14284,424 +15329,441 @@
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>DK.FIN.BRCH</t>
+          <t>DK.PRD.LP.PER</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Number of retail bank branches operated by Danish credit institutions.</t>
+          <t>Nominal labour productivity per person employed, indexed so that the EU27 (2020 composition) equals 100 in each year.</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Consolidation and digitalisation both reduce this. The series alone cannot separate the two causes.</t>
+          <t>RELATIVE measure. A rise means Denmark gained ON THE EU AVERAGE; it is not a Danish growth rate and must never be read as one. Per PERSON, so it is sensitive to part-time work - the per-HOUR variant is the cleaner productivity measure. Current prices in PPS, so nominal.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>DK.ECM.IND.BUY</t>
+          <t>DK.FIN.BRCH</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Individuals who purchased goods or services online in the last 12 months.</t>
+          <t>Number of retail bank branches operated by Danish credit institutions.</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>DENOMINATOR BREAK at 2020: % of individuals before, % of internet users after. Never plot 2019 with later years.</t>
+          <t>Consolidation and digitalisation both reduce this. The series alone cannot separate the two causes.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>DK.ECM.ENT.TRN</t>
+          <t>DK.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>E-commerce sales as a share of total enterprise turnover.</t>
+          <t>Individuals who purchased goods or services online in the last 12 months.</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>Measures INTENSITY of online selling, not how many firms sell online. Pair with DK.ECM.ENT.SHR.</t>
+          <t>DENOMINATOR BREAK at 2020: % of individuals before, % of internet users after. Never plot 2019 with later years.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="25" t="inlineStr">
         <is>
-          <t>DK.ECM.ENT.SHR</t>
+          <t>DK.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Share of enterprises making any e-sales.</t>
+          <t>E-commerce sales as a share of total enterprise turnover.</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Measures BREADTH of adoption. Flat breadth with rising intensity means incumbents deepening, not new entrants.</t>
+          <t>Measures INTENSITY of online selling, not how many firms sell online. Pair with DK.ECM.ENT.SHR.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>DK.DGP.EXMP</t>
+          <t>DK.ECM.ENT.SHR</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Citizens formally exempt from mandatory Digital Post under the statutory exemption regime.</t>
+          <t>Share of enterprises making any e-sales.</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>An administrative status, not a measure of capability. A citizen may struggle without being exempt.</t>
+          <t>Measures BREADTH of adoption. Flat breadth with rising intensity means incumbents deepening, not new entrants.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>DK.DGX.DIFF</t>
+          <t>DK.DGP.EXMP</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Population estimated to face difficulties using digital public services.</t>
+          <t>Citizens formally exempt from mandatory Digital Post under the statutory exemption regime.</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>A capability estimate, not an administrative count. Much larger than the exemption rate - that gap is the analytical point.</t>
+          <t>An administrative status, not a measure of capability. A citizen may struggle without being exempt.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>DK.DGX.JUST</t>
+          <t>DK.DGX.DIFF</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Justitia's estimate of the digitally disadvantaged adult population.</t>
+          <t>Population estimated to face difficulties using digital public services.</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>Think-tank estimate, broadest definition of the five. Cite as an upper bound, not as an official statistic.</t>
+          <t>A capability estimate, not an administrative count. Much larger than the exemption rate - that gap is the analytical point.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>DK.GOV.DPS.CIT</t>
+          <t>DK.DGX.JUST</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>eGovernment Benchmark composite score for citizen-facing digital public services.</t>
+          <t>Justitia's estimate of the digitally disadvantaged adult population.</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>A composite index, not a usage rate. Denmark scores BELOW the EU average despite near-universal mandated use.</t>
+          <t>Think-tank estimate, broadest definition of the five. Cite as an upper bound, not as an official statistic.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="25" t="inlineStr">
         <is>
-          <t>DK.ENV.WEEE</t>
+          <t>DK.GOV.DPS.CIT</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Share of collected ICT-related electrical waste recycled or prepared for reuse.</t>
+          <t>eGovernment Benchmark composite score for citizen-facing digital public services.</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>Covers two WEEE categories only. Denominator is waste COLLECTED, not waste generated.</t>
+          <t>A composite index, not a usage rate. Denmark scores BELOW the EU average despite near-universal mandated use.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="25" t="inlineStr">
         <is>
-          <t>DK.PAY.DIG.POS.NUM, DK.PAY.DIG.POS.VAL</t>
+          <t>DK.ENV.WEEE</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Digital share of physical-retail payments, by NUMBER and by VALUE respectively.</t>
+          <t>Share of collected ICT-related electrical waste recycled or prepared for reuse.</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Two different denominators. The value share exceeds the number share because cash survives in small transactions. Never quote one as the other, and never average them.</t>
+          <t>Covers two WEEE categories only. Denominator is waste COLLECTED, not waste generated.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="25" t="inlineStr">
         <is>
-          <t>DK.FIN.INST</t>
+          <t>DK.PAY.DIG.POS.NUM, DK.PAY.DIG.POS.VAL</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Number of financial institutions (credit institutions) operating in Denmark.</t>
+          <t>Digital share of physical-retail payments, by NUMBER and by VALUE respectively.</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>Base year 1991. Do NOT difference against DK.FIN.BRCH, which starts in 2004 - see F9_CONSOLIDATION.</t>
+          <t>Two different denominators. The value share exceeds the number share because cash survives in small transactions. Never quote one as the other, and never average them.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="25" t="inlineStr">
         <is>
-          <t>DK.FIN.EMP</t>
+          <t>DK.FIN.INST</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>Number of persons employed by Danish banks.</t>
+          <t>Number of financial institutions (credit institutions) operating in Denmark.</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Base year 1991, so comparable with DK.FIN.INST but NOT with the branch series. Falls far less than institutions - that asymmetry is the finding in F9_CONSOLIDATION, not a data error.</t>
+          <t>Base year 1991. Do NOT difference against DK.FIN.BRCH, which starts in 2004 - see F9_CONSOLIDATION.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="25" t="inlineStr">
         <is>
+          <t>DK.FIN.EMP</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>Number of persons employed by Danish banks.</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Base year 1991, so comparable with DK.FIN.INST but NOT with the branch series. Falls far less than institutions - that asymmetry is the finding in F9_CONSOLIDATION, not a data error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
           <t>DK.SKL.1624, DK.SKL.2554, DK.SKL.5574
 (EU.SKL.1624, EU.SKL.2554, EU.SKL.5574)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>Individuals with at least basic overall digital skills, by age band. EU.SKL.* are the matching EU-27 comparators.</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>Age bands, not a time series - all three are the same reference year. The DIGCOMP methodology was revised in 2021; do not join to pre-2021 skills figures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>DK.DGP.EXMP.N</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>Citizens formally exempt from Digital Post, as a HEADCOUNT.</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>A count, not a rate. Converting between this and DK.DGP.EXMP requires DK.POP.TOT and an assumption about the 15+ denominator - see 07_LIMITATIONS.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="25" t="inlineStr">
         <is>
-          <t>DK.DGP.EXMP.7584, DK.DGP.EXMP.85P</t>
+          <t>DK.DGP.EXMP.N</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>Digital Post exemption rate within the 75-84 and 85+ age bands.</t>
+          <t>Citizens formally exempt from Digital Post, as a HEADCOUNT.</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>Denominator is the age group, not the population. These are far above the headline 4.7% and must not be compared with it directly.</t>
+          <t>A count, not a rate. Converting between this and DK.DGP.EXMP requires DK.POP.TOT and an assumption about the 15+ denominator - see 07_LIMITATIONS.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>DK.DGX.NOUSE</t>
+          <t>DK.DGP.EXMP.7584, DK.DGP.EXMP.85P</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Individuals who do not use digital public services at all.</t>
+          <t>Digital Post exemption rate within the 75-84 and 85+ age bands.</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Non-use, not inability. Includes those with no need to transact as well as those unable to.</t>
+          <t>Denominator is the age group, not the population. These are far above the headline 4.7% and must not be compared with it directly.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="25" t="inlineStr">
         <is>
-          <t>DK.DGX.DISADV.LO, DK.DGX.DISADV.HI</t>
+          <t>DK.DGX.NOUSE</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Lower and upper bound of the 'digitally disadvantaged' adult population.</t>
+          <t>Individuals who do not use digital public services at all.</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>A RANGE published as a range. Quote both bounds; citing either alone misrepresents the source's own uncertainty.</t>
+          <t>Non-use, not inability. Includes those with no need to transact as well as those unable to.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>DK.POP.TOT</t>
+          <t>DK.DGX.DISADV.LO, DK.DGX.DISADV.HI</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Resident population of Denmark.</t>
+          <t>Lower and upper bound of the 'digitally disadvantaged' adult population.</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Used only as a denominator for converting headcounts to rates. Total residents, not the 15+ base the exemption rate actually uses.</t>
+          <t>A RANGE published as a range. Quote both bounds; citing either alone misrepresents the source's own uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t>DK.TRU.DPS</t>
+          <t>DK.POP.TOT</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Share of the population expressing trust in digital public solutions.</t>
+          <t>Resident population of Denmark.</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Self-reported attitude, not behaviour. High trust coexists with the exclusion measures in F4 - the two are not in contradiction.</t>
+          <t>Used only as a denominator for converting headcounts to rates. Total residents, not the 15+ base the exemption rate actually uses.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t>DK.TRU.DGP.SEC</t>
+          <t>DK.TRU.DPS</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Share of the population perceiving Digital Post as secure.</t>
+          <t>Share of the population expressing trust in digital public solutions.</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Narrower than DK.TRU.DPS: one service, not the whole system. Do not treat the two as one series.</t>
+          <t>Self-reported attitude, not behaviour. High trust coexists with the exclusion measures in F4 - the two are not in contradiction.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="44" customHeight="1">
       <c r="A27" s="25" t="inlineStr">
         <is>
-          <t>DK.ENT.DII</t>
+          <t>DK.TRU.DGP.SEC</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>SMEs reaching at least basic digital intensity (DII).</t>
+          <t>Share of the population perceiving Digital Post as secure.</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>A composite threshold count of adopted technologies, not an intensity of use. A firm clears it by adopting breadth cheaply.</t>
+          <t>Narrower than DK.TRU.DPS: one service, not the whole system. Do not treat the two as one series.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="25" t="inlineStr">
         <is>
-          <t>DK.ENT.AI, DK.ENT.AI.LRG, DK.ENT.AI.SME</t>
+          <t>DK.ENT.DII</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Enterprises adopting AI: all, large (250+) and SMEs (10-249).</t>
+          <t>SMEs reaching at least basic digital intensity (DII).</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>The headline rate is close to the SME rate because SMEs dominate by count. The large-firm gap is the real dispersion - report the split, not just the average.</t>
+          <t>A composite threshold count of adopted technologies, not an intensity of use. A firm clears it by adopting breadth cheaply.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="44" customHeight="1">
       <c r="A29" s="25" t="inlineStr">
         <is>
-          <t>DK.GOV.DPS.XB</t>
+          <t>DK.ENT.AI, DK.ENT.AI.LRG, DK.ENT.AI.SME</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>eGovernment Benchmark score for CROSS-BORDER citizen services.</t>
+          <t>Enterprises adopting AI: all, large (250+) and SMEs (10-249).</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>Scored against a different service basket from DK.GOV.DPS.CIT. Lower is not evidence of decline; it is a different test.</t>
+          <t>The headline rate is close to the SME rate because SMEs dominate by count. The large-firm gap is the real dispersion - report the split, not just the average.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="44" customHeight="1">
       <c r="A30" s="25" t="inlineStr">
         <is>
-          <t>DK.GOV.DGP.SAVE.PLAN, DK.GOV.DGP.SAVE.VERIF</t>
+          <t>DK.GOV.DPS.XB</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Digital Post annual public saving: as projected, and as verifiable by audit.</t>
+          <t>eGovernment Benchmark score for CROSS-BORDER citizen services.</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>The pair exists to be compared - the verified figure is well under half the projection. Never cite the projection alone as a realised saving.</t>
+          <t>Scored against a different service basket from DK.GOV.DPS.CIT. Lower is not evidence of decline; it is a different test.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="44" customHeight="1">
       <c r="A31" s="25" t="inlineStr">
         <is>
+          <t>DK.GOV.DGP.SAVE.PLAN, DK.GOV.DGP.SAVE.VERIF</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Digital Post annual public saving: as projected, and as verifiable by audit.</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>The pair exists to be compared - the verified figure is well under half the projection. Never cite the projection alone as a realised saving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="44" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
           <t>DK.SME.SMVD.PROJ, DK.SME.SMVD.INV, DK.SME.SMVD.NOINV</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>SMV:Digital programme: projects supported, and participants who did or did not invest further.</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C32" s="15" t="inlineStr">
         <is>
           <t>Self-reported by participants, with no control group. Cannot support a causal claim about the programme - see the withdrawn claim in 07_LIMITATIONS and 08_AI_LOG.</t>
         </is>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -14318,7 +14318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -15212,6 +15212,191 @@
       <c r="G25" s="15" t="inlineStr">
         <is>
           <t>Eurostat 2026, Labour productivity per person employed and hour worked (EU27_2020=100), dataset tesem160, last updated 9 September 2026, Eurostat, accessed 13 September 2026, &lt;https://ec.europa.eu/eurostat/databrowser/view/tesem160/default/table?lang=en&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="46" customHeight="1">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>LOV1</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Folketinget</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Lov om fravigelse fra obligatorisk digital selvbetjening (Act on derogation from mandatory digital self-service)</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>LOV nr 603 af 31/05/2023</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>https://www.retsinformation.dk/eli/lta/2023/603</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>13 September 2026</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>Folketinget 2023, Lov om fravigelse fra obligatorisk digital selvbetjening, LOV nr 603 af 31. maj 2023, in force 1 June 2023, Retsinformation, accessed 13 September 2026, &lt;https://www.retsinformation.dk/eli/lta/2023/603&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="46" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>DG5</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>Digitaliseringsstyrelsen</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Effektmaaling af SMV:Digital - register-based effect measurement of grant recipients against a matched control group, with accompanying method note</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>Effektmaaling 2025</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>https://digst.dk/media/yz2ouzzz/effektmaaling-af-smvdigital-2025.pdf</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>13 September 2026</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>Digitaliseringsstyrelsen 2025, Effektmaaling af SMV:Digital, June 2025, Agency for Digital Government, accessed 13 September 2026, &lt;https://digst.dk/media/yz2ouzzz/effektmaaling-af-smvdigital-2025.pdf&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="46" customHeight="1">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>BRH1</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Bundesrechnungshof</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Bemerkungen 2022 zur Haushalts- und Wirtschaftsfuehrung des Bundes - findings on the Digital Jetzt lottery allocation</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>Bemerkungen 2022</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>13 September 2026</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>Bundesrechnungshof 2022, Bemerkungen 2022 zur Haushalts- und Wirtschaftsfuehrung des Bundes, German Federal Court of Auditors, accessed 13 September 2026, &lt;https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="46" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>CE1</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>Conseil d'Etat (France)</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Decision No. 452798 - partial annulment of the ANEF decree mandating online-only residence permit applications</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>No. 452798</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>13 September 2026</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>Conseil d'Etat 2022, Decision No. 452798, 3 June 2022, Conseil d'Etat, Paris, accessed 13 September 2026, &lt;https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="46" customHeight="1">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>BE1</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>Cour constitutionnelle (Belgium)</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Arret no. 126/2025 - Brussels Digital ordinance; cumulative non-digital access guarantees</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>ECLI:BE:GHCC:2025:ARR.126</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>https://fr.const-court.be/public/f/2025/2025-126f.pdf</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>13 September 2026</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>Cour constitutionnelle 2025, Arret no. 126/2025, 25 September 2025, ECLI:BE:GHCC:2025:ARR.126, Cour constitutionnelle, Brussels, accessed 13 September 2026, &lt;https://fr.const-court.be/public/f/2025/2025-126f.pdf&gt;.</t>
         </is>
       </c>
     </row>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -14413,7 +14413,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Danskerne betaler mere digitalt – det gør offline-betalinger endnu vigtigere som beredskab (press release, 26 June 2026)</t>
+          <t>Danskerne betaler mere digitalt – det gør offline-betalinger endnu vigtigere som beredskab (press release, 26 June 2026)</t>
         </is>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Rettigheder i den digitale velfærdsstat, December 2023</t>
+          <t>Rettigheder i den digitale velfærdsstat, December 2023</t>
         </is>
       </c>
       <c r="D16" s="15" t="inlineStr"/>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -14318,7 +14318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -15397,6 +15397,191 @@
       <c r="G30" s="15" t="inlineStr">
         <is>
           <t>Cour constitutionnelle 2025, Arret no. 126/2025, 25 September 2025, ECLI:BE:GHCC:2025:ARR.126, Cour constitutionnelle, Brussels, accessed 13 September 2026, &lt;https://fr.const-court.be/public/f/2025/2025-126f.pdf&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="46" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>OMB1</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>Folketingets Ombudsmand</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Offentlig Digital Post skal indrettes i overensstemmelse med de almindelige forvaltningsretlige krav</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>FOB 2015-22</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>https://www.ombudsmanden.dk/find-viden/udtalelser/2015/2015-22</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>13 September 2026</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>Folketingets Ombudsmand 2015, Offentlig Digital Post skal indrettes i overensstemmelse med de almindelige forvaltningsretlige krav, FOB 2015-22, Parliamentary Ombudsman, Copenhagen, accessed 13 September 2026, &lt;https://www.ombudsmanden.dk/find-viden/udtalelser/2015/2015-22&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="46" customHeight="1">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>OMB2</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Folketingets Ombudsmand</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Klage har foert til ny praksis i forhold til sene digitale klager - complaint sent through Digital Post at 23:43 on the deadline day</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>News item, 2024</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>https://www.ombudsmanden.dk/find-viden/nyheder/2024/klage-har-foert-til-ny-praksis-i-forhold-til-sene-digitale-klager</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>13 September 2026</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>Folketingets Ombudsmand 2024, Klage har foert til ny praksis i forhold til sene digitale klager, Parliamentary Ombudsman, Copenhagen, accessed 13 September 2026, &lt;https://www.ombudsmanden.dk/find-viden/nyheder/2024/klage-har-foert-til-ny-praksis-i-forhold-til-sene-digitale-klager&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="46" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>NO1</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Digitaliseringsdirektoratet (Digdir)</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Kontakt- og reservasjonsregisteret and the statutory right to opt out of digital communication under eForvaltningsforskriften</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>KRR</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>13 September 2026</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>Digitaliseringsdirektoratet 2025, Kontakt- og reservasjonsregisteret, Norwegian Digitalisation Agency, accessed 13 September 2026, &lt;https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865&gt;.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="46" customHeight="1">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>HOW1</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Howell, S.T.</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Financing Innovation: Evidence from R&amp;D Grants</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>American Economic Review 107(4)</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>https://www.aeaweb.org/articles?id=10.1257%2Faer.20150808</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>13 September 2026</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>Howell, ST 2017, 'Financing innovation: evidence from R&amp;D grants', American Economic Review, vol. 107, no. 4, pp. 1136-1164.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="46" customHeight="1">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>SAN1</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Santoleri, P., Barrows, G., Caravella, S., Crespi, F. and Pellegrino, G.</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] The Causal Effects of R&amp;D Grants: Evidence from a Regression Discontinuity - the Horizon 2020 SME Instrument scoring threshold</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>Working paper</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>https://pietrosantoleri.github.io/files/Santoleri_et_al_The_effects_of_R_D_grants.pdf</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>13 September 2026</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>Santoleri, P, Barrows, G, Caravella, S, Crespi, F and Pellegrino, G 2022, The causal effects of R&amp;D grants: evidence from a regression discontinuity, working paper, accessed 13 September 2026, &lt;https://pietrosantoleri.github.io/files/Santoleri_et_al_The_effects_of_R_D_grants.pdf&gt;.</t>
         </is>
       </c>
     </row>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -15265,12 +15265,12 @@
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Effektmaaling af SMV:Digital - register-based effect measurement of grant recipients against a matched control group, with accompanying method note</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Effektmåling af SMV:Digital - register-based effect measurement of grant recipients against a matched control group, with accompanying method note</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>Effektmaaling 2025</t>
+          <t>Effektmåling 2025</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
@@ -15285,7 +15285,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen 2025, Effektmaaling af SMV:Digital, June 2025, Agency for Digital Government, accessed 13 September 2026, &lt;https://digst.dk/media/yz2ouzzz/effektmaaling-af-smvdigital-2025.pdf&gt;.</t>
+          <t>Digitaliseringsstyrelsen 2025, Effektmåling af SMV:Digital, June 2025, Agency for Digital Government, accessed 13 September 2026, &lt;https://digst.dk/media/yz2ouzzz/effektmaaling-af-smvdigital-2025.pdf&gt;.</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Bemerkungen 2022 zur Haushalts- und Wirtschaftsfuehrung des Bundes - findings on the Digital Jetzt lottery allocation</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes - findings on the Digital Jetzt lottery allocation</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
@@ -15322,7 +15322,7 @@
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
-          <t>Bundesrechnungshof 2022, Bemerkungen 2022 zur Haushalts- und Wirtschaftsfuehrung des Bundes, German Federal Court of Auditors, accessed 13 September 2026, &lt;https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html&gt;.</t>
+          <t>Bundesrechnungshof 2022, Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes, German Federal Court of Auditors, accessed 13 September 2026, &lt;https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html&gt;.</t>
         </is>
       </c>
     </row>
@@ -15334,7 +15334,7 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Conseil d'Etat (France)</t>
+          <t>Conseil d'État (France)</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
@@ -15359,7 +15359,7 @@
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
-          <t>Conseil d'Etat 2022, Decision No. 452798, 3 June 2022, Conseil d'Etat, Paris, accessed 13 September 2026, &lt;https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798&gt;.</t>
+          <t>Conseil d'État 2022, Decision No. 452798, 3 June 2022, Conseil d'État, Paris, accessed 13 September 2026, &lt;https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798&gt;.</t>
         </is>
       </c>
     </row>
@@ -15376,7 +15376,7 @@
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Arret no. 126/2025 - Brussels Digital ordinance; cumulative non-digital access guarantees</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Arrêt no. 126/2025 - Brussels Digital ordinance; cumulative non-digital access guarantees</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
-          <t>Cour constitutionnelle 2025, Arret no. 126/2025, 25 September 2025, ECLI:BE:GHCC:2025:ARR.126, Cour constitutionnelle, Brussels, accessed 13 September 2026, &lt;https://fr.const-court.be/public/f/2025/2025-126f.pdf&gt;.</t>
+          <t>Cour constitutionnelle 2025, Arrêt no. 126/2025, 25 September 2025, ECLI:BE:GHCC:2025:ARR.126, Cour constitutionnelle, Brussels, accessed 13 September 2026, &lt;https://fr.const-court.be/public/f/2025/2025-126f.pdf&gt;.</t>
         </is>
       </c>
     </row>
@@ -15450,7 +15450,7 @@
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Klage har foert til ny praksis i forhold til sene digitale klager - complaint sent through Digital Post at 23:43 on the deadline day</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Klage har ført til ny praksis i forhold til sene digitale klager - complaint sent through Digital Post at 23:43 on the deadline day</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="G32" s="15" t="inlineStr">
         <is>
-          <t>Folketingets Ombudsmand 2024, Klage har foert til ny praksis i forhold til sene digitale klager, Parliamentary Ombudsman, Copenhagen, accessed 13 September 2026, &lt;https://www.ombudsmanden.dk/find-viden/nyheder/2024/klage-har-foert-til-ny-praksis-i-forhold-til-sene-digitale-klager&gt;.</t>
+          <t>Folketingets Ombudsmand 2024, Klage har ført til ny praksis i forhold til sene digitale klager, Parliamentary Ombudsman, Copenhagen, accessed 13 September 2026, &lt;https://www.ombudsmanden.dk/find-viden/nyheder/2024/klage-har-foert-til-ny-praksis-i-forhold-til-sene-digitale-klager&gt;.</t>
         </is>
       </c>
     </row>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -2786,7 +2786,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Denmark: Digital Adoption and Policy Outcomes [data workbook], v1.0, 2026-09-13. Compiled from the sources listed in 03_SOURCES.</t>
+          <t>Denmark: Digital Adoption and Policy Outcomes [data workbook], v1.0, 2026-09-14. Compiled from the sources listed in 03_SOURCES.</t>
         </is>
       </c>
     </row>
@@ -14318,7 +14318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14403,23 +14403,23 @@
     <row r="3" ht="46" customHeight="1">
       <c r="A3" s="23" t="inlineStr">
         <is>
-          <t>NB2</t>
+          <t>FD1</t>
         </is>
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>Danmarks Nationalbank</t>
+          <t>Finans Danmark</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>Danskerne betaler mere digitalt – det gør offline-betalinger endnu vigtigere som beredskab (press release, 26 June 2026)</t>
+          <t>Institutter, filialer &amp; ansatte</t>
         </is>
       </c>
       <c r="D3" s="15" t="inlineStr"/>
       <c r="E3" s="15" t="inlineStr">
         <is>
-          <t>https://www.nationalbanken.dk/da/viden-og-nyheder/presse/arkiv/2026/danskerne-betaler-mere-digitalt-det-goer-offline-betalinger-endnu-vigtigere-som-beredskab-26-06-2026</t>
+          <t>https://finansdanmark.dk/tal-og-data/institutter-filialer-ansatte/</t>
         </is>
       </c>
       <c r="F3" s="15" t="inlineStr">
@@ -14429,30 +14429,34 @@
       </c>
       <c r="G3" s="15" t="inlineStr">
         <is>
-          <t>Danmarks Nationalbank 2026, Danskerne betaler mere digitalt – det gør offline-betalinger endnu vigtigere som beredskab, press release, 26 June, Danmarks Nationalbank, Copenhagen, accessed 12 September 2026.</t>
+          <t>Finans Danmark 2025, Institutter, filialer &amp; ansatte, Finans Danmark, Copenhagen, accessed 12 September 2026, &lt;https://finansdanmark.dk/tal-og-data/institutter-filialer-ansatte/&gt;.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="23" t="inlineStr">
         <is>
-          <t>FD1</t>
+          <t>ES1</t>
         </is>
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>Finans Danmark</t>
+          <t>Eurostat</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>Institutter, filialer &amp; ansatte</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="inlineStr"/>
+          <t>E-commerce statistics for individuals (Statistics Explained)</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>isoc_ec_ib20 / isoc_ec_ibuy</t>
+        </is>
+      </c>
       <c r="E4" s="15" t="inlineStr">
         <is>
-          <t>https://finansdanmark.dk/tal-og-data/institutter-filialer-ansatte/</t>
+          <t>https://ec.europa.eu/eurostat/statistics-explained/index.php?title=E-commerce_statistics_for_individuals</t>
         </is>
       </c>
       <c r="F4" s="15" t="inlineStr">
@@ -14462,14 +14466,14 @@
       </c>
       <c r="G4" s="15" t="inlineStr">
         <is>
-          <t>Finans Danmark 2025, Institutter, filialer &amp; ansatte, Finans Danmark, Copenhagen, accessed 12 September 2026, &lt;https://finansdanmark.dk/tal-og-data/institutter-filialer-ansatte/&gt;.</t>
+          <t>Eurostat 2025, E-commerce statistics for individuals, Statistics Explained, European Commission, Luxembourg, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="46" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
         <is>
-          <t>ES1</t>
+          <t>ES2</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
@@ -14479,17 +14483,17 @@
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>E-commerce statistics for individuals (Statistics Explained)</t>
+          <t>Online shopping ever more popular in 2020 (ddn-20210217-1)</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>isoc_ec_ib20 / isoc_ec_ibuy</t>
+          <t>isoc_ec_ib20</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/statistics-explained/index.php?title=E-commerce_statistics_for_individuals</t>
+          <t>https://ec.europa.eu/eurostat/web/products-eurostat-news/-/ddn-20210217-1</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr">
@@ -14499,14 +14503,14 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>Eurostat 2025, E-commerce statistics for individuals, Statistics Explained, European Commission, Luxembourg, accessed 12 September 2026.</t>
+          <t>Eurostat 2021, Online shopping ever more popular in 2020, European Commission, Luxembourg, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
       <c r="A6" s="23" t="inlineStr">
         <is>
-          <t>ES2</t>
+          <t>ES3</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
@@ -14516,7 +14520,7 @@
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Online shopping ever more popular in 2020 (ddn-20210217-1)</t>
+          <t>Online shopping ever more popular (ddn-20220202-1)</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
@@ -14526,7 +14530,7 @@
       </c>
       <c r="E6" s="15" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/web/products-eurostat-news/-/ddn-20210217-1</t>
+          <t>https://ec.europa.eu/eurostat/web/products-eurostat-news/-/ddn-20220202-1</t>
         </is>
       </c>
       <c r="F6" s="15" t="inlineStr">
@@ -14536,14 +14540,14 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>Eurostat 2021, Online shopping ever more popular in 2020, European Commission, Luxembourg, accessed 12 September 2026.</t>
+          <t>Eurostat 2022, Online shopping ever more popular, European Commission, Luxembourg, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t>ES3</t>
+          <t>ES4</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
@@ -14553,7 +14557,7 @@
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Online shopping ever more popular (ddn-20220202-1)</t>
+          <t>E-commerce statistics for individuals, 2024 reference year (ddn-20250220-3)</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
@@ -14563,7 +14567,7 @@
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/web/products-eurostat-news/-/ddn-20220202-1</t>
+          <t>https://ec.europa.eu/eurostat/web/products-eurostat-news/w/ddn-20250220-3</t>
         </is>
       </c>
       <c r="F7" s="15" t="inlineStr">
@@ -14573,14 +14577,14 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>Eurostat 2022, Online shopping ever more popular, European Commission, Luxembourg, accessed 12 September 2026.</t>
+          <t>Eurostat 2025, E-commerce statistics for individuals, European Commission, Luxembourg, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="23" t="inlineStr">
         <is>
-          <t>ES4</t>
+          <t>ES5</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
@@ -14590,17 +14594,17 @@
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>E-commerce statistics for individuals, 2024 reference year (ddn-20250220-3)</t>
+          <t>EU enterprises' online sales reach new heights in 2023 (ddn-20250227-2)</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>isoc_ec_ib20</t>
+          <t>isoc_ec_evaln2 / tin00110</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/web/products-eurostat-news/w/ddn-20250220-3</t>
+          <t>https://ec.europa.eu/eurostat/web/products-eurostat-news/w/ddn-20250227-2</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
@@ -14610,14 +14614,14 @@
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>Eurostat 2025, E-commerce statistics for individuals, European Commission, Luxembourg, accessed 12 September 2026.</t>
+          <t>Eurostat 2025, EU enterprises' online sales reach new heights, European Commission, Luxembourg, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
         <is>
-          <t>ES5</t>
+          <t>ES6</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -14627,17 +14631,17 @@
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>EU enterprises' online sales reach new heights in 2023 (ddn-20250227-2)</t>
+          <t>Share of enterprises' turnover on e-commerce, by country (country-level values retrieved via search of the Eurostat indicator)</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>isoc_ec_evaln2 / tin00110</t>
+          <t>tin00110</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/web/products-eurostat-news/w/ddn-20250227-2</t>
+          <t>https://ec.europa.eu/eurostat/databrowser/view/tin00110/default/table?lang=en</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
@@ -14647,34 +14651,34 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>Eurostat 2025, EU enterprises' online sales reach new heights, European Commission, Luxembourg, accessed 12 September 2026.</t>
+          <t>Eurostat 2025, Share of enterprises' turnover on e-commerce (tin00110), European Commission, Luxembourg, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="23" t="inlineStr">
         <is>
-          <t>ES6</t>
+          <t>EC1</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>Eurostat</t>
+          <t>European Commission</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Share of enterprises' turnover on e-commerce, by country (country-level values retrieved via search of the Eurostat indicator)</t>
+          <t>Digital Decade 2026 country report: Denmark, SWD(2026) 155 final, Part 7/27, 17 June 2026</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>tin00110</t>
+          <t>DESI 2026</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/databrowser/view/tin00110/default/table?lang=en</t>
+          <t>https://digital-strategy.ec.europa.eu/en/policies/desi</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -14684,34 +14688,30 @@
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>Eurostat 2025, Share of enterprises' turnover on e-commerce (tin00110), European Commission, Luxembourg, accessed 12 September 2026.</t>
+          <t>European Commission 2026, Digital Decade 2026 country report: Denmark, SWD(2026) 155 final, Part 7/27, European Commission, Brussels.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>EC1</t>
+          <t>DG1</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>European Commission</t>
+          <t>Digitaliseringsstyrelsen (Danish Agency for Digital Government)</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>Digital Decade 2026 country report: Denmark, SWD(2026) 155 final, Part 7/27, 17 June 2026</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>DESI 2026</t>
-        </is>
-      </c>
+          <t>Statistik om Digital Post</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr"/>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>https://digital-strategy.ec.europa.eu/en/policies/desi</t>
+          <t>https://digst.dk/tal-og-statistik/</t>
         </is>
       </c>
       <c r="F11" s="15" t="inlineStr">
@@ -14721,14 +14721,14 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>European Commission 2026, Digital Decade 2026 country report: Denmark, SWD(2026) 155 final, Part 7/27, European Commission, Brussels.</t>
+          <t>Digitaliseringsstyrelsen 2026, Statistik om Digital Post, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="23" t="inlineStr">
         <is>
-          <t>DG1</t>
+          <t>DG2</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
@@ -14738,13 +14738,13 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Statistik om Digital Post</t>
+          <t>Hvem oplever udfordringer ved det digitale?</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr"/>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>https://digst.dk/tal-og-statistik/</t>
+          <t>https://digst.dk/digital-inklusion/viden-om-digital-inklusion/hvem-oplever-udfordringer-ved-det-digitale/</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
@@ -14754,30 +14754,30 @@
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen 2026, Statistik om Digital Post, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
+          <t>Digitaliseringsstyrelsen 2025, Hvem oplever udfordringer ved det digitale?, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>DG2</t>
+          <t>DG3</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen (Danish Agency for Digital Government)</t>
+          <t>Digitaliseringsstyrelsen / Danmarks Statistik</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>Hvem oplever udfordringer ved det digitale?</t>
+          <t>Effektmåling af SMV:Digital, June 2025</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr"/>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>https://digst.dk/digital-inklusion/viden-om-digital-inklusion/hvem-oplever-udfordringer-ved-det-digitale/</t>
+          <t>https://digst.dk/media/yz2ouzzz/effektmaaling-af-smvdigital-2025.pdf</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
@@ -14787,30 +14787,34 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen 2025, Hvem oplever udfordringer ved det digitale?, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
+          <t>Digitaliseringsstyrelsen 2025, Effektmåling af SMV:Digital, prepared by Danmarks Statistik, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
         <is>
-          <t>DG3</t>
+          <t>JU1</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen / Danmarks Statistik</t>
+          <t>Justitia (independent Danish legal think tank)</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Effektmåling af SMV:Digital, June 2025</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr"/>
+          <t>Retssikkerhed for digitalt udsatte borgere, July 2022</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Folketinget DIU Alm.del bilag 32</t>
+        </is>
+      </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>https://digst.dk/media/yz2ouzzz/effektmaaling-af-smvdigital-2025.pdf</t>
+          <t>https://justitia-int.org/wp-content/uploads/2022/09/Rapport_Retssikkerhed-for-digitalt-udsatte-borgere-1.pdf</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
@@ -14820,34 +14824,30 @@
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen 2025, Effektmåling af SMV:Digital, prepared by Danmarks Statistik, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
+          <t>Justitia 2022, Retssikkerhed for digitalt udsatte borgere, Justitia, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>JU1</t>
+          <t>IMR1</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>Justitia (independent Danish legal think tank)</t>
+          <t>Institut for Menneskerettigheder (Danish Institute for Human Rights)</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>Retssikkerhed for digitalt udsatte borgere, July 2022</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>Folketinget DIU Alm.del bilag 32</t>
-        </is>
-      </c>
+          <t>Rettigheder i den digitale velfærdsstat, December 2023</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr"/>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>https://justitia-int.org/wp-content/uploads/2022/09/Rapport_Retssikkerhed-for-digitalt-udsatte-borgere-1.pdf</t>
+          <t>https://menneskeret.dk/sites/menneskeret.dk/files/media/document/Rettigheder%20i%20den%20digitale%20velf%C3%A6rdsstat.%20Analyse,%20Institut%20for%20Menneskerettigheder,%20december%202023.PDF</t>
         </is>
       </c>
       <c r="F15" s="15" t="inlineStr">
@@ -14857,30 +14857,34 @@
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>Justitia 2022, Retssikkerhed for digitalt udsatte borgere, Justitia, Copenhagen, accessed 12 September 2026.</t>
+          <t>Institut for Menneskerettigheder 2023, Rettigheder i den digitale velfaerdsstat, Danish Institute for Human Rights, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="23" t="inlineStr">
         <is>
-          <t>IMR1</t>
+          <t>RI1</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Institut for Menneskerettigheder (Danish Institute for Human Rights)</t>
+          <t>Retsinformation (Danish official legal information portal)</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Rettigheder i den digitale velfærdsstat, December 2023</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="inlineStr"/>
+          <t>Lov om Offentlig Digital Post, LOV nr 528 af 11/06/2012</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>ELI: lta/2012/528</t>
+        </is>
+      </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>https://menneskeret.dk/sites/menneskeret.dk/files/media/document/Rettigheder%20i%20den%20digitale%20velf%C3%A6rdsstat.%20Analyse,%20Institut%20for%20Menneskerettigheder,%20december%202023.PDF</t>
+          <t>https://www.retsinformation.dk/eli/lta/2012/528</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
@@ -14890,34 +14894,30 @@
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>Institut for Menneskerettigheder 2023, Rettigheder i den digitale velfaerdsstat, Danish Institute for Human Rights, Copenhagen, accessed 12 September 2026.</t>
+          <t>Denmark 2012, Lov om Offentlig Digital Post (LOV nr 528 af 11/06/2012), Retsinformation, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="23" t="inlineStr">
         <is>
-          <t>RI1</t>
+          <t>RR1</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Retsinformation (Danish official legal information portal)</t>
+          <t>Rigsrevisionen (Danish National Audit Office)</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>Lov om Offentlig Digital Post, LOV nr 528 af 11/06/2012</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>ELI: lta/2012/528</t>
-        </is>
-      </c>
+          <t>Beretning om besparelsespotentialet ved obligatorisk Digital Post på ca. 1 mia. kr. om året, January 2016</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr"/>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>https://www.retsinformation.dk/eli/lta/2012/528</t>
+          <t>https://www.rigsrevisionen.dk/revisionssager-arkiv/2016/jan/beretning-om-besparelsespotentialet-ved-obligatorisk-digital-post-paa-ca-1-mia-kr-om-aaret</t>
         </is>
       </c>
       <c r="F17" s="15" t="inlineStr">
@@ -14927,30 +14927,34 @@
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>Denmark 2012, Lov om Offentlig Digital Post (LOV nr 528 af 11/06/2012), Retsinformation, Copenhagen, accessed 12 September 2026.</t>
+          <t>Rigsrevisionen 2016, Beretning om besparelsespotentialet ved obligatorisk Digital Post på ca. 1 mia. kr. om året, National Audit Office of Denmark, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1">
       <c r="A18" s="23" t="inlineStr">
         <is>
-          <t>RR1</t>
+          <t>RI2</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>Rigsrevisionen (Danish National Audit Office)</t>
+          <t>Finanstilsynet (Danish Financial Supervisory Authority)</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Beretning om besparelsespotentialet ved obligatorisk Digital Post på ca. 1 mia. kr. om året, January 2016</t>
-        </is>
-      </c>
-      <c r="D18" s="15" t="inlineStr"/>
+          <t>Kontantreglen – lov om betalinger § 81</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Lov om betalinger, § 81</t>
+        </is>
+      </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>https://www.rigsrevisionen.dk/revisionssager-arkiv/2016/jan/beretning-om-besparelsespotentialet-ved-obligatorisk-digital-post-paa-ca-1-mia-kr-om-aaret</t>
+          <t>https://www.finanstilsynet.dk/finansielle-temaer/betalingstjenester-og-e-penge/kontantreglen</t>
         </is>
       </c>
       <c r="F18" s="15" t="inlineStr">
@@ -14960,34 +14964,30 @@
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>Rigsrevisionen 2016, Beretning om besparelsespotentialet ved obligatorisk Digital Post på ca. 1 mia. kr. om året, National Audit Office of Denmark, Copenhagen, accessed 12 September 2026.</t>
+          <t>Finanstilsynet 2025, Kontantreglen, Danish Financial Supervisory Authority, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>RI2</t>
+          <t>DG4</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Finanstilsynet (Danish Financial Supervisory Authority)</t>
+          <t>Digitaliseringsstyrelsen (Danish Agency for Digital Government)</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>Kontantreglen – lov om betalinger § 81</t>
-        </is>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>Lov om betalinger, § 81</t>
-        </is>
-      </c>
+          <t>Digital Post – lovgivning, and the MitID transition news archive</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr"/>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>https://www.finanstilsynet.dk/finansielle-temaer/betalingstjenester-og-e-penge/kontantreglen</t>
+          <t>https://digst.dk/it-loesninger/digital-post/lovgivning/</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
@@ -14997,30 +14997,30 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>Finanstilsynet 2025, Kontantreglen, Danish Financial Supervisory Authority, Copenhagen, accessed 12 September 2026.</t>
+          <t>Digitaliseringsstyrelsen 2025, Digital Post – lovgivning, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="46" customHeight="1">
       <c r="A20" s="23" t="inlineStr">
         <is>
-          <t>DG4</t>
+          <t>SMV1</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen (Danish Agency for Digital Government)</t>
+          <t>SMV:Digital (Danish SME digitalisation grant scheme)</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Digital Post – lovgivning, and the MitID transition news archive</t>
+          <t>Tilskudspuljer i 2026</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr"/>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>https://digst.dk/it-loesninger/digital-post/lovgivning/</t>
+          <t>https://smvdigital.dk/content/ydelser/tilskudspuljer-i-2026/8efa07f4-5032-47f4-b7fa-bab57412b762/</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
@@ -15030,30 +15030,34 @@
       </c>
       <c r="G20" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen 2025, Digital Post – lovgivning, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
+          <t>SMV:Digital 2026, Tilskudspuljer i 2026, SMV:Digital, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="46" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>SMV1</t>
+          <t>DST2</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>SMV:Digital (Danish SME digitalisation grant scheme)</t>
+          <t>Danmarks Statistik</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>Tilskudspuljer i 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr"/>
+          <t>Befolkningstal (population figures)</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>StatBank FOLK1A</t>
+        </is>
+      </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>https://smvdigital.dk/content/ydelser/tilskudspuljer-i-2026/8efa07f4-5032-47f4-b7fa-bab57412b762/</t>
+          <t>https://www.dst.dk/da/Statistik/emner/borgere/befolkning/befolkningstal</t>
         </is>
       </c>
       <c r="F21" s="15" t="inlineStr">
@@ -15063,34 +15067,34 @@
       </c>
       <c r="G21" s="15" t="inlineStr">
         <is>
-          <t>SMV:Digital 2026, Tilskudspuljer i 2026, SMV:Digital, Copenhagen, accessed 12 September 2026.</t>
+          <t>Danmarks Statistik 2026, Befolkningstal, Statistics Denmark, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="46" customHeight="1">
       <c r="A22" s="23" t="inlineStr">
         <is>
-          <t>DST2</t>
+          <t>ES7</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Danmarks Statistik</t>
+          <t>Eurostat</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Befolkningstal (population figures)</t>
+          <t>Internet purchases by individuals (2020 onwards) - custom extraction, all individuals, last online purchase in the 12 months, percentage of individuals who used internet within the last year, 2024</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>StatBank FOLK1A</t>
+          <t>isoc_ec_ib20</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>https://www.dst.dk/da/Statistik/emner/borgere/befolkning/befolkningstal</t>
+          <t>https://ec.europa.eu/eurostat/databrowser/view/isoc_ec_ib20/default/table?lang=en</t>
         </is>
       </c>
       <c r="F22" s="15" t="inlineStr">
@@ -15100,34 +15104,34 @@
       </c>
       <c r="G22" s="15" t="inlineStr">
         <is>
-          <t>Danmarks Statistik 2026, Befolkningstal, Statistics Denmark, Copenhagen, accessed 12 September 2026.</t>
+          <t>Eurostat 2026, Internet purchases by individuals (2020 onwards), dataset isoc_ec_ib20, Statistical Office of the European Union, Luxembourg, data last updated 17 April 2026, accessed 12 September 2026, &lt;https://ec.europa.eu/eurostat/databrowser/view/isoc_ec_ib20/default/table?lang=en&gt;.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="46" customHeight="1">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>ES7</t>
+          <t>DST1</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Eurostat</t>
+          <t>Danmarks Statistik</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Internet purchases by individuals (2020 onwards) - custom extraction, all individuals, last online purchase in the 12 months, percentage of individuals who used internet within the last year, 2024</t>
+          <t>Detailomsætningsindeks (retail trade turnover index)</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>isoc_ec_ib20</t>
+          <t>StatBank; base year rebased 2015 -&gt; 2021</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/databrowser/view/isoc_ec_ib20/default/table?lang=en</t>
+          <t>https://www.dst.dk/da/Statistik/dokumentation/statistikdokumentation/detailomsaetningsindeks</t>
         </is>
       </c>
       <c r="F23" s="15" t="inlineStr">
@@ -15137,71 +15141,71 @@
       </c>
       <c r="G23" s="15" t="inlineStr">
         <is>
-          <t>Eurostat 2026, Internet purchases by individuals (2020 onwards), dataset isoc_ec_ib20, Statistical Office of the European Union, Luxembourg, data last updated 17 April 2026, accessed 12 September 2026, &lt;https://ec.europa.eu/eurostat/databrowser/view/isoc_ec_ib20/default/table?lang=en&gt;.</t>
+          <t>Danmarks Statistik 2025, Detailomsætningsindeks, Statistics Denmark, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="46" customHeight="1">
       <c r="A24" s="23" t="inlineStr">
         <is>
-          <t>DST1</t>
+          <t>ES8</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Danmarks Statistik</t>
+          <t>Eurostat</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>Detailomsætningsindeks (retail trade turnover index)</t>
+          <t>Labour productivity per person employed and hour worked (EU27_2020=100) - custom extraction, nominal labour productivity per person, Denmark, 2005-2025</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>StatBank; base year rebased 2015 -&gt; 2021</t>
+          <t>tesem160</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>https://www.dst.dk/da/Statistik/dokumentation/statistikdokumentation/detailomsaetningsindeks</t>
+          <t>https://ec.europa.eu/eurostat/databrowser/view/tesem160/default/table?lang=en</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>13 September 2026</t>
         </is>
       </c>
       <c r="G24" s="15" t="inlineStr">
         <is>
-          <t>Danmarks Statistik 2025, Detailomsætningsindeks, Statistics Denmark, Copenhagen, accessed 12 September 2026.</t>
+          <t>Eurostat 2026, Labour productivity per person employed and hour worked (EU27_2020=100), dataset tesem160, last updated 9 September 2026, Eurostat, accessed 13 September 2026, &lt;https://ec.europa.eu/eurostat/databrowser/view/tesem160/default/table?lang=en&gt;.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="46" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>ES8</t>
+          <t>LOV1</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Eurostat</t>
+          <t>Folketinget</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Labour productivity per person employed and hour worked (EU27_2020=100) - custom extraction, nominal labour productivity per person, Denmark, 2005-2025</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Lov om fravigelse fra obligatorisk digital selvbetjening (Act on derogation from mandatory digital self-service)</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>tesem160</t>
+          <t>LOV nr 603 af 31/05/2023</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/eurostat/databrowser/view/tesem160/default/table?lang=en</t>
+          <t>https://www.retsinformation.dk/eli/lta/2023/603</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">
@@ -15211,34 +15215,34 @@
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>Eurostat 2026, Labour productivity per person employed and hour worked (EU27_2020=100), dataset tesem160, last updated 9 September 2026, Eurostat, accessed 13 September 2026, &lt;https://ec.europa.eu/eurostat/databrowser/view/tesem160/default/table?lang=en&gt;.</t>
+          <t>Folketinget 2023, Lov om fravigelse fra obligatorisk digital selvbetjening, LOV nr 603 af 31. maj 2023, in force 1 June 2023, Retsinformation, accessed 13 September 2026, &lt;https://www.retsinformation.dk/eli/lta/2023/603&gt;.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="46" customHeight="1">
       <c r="A26" s="23" t="inlineStr">
         <is>
-          <t>LOV1</t>
+          <t>DG5</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Folketinget</t>
+          <t>Digitaliseringsstyrelsen</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Lov om fravigelse fra obligatorisk digital selvbetjening (Act on derogation from mandatory digital self-service)</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Effektmåling af SMV:Digital - register-based effect measurement of grant recipients against a matched control group, with accompanying method note</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>LOV nr 603 af 31/05/2023</t>
+          <t>Effektmåling 2025</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>https://www.retsinformation.dk/eli/lta/2023/603</t>
+          <t>https://digst.dk/media/yz2ouzzz/effektmaaling-af-smvdigital-2025.pdf</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
@@ -15248,34 +15252,34 @@
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
-          <t>Folketinget 2023, Lov om fravigelse fra obligatorisk digital selvbetjening, LOV nr 603 af 31. maj 2023, in force 1 June 2023, Retsinformation, accessed 13 September 2026, &lt;https://www.retsinformation.dk/eli/lta/2023/603&gt;.</t>
+          <t>Digitaliseringsstyrelsen 2025, Effektmåling af SMV:Digital, June 2025, Agency for Digital Government, accessed 13 September 2026, &lt;https://digst.dk/media/yz2ouzzz/effektmaaling-af-smvdigital-2025.pdf&gt;.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="46" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>DG5</t>
+          <t>BRH1</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen</t>
+          <t>Bundesrechnungshof</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Effektmåling af SMV:Digital - register-based effect measurement of grant recipients against a matched control group, with accompanying method note</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes - findings on the Digital Jetzt lottery allocation</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>Effektmåling 2025</t>
+          <t>Bemerkungen 2022</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>https://digst.dk/media/yz2ouzzz/effektmaaling-af-smvdigital-2025.pdf</t>
+          <t>https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html</t>
         </is>
       </c>
       <c r="F27" s="15" t="inlineStr">
@@ -15285,34 +15289,34 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen 2025, Effektmåling af SMV:Digital, June 2025, Agency for Digital Government, accessed 13 September 2026, &lt;https://digst.dk/media/yz2ouzzz/effektmaaling-af-smvdigital-2025.pdf&gt;.</t>
+          <t>Bundesrechnungshof 2022, Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes, German Federal Court of Auditors, accessed 13 September 2026, &lt;https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html&gt;.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="46" customHeight="1">
       <c r="A28" s="23" t="inlineStr">
         <is>
-          <t>BRH1</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Bundesrechnungshof</t>
+          <t>Conseil d'État (France)</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes - findings on the Digital Jetzt lottery allocation</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Decision No. 452798 - partial annulment of the ANEF decree mandating online-only residence permit applications</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>Bemerkungen 2022</t>
+          <t>No. 452798</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html</t>
+          <t>https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
@@ -15322,34 +15326,34 @@
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
-          <t>Bundesrechnungshof 2022, Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes, German Federal Court of Auditors, accessed 13 September 2026, &lt;https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html&gt;.</t>
+          <t>Conseil d'État 2022, Decision No. 452798, 3 June 2022, Conseil d'État, Paris, accessed 13 September 2026, &lt;https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798&gt;.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="46" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>CE1</t>
+          <t>BE1</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Conseil d'État (France)</t>
+          <t>Cour constitutionnelle (Belgium)</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Decision No. 452798 - partial annulment of the ANEF decree mandating online-only residence permit applications</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Arrêt no. 126/2025 - Brussels Digital ordinance; cumulative non-digital access guarantees</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>No. 452798</t>
+          <t>ECLI:BE:GHCC:2025:ARR.126</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798</t>
+          <t>https://fr.const-court.be/public/f/2025/2025-126f.pdf</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
@@ -15359,34 +15363,34 @@
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
-          <t>Conseil d'État 2022, Decision No. 452798, 3 June 2022, Conseil d'État, Paris, accessed 13 September 2026, &lt;https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798&gt;.</t>
+          <t>Cour constitutionnelle 2025, Arrêt no. 126/2025, 25 September 2025, ECLI:BE:GHCC:2025:ARR.126, Cour constitutionnelle, Brussels, accessed 13 September 2026, &lt;https://fr.const-court.be/public/f/2025/2025-126f.pdf&gt;.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="46" customHeight="1">
       <c r="A30" s="23" t="inlineStr">
         <is>
-          <t>BE1</t>
+          <t>NO1</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Cour constitutionnelle (Belgium)</t>
+          <t>Digitaliseringsdirektoratet (Digdir)</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Arrêt no. 126/2025 - Brussels Digital ordinance; cumulative non-digital access guarantees</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Kontakt- og reservasjonsregisteret and the statutory right to opt out of digital communication under eForvaltningsforskriften</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>ECLI:BE:GHCC:2025:ARR.126</t>
+          <t>KRR</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>https://fr.const-court.be/public/f/2025/2025-126f.pdf</t>
+          <t>https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865</t>
         </is>
       </c>
       <c r="F30" s="15" t="inlineStr">
@@ -15396,34 +15400,34 @@
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
-          <t>Cour constitutionnelle 2025, Arrêt no. 126/2025, 25 September 2025, ECLI:BE:GHCC:2025:ARR.126, Cour constitutionnelle, Brussels, accessed 13 September 2026, &lt;https://fr.const-court.be/public/f/2025/2025-126f.pdf&gt;.</t>
+          <t>Digitaliseringsdirektoratet 2025, Kontakt- og reservasjonsregisteret, Norwegian Digitalisation Agency, accessed 13 September 2026, &lt;https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865&gt;.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="46" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>OMB1</t>
+          <t>HOW1</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Folketingets Ombudsmand</t>
+          <t>Howell, S.T.</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Offentlig Digital Post skal indrettes i overensstemmelse med de almindelige forvaltningsretlige krav</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Financing Innovation: Evidence from R&amp;D Grants</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>FOB 2015-22</t>
+          <t>American Economic Review 107(4)</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>https://www.ombudsmanden.dk/find-viden/udtalelser/2015/2015-22</t>
+          <t>https://www.aeaweb.org/articles?id=10.1257%2Faer.20150808</t>
         </is>
       </c>
       <c r="F31" s="15" t="inlineStr">
@@ -15433,34 +15437,34 @@
       </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Folketingets Ombudsmand 2015, Offentlig Digital Post skal indrettes i overensstemmelse med de almindelige forvaltningsretlige krav, FOB 2015-22, Parliamentary Ombudsman, Copenhagen, accessed 13 September 2026, &lt;https://www.ombudsmanden.dk/find-viden/udtalelser/2015/2015-22&gt;.</t>
+          <t>Howell, ST 2017, 'Financing innovation: evidence from R&amp;D grants', American Economic Review, vol. 107, no. 4, pp. 1136-1164.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="46" customHeight="1">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>OMB2</t>
+          <t>SAN1</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Folketingets Ombudsmand</t>
+          <t>Santoleri, P., Barrows, G., Caravella, S., Crespi, F. and Pellegrino, G.</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Klage har ført til ny praksis i forhold til sene digitale klager - complaint sent through Digital Post at 23:43 on the deadline day</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] The Causal Effects of R&amp;D Grants: Evidence from a Regression Discontinuity - the Horizon 2020 SME Instrument scoring threshold</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>News item, 2024</t>
+          <t>Working paper</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>https://www.ombudsmanden.dk/find-viden/nyheder/2024/klage-har-foert-til-ny-praksis-i-forhold-til-sene-digitale-klager</t>
+          <t>https://pietrosantoleri.github.io/files/Santoleri_et_al_The_effects_of_R_D_grants.pdf</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
@@ -15469,117 +15473,6 @@
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr">
-        <is>
-          <t>Folketingets Ombudsmand 2024, Klage har ført til ny praksis i forhold til sene digitale klager, Parliamentary Ombudsman, Copenhagen, accessed 13 September 2026, &lt;https://www.ombudsmanden.dk/find-viden/nyheder/2024/klage-har-foert-til-ny-praksis-i-forhold-til-sene-digitale-klager&gt;.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="46" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
-        <is>
-          <t>NO1</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>Digitaliseringsdirektoratet (Digdir)</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="inlineStr">
-        <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Kontakt- og reservasjonsregisteret and the statutory right to opt out of digital communication under eForvaltningsforskriften</t>
-        </is>
-      </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>KRR</t>
-        </is>
-      </c>
-      <c r="E33" s="15" t="inlineStr">
-        <is>
-          <t>https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865</t>
-        </is>
-      </c>
-      <c r="F33" s="15" t="inlineStr">
-        <is>
-          <t>13 September 2026</t>
-        </is>
-      </c>
-      <c r="G33" s="15" t="inlineStr">
-        <is>
-          <t>Digitaliseringsdirektoratet 2025, Kontakt- og reservasjonsregisteret, Norwegian Digitalisation Agency, accessed 13 September 2026, &lt;https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865&gt;.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="46" customHeight="1">
-      <c r="A34" s="23" t="inlineStr">
-        <is>
-          <t>HOW1</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>Howell, S.T.</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Financing Innovation: Evidence from R&amp;D Grants</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>American Economic Review 107(4)</t>
-        </is>
-      </c>
-      <c r="E34" s="15" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/articles?id=10.1257%2Faer.20150808</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="inlineStr">
-        <is>
-          <t>13 September 2026</t>
-        </is>
-      </c>
-      <c r="G34" s="15" t="inlineStr">
-        <is>
-          <t>Howell, ST 2017, 'Financing innovation: evidence from R&amp;D grants', American Economic Review, vol. 107, no. 4, pp. 1136-1164.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="46" customHeight="1">
-      <c r="A35" s="23" t="inlineStr">
-        <is>
-          <t>SAN1</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>Santoleri, P., Barrows, G., Caravella, S., Crespi, F. and Pellegrino, G.</t>
-        </is>
-      </c>
-      <c r="C35" s="15" t="inlineStr">
-        <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] The Causal Effects of R&amp;D Grants: Evidence from a Regression Discontinuity - the Horizon 2020 SME Instrument scoring threshold</t>
-        </is>
-      </c>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>Working paper</t>
-        </is>
-      </c>
-      <c r="E35" s="15" t="inlineStr">
-        <is>
-          <t>https://pietrosantoleri.github.io/files/Santoleri_et_al_The_effects_of_R_D_grants.pdf</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="inlineStr">
-        <is>
-          <t>13 September 2026</t>
-        </is>
-      </c>
-      <c r="G35" s="15" t="inlineStr">
         <is>
           <t>Santoleri, P, Barrows, G, Caravella, S, Crespi, F and Pellegrino, G 2022, The causal effects of R&amp;D grants: evidence from a regression discontinuity, working paper, accessed 13 September 2026, &lt;https://pietrosantoleri.github.io/files/Santoleri_et_al_The_effects_of_R_D_grants.pdf&gt;.</t>
         </is>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -14318,7 +14318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -15407,72 +15407,101 @@
     <row r="31" ht="46" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>HOW1</t>
+          <t>GS1</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Howell, S.T.</t>
+          <t>Tran, T.T.</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Financing Innovation: Evidence from R&amp;D Grants</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Guest speaker session: corporate sustainability and the adoption of artificial intelligence</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>American Economic Review 107(4)</t>
-        </is>
-      </c>
-      <c r="E31" s="15" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/articles?id=10.1257%2Faer.20150808</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="inlineStr">
-        <is>
-          <t>13 September 2026</t>
-        </is>
-      </c>
+          <t>ECON1596/ECON1597 guest lecture</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr"/>
+      <c r="F31" s="15" t="inlineStr"/>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Howell, ST 2017, 'Financing innovation: evidence from R&amp;D grants', American Economic Review, vol. 107, no. 4, pp. 1136-1164.</t>
+          <t>Tran, TT 2026, 'Guest speaker session: corporate sustainability and the adoption of artificial intelligence', guest lecture, ECON1596 Business Challenges in the Digital Economy, RMIT University Vietnam, Ho Chi Minh City, [LECTURE DATE: to be completed by the author].</t>
         </is>
       </c>
     </row>
     <row r="32" ht="46" customHeight="1">
       <c r="A32" s="23" t="inlineStr">
         <is>
+          <t>HOW1</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Howell, S.T.</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Financing Innovation: Evidence from R&amp;D Grants</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>American Economic Review 107(4)</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>https://www.aeaweb.org/articles?id=10.1257%2Faer.20150808</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>13 September 2026</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>Howell, ST 2017, 'Financing innovation: evidence from R&amp;D grants', American Economic Review, vol. 107, no. 4, pp. 1136-1164.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="46" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
           <t>SAN1</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>Santoleri, P., Barrows, G., Caravella, S., Crespi, F. and Pellegrino, G.</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] The Causal Effects of R&amp;D Grants: Evidence from a Regression Discontinuity - the Horizon 2020 SME Instrument scoring threshold</t>
         </is>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="D33" s="15" t="inlineStr">
         <is>
           <t>Working paper</t>
         </is>
       </c>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="E33" s="15" t="inlineStr">
         <is>
           <t>https://pietrosantoleri.github.io/files/Santoleri_et_al_The_effects_of_R_D_grants.pdf</t>
         </is>
       </c>
-      <c r="F32" s="15" t="inlineStr">
+      <c r="F33" s="15" t="inlineStr">
         <is>
           <t>13 September 2026</t>
         </is>
       </c>
-      <c r="G32" s="15" t="inlineStr">
+      <c r="G33" s="15" t="inlineStr">
         <is>
           <t>Santoleri, P, Barrows, G, Caravella, S, Crespi, F and Pellegrino, G 2022, The causal effects of R&amp;D grants: evidence from a regression discontinuity, working paper, accessed 13 September 2026, &lt;https://pietrosantoleri.github.io/files/Santoleri_et_al_The_effects_of_R_D_grants.pdf&gt;.</t>
         </is>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -14318,7 +14318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14787,7 +14787,7 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen 2025, Effektmåling af SMV:Digital, prepared by Danmarks Statistik, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
+          <t>Digitaliseringsstyrelsen 2025, Effektmåling af SMV:Digital, prepared by Danmarks Statistik, Agency for Digital Government, Copenhagen, accessed 12 September 2026, &lt;https://digst.dk/media/yz2ouzzz/effektmaaling-af-smvdigital-2025.pdf&gt;.</t>
         </is>
       </c>
     </row>
@@ -14857,7 +14857,7 @@
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t>Institut for Menneskerettigheder 2023, Rettigheder i den digitale velfaerdsstat, Danish Institute for Human Rights, Copenhagen, accessed 12 September 2026.</t>
+          <t>Institut for Menneskerettigheder 2023, Rettigheder i den digitale velfærdsstat, Danish Institute for Human Rights, Copenhagen, accessed 12 September 2026.</t>
         </is>
       </c>
     </row>
@@ -15222,27 +15222,27 @@
     <row r="26" ht="46" customHeight="1">
       <c r="A26" s="23" t="inlineStr">
         <is>
-          <t>DG5</t>
+          <t>BRH1</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen</t>
+          <t>Bundesrechnungshof</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Effektmåling af SMV:Digital - register-based effect measurement of grant recipients against a matched control group, with accompanying method note</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes - findings on the Digital Jetzt lottery allocation</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>Effektmåling 2025</t>
+          <t>Bemerkungen 2022</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>https://digst.dk/media/yz2ouzzz/effektmaaling-af-smvdigital-2025.pdf</t>
+          <t>https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
@@ -15252,34 +15252,34 @@
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsstyrelsen 2025, Effektmåling af SMV:Digital, June 2025, Agency for Digital Government, accessed 13 September 2026, &lt;https://digst.dk/media/yz2ouzzz/effektmaaling-af-smvdigital-2025.pdf&gt;.</t>
+          <t>Bundesrechnungshof 2022, Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes, German Federal Court of Auditors, accessed 13 September 2026, &lt;https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html&gt;.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="46" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>BRH1</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Bundesrechnungshof</t>
+          <t>Conseil d'État (France)</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes - findings on the Digital Jetzt lottery allocation</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Decision No. 452798 - partial annulment of the ANEF decree mandating online-only residence permit applications</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>Bemerkungen 2022</t>
+          <t>No. 452798</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html</t>
+          <t>https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798</t>
         </is>
       </c>
       <c r="F27" s="15" t="inlineStr">
@@ -15289,34 +15289,34 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>Bundesrechnungshof 2022, Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes, German Federal Court of Auditors, accessed 13 September 2026, &lt;https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html&gt;.</t>
+          <t>Conseil d'État 2022, Decision No. 452798, 3 June 2022, Conseil d'État, Paris, accessed 13 September 2026, &lt;https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798&gt;.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="46" customHeight="1">
       <c r="A28" s="23" t="inlineStr">
         <is>
-          <t>CE1</t>
+          <t>BE1</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Conseil d'État (France)</t>
+          <t>Cour constitutionnelle (Belgium)</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Decision No. 452798 - partial annulment of the ANEF decree mandating online-only residence permit applications</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Arrêt no. 126/2025 - Brussels Digital ordinance; cumulative non-digital access guarantees</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>No. 452798</t>
+          <t>ECLI:BE:GHCC:2025:ARR.126</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798</t>
+          <t>https://fr.const-court.be/public/f/2025/2025-126f.pdf</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
@@ -15326,34 +15326,34 @@
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
-          <t>Conseil d'État 2022, Decision No. 452798, 3 June 2022, Conseil d'État, Paris, accessed 13 September 2026, &lt;https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798&gt;.</t>
+          <t>Cour constitutionnelle 2025, Arrêt no. 126/2025, 25 September 2025, ECLI:BE:GHCC:2025:ARR.126, Cour constitutionnelle, Brussels, accessed 13 September 2026, &lt;https://fr.const-court.be/public/f/2025/2025-126f.pdf&gt;.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="46" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>BE1</t>
+          <t>NO1</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Cour constitutionnelle (Belgium)</t>
+          <t>Digitaliseringsdirektoratet (Digdir)</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Arrêt no. 126/2025 - Brussels Digital ordinance; cumulative non-digital access guarantees</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Kontakt- og reservasjonsregisteret and the statutory right to opt out of digital communication under eForvaltningsforskriften</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>ECLI:BE:GHCC:2025:ARR.126</t>
+          <t>KRR</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>https://fr.const-court.be/public/f/2025/2025-126f.pdf</t>
+          <t>https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
@@ -15363,100 +15363,100 @@
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
-          <t>Cour constitutionnelle 2025, Arrêt no. 126/2025, 25 September 2025, ECLI:BE:GHCC:2025:ARR.126, Cour constitutionnelle, Brussels, accessed 13 September 2026, &lt;https://fr.const-court.be/public/f/2025/2025-126f.pdf&gt;.</t>
+          <t>Digitaliseringsdirektoratet 2025, Kontakt- og reservasjonsregisteret, Norwegian Digitalisation Agency, accessed 13 September 2026, &lt;https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865&gt;.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="46" customHeight="1">
       <c r="A30" s="23" t="inlineStr">
         <is>
-          <t>NO1</t>
+          <t>GS1</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsdirektoratet (Digdir)</t>
+          <t>Tran, T.T.</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Kontakt- og reservasjonsregisteret and the statutory right to opt out of digital communication under eForvaltningsforskriften</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Guest speaker session: corporate sustainability and the adoption of artificial intelligence</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>KRR</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="inlineStr">
-        <is>
-          <t>13 September 2026</t>
-        </is>
-      </c>
+          <t>ECON1596/ECON1597 guest lecture</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr"/>
+      <c r="F30" s="15" t="inlineStr"/>
       <c r="G30" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsdirektoratet 2025, Kontakt- og reservasjonsregisteret, Norwegian Digitalisation Agency, accessed 13 September 2026, &lt;https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865&gt;.</t>
+          <t>Tran, TT 2026, 'Guest speaker session: corporate sustainability and the adoption of artificial intelligence', guest lecture, ECON1596 Business Challenges in the Digital Economy, RMIT University Vietnam, Ho Chi Minh City, [LECTURE DATE: to be completed by the author].</t>
         </is>
       </c>
     </row>
     <row r="31" ht="46" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>GS1</t>
+          <t>HOW1</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Tran, T.T.</t>
+          <t>Howell, S.T.</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Guest speaker session: corporate sustainability and the adoption of artificial intelligence</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Financing Innovation: Evidence from R&amp;D Grants</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>ECON1596/ECON1597 guest lecture</t>
-        </is>
-      </c>
-      <c r="E31" s="15" t="inlineStr"/>
-      <c r="F31" s="15" t="inlineStr"/>
+          <t>American Economic Review 107(4)</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>https://www.aeaweb.org/articles?id=10.1257%2Faer.20150808</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>13 September 2026</t>
+        </is>
+      </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Tran, TT 2026, 'Guest speaker session: corporate sustainability and the adoption of artificial intelligence', guest lecture, ECON1596 Business Challenges in the Digital Economy, RMIT University Vietnam, Ho Chi Minh City, [LECTURE DATE: to be completed by the author].</t>
+          <t>Howell, ST 2017, 'Financing innovation: evidence from R&amp;D grants', American Economic Review, vol. 107, no. 4, pp. 1136-1164.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="46" customHeight="1">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>HOW1</t>
+          <t>SAN1</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Howell, S.T.</t>
+          <t>Santoleri, P., Barrows, G., Caravella, S., Crespi, F. and Pellegrino, G.</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Financing Innovation: Evidence from R&amp;D Grants</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] The Causal Effects of R&amp;D Grants: Evidence from a Regression Discontinuity - the Horizon 2020 SME Instrument scoring threshold</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>American Economic Review 107(4)</t>
+          <t>Working paper</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>https://www.aeaweb.org/articles?id=10.1257%2Faer.20150808</t>
+          <t>https://pietrosantoleri.github.io/files/Santoleri_et_al_The_effects_of_R_D_grants.pdf</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr">
@@ -15465,43 +15465,6 @@
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr">
-        <is>
-          <t>Howell, ST 2017, 'Financing innovation: evidence from R&amp;D grants', American Economic Review, vol. 107, no. 4, pp. 1136-1164.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="46" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
-        <is>
-          <t>SAN1</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>Santoleri, P., Barrows, G., Caravella, S., Crespi, F. and Pellegrino, G.</t>
-        </is>
-      </c>
-      <c r="C33" s="15" t="inlineStr">
-        <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] The Causal Effects of R&amp;D Grants: Evidence from a Regression Discontinuity - the Horizon 2020 SME Instrument scoring threshold</t>
-        </is>
-      </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>Working paper</t>
-        </is>
-      </c>
-      <c r="E33" s="15" t="inlineStr">
-        <is>
-          <t>https://pietrosantoleri.github.io/files/Santoleri_et_al_The_effects_of_R_D_grants.pdf</t>
-        </is>
-      </c>
-      <c r="F33" s="15" t="inlineStr">
-        <is>
-          <t>13 September 2026</t>
-        </is>
-      </c>
-      <c r="G33" s="15" t="inlineStr">
         <is>
           <t>Santoleri, P, Barrows, G, Caravella, S, Crespi, F and Pellegrino, G 2022, The causal effects of R&amp;D grants: evidence from a regression discontinuity, working paper, accessed 13 September 2026, &lt;https://pietrosantoleri.github.io/files/Santoleri_et_al_The_effects_of_R_D_grants.pdf&gt;.</t>
         </is>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -23,10 +23,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F8_SMVDIGITAL" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F9_CONSOLIDATION" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F10_SKILLS" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_RETAIL_GAP" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_LIMITATIONS" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_AI_LOG" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_POLICY" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F11_EWASTE" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_RETAIL_GAP" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_LIMITATIONS" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_AI_LOG" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_POLICY" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_MASTER'!$A$1:$L$135</definedName>
@@ -784,6 +785,105 @@
                 </a:pPr>
                 <a:r>
                   <a:t>% of age group</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <overlay val="0"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'F11_EWASTE'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="2E6DB4"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'F11_EWASTE'!$A$5:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'F11_EWASTE'!$B$5:$B$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="80"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <spPr>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="100"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% of ICT waste collected</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -2148,6 +2248,33 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -2697,7 +2824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3048,46 +3175,58 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>09_POLICY</t>
+          <t>F11_EWASTE</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Policy events - dated instruments with legal citations</t>
+          <t>Figure 11 - ICT waste recovery, DK vs EU-27</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>06_RETAIL_GAP</t>
+          <t>09_POLICY</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Documented gap - retail volume index not retrieved</t>
+          <t>Policy events - dated instruments with legal citations</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>07_LIMITATIONS</t>
+          <t>06_RETAIL_GAP</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Data quality statement - read before citing</t>
+          <t>Documented gap - retail volume index not retrieved</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
+          <t>07_LIMITATIONS</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Data quality statement - read before citing</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
           <t>08_AI_LOG</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>AI use and validation log</t>
         </is>
@@ -6139,6 +6278,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Figure 11 - ICT waste recycled or prepared for reuse, 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>Denmark against the EU-27 average, as a share of ICT-related WEEE collected. Same publication, same definition, same year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="E3" s="33" t="inlineStr">
+        <is>
+          <t>ICT waste recovery, Denmark against the EU-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>geography</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>% recovered</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>gap to EU-27</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t>The one indicator on which Denmark's digital economy ranks near the bottom of the Union rather than the top.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B5" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENV.WEEE",'02_MASTER'!$E:$E,2023)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENV.WEEE",'02_MASTER'!$E:$E,2023))</f>
+        <v/>
+      </c>
+      <c r="C5" s="40">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.ENV.WEEE",'02_MASTER'!$E:$E,2023)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.ENV.WEEE",'02_MASTER'!$E:$E,2023))-IF(COUNTIFS('02_MASTER'!$B:$B,"EU.ENV.WEEE",'02_MASTER'!$E:$E,2023)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.ENV.WEEE",'02_MASTER'!$E:$E,2023))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="38" t="inlineStr">
+        <is>
+          <t>EU-27</t>
+        </is>
+      </c>
+      <c r="B6" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.ENV.WEEE",'02_MASTER'!$E:$E,2023)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.ENV.WEEE",'02_MASTER'!$E:$E,2023))</f>
+        <v/>
+      </c>
+      <c r="C6" s="40">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.ENV.WEEE",'02_MASTER'!$E:$E,2023)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.ENV.WEEE",'02_MASTER'!$E:$E,2023))-IF(COUNTIFS('02_MASTER'!$B:$B,"EU.ENV.WEEE",'02_MASTER'!$E:$E,2023)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.ENV.WEEE",'02_MASTER'!$E:$E,2023))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>Source: European Commission, Digital Decade 2026 country report for Denmark (EC1). READING: Denmark recovers 15.37% of the ICT waste it collects against an EU-27 average of 80.23%, a gap of roughly 65 percentage points. DENOMINATOR: the base is ICT-related WEEE COLLECTED, not ICT equipment placed on the market, so this measures what happens to devices that reach the waste stream and says nothing about how many never do. The source publishes a single year, so no trend is available and none is claimed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6261,7 +6500,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6513,289 +6752,6 @@
       <c r="B22" s="20" t="inlineStr">
         <is>
           <t>An earlier candidate dataset was rejected in full after verification found fabricated values carrying authentic dataset codes and extraction dates - including a Eurostat cross-section that inverted the true EU country ranking. None of it survives in this workbook.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>AI use and validation log</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="26" t="inlineStr">
-        <is>
-          <t>Raw material for the AI Use and Validation Appendix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>step</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>AI assistance used</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>how it was validated</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>outcome</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>Source identification</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>AI used to identify candidate statistical sources and dataset codes.</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>Each source opened or search-verified against the issuing authority.</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>Source register in 03_SOURCES.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>Value retrieval</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>AI used to search for published values by authority and indicator.</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>Each value checked against a result reporting the issuing authority's own publication.</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>Every retained observation carries a source_id.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>Rejection of a prior dataset</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>A candidate dataset produced with AI assistance was reviewed.</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Cross-checked against Eurostat's published country ranking; the values inverted the true ranking and contained duplicated and interpolated cells.</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Dataset rejected in full and excluded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>Withdrawal of an AI-suggested claim</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>An AI-assisted draft asserted that the SMV:Digital grant scheme was being defunded, and an argument was built on the contrast between a programme with measured positive effects and a programme being cut.</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Searched for the scheme's funding status. The scheme's own 2026 grant-pool page documents pools still open and a further pool opening 26 October 2026. No source supported the defunding claim.</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>Claim withdrawn from the dataset and the argument; the withdrawal is recorded in 09_POLICY and 07_LIMITATIONS rather than erased.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>Statistical self-audit</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>AI was asked to audit its own workbook as a macroeconomic policy reviewer would.</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>The audit found that Figure 6's adoption column had been assembled from a press release naming only the top three, bottom three and three large movers - a sample drawn from the tails, which inflates R-squared by construction.</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>R-squared removed from the chart face; a selection warning added to F6; the limitation recorded in 07_LIMITATIONS. Later resolved - see the two rows below.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Failed verification attempt</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>AI was asked to retrieve Eurostat isoc_ec_ib20 for 2024 for the twelve member states missing from Figure 6, so the tail selection could be removed.</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Eurostat and the national statistical offices are unreachable from the build environment. Web search returned only the press release naming the same tails, two country values with no attributable source, and one answer mixing the '% of internet users' and '% of individuals' denominators in a single paragraph.</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>No values accepted. Recorded because the honest outcome of a verification attempt is sometimes that it failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>Author-supplied authoritative extract</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>The author retrieved the complete isoc_ec_ib20 table from the Eurostat databrowser and supplied it as a spreadsheet; AI parsed it into the dataset.</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>The extract carries its own provenance header - dataset code, extraction timestamp, last-update date, and an explicit unit of 'percentage of individuals who used internet within the last year'. The ten values it overlapped with were compared against the rounded press-release figures already held; all ten agreed to rounding.</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>All 27 member states plus the EU-27 aggregate added under source ES7. Figure 6 went from n=6 to n=18 and R-squared was restored to the chart face. The superseded rounded values are recorded in each row's note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Workbook construction</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>AI wrote the Python build script that generates this workbook.</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Structural assertions run at build time: source_ids resolve, units and denominators present, no duplicate observations, break flags set.</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>build_workbook.py, re-runnable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Analytical framing</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>AI used to interpret patterns and suggest framings.</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Author reviewed each interpretation against the underlying values.</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>Interpretations appear in the report, attributed to the author.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Not delegated to AI</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>Selection of the research question, country, industries, SDG and policy comparator; the argument; the conclusions.</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>Author's own work.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="34" t="inlineStr">
-        <is>
-          <t>This log records assistance during data assembly. Complete it with any further AI use during drafting before submission. The assessment requires that AI-assisted content be verified and acknowledged.</t>
         </is>
       </c>
     </row>
@@ -7020,6 +6976,289 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>AI use and validation log</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>Raw material for the AI Use and Validation Appendix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>AI assistance used</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>how it was validated</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Source identification</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>AI used to identify candidate statistical sources and dataset codes.</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Each source opened or search-verified against the issuing authority.</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Source register in 03_SOURCES.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>Value retrieval</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>AI used to search for published values by authority and indicator.</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Each value checked against a result reporting the issuing authority's own publication.</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Every retained observation carries a source_id.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Rejection of a prior dataset</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>A candidate dataset produced with AI assistance was reviewed.</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Cross-checked against Eurostat's published country ranking; the values inverted the true ranking and contained duplicated and interpolated cells.</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Dataset rejected in full and excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Withdrawal of an AI-suggested claim</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>An AI-assisted draft asserted that the SMV:Digital grant scheme was being defunded, and an argument was built on the contrast between a programme with measured positive effects and a programme being cut.</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Searched for the scheme's funding status. The scheme's own 2026 grant-pool page documents pools still open and a further pool opening 26 October 2026. No source supported the defunding claim.</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Claim withdrawn from the dataset and the argument; the withdrawal is recorded in 09_POLICY and 07_LIMITATIONS rather than erased.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Statistical self-audit</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>AI was asked to audit its own workbook as a macroeconomic policy reviewer would.</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>The audit found that Figure 6's adoption column had been assembled from a press release naming only the top three, bottom three and three large movers - a sample drawn from the tails, which inflates R-squared by construction.</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>R-squared removed from the chart face; a selection warning added to F6; the limitation recorded in 07_LIMITATIONS. Later resolved - see the two rows below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Failed verification attempt</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>AI was asked to retrieve Eurostat isoc_ec_ib20 for 2024 for the twelve member states missing from Figure 6, so the tail selection could be removed.</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Eurostat and the national statistical offices are unreachable from the build environment. Web search returned only the press release naming the same tails, two country values with no attributable source, and one answer mixing the '% of internet users' and '% of individuals' denominators in a single paragraph.</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>No values accepted. Recorded because the honest outcome of a verification attempt is sometimes that it failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Author-supplied authoritative extract</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>The author retrieved the complete isoc_ec_ib20 table from the Eurostat databrowser and supplied it as a spreadsheet; AI parsed it into the dataset.</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>The extract carries its own provenance header - dataset code, extraction timestamp, last-update date, and an explicit unit of 'percentage of individuals who used internet within the last year'. The ten values it overlapped with were compared against the rounded press-release figures already held; all ten agreed to rounding.</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>All 27 member states plus the EU-27 aggregate added under source ES7. Figure 6 went from n=6 to n=18 and R-squared was restored to the chart face. The superseded rounded values are recorded in each row's note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Workbook construction</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>AI wrote the Python build script that generates this workbook.</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Structural assertions run at build time: source_ids resolve, units and denominators present, no duplicate observations, break flags set.</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>build_workbook.py, re-runnable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Analytical framing</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>AI used to interpret patterns and suggest framings.</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Author reviewed each interpretation against the underlying values.</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Interpretations appear in the report, attributed to the author.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Not delegated to AI</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Selection of the research question, country, industries, SDG and policy comparator; the argument; the conclusions.</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>Author's own work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>This log records assistance during data assembly. Complete it with any further AI use during drafting before submission. The assessment requires that AI-assisted content be verified and acknowledged.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -30,7 +30,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_POLICY" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_MASTER'!$A$1:$L$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_MASTER'!$A$1:$L$137</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>136</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L135"/>
+  <dimension ref="A1:L137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="B2" s="14" t="inlineStr">
         <is>
-          <t>DK.PAY.CASH.POS</t>
+          <t>DK.DGX.EGOV.USE</t>
         </is>
       </c>
       <c r="C2" s="15" t="inlineStr">
         <is>
-          <t>Cash share of payments, physical retail</t>
+          <t>Individuals interacting with public authorities online</t>
         </is>
       </c>
       <c r="D2" s="13" t="inlineStr">
@@ -7821,10 +7821,10 @@
         </is>
       </c>
       <c r="E2" s="13" t="n">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="F2" s="16" t="n">
-        <v>23</v>
+        <v>98.5</v>
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
@@ -7833,13 +7833,13 @@
       </c>
       <c r="H2" s="15" t="inlineStr">
         <is>
-          <t>share of number of payments in physical retail</t>
+          <t>individuals aged 16 to 74</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr"/>
       <c r="J2" s="14" t="inlineStr">
         <is>
-          <t>NB1</t>
+          <t>ES9</t>
         </is>
       </c>
       <c r="K2" s="13" t="inlineStr">
@@ -7847,7 +7847,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L2" s="15" t="inlineStr"/>
+      <c r="L2" s="15" t="inlineStr">
+        <is>
+          <t>Website or app of a public authority, last 12 months. Highest in EU-27.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="n">
@@ -7855,24 +7859,24 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>DK.PAY.CASH.POS</t>
+          <t>EU.DGX.EGOV.USE</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>Cash share of payments, physical retail</t>
+          <t>Individuals interacting with public authorities online</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>EU27</t>
         </is>
       </c>
       <c r="E3" s="13" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="16" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
@@ -7881,13 +7885,13 @@
       </c>
       <c r="H3" s="15" t="inlineStr">
         <is>
-          <t>share of number of payments in physical retail</t>
+          <t>individuals aged 16 to 74</t>
         </is>
       </c>
       <c r="I3" s="13" t="inlineStr"/>
       <c r="J3" s="14" t="inlineStr">
         <is>
-          <t>NB1</t>
+          <t>ES9</t>
         </is>
       </c>
       <c r="K3" s="13" t="inlineStr">
@@ -7895,7 +7899,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L3" s="15" t="inlineStr"/>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>EU-27 aggregate, same base and reference period as the Danish value.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="n">
@@ -7917,10 +7925,10 @@
         </is>
       </c>
       <c r="E4" s="13" t="n">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
@@ -7951,12 +7959,12 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>DK.PAY.CRD.PHYS</t>
+          <t>DK.PAY.CASH.POS</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Physical payment card share of payments</t>
+          <t>Cash share of payments, physical retail</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -7965,10 +7973,10 @@
         </is>
       </c>
       <c r="E5" s="13" t="n">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
@@ -7999,12 +8007,12 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>DK.PAY.CRD.PHYS</t>
+          <t>DK.PAY.CASH.POS</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Physical payment card share of payments</t>
+          <t>Cash share of payments, physical retail</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
@@ -8016,7 +8024,7 @@
         <v>2025</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
@@ -8047,12 +8055,12 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>DK.PAY.WLT.SHR</t>
+          <t>DK.PAY.CRD.PHYS</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>Mobile wallet share of payments</t>
+          <t>Physical payment card share of payments</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -8061,10 +8069,10 @@
         </is>
       </c>
       <c r="E7" s="13" t="n">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
@@ -8087,11 +8095,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L7" s="15" t="inlineStr">
-        <is>
-          <t>Card-based wallets on mobile phones (e.g. Apple Pay, Google Pay).</t>
-        </is>
-      </c>
+      <c r="L7" s="15" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="13" t="n">
@@ -8099,12 +8103,12 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>DK.PAY.DIG.POS.NUM</t>
+          <t>DK.PAY.CRD.PHYS</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Digital share of payments, by number</t>
+          <t>Physical payment card share of payments</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -8116,7 +8120,7 @@
         <v>2025</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -8147,12 +8151,12 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>DK.PAY.DIG.POS.VAL</t>
+          <t>DK.PAY.WLT.SHR</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>Digital share of payments, by value</t>
+          <t>Mobile wallet share of payments</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
@@ -8164,7 +8168,7 @@
         <v>2025</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
@@ -8173,7 +8177,7 @@
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>share of value of payments in physical retail</t>
+          <t>share of number of payments in physical retail</t>
         </is>
       </c>
       <c r="I9" s="13" t="inlineStr"/>
@@ -8189,7 +8193,7 @@
       </c>
       <c r="L9" s="15" t="inlineStr">
         <is>
-          <t>Different denominator from the by-number series - do not plot together.</t>
+          <t>Card-based wallets on mobile phones (e.g. Apple Pay, Google Pay).</t>
         </is>
       </c>
     </row>
@@ -8199,12 +8203,12 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>DK.PAY.WLT.OWN</t>
+          <t>DK.PAY.DIG.POS.NUM</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Citizens holding a mobile wallet solution</t>
+          <t>Digital share of payments, by number</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -8213,10 +8217,10 @@
         </is>
       </c>
       <c r="E10" s="13" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
@@ -8225,7 +8229,7 @@
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>% of citizens</t>
+          <t>share of number of payments in physical retail</t>
         </is>
       </c>
       <c r="I10" s="13" t="inlineStr"/>
@@ -8239,11 +8243,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L10" s="15" t="inlineStr">
-        <is>
-          <t>Memo only - denominator differs from F2 series.</t>
-        </is>
-      </c>
+      <c r="L10" s="15" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="13" t="n">
@@ -8251,12 +8251,12 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>DK.PAY.WLT.OWN</t>
+          <t>DK.PAY.DIG.POS.VAL</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>Citizens holding a mobile wallet solution</t>
+          <t>Digital share of payments, by value</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
@@ -8265,10 +8265,10 @@
         </is>
       </c>
       <c r="E11" s="13" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>% of citizens</t>
+          <t>share of value of payments in physical retail</t>
         </is>
       </c>
       <c r="I11" s="13" t="inlineStr"/>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="L11" s="15" t="inlineStr">
         <is>
-          <t>Memo only - denominator differs from F2 series.</t>
+          <t>Different denominator from the by-number series - do not plot together.</t>
         </is>
       </c>
     </row>
@@ -8317,10 +8317,10 @@
         </is>
       </c>
       <c r="E12" s="13" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>DK.FIN.BRCH</t>
+          <t>DK.PAY.WLT.OWN</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>Bank branches</t>
+          <t>Citizens holding a mobile wallet solution</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
@@ -8369,25 +8369,25 @@
         </is>
       </c>
       <c r="E13" s="13" t="n">
-        <v>2004</v>
-      </c>
-      <c r="F13" s="17" t="n">
-        <v>2025</v>
+        <v>2023</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>41</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>branches</t>
+          <t>% of citizens</t>
         </is>
       </c>
       <c r="I13" s="13" t="inlineStr"/>
       <c r="J13" s="14" t="inlineStr">
         <is>
-          <t>FD1</t>
+          <t>NB1</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
@@ -8395,7 +8395,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L13" s="15" t="inlineStr"/>
+      <c r="L13" s="15" t="inlineStr">
+        <is>
+          <t>Memo only - denominator differs from F2 series.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="n">
@@ -8403,12 +8407,12 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>DK.FIN.BRCH</t>
+          <t>DK.PAY.WLT.OWN</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Bank branches</t>
+          <t>Citizens holding a mobile wallet solution</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
@@ -8417,25 +8421,25 @@
         </is>
       </c>
       <c r="E14" s="13" t="n">
-        <v>2006</v>
-      </c>
-      <c r="F14" s="17" t="n">
-        <v>1975</v>
+        <v>2025</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>51</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>branches</t>
+          <t>% of citizens</t>
         </is>
       </c>
       <c r="I14" s="13" t="inlineStr"/>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>FD1</t>
+          <t>NB1</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
@@ -8443,7 +8447,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L14" s="15" t="inlineStr"/>
+      <c r="L14" s="15" t="inlineStr">
+        <is>
+          <t>Memo only - denominator differs from F2 series.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="n">
@@ -8465,10 +8473,10 @@
         </is>
       </c>
       <c r="E15" s="13" t="n">
-        <v>2010</v>
+        <v>2004</v>
       </c>
       <c r="F15" s="17" t="n">
-        <v>1598</v>
+        <v>2025</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -8513,10 +8521,10 @@
         </is>
       </c>
       <c r="E16" s="13" t="n">
-        <v>2016</v>
+        <v>2006</v>
       </c>
       <c r="F16" s="17" t="n">
-        <v>948</v>
+        <v>1975</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
@@ -8561,10 +8569,10 @@
         </is>
       </c>
       <c r="E17" s="13" t="n">
-        <v>2021</v>
+        <v>2010</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>701</v>
+        <v>1598</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -8609,10 +8617,10 @@
         </is>
       </c>
       <c r="E18" s="13" t="n">
-        <v>2024</v>
+        <v>2016</v>
       </c>
       <c r="F18" s="17" t="n">
-        <v>665</v>
+        <v>948</v>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
@@ -8643,12 +8651,12 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>DK.FIN.INST</t>
+          <t>DK.FIN.BRCH</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>Financial institutions</t>
+          <t>Bank branches</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
@@ -8657,10 +8665,10 @@
         </is>
       </c>
       <c r="E19" s="13" t="n">
-        <v>1991</v>
+        <v>2021</v>
       </c>
       <c r="F19" s="17" t="n">
-        <v>219</v>
+        <v>701</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -8669,7 +8677,7 @@
       </c>
       <c r="H19" s="15" t="inlineStr">
         <is>
-          <t>institutions</t>
+          <t>branches</t>
         </is>
       </c>
       <c r="I19" s="13" t="inlineStr"/>
@@ -8691,12 +8699,12 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>DK.FIN.INST</t>
+          <t>DK.FIN.BRCH</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>Financial institutions</t>
+          <t>Bank branches</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
@@ -8708,7 +8716,7 @@
         <v>2024</v>
       </c>
       <c r="F20" s="17" t="n">
-        <v>51</v>
+        <v>665</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -8717,7 +8725,7 @@
       </c>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>institutions</t>
+          <t>branches</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr"/>
@@ -8734,116 +8742,100 @@
       <c r="L20" s="15" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>DK.FIN.EMP</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>Bank employees</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>DK.FIN.INST</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Financial institutions</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E21" s="13" t="n">
         <v>1991</v>
       </c>
-      <c r="F21" s="21" t="n">
-        <v>51000</v>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
+      <c r="F21" s="17" t="n">
+        <v>219</v>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="H21" s="20" t="inlineStr">
-        <is>
-          <t>persons employed</t>
-        </is>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J21" s="19" t="inlineStr">
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>institutions</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr"/>
+      <c r="J21" s="14" t="inlineStr">
         <is>
           <t>FD1</t>
         </is>
       </c>
-      <c r="K21" s="18" t="inlineStr">
+      <c r="K21" s="13" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L21" s="20" t="inlineStr">
-        <is>
-          <t>Source states 'around 51,000'.</t>
-        </is>
-      </c>
+      <c r="L21" s="15" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>DK.FIN.EMP</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>Bank employees</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>DK.FIN.INST</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Financial institutions</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E22" s="18" t="n">
+      <c r="E22" s="13" t="n">
         <v>2024</v>
       </c>
-      <c r="F22" s="21" t="n">
-        <v>36000</v>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
+      <c r="F22" s="17" t="n">
+        <v>51</v>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="H22" s="20" t="inlineStr">
-        <is>
-          <t>persons employed</t>
-        </is>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J22" s="19" t="inlineStr">
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>institutions</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr"/>
+      <c r="J22" s="14" t="inlineStr">
         <is>
           <t>FD1</t>
         </is>
       </c>
-      <c r="K22" s="18" t="inlineStr">
+      <c r="K22" s="13" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L22" s="20" t="inlineStr">
-        <is>
-          <t>Source states 'just under 36,000'.</t>
-        </is>
-      </c>
+      <c r="L22" s="15" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="18" t="n">
@@ -8851,157 +8843,165 @@
       </c>
       <c r="B23" s="19" t="inlineStr">
         <is>
+          <t>DK.FIN.EMP</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>Bank employees</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>1991</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>51000</v>
+      </c>
+      <c r="G23" s="18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>persons employed</t>
+        </is>
+      </c>
+      <c r="I23" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J23" s="19" t="inlineStr">
+        <is>
+          <t>FD1</t>
+        </is>
+      </c>
+      <c r="K23" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L23" s="20" t="inlineStr">
+        <is>
+          <t>Source states 'around 51,000'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>DK.FIN.EMP</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>Bank employees</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F24" s="21" t="n">
+        <v>36000</v>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>persons employed</t>
+        </is>
+      </c>
+      <c r="I24" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J24" s="19" t="inlineStr">
+        <is>
+          <t>FD1</t>
+        </is>
+      </c>
+      <c r="K24" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L24" s="20" t="inlineStr">
+        <is>
+          <t>Source states 'just under 36,000'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
           <t>DK.ECM.IND.BUY</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>Individuals who bought online in last 12 months</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E23" s="18" t="n">
+      <c r="E25" s="18" t="n">
         <v>2019</v>
       </c>
-      <c r="F23" s="22" t="n">
+      <c r="F25" s="22" t="n">
         <v>84</v>
       </c>
-      <c r="G23" s="18" t="inlineStr">
+      <c r="G25" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H23" s="20" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>% of individuals</t>
         </is>
       </c>
-      <c r="I23" s="18" t="inlineStr">
+      <c r="I25" s="18" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="J23" s="19" t="inlineStr">
+      <c r="J25" s="19" t="inlineStr">
         <is>
           <t>ES1</t>
         </is>
       </c>
-      <c r="K23" s="18" t="inlineStr">
+      <c r="K25" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L23" s="20" t="inlineStr">
+      <c r="L25" s="20" t="inlineStr">
         <is>
           <t>BREAK: denominator is % of individuals. Highest in EU that year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>DK.ECM.IND.BUY</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Individuals who bought online in last 12 months</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="n">
-        <v>2020</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>90</v>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H24" s="15" t="inlineStr">
-        <is>
-          <t>% of internet users</t>
-        </is>
-      </c>
-      <c r="I24" s="13" t="inlineStr"/>
-      <c r="J24" s="14" t="inlineStr">
-        <is>
-          <t>ES2</t>
-        </is>
-      </c>
-      <c r="K24" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L24" s="15" t="inlineStr">
-        <is>
-          <t>Rounded, from a Eurostat news release. Only the 2024 cross-section is available here unrounded, so this series mixes precisions across years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>DK.ECM.IND.BUY</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>Individuals who bought online in last 12 months</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>2021</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>92</v>
-      </c>
-      <c r="G25" s="13" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H25" s="15" t="inlineStr">
-        <is>
-          <t>% of internet users</t>
-        </is>
-      </c>
-      <c r="I25" s="13" t="inlineStr"/>
-      <c r="J25" s="14" t="inlineStr">
-        <is>
-          <t>ES3</t>
-        </is>
-      </c>
-      <c r="K25" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L25" s="15" t="inlineStr">
-        <is>
-          <t>Rounded, from a Eurostat news release. See the 2020 note on mixed precision.</t>
         </is>
       </c>
     </row>
@@ -9011,7 +9011,7 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>EU.ECM.IND.BUY</t>
+          <t>DK.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -9021,14 +9021,14 @@
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>EU27</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="E26" s="13" t="n">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>76.58</v>
+        <v>90</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
       <c r="I26" s="13" t="inlineStr"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>ES7</t>
+          <t>ES2</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
@@ -9051,7 +9051,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L26" s="15" t="inlineStr"/>
+      <c r="L26" s="15" t="inlineStr">
+        <is>
+          <t>Rounded, from a Eurostat news release. Only the 2024 cross-section is available here unrounded, so this series mixes precisions across years.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="n">
@@ -9059,7 +9063,7 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>AT.ECM.IND.BUY</t>
+          <t>DK.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
@@ -9069,14 +9073,14 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="E27" s="13" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>74.18000000000001</v>
+        <v>92</v>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
@@ -9091,7 +9095,7 @@
       <c r="I27" s="13" t="inlineStr"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>ES7</t>
+          <t>ES3</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
@@ -9099,7 +9103,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L27" s="15" t="inlineStr"/>
+      <c r="L27" s="15" t="inlineStr">
+        <is>
+          <t>Rounded, from a Eurostat news release. See the 2020 note on mixed precision.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="n">
@@ -9107,7 +9115,7 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>BE.ECM.IND.BUY</t>
+          <t>EU.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
@@ -9117,14 +9125,14 @@
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>EU27</t>
         </is>
       </c>
       <c r="E28" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>78.98</v>
+        <v>76.58</v>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
@@ -9155,7 +9163,7 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>BG.ECM.IND.BUY</t>
+          <t>AT.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
@@ -9165,14 +9173,14 @@
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="E29" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>57.18</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
@@ -9195,11 +9203,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L29" s="15" t="inlineStr">
-        <is>
-          <t>Lowest of the 27, as the press release reported. Supersedes the rounded 57%.</t>
-        </is>
-      </c>
+      <c r="L29" s="15" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="13" t="n">
@@ -9207,7 +9211,7 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>CY.ECM.IND.BUY</t>
+          <t>BE.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
@@ -9217,14 +9221,14 @@
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E30" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>68.16</v>
+        <v>78.98</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
@@ -9255,7 +9259,7 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>CZ.ECM.IND.BUY</t>
+          <t>BG.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
@@ -9265,14 +9269,14 @@
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="E31" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F31" s="16" t="n">
-        <v>86.20999999999999</v>
+        <v>57.18</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
@@ -9295,7 +9299,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L31" s="15" t="inlineStr"/>
+      <c r="L31" s="15" t="inlineStr">
+        <is>
+          <t>Lowest of the 27, as the press release reported. Supersedes the rounded 57%.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="n">
@@ -9303,7 +9311,7 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>DE.ECM.IND.BUY</t>
+          <t>CY.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
@@ -9313,14 +9321,14 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="E32" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F32" s="16" t="n">
-        <v>82.53</v>
+        <v>68.16</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
@@ -9343,11 +9351,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L32" s="15" t="inlineStr">
-        <is>
-          <t>Supersedes the rounded 83%.</t>
-        </is>
-      </c>
+      <c r="L32" s="15" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="13" t="n">
@@ -9355,7 +9359,7 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>DK.ECM.IND.BUY</t>
+          <t>CZ.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
@@ -9365,14 +9369,14 @@
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="E33" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F33" s="16" t="n">
-        <v>90.86</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
@@ -9395,11 +9399,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L33" s="15" t="inlineStr">
-        <is>
-          <t>Supersedes the rounded 91% taken from the Eurostat press release.</t>
-        </is>
-      </c>
+      <c r="L33" s="15" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="13" t="n">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>EE.ECM.IND.BUY</t>
+          <t>DE.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
@@ -9417,14 +9417,14 @@
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E34" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F34" s="16" t="n">
-        <v>78.72</v>
+        <v>82.53</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
@@ -9447,7 +9447,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L34" s="15" t="inlineStr"/>
+      <c r="L34" s="15" t="inlineStr">
+        <is>
+          <t>Supersedes the rounded 83%.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="13" t="n">
@@ -9455,7 +9459,7 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>EL.ECM.IND.BUY</t>
+          <t>DK.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
@@ -9465,14 +9469,14 @@
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="E35" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>74.66</v>
+        <v>90.86</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
@@ -9495,7 +9499,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L35" s="15" t="inlineStr"/>
+      <c r="L35" s="15" t="inlineStr">
+        <is>
+          <t>Supersedes the rounded 91% taken from the Eurostat press release.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="n">
@@ -9503,7 +9511,7 @@
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>ES.ECM.IND.BUY</t>
+          <t>EE.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
@@ -9513,14 +9521,14 @@
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="E36" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F36" s="16" t="n">
-        <v>71.54000000000001</v>
+        <v>78.72</v>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
@@ -9551,7 +9559,7 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>FI.ECM.IND.BUY</t>
+          <t>EL.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
@@ -9561,14 +9569,14 @@
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="E37" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>80.40000000000001</v>
+        <v>74.66</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
@@ -9599,7 +9607,7 @@
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>FR.ECM.IND.BUY</t>
+          <t>ES.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
@@ -9609,14 +9617,14 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E38" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F38" s="16" t="n">
-        <v>84.37</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
@@ -9647,7 +9655,7 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>HR.ECM.IND.BUY</t>
+          <t>FI.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
@@ -9657,14 +9665,14 @@
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="E39" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F39" s="16" t="n">
-        <v>70.06999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
@@ -9695,7 +9703,7 @@
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>HU.ECM.IND.BUY</t>
+          <t>FR.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
@@ -9705,14 +9713,14 @@
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E40" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F40" s="16" t="n">
-        <v>78.87</v>
+        <v>84.37</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
@@ -9735,11 +9743,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L40" s="15" t="inlineStr">
-        <is>
-          <t>Supersedes the rounded 79%.</t>
-        </is>
-      </c>
+      <c r="L40" s="15" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="13" t="n">
@@ -9747,7 +9751,7 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>IE.ECM.IND.BUY</t>
+          <t>HR.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
@@ -9757,14 +9761,14 @@
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E41" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F41" s="16" t="n">
-        <v>95.79000000000001</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -9787,11 +9791,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L41" s="15" t="inlineStr">
-        <is>
-          <t>Highest in EU. Supersedes the rounded 96%.</t>
-        </is>
-      </c>
+      <c r="L41" s="15" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="13" t="n">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>IT.ECM.IND.BUY</t>
+          <t>HU.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
@@ -9809,14 +9809,14 @@
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E42" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F42" s="16" t="n">
-        <v>59.6</v>
+        <v>78.87</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
       </c>
       <c r="L42" s="15" t="inlineStr">
         <is>
-          <t>Second lowest of the 27. Supersedes the rounded 60%, which tied Italy with Romania; unrounded Italy is below Romania, so they are not tied.</t>
+          <t>Supersedes the rounded 79%.</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>LT.ECM.IND.BUY</t>
+          <t>IE.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C43" s="15" t="inlineStr">
@@ -9861,14 +9861,14 @@
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="E43" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F43" s="16" t="n">
-        <v>71.95999999999999</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="L43" s="15" t="inlineStr">
         <is>
-          <t>Supersedes the rounded 72%.</t>
+          <t>Highest in EU. Supersedes the rounded 96%.</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>LU.ECM.IND.BUY</t>
+          <t>IT.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
@@ -9913,14 +9913,14 @@
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E44" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F44" s="16" t="n">
-        <v>81.34</v>
+        <v>59.6</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
@@ -9943,7 +9943,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L44" s="15" t="inlineStr"/>
+      <c r="L44" s="15" t="inlineStr">
+        <is>
+          <t>Second lowest of the 27. Supersedes the rounded 60%, which tied Italy with Romania; unrounded Italy is below Romania, so they are not tied.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="13" t="n">
@@ -9951,7 +9955,7 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>LV.ECM.IND.BUY</t>
+          <t>LT.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C45" s="15" t="inlineStr">
@@ -9961,14 +9965,14 @@
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="E45" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F45" s="16" t="n">
-        <v>69.34999999999999</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
@@ -9991,7 +9995,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L45" s="15" t="inlineStr"/>
+      <c r="L45" s="15" t="inlineStr">
+        <is>
+          <t>Supersedes the rounded 72%.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="n">
@@ -9999,7 +10007,7 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>MT.ECM.IND.BUY</t>
+          <t>LU.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
@@ -10009,14 +10017,14 @@
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E46" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F46" s="16" t="n">
-        <v>73.2</v>
+        <v>81.34</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
@@ -10047,7 +10055,7 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>NL.ECM.IND.BUY</t>
+          <t>LV.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C47" s="15" t="inlineStr">
@@ -10057,14 +10065,14 @@
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="E47" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F47" s="16" t="n">
-        <v>94.42</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
@@ -10087,11 +10095,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L47" s="15" t="inlineStr">
-        <is>
-          <t>Supersedes the rounded 94%.</t>
-        </is>
-      </c>
+      <c r="L47" s="15" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="13" t="n">
@@ -10099,7 +10103,7 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>PL.ECM.IND.BUY</t>
+          <t>MT.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
@@ -10109,14 +10113,14 @@
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E48" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F48" s="16" t="n">
-        <v>75.06999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
@@ -10147,7 +10151,7 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>PT.ECM.IND.BUY</t>
+          <t>NL.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C49" s="15" t="inlineStr">
@@ -10157,14 +10161,14 @@
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="E49" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F49" s="16" t="n">
-        <v>66.64</v>
+        <v>94.42</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
@@ -10187,7 +10191,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L49" s="15" t="inlineStr"/>
+      <c r="L49" s="15" t="inlineStr">
+        <is>
+          <t>Supersedes the rounded 94%.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="13" t="n">
@@ -10195,7 +10203,7 @@
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>RO.ECM.IND.BUY</t>
+          <t>PL.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
@@ -10205,14 +10213,14 @@
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E50" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F50" s="16" t="n">
-        <v>59.73</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
@@ -10235,11 +10243,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L50" s="15" t="inlineStr">
-        <is>
-          <t>Supersedes the rounded 60%. See the Italy note on the tie.</t>
-        </is>
-      </c>
+      <c r="L50" s="15" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="13" t="n">
@@ -10247,7 +10251,7 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>SE.ECM.IND.BUY</t>
+          <t>PT.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C51" s="15" t="inlineStr">
@@ -10257,14 +10261,14 @@
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="E51" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F51" s="16" t="n">
-        <v>89.89</v>
+        <v>66.64</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
@@ -10295,7 +10299,7 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>SI.ECM.IND.BUY</t>
+          <t>RO.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
@@ -10305,14 +10309,14 @@
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="E52" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F52" s="16" t="n">
-        <v>72.39</v>
+        <v>59.73</v>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
@@ -10335,7 +10339,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L52" s="15" t="inlineStr"/>
+      <c r="L52" s="15" t="inlineStr">
+        <is>
+          <t>Supersedes the rounded 60%. See the Italy note on the tie.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="13" t="n">
@@ -10343,7 +10351,7 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>SK.ECM.IND.BUY</t>
+          <t>SE.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C53" s="15" t="inlineStr">
@@ -10353,14 +10361,14 @@
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="E53" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F53" s="16" t="n">
-        <v>85.13</v>
+        <v>89.89</v>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
@@ -10391,7 +10399,7 @@
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>EU.ECM.IND.BUY</t>
+          <t>SI.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
@@ -10401,14 +10409,14 @@
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>EU27</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E54" s="13" t="n">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="F54" s="16" t="n">
-        <v>59</v>
+        <v>72.39</v>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
@@ -10423,7 +10431,7 @@
       <c r="I54" s="13" t="inlineStr"/>
       <c r="J54" s="14" t="inlineStr">
         <is>
-          <t>ES4</t>
+          <t>ES7</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -10439,24 +10447,24 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>DK.ECM.ENT.TRN</t>
+          <t>SK.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
-          <t>E-sales as share of enterprise turnover</t>
+          <t>Individuals who bought online in last 12 months</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="E55" s="13" t="n">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="F55" s="16" t="n">
-        <v>17.05</v>
+        <v>85.13</v>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
@@ -10465,13 +10473,13 @@
       </c>
       <c r="H55" s="15" t="inlineStr">
         <is>
-          <t>% of total enterprise turnover</t>
+          <t>% of internet users</t>
         </is>
       </c>
       <c r="I55" s="13" t="inlineStr"/>
       <c r="J55" s="14" t="inlineStr">
         <is>
-          <t>ES5</t>
+          <t>ES7</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -10487,24 +10495,24 @@
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>DK.ECM.ENT.TRN</t>
+          <t>EU.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>E-sales as share of enterprise turnover</t>
+          <t>Individuals who bought online in last 12 months</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>EU27</t>
         </is>
       </c>
       <c r="E56" s="13" t="n">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="F56" s="16" t="n">
-        <v>33.31</v>
+        <v>59</v>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
@@ -10513,13 +10521,13 @@
       </c>
       <c r="H56" s="15" t="inlineStr">
         <is>
-          <t>% of total enterprise turnover</t>
+          <t>% of internet users</t>
         </is>
       </c>
       <c r="I56" s="13" t="inlineStr"/>
       <c r="J56" s="14" t="inlineStr">
         <is>
-          <t>ES5</t>
+          <t>ES4</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -10527,11 +10535,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L56" s="15" t="inlineStr">
-        <is>
-          <t>2nd in EU after Ireland.</t>
-        </is>
-      </c>
+      <c r="L56" s="15" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="13" t="n">
@@ -10539,7 +10543,7 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>EU.ECM.ENT.TRN</t>
+          <t>DK.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C57" s="15" t="inlineStr">
@@ -10549,14 +10553,14 @@
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>EU27</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="E57" s="13" t="n">
         <v>2014</v>
       </c>
       <c r="F57" s="16" t="n">
-        <v>16.43</v>
+        <v>17.05</v>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
@@ -10587,7 +10591,7 @@
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>EU.ECM.ENT.TRN</t>
+          <t>DK.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
@@ -10597,14 +10601,14 @@
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>EU27</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="E58" s="13" t="n">
         <v>2024</v>
       </c>
       <c r="F58" s="16" t="n">
-        <v>19.49</v>
+        <v>33.31</v>
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
@@ -10627,7 +10631,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L58" s="15" t="inlineStr"/>
+      <c r="L58" s="15" t="inlineStr">
+        <is>
+          <t>2nd in EU after Ireland.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="13" t="n">
@@ -10635,7 +10643,7 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>IE.ECM.ENT.TRN</t>
+          <t>EU.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C59" s="15" t="inlineStr">
@@ -10645,14 +10653,14 @@
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>EU27</t>
         </is>
       </c>
       <c r="E59" s="13" t="n">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="F59" s="16" t="n">
-        <v>38.25</v>
+        <v>16.43</v>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
@@ -10675,115 +10683,107 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L59" s="15" t="inlineStr">
+      <c r="L59" s="15" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>EU.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>EU27</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F60" s="16" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="G60" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I60" s="13" t="inlineStr"/>
+      <c r="J60" s="14" t="inlineStr">
+        <is>
+          <t>ES5</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L60" s="15" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>IE.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C61" s="15" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F61" s="16" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="G61" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I61" s="13" t="inlineStr"/>
+      <c r="J61" s="14" t="inlineStr">
+        <is>
+          <t>ES5</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L61" s="15" t="inlineStr">
         <is>
           <t>Highest in EU.</t>
         </is>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="18" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="19" t="inlineStr">
-        <is>
-          <t>BE.ECM.ENT.TRN</t>
-        </is>
-      </c>
-      <c r="C60" s="20" t="inlineStr">
-        <is>
-          <t>E-sales as share of enterprise turnover</t>
-        </is>
-      </c>
-      <c r="D60" s="18" t="inlineStr">
-        <is>
-          <t>BE</t>
-        </is>
-      </c>
-      <c r="E60" s="18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F60" s="22" t="n">
-        <v>29.51</v>
-      </c>
-      <c r="G60" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H60" s="20" t="inlineStr">
-        <is>
-          <t>% of total enterprise turnover</t>
-        </is>
-      </c>
-      <c r="I60" s="18" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="J60" s="19" t="inlineStr">
-        <is>
-          <t>ES6</t>
-        </is>
-      </c>
-      <c r="K60" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L60" s="20" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="18" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="19" t="inlineStr">
-        <is>
-          <t>SE.ECM.ENT.TRN</t>
-        </is>
-      </c>
-      <c r="C61" s="20" t="inlineStr">
-        <is>
-          <t>E-sales as share of enterprise turnover</t>
-        </is>
-      </c>
-      <c r="D61" s="18" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="E61" s="18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F61" s="22" t="n">
-        <v>26.32</v>
-      </c>
-      <c r="G61" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H61" s="20" t="inlineStr">
-        <is>
-          <t>% of total enterprise turnover</t>
-        </is>
-      </c>
-      <c r="I61" s="18" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="J61" s="19" t="inlineStr">
-        <is>
-          <t>ES6</t>
-        </is>
-      </c>
-      <c r="K61" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L61" s="20" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="18" t="n">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="B62" s="19" t="inlineStr">
         <is>
-          <t>CZ.ECM.ENT.TRN</t>
+          <t>BE.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C62" s="20" t="inlineStr">
@@ -10801,14 +10801,14 @@
       </c>
       <c r="D62" s="18" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="E62" s="18" t="n">
         <v>2024</v>
       </c>
       <c r="F62" s="22" t="n">
-        <v>25.65</v>
+        <v>29.51</v>
       </c>
       <c r="G62" s="18" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
       </c>
       <c r="B63" s="19" t="inlineStr">
         <is>
-          <t>LU.ECM.ENT.TRN</t>
+          <t>SE.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C63" s="20" t="inlineStr">
@@ -10853,14 +10853,14 @@
       </c>
       <c r="D63" s="18" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="E63" s="18" t="n">
         <v>2024</v>
       </c>
       <c r="F63" s="22" t="n">
-        <v>23.86</v>
+        <v>26.32</v>
       </c>
       <c r="G63" s="18" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
       </c>
       <c r="B64" s="19" t="inlineStr">
         <is>
-          <t>HU.ECM.ENT.TRN</t>
+          <t>CZ.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
@@ -10905,14 +10905,14 @@
       </c>
       <c r="D64" s="18" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="E64" s="18" t="n">
         <v>2024</v>
       </c>
       <c r="F64" s="22" t="n">
-        <v>21.35</v>
+        <v>25.65</v>
       </c>
       <c r="G64" s="18" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
       </c>
       <c r="B65" s="19" t="inlineStr">
         <is>
-          <t>DE.ECM.ENT.TRN</t>
+          <t>LU.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C65" s="20" t="inlineStr">
@@ -10957,14 +10957,14 @@
       </c>
       <c r="D65" s="18" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="E65" s="18" t="n">
         <v>2024</v>
       </c>
       <c r="F65" s="22" t="n">
-        <v>19.05</v>
+        <v>23.86</v>
       </c>
       <c r="G65" s="18" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="B66" s="19" t="inlineStr">
         <is>
-          <t>AT.ECM.ENT.TRN</t>
+          <t>HU.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
@@ -11009,14 +11009,14 @@
       </c>
       <c r="D66" s="18" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="E66" s="18" t="n">
         <v>2024</v>
       </c>
       <c r="F66" s="22" t="n">
-        <v>18.96</v>
+        <v>21.35</v>
       </c>
       <c r="G66" s="18" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="B67" s="19" t="inlineStr">
         <is>
-          <t>HR.ECM.ENT.TRN</t>
+          <t>DE.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C67" s="20" t="inlineStr">
@@ -11061,14 +11061,14 @@
       </c>
       <c r="D67" s="18" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="E67" s="18" t="n">
         <v>2024</v>
       </c>
       <c r="F67" s="22" t="n">
-        <v>18.48</v>
+        <v>19.05</v>
       </c>
       <c r="G67" s="18" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
       </c>
       <c r="B68" s="19" t="inlineStr">
         <is>
-          <t>ES.ECM.ENT.TRN</t>
+          <t>AT.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
@@ -11113,14 +11113,14 @@
       </c>
       <c r="D68" s="18" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="E68" s="18" t="n">
         <v>2024</v>
       </c>
       <c r="F68" s="22" t="n">
-        <v>18.27</v>
+        <v>18.96</v>
       </c>
       <c r="G68" s="18" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="B69" s="19" t="inlineStr">
         <is>
-          <t>PL.ECM.ENT.TRN</t>
+          <t>HR.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C69" s="20" t="inlineStr">
@@ -11165,14 +11165,14 @@
       </c>
       <c r="D69" s="18" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="E69" s="18" t="n">
         <v>2024</v>
       </c>
       <c r="F69" s="22" t="n">
-        <v>17.66</v>
+        <v>18.48</v>
       </c>
       <c r="G69" s="18" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="B70" s="19" t="inlineStr">
         <is>
-          <t>SI.ECM.ENT.TRN</t>
+          <t>ES.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
@@ -11217,14 +11217,14 @@
       </c>
       <c r="D70" s="18" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="E70" s="18" t="n">
         <v>2024</v>
       </c>
       <c r="F70" s="22" t="n">
-        <v>16.78</v>
+        <v>18.27</v>
       </c>
       <c r="G70" s="18" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="B71" s="19" t="inlineStr">
         <is>
-          <t>IT.ECM.ENT.TRN</t>
+          <t>PL.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C71" s="20" t="inlineStr">
@@ -11269,14 +11269,14 @@
       </c>
       <c r="D71" s="18" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E71" s="18" t="n">
         <v>2024</v>
       </c>
       <c r="F71" s="22" t="n">
-        <v>15.66</v>
+        <v>17.66</v>
       </c>
       <c r="G71" s="18" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="B72" s="19" t="inlineStr">
         <is>
-          <t>MT.ECM.ENT.TRN</t>
+          <t>SI.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C72" s="20" t="inlineStr">
@@ -11321,14 +11321,14 @@
       </c>
       <c r="D72" s="18" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="E72" s="18" t="n">
         <v>2024</v>
       </c>
       <c r="F72" s="22" t="n">
-        <v>15.46</v>
+        <v>16.78</v>
       </c>
       <c r="G72" s="18" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
       </c>
       <c r="B73" s="19" t="inlineStr">
         <is>
-          <t>FR.ECM.ENT.TRN</t>
+          <t>IT.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C73" s="20" t="inlineStr">
@@ -11373,14 +11373,14 @@
       </c>
       <c r="D73" s="18" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E73" s="18" t="n">
         <v>2024</v>
       </c>
       <c r="F73" s="22" t="n">
-        <v>14.25</v>
+        <v>15.66</v>
       </c>
       <c r="G73" s="18" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
       </c>
       <c r="B74" s="19" t="inlineStr">
         <is>
-          <t>CY.ECM.ENT.TRN</t>
+          <t>MT.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
@@ -11425,14 +11425,14 @@
       </c>
       <c r="D74" s="18" t="inlineStr">
         <is>
-          <t>CY</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E74" s="18" t="n">
         <v>2024</v>
       </c>
       <c r="F74" s="22" t="n">
-        <v>13.36</v>
+        <v>15.46</v>
       </c>
       <c r="G74" s="18" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="B75" s="19" t="inlineStr">
         <is>
-          <t>BG.ECM.ENT.TRN</t>
+          <t>FR.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="C75" s="20" t="inlineStr">
@@ -11477,145 +11477,145 @@
       </c>
       <c r="D75" s="18" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E75" s="18" t="n">
         <v>2024</v>
       </c>
       <c r="F75" s="22" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="G75" s="18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H75" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I75" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J75" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K75" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L75" s="20" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="18" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="19" t="inlineStr">
+        <is>
+          <t>CY.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C76" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F76" s="22" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="G76" s="18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H76" s="20" t="inlineStr">
+        <is>
+          <t>% of total enterprise turnover</t>
+        </is>
+      </c>
+      <c r="I76" s="18" t="inlineStr">
+        <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J76" s="19" t="inlineStr">
+        <is>
+          <t>ES6</t>
+        </is>
+      </c>
+      <c r="K76" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L76" s="20" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="18" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="19" t="inlineStr">
+        <is>
+          <t>BG.ECM.ENT.TRN</t>
+        </is>
+      </c>
+      <c r="C77" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as share of enterprise turnover</t>
+        </is>
+      </c>
+      <c r="D77" s="18" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F77" s="22" t="n">
         <v>7.63</v>
       </c>
-      <c r="G75" s="18" t="inlineStr">
+      <c r="G77" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H75" s="20" t="inlineStr">
+      <c r="H77" s="20" t="inlineStr">
         <is>
           <t>% of total enterprise turnover</t>
         </is>
       </c>
-      <c r="I75" s="18" t="inlineStr">
+      <c r="I77" s="18" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="J75" s="19" t="inlineStr">
+      <c r="J77" s="19" t="inlineStr">
         <is>
           <t>ES6</t>
         </is>
       </c>
-      <c r="K75" s="18" t="inlineStr">
+      <c r="K77" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L75" s="20" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="13" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="14" t="inlineStr">
-        <is>
-          <t>DK.ECM.ENT.SHR</t>
-        </is>
-      </c>
-      <c r="C76" s="15" t="inlineStr">
-        <is>
-          <t>Enterprises making e-sales</t>
-        </is>
-      </c>
-      <c r="D76" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E76" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F76" s="16" t="n">
-        <v>38.78</v>
-      </c>
-      <c r="G76" s="13" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H76" s="15" t="inlineStr">
-        <is>
-          <t>% of enterprises</t>
-        </is>
-      </c>
-      <c r="I76" s="13" t="inlineStr"/>
-      <c r="J76" s="14" t="inlineStr">
-        <is>
-          <t>ES5</t>
-        </is>
-      </c>
-      <c r="K76" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L76" s="15" t="inlineStr">
-        <is>
-          <t>2nd in EU after Lithuania.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="13" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="14" t="inlineStr">
-        <is>
-          <t>LT.ECM.ENT.SHR</t>
-        </is>
-      </c>
-      <c r="C77" s="15" t="inlineStr">
-        <is>
-          <t>Enterprises making e-sales</t>
-        </is>
-      </c>
-      <c r="D77" s="13" t="inlineStr">
-        <is>
-          <t>LT</t>
-        </is>
-      </c>
-      <c r="E77" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F77" s="16" t="n">
-        <v>43.03</v>
-      </c>
-      <c r="G77" s="13" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H77" s="15" t="inlineStr">
-        <is>
-          <t>% of enterprises</t>
-        </is>
-      </c>
-      <c r="I77" s="13" t="inlineStr"/>
-      <c r="J77" s="14" t="inlineStr">
-        <is>
-          <t>ES5</t>
-        </is>
-      </c>
-      <c r="K77" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L77" s="15" t="inlineStr">
-        <is>
-          <t>Highest in EU.</t>
-        </is>
-      </c>
+      <c r="L77" s="20" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="13" t="n">
@@ -11623,12 +11623,12 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>DK.DGP.EXMP</t>
+          <t>DK.ECM.ENT.SHR</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Citizens formally exempt from Digital Post</t>
+          <t>Enterprises making e-sales</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr">
@@ -11637,10 +11637,10 @@
         </is>
       </c>
       <c r="E78" s="13" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F78" s="16" t="n">
-        <v>5</v>
+        <v>38.78</v>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
@@ -11649,13 +11649,13 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>% of citizens aged 15+ resident in Denmark</t>
+          <t>% of enterprises</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr"/>
       <c r="J78" s="14" t="inlineStr">
         <is>
-          <t>DG1</t>
+          <t>ES5</t>
         </is>
       </c>
       <c r="K78" s="13" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>April 2025; approx. 256,000 citizens.</t>
+          <t>2nd in EU after Lithuania.</t>
         </is>
       </c>
     </row>
@@ -11675,24 +11675,24 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>DK.DGP.EXMP</t>
+          <t>LT.ECM.ENT.SHR</t>
         </is>
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>Citizens formally exempt from Digital Post</t>
+          <t>Enterprises making e-sales</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="E79" s="13" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="F79" s="16" t="n">
-        <v>4.7</v>
+        <v>43.03</v>
       </c>
       <c r="G79" s="13" t="inlineStr">
         <is>
@@ -11701,351 +11701,343 @@
       </c>
       <c r="H79" s="15" t="inlineStr">
         <is>
-          <t>% of citizens aged 15+ resident in Denmark</t>
+          <t>% of enterprises</t>
         </is>
       </c>
       <c r="I79" s="13" t="inlineStr"/>
       <c r="J79" s="14" t="inlineStr">
         <is>
+          <t>ES5</t>
+        </is>
+      </c>
+      <c r="K79" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L79" s="15" t="inlineStr">
+        <is>
+          <t>Highest in EU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>DK.DGP.EXMP</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>Citizens formally exempt from Digital Post</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F80" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G80" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H80" s="15" t="inlineStr">
+        <is>
+          <t>% of citizens aged 15+ resident in Denmark</t>
+        </is>
+      </c>
+      <c r="I80" s="13" t="inlineStr"/>
+      <c r="J80" s="14" t="inlineStr">
+        <is>
           <t>DG1</t>
         </is>
       </c>
-      <c r="K79" s="13" t="inlineStr">
+      <c r="K80" s="13" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L79" s="15" t="inlineStr">
+      <c r="L80" s="15" t="inlineStr">
+        <is>
+          <t>April 2025; approx. 256,000 citizens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>DK.DGP.EXMP</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>Citizens formally exempt from Digital Post</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F81" s="16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G81" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H81" s="15" t="inlineStr">
+        <is>
+          <t>% of citizens aged 15+ resident in Denmark</t>
+        </is>
+      </c>
+      <c r="I81" s="13" t="inlineStr"/>
+      <c r="J81" s="14" t="inlineStr">
+        <is>
+          <t>DG1</t>
+        </is>
+      </c>
+      <c r="K81" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L81" s="15" t="inlineStr">
         <is>
           <t>Q1 2026; 238,479 citizens. 95.2% enrolled.</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="18" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="19" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="18" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="19" t="inlineStr">
         <is>
           <t>DK.DGP.EXMP.7584</t>
         </is>
       </c>
-      <c r="C80" s="20" t="inlineStr">
+      <c r="C82" s="20" t="inlineStr">
         <is>
           <t>Exemption rate, age 75-84</t>
         </is>
       </c>
-      <c r="D80" s="18" t="inlineStr">
+      <c r="D82" s="18" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E80" s="18" t="n">
+      <c r="E82" s="18" t="n">
         <v>2022</v>
       </c>
-      <c r="F80" s="22" t="n">
+      <c r="F82" s="22" t="n">
         <v>20</v>
       </c>
-      <c r="G80" s="18" t="inlineStr">
+      <c r="G82" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H80" s="20" t="inlineStr">
+      <c r="H82" s="20" t="inlineStr">
         <is>
           <t>% of age group</t>
         </is>
       </c>
-      <c r="I80" s="18" t="inlineStr">
+      <c r="I82" s="18" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="J80" s="19" t="inlineStr">
+      <c r="J82" s="19" t="inlineStr">
         <is>
           <t>DG1</t>
         </is>
       </c>
-      <c r="K80" s="18" t="inlineStr">
+      <c r="K82" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L80" s="20" t="inlineStr">
+      <c r="L82" s="20" t="inlineStr">
         <is>
           <t>Source states 'nearly one in five'.</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="18" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="19" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="18" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="19" t="inlineStr">
         <is>
           <t>DK.DGP.EXMP.85P</t>
         </is>
       </c>
-      <c r="C81" s="20" t="inlineStr">
+      <c r="C83" s="20" t="inlineStr">
         <is>
           <t>Exemption rate, age 85+</t>
         </is>
       </c>
-      <c r="D81" s="18" t="inlineStr">
+      <c r="D83" s="18" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E81" s="18" t="n">
+      <c r="E83" s="18" t="n">
         <v>2022</v>
       </c>
-      <c r="F81" s="22" t="n">
+      <c r="F83" s="22" t="n">
         <v>33</v>
       </c>
-      <c r="G81" s="18" t="inlineStr">
+      <c r="G83" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H81" s="20" t="inlineStr">
+      <c r="H83" s="20" t="inlineStr">
         <is>
           <t>% of age group</t>
         </is>
       </c>
-      <c r="I81" s="18" t="inlineStr">
+      <c r="I83" s="18" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="J81" s="19" t="inlineStr">
+      <c r="J83" s="19" t="inlineStr">
         <is>
           <t>DG1</t>
         </is>
       </c>
-      <c r="K81" s="18" t="inlineStr">
+      <c r="K83" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L81" s="20" t="inlineStr">
+      <c r="L83" s="20" t="inlineStr">
         <is>
           <t>Source states 'roughly one in three'.</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="13" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="14" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
         <is>
           <t>DK.DGX.NOUSE</t>
         </is>
       </c>
-      <c r="C82" s="15" t="inlineStr">
+      <c r="C84" s="15" t="inlineStr">
         <is>
           <t>Do not use digital public services at all</t>
         </is>
       </c>
-      <c r="D82" s="13" t="inlineStr">
+      <c r="D84" s="13" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E82" s="13" t="n">
+      <c r="E84" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="F82" s="16" t="n">
+      <c r="F84" s="16" t="n">
         <v>6.5</v>
       </c>
-      <c r="G82" s="13" t="inlineStr">
+      <c r="G84" s="13" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H82" s="15" t="inlineStr">
+      <c r="H84" s="15" t="inlineStr">
         <is>
           <t>% of population</t>
         </is>
       </c>
-      <c r="I82" s="13" t="inlineStr"/>
-      <c r="J82" s="14" t="inlineStr">
+      <c r="I84" s="13" t="inlineStr"/>
+      <c r="J84" s="14" t="inlineStr">
         <is>
           <t>EC1</t>
         </is>
       </c>
-      <c r="K82" s="13" t="inlineStr">
+      <c r="K84" s="13" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L82" s="15" t="inlineStr">
+      <c r="L84" s="15" t="inlineStr">
         <is>
           <t>Agency for Digital Government estimate.</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="13" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="14" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="13" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
         <is>
           <t>DK.DGX.DIFF</t>
         </is>
       </c>
-      <c r="C83" s="15" t="inlineStr">
+      <c r="C85" s="15" t="inlineStr">
         <is>
           <t>Face difficulties using digital public services</t>
         </is>
       </c>
-      <c r="D83" s="13" t="inlineStr">
+      <c r="D85" s="13" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E83" s="13" t="n">
+      <c r="E85" s="13" t="n">
         <v>2026</v>
       </c>
-      <c r="F83" s="16" t="n">
+      <c r="F85" s="16" t="n">
         <v>16.5</v>
       </c>
-      <c r="G83" s="13" t="inlineStr">
+      <c r="G85" s="13" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H83" s="15" t="inlineStr">
+      <c r="H85" s="15" t="inlineStr">
         <is>
           <t>% of population</t>
         </is>
       </c>
-      <c r="I83" s="13" t="inlineStr"/>
-      <c r="J83" s="14" t="inlineStr">
+      <c r="I85" s="13" t="inlineStr"/>
+      <c r="J85" s="14" t="inlineStr">
         <is>
           <t>EC1</t>
         </is>
       </c>
-      <c r="K83" s="13" t="inlineStr">
+      <c r="K85" s="13" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L83" s="15" t="inlineStr">
+      <c r="L85" s="15" t="inlineStr">
         <is>
           <t>Agency for Digital Government estimate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="18" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="19" t="inlineStr">
-        <is>
-          <t>DK.DGX.DISADV.LO</t>
-        </is>
-      </c>
-      <c r="C84" s="20" t="inlineStr">
-        <is>
-          <t>'Digitally disadvantaged' - lower bound</t>
-        </is>
-      </c>
-      <c r="D84" s="18" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E84" s="18" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>17</v>
-      </c>
-      <c r="G84" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H84" s="20" t="inlineStr">
-        <is>
-          <t>% of adult population</t>
-        </is>
-      </c>
-      <c r="I84" s="18" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J84" s="19" t="inlineStr">
-        <is>
-          <t>DG2</t>
-        </is>
-      </c>
-      <c r="K84" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L84" s="20" t="inlineStr">
-        <is>
-          <t>Published as a 17-22% range.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="18" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="19" t="inlineStr">
-        <is>
-          <t>DK.DGX.DISADV.HI</t>
-        </is>
-      </c>
-      <c r="C85" s="20" t="inlineStr">
-        <is>
-          <t>'Digitally disadvantaged' - upper bound</t>
-        </is>
-      </c>
-      <c r="D85" s="18" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E85" s="18" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F85" s="22" t="n">
-        <v>22</v>
-      </c>
-      <c r="G85" s="18" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H85" s="20" t="inlineStr">
-        <is>
-          <t>% of adult population</t>
-        </is>
-      </c>
-      <c r="I85" s="18" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J85" s="19" t="inlineStr">
-        <is>
-          <t>DG2</t>
-        </is>
-      </c>
-      <c r="K85" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L85" s="20" t="inlineStr">
-        <is>
-          <t>Published as a 17-22% range.</t>
         </is>
       </c>
     </row>
@@ -12055,153 +12047,165 @@
       </c>
       <c r="B86" s="19" t="inlineStr">
         <is>
+          <t>DK.DGX.DISADV.LO</t>
+        </is>
+      </c>
+      <c r="C86" s="20" t="inlineStr">
+        <is>
+          <t>'Digitally disadvantaged' - lower bound</t>
+        </is>
+      </c>
+      <c r="D86" s="18" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E86" s="18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F86" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="G86" s="18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H86" s="20" t="inlineStr">
+        <is>
+          <t>% of adult population</t>
+        </is>
+      </c>
+      <c r="I86" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J86" s="19" t="inlineStr">
+        <is>
+          <t>DG2</t>
+        </is>
+      </c>
+      <c r="K86" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L86" s="20" t="inlineStr">
+        <is>
+          <t>Published as a 17-22% range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="19" t="inlineStr">
+        <is>
+          <t>DK.DGX.DISADV.HI</t>
+        </is>
+      </c>
+      <c r="C87" s="20" t="inlineStr">
+        <is>
+          <t>'Digitally disadvantaged' - upper bound</t>
+        </is>
+      </c>
+      <c r="D87" s="18" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E87" s="18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F87" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="G87" s="18" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H87" s="20" t="inlineStr">
+        <is>
+          <t>% of adult population</t>
+        </is>
+      </c>
+      <c r="I87" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J87" s="19" t="inlineStr">
+        <is>
+          <t>DG2</t>
+        </is>
+      </c>
+      <c r="K87" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L87" s="20" t="inlineStr">
+        <is>
+          <t>Published as a 17-22% range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="18" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="19" t="inlineStr">
+        <is>
           <t>DK.DGX.JUST</t>
         </is>
       </c>
-      <c r="C86" s="20" t="inlineStr">
+      <c r="C88" s="20" t="inlineStr">
         <is>
           <t>'Digitally disadvantaged' - Justitia estimate</t>
         </is>
       </c>
-      <c r="D86" s="18" t="inlineStr">
+      <c r="D88" s="18" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E86" s="18" t="n">
+      <c r="E88" s="18" t="n">
         <v>2022</v>
       </c>
-      <c r="F86" s="22" t="n">
+      <c r="F88" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="G86" s="18" t="inlineStr">
+      <c r="G88" s="18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="H86" s="20" t="inlineStr">
+      <c r="H88" s="20" t="inlineStr">
         <is>
           <t>% of adult population</t>
         </is>
       </c>
-      <c r="I86" s="18" t="inlineStr">
+      <c r="I88" s="18" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="J86" s="19" t="inlineStr">
+      <c r="J88" s="19" t="inlineStr">
         <is>
           <t>JU1</t>
         </is>
       </c>
-      <c r="K86" s="18" t="inlineStr">
+      <c r="K88" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L86" s="20" t="inlineStr">
+      <c r="L88" s="20" t="inlineStr">
         <is>
           <t>Report states 'up to a quarter of the adult population'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="13" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="14" t="inlineStr">
-        <is>
-          <t>DK.TRU.DPS</t>
-        </is>
-      </c>
-      <c r="C87" s="15" t="inlineStr">
-        <is>
-          <t>Trust in digital public solutions</t>
-        </is>
-      </c>
-      <c r="D87" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E87" s="13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F87" s="16" t="n">
-        <v>82</v>
-      </c>
-      <c r="G87" s="13" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H87" s="15" t="inlineStr">
-        <is>
-          <t>% of population</t>
-        </is>
-      </c>
-      <c r="I87" s="13" t="inlineStr"/>
-      <c r="J87" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K87" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L87" s="15" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="13" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="14" t="inlineStr">
-        <is>
-          <t>DK.TRU.DPS</t>
-        </is>
-      </c>
-      <c r="C88" s="15" t="inlineStr">
-        <is>
-          <t>Trust in digital public solutions</t>
-        </is>
-      </c>
-      <c r="D88" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E88" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F88" s="16" t="n">
-        <v>84</v>
-      </c>
-      <c r="G88" s="13" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H88" s="15" t="inlineStr">
-        <is>
-          <t>% of population</t>
-        </is>
-      </c>
-      <c r="I88" s="13" t="inlineStr"/>
-      <c r="J88" s="14" t="inlineStr">
-        <is>
-          <t>EC1</t>
-        </is>
-      </c>
-      <c r="K88" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L88" s="15" t="inlineStr">
-        <is>
-          <t>Record high.</t>
         </is>
       </c>
     </row>
@@ -12211,12 +12215,12 @@
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>DK.TRU.DGP.SEC</t>
+          <t>DK.TRU.DPS</t>
         </is>
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>Perceived security of Digital Post</t>
+          <t>Trust in digital public solutions</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr">
@@ -12225,10 +12229,10 @@
         </is>
       </c>
       <c r="E89" s="13" t="n">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="F89" s="16" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G89" s="13" t="inlineStr">
         <is>
@@ -12259,12 +12263,12 @@
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>DK.TRU.DGP.SEC</t>
+          <t>DK.TRU.DPS</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Perceived security of Digital Post</t>
+          <t>Trust in digital public solutions</t>
         </is>
       </c>
       <c r="D90" s="13" t="inlineStr">
@@ -12276,7 +12280,7 @@
         <v>2025</v>
       </c>
       <c r="F90" s="16" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
@@ -12299,7 +12303,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L90" s="15" t="inlineStr"/>
+      <c r="L90" s="15" t="inlineStr">
+        <is>
+          <t>Record high.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="13" t="n">
@@ -12307,12 +12315,12 @@
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>DK.SKL.1624</t>
+          <t>DK.TRU.DGP.SEC</t>
         </is>
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>At least basic digital skills, age 16-24</t>
+          <t>Perceived security of Digital Post</t>
         </is>
       </c>
       <c r="D91" s="13" t="inlineStr">
@@ -12321,10 +12329,10 @@
         </is>
       </c>
       <c r="E91" s="13" t="n">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="F91" s="16" t="n">
-        <v>92.06</v>
+        <v>77</v>
       </c>
       <c r="G91" s="13" t="inlineStr">
         <is>
@@ -12333,7 +12341,7 @@
       </c>
       <c r="H91" s="15" t="inlineStr">
         <is>
-          <t>% of age group</t>
+          <t>% of population</t>
         </is>
       </c>
       <c r="I91" s="13" t="inlineStr"/>
@@ -12347,11 +12355,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L91" s="15" t="inlineStr">
-        <is>
-          <t>EU average carried as EU.SKL.1624.</t>
-        </is>
-      </c>
+      <c r="L91" s="15" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="13" t="n">
@@ -12359,12 +12363,12 @@
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>DK.SKL.2554</t>
+          <t>DK.TRU.DGP.SEC</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>At least basic digital skills, age 25-54</t>
+          <t>Perceived security of Digital Post</t>
         </is>
       </c>
       <c r="D92" s="13" t="inlineStr">
@@ -12376,7 +12380,7 @@
         <v>2025</v>
       </c>
       <c r="F92" s="16" t="n">
-        <v>86.89</v>
+        <v>89</v>
       </c>
       <c r="G92" s="13" t="inlineStr">
         <is>
@@ -12385,7 +12389,7 @@
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>% of age group</t>
+          <t>% of population</t>
         </is>
       </c>
       <c r="I92" s="13" t="inlineStr"/>
@@ -12399,11 +12403,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L92" s="15" t="inlineStr">
-        <is>
-          <t>EU average carried as EU.SKL.2554.</t>
-        </is>
-      </c>
+      <c r="L92" s="15" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="13" t="n">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>DK.SKL.5574</t>
+          <t>DK.SKL.1624</t>
         </is>
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>At least basic digital skills, age 55-74</t>
+          <t>At least basic digital skills, age 16-24</t>
         </is>
       </c>
       <c r="D93" s="13" t="inlineStr">
@@ -12428,7 +12428,7 @@
         <v>2025</v>
       </c>
       <c r="F93" s="16" t="n">
-        <v>67.81</v>
+        <v>92.06</v>
       </c>
       <c r="G93" s="13" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="L93" s="15" t="inlineStr">
         <is>
-          <t>EU average carried as EU.SKL.5574.</t>
+          <t>EU average carried as EU.SKL.1624.</t>
         </is>
       </c>
     </row>
@@ -12463,24 +12463,24 @@
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>EU.SKL.1624</t>
+          <t>DK.SKL.2554</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>At least basic digital skills, age 16-24</t>
+          <t>At least basic digital skills, age 25-54</t>
         </is>
       </c>
       <c r="D94" s="13" t="inlineStr">
         <is>
-          <t>EU27</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="E94" s="13" t="n">
         <v>2025</v>
       </c>
       <c r="F94" s="16" t="n">
-        <v>74.55</v>
+        <v>86.89</v>
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>Comparator for DK.SKL.1624.</t>
+          <t>EU average carried as EU.SKL.2554.</t>
         </is>
       </c>
     </row>
@@ -12515,24 +12515,24 @@
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>EU.SKL.2554</t>
+          <t>DK.SKL.5574</t>
         </is>
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>At least basic digital skills, age 25-54</t>
+          <t>At least basic digital skills, age 55-74</t>
         </is>
       </c>
       <c r="D95" s="13" t="inlineStr">
         <is>
-          <t>EU27</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="E95" s="13" t="n">
         <v>2025</v>
       </c>
       <c r="F95" s="16" t="n">
-        <v>68.56999999999999</v>
+        <v>67.81</v>
       </c>
       <c r="G95" s="13" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
       </c>
       <c r="L95" s="15" t="inlineStr">
         <is>
-          <t>Comparator for DK.SKL.2554.</t>
+          <t>EU average carried as EU.SKL.5574.</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>EU.SKL.5574</t>
+          <t>EU.SKL.1624</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
         <is>
-          <t>At least basic digital skills, age 55-74</t>
+          <t>At least basic digital skills, age 16-24</t>
         </is>
       </c>
       <c r="D96" s="13" t="inlineStr">
@@ -12584,7 +12584,7 @@
         <v>2025</v>
       </c>
       <c r="F96" s="16" t="n">
-        <v>42.6</v>
+        <v>74.55</v>
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>Comparator for DK.SKL.5574.</t>
+          <t>Comparator for DK.SKL.1624.</t>
         </is>
       </c>
     </row>
@@ -12619,24 +12619,24 @@
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>DK.ENT.DII</t>
+          <t>EU.SKL.2554</t>
         </is>
       </c>
       <c r="C97" s="15" t="inlineStr">
         <is>
-          <t>SMEs with at least basic digital intensity</t>
+          <t>At least basic digital skills, age 25-54</t>
         </is>
       </c>
       <c r="D97" s="13" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>EU27</t>
         </is>
       </c>
       <c r="E97" s="13" t="n">
         <v>2025</v>
       </c>
       <c r="F97" s="16" t="n">
-        <v>92.45</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
       </c>
       <c r="H97" s="15" t="inlineStr">
         <is>
-          <t>% of SMEs</t>
+          <t>% of age group</t>
         </is>
       </c>
       <c r="I97" s="13" t="inlineStr"/>
@@ -12661,7 +12661,7 @@
       </c>
       <c r="L97" s="15" t="inlineStr">
         <is>
-          <t>EU average 71.39%.</t>
+          <t>Comparator for DK.SKL.2554.</t>
         </is>
       </c>
     </row>
@@ -12671,12 +12671,12 @@
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>EU.ENT.DII</t>
+          <t>EU.SKL.5574</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>SMEs with at least basic digital intensity</t>
+          <t>At least basic digital skills, age 55-74</t>
         </is>
       </c>
       <c r="D98" s="13" t="inlineStr">
@@ -12688,7 +12688,7 @@
         <v>2025</v>
       </c>
       <c r="F98" s="16" t="n">
-        <v>71.39</v>
+        <v>42.6</v>
       </c>
       <c r="G98" s="13" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
       </c>
       <c r="H98" s="15" t="inlineStr">
         <is>
-          <t>% of SMEs</t>
+          <t>% of age group</t>
         </is>
       </c>
       <c r="I98" s="13" t="inlineStr"/>
@@ -12711,7 +12711,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L98" s="15" t="inlineStr"/>
+      <c r="L98" s="15" t="inlineStr">
+        <is>
+          <t>Comparator for DK.SKL.5574.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="13" t="n">
@@ -12719,12 +12723,12 @@
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>DK.ENT.AI</t>
+          <t>DK.ENT.DII</t>
         </is>
       </c>
       <c r="C99" s="15" t="inlineStr">
         <is>
-          <t>Enterprises adopting AI</t>
+          <t>SMEs with at least basic digital intensity</t>
         </is>
       </c>
       <c r="D99" s="13" t="inlineStr">
@@ -12736,7 +12740,7 @@
         <v>2025</v>
       </c>
       <c r="F99" s="16" t="n">
-        <v>42.03</v>
+        <v>92.45</v>
       </c>
       <c r="G99" s="13" t="inlineStr">
         <is>
@@ -12745,7 +12749,7 @@
       </c>
       <c r="H99" s="15" t="inlineStr">
         <is>
-          <t>% of enterprises</t>
+          <t>% of SMEs</t>
         </is>
       </c>
       <c r="I99" s="13" t="inlineStr"/>
@@ -12761,7 +12765,7 @@
       </c>
       <c r="L99" s="15" t="inlineStr">
         <is>
-          <t>EU average 19.95%.</t>
+          <t>EU average 71.39%.</t>
         </is>
       </c>
     </row>
@@ -12771,24 +12775,24 @@
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>DK.ENT.AI.LRG</t>
+          <t>EU.ENT.DII</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Large enterprises adopting AI</t>
+          <t>SMEs with at least basic digital intensity</t>
         </is>
       </c>
       <c r="D100" s="13" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>EU27</t>
         </is>
       </c>
       <c r="E100" s="13" t="n">
         <v>2025</v>
       </c>
       <c r="F100" s="16" t="n">
-        <v>74.52</v>
+        <v>71.39</v>
       </c>
       <c r="G100" s="13" t="inlineStr">
         <is>
@@ -12797,7 +12801,7 @@
       </c>
       <c r="H100" s="15" t="inlineStr">
         <is>
-          <t>% of large enterprises (250+)</t>
+          <t>% of SMEs</t>
         </is>
       </c>
       <c r="I100" s="13" t="inlineStr"/>
@@ -12819,12 +12823,12 @@
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>DK.ENT.AI.SME</t>
+          <t>DK.ENT.AI</t>
         </is>
       </c>
       <c r="C101" s="15" t="inlineStr">
         <is>
-          <t>SMEs adopting AI</t>
+          <t>Enterprises adopting AI</t>
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr">
@@ -12836,7 +12840,7 @@
         <v>2025</v>
       </c>
       <c r="F101" s="16" t="n">
-        <v>40.99</v>
+        <v>42.03</v>
       </c>
       <c r="G101" s="13" t="inlineStr">
         <is>
@@ -12845,7 +12849,7 @@
       </c>
       <c r="H101" s="15" t="inlineStr">
         <is>
-          <t>% of SMEs (10-249)</t>
+          <t>% of enterprises</t>
         </is>
       </c>
       <c r="I101" s="13" t="inlineStr"/>
@@ -12859,7 +12863,11 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L101" s="15" t="inlineStr"/>
+      <c r="L101" s="15" t="inlineStr">
+        <is>
+          <t>EU average 19.95%.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="13" t="n">
@@ -12867,12 +12875,12 @@
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>DK.GOV.DPS.CIT</t>
+          <t>DK.ENT.AI.LRG</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Digital public services for citizens (score)</t>
+          <t>Large enterprises adopting AI</t>
         </is>
       </c>
       <c r="D102" s="13" t="inlineStr">
@@ -12884,16 +12892,16 @@
         <v>2025</v>
       </c>
       <c r="F102" s="16" t="n">
-        <v>82.2</v>
+        <v>74.52</v>
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
-          <t>score 0-100</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H102" s="15" t="inlineStr">
         <is>
-          <t>eGovernment Benchmark score</t>
+          <t>% of large enterprises (250+)</t>
         </is>
       </c>
       <c r="I102" s="13" t="inlineStr"/>
@@ -12907,11 +12915,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L102" s="15" t="inlineStr">
-        <is>
-          <t>BELOW the EU average of 84.64.</t>
-        </is>
-      </c>
+      <c r="L102" s="15" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="13" t="n">
@@ -12919,33 +12923,33 @@
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>EU.GOV.DPS.CIT</t>
+          <t>DK.ENT.AI.SME</t>
         </is>
       </c>
       <c r="C103" s="15" t="inlineStr">
         <is>
-          <t>Digital public services for citizens (score)</t>
+          <t>SMEs adopting AI</t>
         </is>
       </c>
       <c r="D103" s="13" t="inlineStr">
         <is>
-          <t>EU27</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="E103" s="13" t="n">
         <v>2025</v>
       </c>
       <c r="F103" s="16" t="n">
-        <v>84.64</v>
+        <v>40.99</v>
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>score 0-100</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H103" s="15" t="inlineStr">
         <is>
-          <t>eGovernment Benchmark score</t>
+          <t>% of SMEs (10-249)</t>
         </is>
       </c>
       <c r="I103" s="13" t="inlineStr"/>
@@ -12967,12 +12971,12 @@
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>DK.GOV.DPS.XB</t>
+          <t>DK.GOV.DPS.CIT</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Cross-border digital public services, citizens (score)</t>
+          <t>Digital public services for citizens (score)</t>
         </is>
       </c>
       <c r="D104" s="13" t="inlineStr">
@@ -12984,7 +12988,7 @@
         <v>2025</v>
       </c>
       <c r="F104" s="16" t="n">
-        <v>64.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="G104" s="13" t="inlineStr">
         <is>
@@ -13009,7 +13013,7 @@
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>EU average 75.28.</t>
+          <t>BELOW the EU average of 84.64.</t>
         </is>
       </c>
     </row>
@@ -13019,33 +13023,33 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>DK.ENV.WEEE</t>
+          <t>EU.GOV.DPS.CIT</t>
         </is>
       </c>
       <c r="C105" s="15" t="inlineStr">
         <is>
-          <t>ICT waste recycled or prepared for reuse</t>
+          <t>Digital public services for citizens (score)</t>
         </is>
       </c>
       <c r="D105" s="13" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>EU27</t>
         </is>
       </c>
       <c r="E105" s="13" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="F105" s="16" t="n">
-        <v>15.37</v>
+        <v>84.64</v>
       </c>
       <c r="G105" s="13" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>score 0-100</t>
         </is>
       </c>
       <c r="H105" s="15" t="inlineStr">
         <is>
-          <t>% of ICT-related WEEE collected</t>
+          <t>eGovernment Benchmark score</t>
         </is>
       </c>
       <c r="I105" s="13" t="inlineStr"/>
@@ -13059,11 +13063,7 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L105" s="15" t="inlineStr">
-        <is>
-          <t>Among the lowest in the EU; EU average 80.23%.</t>
-        </is>
-      </c>
+      <c r="L105" s="15" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="13" t="n">
@@ -13071,33 +13071,33 @@
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>EU.ENV.WEEE</t>
+          <t>DK.GOV.DPS.XB</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>ICT waste recycled or prepared for reuse</t>
+          <t>Cross-border digital public services, citizens (score)</t>
         </is>
       </c>
       <c r="D106" s="13" t="inlineStr">
         <is>
-          <t>EU27</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="E106" s="13" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="F106" s="16" t="n">
-        <v>80.23</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G106" s="13" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>score 0-100</t>
         </is>
       </c>
       <c r="H106" s="15" t="inlineStr">
         <is>
-          <t>% of ICT-related WEEE collected</t>
+          <t>eGovernment Benchmark score</t>
         </is>
       </c>
       <c r="I106" s="13" t="inlineStr"/>
@@ -13111,61 +13111,61 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L106" s="15" t="inlineStr"/>
+      <c r="L106" s="15" t="inlineStr">
+        <is>
+          <t>EU average 75.28.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="18" t="n">
+      <c r="A107" s="13" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="19" t="inlineStr">
-        <is>
-          <t>DK.SME.SMVD.PROJ</t>
-        </is>
-      </c>
-      <c r="C107" s="20" t="inlineStr">
-        <is>
-          <t>SMV:Digital projects supported since 2018</t>
-        </is>
-      </c>
-      <c r="D107" s="18" t="inlineStr">
+      <c r="B107" s="14" t="inlineStr">
+        <is>
+          <t>DK.ENV.WEEE</t>
+        </is>
+      </c>
+      <c r="C107" s="15" t="inlineStr">
+        <is>
+          <t>ICT waste recycled or prepared for reuse</t>
+        </is>
+      </c>
+      <c r="D107" s="13" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E107" s="18" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F107" s="21" t="n">
-        <v>7000</v>
-      </c>
-      <c r="G107" s="18" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H107" s="20" t="inlineStr">
-        <is>
-          <t>digitalisation projects</t>
-        </is>
-      </c>
-      <c r="I107" s="18" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J107" s="19" t="inlineStr">
-        <is>
-          <t>DG3</t>
-        </is>
-      </c>
-      <c r="K107" s="18" t="inlineStr">
+      <c r="E107" s="13" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F107" s="16" t="n">
+        <v>15.37</v>
+      </c>
+      <c r="G107" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H107" s="15" t="inlineStr">
+        <is>
+          <t>% of ICT-related WEEE collected</t>
+        </is>
+      </c>
+      <c r="I107" s="13" t="inlineStr"/>
+      <c r="J107" s="14" t="inlineStr">
+        <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K107" s="13" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L107" s="20" t="inlineStr">
-        <is>
-          <t>Source states 'knap 7.000' (just under 7,000).</t>
+      <c r="L107" s="15" t="inlineStr">
+        <is>
+          <t>Among the lowest in the EU; EU average 80.23%.</t>
         </is>
       </c>
     </row>
@@ -13175,24 +13175,24 @@
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>DK.SME.SMVD.INV</t>
+          <t>EU.ENV.WEEE</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>Participants who invested further during the project</t>
+          <t>ICT waste recycled or prepared for reuse</t>
         </is>
       </c>
       <c r="D108" s="13" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>EU27</t>
         </is>
       </c>
       <c r="E108" s="13" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="F108" s="16" t="n">
-        <v>65</v>
+        <v>80.23</v>
       </c>
       <c r="G108" s="13" t="inlineStr">
         <is>
@@ -13201,69 +13201,77 @@
       </c>
       <c r="H108" s="15" t="inlineStr">
         <is>
-          <t>% of participating enterprises</t>
+          <t>% of ICT-related WEEE collected</t>
         </is>
       </c>
       <c r="I108" s="13" t="inlineStr"/>
       <c r="J108" s="14" t="inlineStr">
         <is>
+          <t>EC1</t>
+        </is>
+      </c>
+      <c r="K108" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L108" s="15" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="18" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="19" t="inlineStr">
+        <is>
+          <t>DK.SME.SMVD.PROJ</t>
+        </is>
+      </c>
+      <c r="C109" s="20" t="inlineStr">
+        <is>
+          <t>SMV:Digital projects supported since 2018</t>
+        </is>
+      </c>
+      <c r="D109" s="18" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E109" s="18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F109" s="21" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G109" s="18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H109" s="20" t="inlineStr">
+        <is>
+          <t>digitalisation projects</t>
+        </is>
+      </c>
+      <c r="I109" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J109" s="19" t="inlineStr">
+        <is>
           <t>DG3</t>
         </is>
       </c>
-      <c r="K108" s="13" t="inlineStr">
+      <c r="K109" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L108" s="15" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="13" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" s="14" t="inlineStr">
-        <is>
-          <t>DK.SME.SMVD.NOINV</t>
-        </is>
-      </c>
-      <c r="C109" s="15" t="inlineStr">
-        <is>
-          <t>Participants with no further investment plans</t>
-        </is>
-      </c>
-      <c r="D109" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E109" s="13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F109" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G109" s="13" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="H109" s="15" t="inlineStr">
-        <is>
-          <t>% of participating enterprises</t>
-        </is>
-      </c>
-      <c r="I109" s="13" t="inlineStr"/>
-      <c r="J109" s="14" t="inlineStr">
-        <is>
-          <t>DG3</t>
-        </is>
-      </c>
-      <c r="K109" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L109" s="15" t="inlineStr"/>
+      <c r="L109" s="20" t="inlineStr">
+        <is>
+          <t>Source states 'knap 7.000' (just under 7,000).</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="13" t="n">
@@ -13271,12 +13279,12 @@
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>DK.POP.TOT</t>
+          <t>DK.SME.SMVD.INV</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>Resident population</t>
+          <t>Participants who invested further during the project</t>
         </is>
       </c>
       <c r="D110" s="13" t="inlineStr">
@@ -13285,25 +13293,25 @@
         </is>
       </c>
       <c r="E110" s="13" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F110" s="17" t="n">
-        <v>6025603</v>
+        <v>2025</v>
+      </c>
+      <c r="F110" s="16" t="n">
+        <v>65</v>
       </c>
       <c r="G110" s="13" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>%</t>
         </is>
       </c>
       <c r="H110" s="15" t="inlineStr">
         <is>
-          <t>persons resident in Denmark</t>
+          <t>% of participating enterprises</t>
         </is>
       </c>
       <c r="I110" s="13" t="inlineStr"/>
       <c r="J110" s="14" t="inlineStr">
         <is>
-          <t>DST2</t>
+          <t>DG3</t>
         </is>
       </c>
       <c r="K110" s="13" t="inlineStr">
@@ -13311,67 +13319,55 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L110" s="15" t="inlineStr">
-        <is>
-          <t>As at 1 January 2026.</t>
-        </is>
-      </c>
+      <c r="L110" s="15" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="18" t="n">
+      <c r="A111" s="13" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="19" t="inlineStr">
-        <is>
-          <t>DK.DGP.EXMP.N</t>
-        </is>
-      </c>
-      <c r="C111" s="20" t="inlineStr">
-        <is>
-          <t>Citizens formally exempt from Digital Post</t>
-        </is>
-      </c>
-      <c r="D111" s="18" t="inlineStr">
+      <c r="B111" s="14" t="inlineStr">
+        <is>
+          <t>DK.SME.SMVD.NOINV</t>
+        </is>
+      </c>
+      <c r="C111" s="15" t="inlineStr">
+        <is>
+          <t>Participants with no further investment plans</t>
+        </is>
+      </c>
+      <c r="D111" s="13" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E111" s="18" t="n">
+      <c r="E111" s="13" t="n">
         <v>2025</v>
       </c>
-      <c r="F111" s="21" t="n">
-        <v>256000</v>
-      </c>
-      <c r="G111" s="18" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="H111" s="20" t="inlineStr">
-        <is>
-          <t>citizens aged 15+ resident in Denmark</t>
-        </is>
-      </c>
-      <c r="I111" s="18" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="J111" s="19" t="inlineStr">
-        <is>
-          <t>DG1</t>
-        </is>
-      </c>
-      <c r="K111" s="18" t="inlineStr">
+      <c r="F111" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G111" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H111" s="15" t="inlineStr">
+        <is>
+          <t>% of participating enterprises</t>
+        </is>
+      </c>
+      <c r="I111" s="13" t="inlineStr"/>
+      <c r="J111" s="14" t="inlineStr">
+        <is>
+          <t>DG3</t>
+        </is>
+      </c>
+      <c r="K111" s="13" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L111" s="20" t="inlineStr">
-        <is>
-          <t>April 2025; source states approx. 256,000.</t>
-        </is>
-      </c>
+      <c r="L111" s="15" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="13" t="n">
@@ -13379,12 +13375,12 @@
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>DK.DGP.EXMP.N</t>
+          <t>DK.POP.TOT</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Citizens formally exempt from Digital Post</t>
+          <t>Resident population</t>
         </is>
       </c>
       <c r="D112" s="13" t="inlineStr">
@@ -13396,7 +13392,7 @@
         <v>2026</v>
       </c>
       <c r="F112" s="17" t="n">
-        <v>238479</v>
+        <v>6025603</v>
       </c>
       <c r="G112" s="13" t="inlineStr">
         <is>
@@ -13405,13 +13401,13 @@
       </c>
       <c r="H112" s="15" t="inlineStr">
         <is>
-          <t>citizens aged 15+ resident in Denmark</t>
+          <t>persons resident in Denmark</t>
         </is>
       </c>
       <c r="I112" s="13" t="inlineStr"/>
       <c r="J112" s="14" t="inlineStr">
         <is>
-          <t>DG1</t>
+          <t>DST2</t>
         </is>
       </c>
       <c r="K112" s="13" t="inlineStr">
@@ -13421,7 +13417,7 @@
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>Q1 2026. Paired with the 4.7% rate, implies a 15+ base of about 5.07m.</t>
+          <t>As at 1 January 2026.</t>
         </is>
       </c>
     </row>
@@ -13431,207 +13427,219 @@
       </c>
       <c r="B113" s="19" t="inlineStr">
         <is>
+          <t>DK.DGP.EXMP.N</t>
+        </is>
+      </c>
+      <c r="C113" s="20" t="inlineStr">
+        <is>
+          <t>Citizens formally exempt from Digital Post</t>
+        </is>
+      </c>
+      <c r="D113" s="18" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E113" s="18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F113" s="21" t="n">
+        <v>256000</v>
+      </c>
+      <c r="G113" s="18" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H113" s="20" t="inlineStr">
+        <is>
+          <t>citizens aged 15+ resident in Denmark</t>
+        </is>
+      </c>
+      <c r="I113" s="18" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="J113" s="19" t="inlineStr">
+        <is>
+          <t>DG1</t>
+        </is>
+      </c>
+      <c r="K113" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L113" s="20" t="inlineStr">
+        <is>
+          <t>April 2025; source states approx. 256,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="13" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="14" t="inlineStr">
+        <is>
+          <t>DK.DGP.EXMP.N</t>
+        </is>
+      </c>
+      <c r="C114" s="15" t="inlineStr">
+        <is>
+          <t>Citizens formally exempt from Digital Post</t>
+        </is>
+      </c>
+      <c r="D114" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E114" s="13" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F114" s="17" t="n">
+        <v>238479</v>
+      </c>
+      <c r="G114" s="13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H114" s="15" t="inlineStr">
+        <is>
+          <t>citizens aged 15+ resident in Denmark</t>
+        </is>
+      </c>
+      <c r="I114" s="13" t="inlineStr"/>
+      <c r="J114" s="14" t="inlineStr">
+        <is>
+          <t>DG1</t>
+        </is>
+      </c>
+      <c r="K114" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L114" s="15" t="inlineStr">
+        <is>
+          <t>Q1 2026. Paired with the 4.7% rate, implies a 15+ base of about 5.07m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="18" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="19" t="inlineStr">
+        <is>
           <t>DK.GOV.DGP.SAVE.PLAN</t>
         </is>
       </c>
-      <c r="C113" s="20" t="inlineStr">
+      <c r="C115" s="20" t="inlineStr">
         <is>
           <t>Digital Post: projected annual public saving</t>
         </is>
       </c>
-      <c r="D113" s="18" t="inlineStr">
+      <c r="D115" s="18" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E113" s="18" t="n">
+      <c r="E115" s="18" t="n">
         <v>2016</v>
       </c>
-      <c r="F113" s="22" t="n">
+      <c r="F115" s="22" t="n">
         <v>1000</v>
       </c>
-      <c r="G113" s="18" t="inlineStr">
+      <c r="G115" s="18" t="inlineStr">
         <is>
           <t>million DKK per year</t>
         </is>
       </c>
-      <c r="H113" s="20" t="inlineStr">
+      <c r="H115" s="20" t="inlineStr">
         <is>
           <t>projected annual saving, whole public sector</t>
         </is>
       </c>
-      <c r="I113" s="18" t="inlineStr">
+      <c r="I115" s="18" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="J113" s="19" t="inlineStr">
+      <c r="J115" s="19" t="inlineStr">
         <is>
           <t>RR1</t>
         </is>
       </c>
-      <c r="K113" s="18" t="inlineStr">
+      <c r="K115" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L113" s="20" t="inlineStr">
+      <c r="L115" s="20" t="inlineStr">
         <is>
           <t>Ministry of Finance business case; Rigsrevisionen reports it as 'approx. 1bn'.</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="18" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" s="19" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="18" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="19" t="inlineStr">
         <is>
           <t>DK.GOV.DGP.SAVE.VERIF</t>
         </is>
       </c>
-      <c r="C114" s="20" t="inlineStr">
+      <c r="C116" s="20" t="inlineStr">
         <is>
           <t>Digital Post: annual saving verifiable by audit</t>
         </is>
       </c>
-      <c r="D114" s="18" t="inlineStr">
+      <c r="D116" s="18" t="inlineStr">
         <is>
           <t>DK</t>
         </is>
       </c>
-      <c r="E114" s="18" t="n">
+      <c r="E116" s="18" t="n">
         <v>2016</v>
       </c>
-      <c r="F114" s="22" t="n">
+      <c r="F116" s="22" t="n">
         <v>450</v>
       </c>
-      <c r="G114" s="18" t="inlineStr">
+      <c r="G116" s="18" t="inlineStr">
         <is>
           <t>million DKK per year</t>
         </is>
       </c>
-      <c r="H114" s="20" t="inlineStr">
+      <c r="H116" s="20" t="inlineStr">
         <is>
           <t>verified annual saving, whole public sector</t>
         </is>
       </c>
-      <c r="I114" s="18" t="inlineStr">
+      <c r="I116" s="18" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="J114" s="19" t="inlineStr">
+      <c r="J116" s="19" t="inlineStr">
         <is>
           <t>RR1</t>
         </is>
       </c>
-      <c r="K114" s="18" t="inlineStr">
+      <c r="K116" s="18" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="L114" s="20" t="inlineStr">
+      <c r="L116" s="20" t="inlineStr">
         <is>
           <t>Postage, paper and envelopes only. The wage and overhead component was never verified: the cross-government study was abandoned after KL declined to take part.</t>
         </is>
       </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="13" t="n">
-        <v>114</v>
-      </c>
-      <c r="B115" s="14" t="inlineStr">
-        <is>
-          <t>DK.PRD.LP.PER</t>
-        </is>
-      </c>
-      <c r="C115" s="15" t="inlineStr">
-        <is>
-          <t>Nominal labour productivity per person</t>
-        </is>
-      </c>
-      <c r="D115" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E115" s="13" t="n">
-        <v>2005</v>
-      </c>
-      <c r="F115" s="16" t="n">
-        <v>109.2</v>
-      </c>
-      <c r="G115" s="13" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="H115" s="15" t="inlineStr">
-        <is>
-          <t>EU27_2020 = 100, current prices, PPS</t>
-        </is>
-      </c>
-      <c r="I115" s="13" t="inlineStr"/>
-      <c r="J115" s="14" t="inlineStr">
-        <is>
-          <t>ES8</t>
-        </is>
-      </c>
-      <c r="K115" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L115" s="15" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="13" t="n">
-        <v>115</v>
-      </c>
-      <c r="B116" s="14" t="inlineStr">
-        <is>
-          <t>DK.PRD.LP.PER</t>
-        </is>
-      </c>
-      <c r="C116" s="15" t="inlineStr">
-        <is>
-          <t>Nominal labour productivity per person</t>
-        </is>
-      </c>
-      <c r="D116" s="13" t="inlineStr">
-        <is>
-          <t>DK</t>
-        </is>
-      </c>
-      <c r="E116" s="13" t="n">
-        <v>2006</v>
-      </c>
-      <c r="F116" s="16" t="n">
-        <v>109.3</v>
-      </c>
-      <c r="G116" s="13" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-      <c r="H116" s="15" t="inlineStr">
-        <is>
-          <t>EU27_2020 = 100, current prices, PPS</t>
-        </is>
-      </c>
-      <c r="I116" s="13" t="inlineStr"/>
-      <c r="J116" s="14" t="inlineStr">
-        <is>
-          <t>ES8</t>
-        </is>
-      </c>
-      <c r="K116" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="L116" s="15" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="13" t="n">
@@ -13653,10 +13661,10 @@
         </is>
       </c>
       <c r="E117" s="13" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="F117" s="16" t="n">
-        <v>107.1</v>
+        <v>109.2</v>
       </c>
       <c r="G117" s="13" t="inlineStr">
         <is>
@@ -13701,10 +13709,10 @@
         </is>
       </c>
       <c r="E118" s="13" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="F118" s="16" t="n">
-        <v>108.5</v>
+        <v>109.3</v>
       </c>
       <c r="G118" s="13" t="inlineStr">
         <is>
@@ -13749,10 +13757,10 @@
         </is>
       </c>
       <c r="E119" s="13" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="F119" s="16" t="n">
-        <v>109.9</v>
+        <v>107.1</v>
       </c>
       <c r="G119" s="13" t="inlineStr">
         <is>
@@ -13797,10 +13805,10 @@
         </is>
       </c>
       <c r="E120" s="13" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="F120" s="16" t="n">
-        <v>115</v>
+        <v>108.5</v>
       </c>
       <c r="G120" s="13" t="inlineStr">
         <is>
@@ -13845,10 +13853,10 @@
         </is>
       </c>
       <c r="E121" s="13" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="F121" s="16" t="n">
-        <v>113.8</v>
+        <v>109.9</v>
       </c>
       <c r="G121" s="13" t="inlineStr">
         <is>
@@ -13893,10 +13901,10 @@
         </is>
       </c>
       <c r="E122" s="13" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="F122" s="16" t="n">
-        <v>113.9</v>
+        <v>115</v>
       </c>
       <c r="G122" s="13" t="inlineStr">
         <is>
@@ -13941,10 +13949,10 @@
         </is>
       </c>
       <c r="E123" s="13" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="F123" s="16" t="n">
-        <v>115.3</v>
+        <v>113.8</v>
       </c>
       <c r="G123" s="13" t="inlineStr">
         <is>
@@ -13989,10 +13997,10 @@
         </is>
       </c>
       <c r="E124" s="13" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="F124" s="16" t="n">
-        <v>115.1</v>
+        <v>113.9</v>
       </c>
       <c r="G124" s="13" t="inlineStr">
         <is>
@@ -14037,10 +14045,10 @@
         </is>
       </c>
       <c r="E125" s="13" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="F125" s="16" t="n">
-        <v>113.9</v>
+        <v>115.3</v>
       </c>
       <c r="G125" s="13" t="inlineStr">
         <is>
@@ -14085,10 +14093,10 @@
         </is>
       </c>
       <c r="E126" s="13" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="F126" s="16" t="n">
-        <v>114.1</v>
+        <v>115.1</v>
       </c>
       <c r="G126" s="13" t="inlineStr">
         <is>
@@ -14133,10 +14141,10 @@
         </is>
       </c>
       <c r="E127" s="13" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="F127" s="16" t="n">
-        <v>116.3</v>
+        <v>113.9</v>
       </c>
       <c r="G127" s="13" t="inlineStr">
         <is>
@@ -14181,10 +14189,10 @@
         </is>
       </c>
       <c r="E128" s="13" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="F128" s="16" t="n">
-        <v>115.3</v>
+        <v>114.1</v>
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
@@ -14229,10 +14237,10 @@
         </is>
       </c>
       <c r="E129" s="13" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="F129" s="16" t="n">
-        <v>113.2</v>
+        <v>116.3</v>
       </c>
       <c r="G129" s="13" t="inlineStr">
         <is>
@@ -14277,10 +14285,10 @@
         </is>
       </c>
       <c r="E130" s="13" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="F130" s="16" t="n">
-        <v>119.6</v>
+        <v>115.3</v>
       </c>
       <c r="G130" s="13" t="inlineStr">
         <is>
@@ -14325,10 +14333,10 @@
         </is>
       </c>
       <c r="E131" s="13" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="F131" s="16" t="n">
-        <v>121</v>
+        <v>113.2</v>
       </c>
       <c r="G131" s="13" t="inlineStr">
         <is>
@@ -14373,10 +14381,10 @@
         </is>
       </c>
       <c r="E132" s="13" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="F132" s="16" t="n">
-        <v>120.2</v>
+        <v>119.6</v>
       </c>
       <c r="G132" s="13" t="inlineStr">
         <is>
@@ -14421,10 +14429,10 @@
         </is>
       </c>
       <c r="E133" s="13" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="F133" s="16" t="n">
-        <v>113.1</v>
+        <v>121</v>
       </c>
       <c r="G133" s="13" t="inlineStr">
         <is>
@@ -14469,10 +14477,10 @@
         </is>
       </c>
       <c r="E134" s="13" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F134" s="16" t="n">
-        <v>116.7</v>
+        <v>120.2</v>
       </c>
       <c r="G134" s="13" t="inlineStr">
         <is>
@@ -14517,10 +14525,10 @@
         </is>
       </c>
       <c r="E135" s="13" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="F135" s="16" t="n">
-        <v>116.8</v>
+        <v>113.1</v>
       </c>
       <c r="G135" s="13" t="inlineStr">
         <is>
@@ -14545,8 +14553,104 @@
       </c>
       <c r="L135" s="15" t="inlineStr"/>
     </row>
+    <row r="136">
+      <c r="A136" s="13" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C136" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D136" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E136" s="13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F136" s="16" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="G136" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H136" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I136" s="13" t="inlineStr"/>
+      <c r="J136" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K136" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L136" s="15" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="13" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="14" t="inlineStr">
+        <is>
+          <t>DK.PRD.LP.PER</t>
+        </is>
+      </c>
+      <c r="C137" s="15" t="inlineStr">
+        <is>
+          <t>Nominal labour productivity per person</t>
+        </is>
+      </c>
+      <c r="D137" s="13" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="E137" s="13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F137" s="16" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="G137" s="13" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="H137" s="15" t="inlineStr">
+        <is>
+          <t>EU27_2020 = 100, current prices, PPS</t>
+        </is>
+      </c>
+      <c r="I137" s="13" t="inlineStr"/>
+      <c r="J137" s="14" t="inlineStr">
+        <is>
+          <t>ES8</t>
+        </is>
+      </c>
+      <c r="K137" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="L137" s="15" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L135"/>
+  <autoFilter ref="A1:L137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14557,7 +14661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -15424,64 +15528,64 @@
     <row r="25" ht="46" customHeight="1">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>LOV1</t>
+          <t>ES9</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Folketinget</t>
+          <t>Eurostat</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Lov om fravigelse fra obligatorisk digital selvbetjening (Act on derogation from mandatory digital self-service)</t>
+          <t>E-government activities of individuals via websites - individuals using the internet for interaction with public authorities, last 12 months</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>LOV nr 603 af 31/05/2023</t>
+          <t>isoc_ciegi_ac</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>https://www.retsinformation.dk/eli/lta/2023/603</t>
+          <t>https://ec.europa.eu/eurostat/databrowser/view/isoc_ciegi_ac/default/table?lang=en</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
-          <t>13 September 2026</t>
+          <t>14 September 2026</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>Folketinget 2023, Lov om fravigelse fra obligatorisk digital selvbetjening, LOV nr 603 af 31. maj 2023, in force 1 June 2023, Retsinformation, accessed 13 September 2026, &lt;https://www.retsinformation.dk/eli/lta/2023/603&gt;.</t>
+          <t>Eurostat 2025, E-government activities of individuals via websites, dataset isoc_ciegi_ac, Eurostat, Luxembourg, accessed 14 September 2026, &lt;https://ec.europa.eu/eurostat/databrowser/view/isoc_ciegi_ac/default/table?lang=en&gt;.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="46" customHeight="1">
       <c r="A26" s="23" t="inlineStr">
         <is>
-          <t>BRH1</t>
+          <t>LOV1</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Bundesrechnungshof</t>
+          <t>Folketinget</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes - findings on the Digital Jetzt lottery allocation</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Lov om fravigelse fra obligatorisk digital selvbetjening (Act on derogation from mandatory digital self-service)</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>Bemerkungen 2022</t>
+          <t>LOV nr 603 af 31/05/2023</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html</t>
+          <t>https://www.retsinformation.dk/eli/lta/2023/603</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
@@ -15491,34 +15595,34 @@
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
-          <t>Bundesrechnungshof 2022, Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes, German Federal Court of Auditors, accessed 13 September 2026, &lt;https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html&gt;.</t>
+          <t>Folketinget 2023, Lov om fravigelse fra obligatorisk digital selvbetjening, LOV nr 603 af 31. maj 2023, in force 1 June 2023, Retsinformation, accessed 13 September 2026, &lt;https://www.retsinformation.dk/eli/lta/2023/603&gt;.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="46" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>CE1</t>
+          <t>BRH1</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Conseil d'État (France)</t>
+          <t>Bundesrechnungshof</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Decision No. 452798 - partial annulment of the ANEF decree mandating online-only residence permit applications</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes - findings on the Digital Jetzt lottery allocation</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>No. 452798</t>
+          <t>Bemerkungen 2022</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798</t>
+          <t>https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html</t>
         </is>
       </c>
       <c r="F27" s="15" t="inlineStr">
@@ -15528,34 +15632,34 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>Conseil d'État 2022, Decision No. 452798, 3 June 2022, Conseil d'État, Paris, accessed 13 September 2026, &lt;https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798&gt;.</t>
+          <t>Bundesrechnungshof 2022, Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes, German Federal Court of Auditors, accessed 13 September 2026, &lt;https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html&gt;.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="46" customHeight="1">
       <c r="A28" s="23" t="inlineStr">
         <is>
-          <t>BE1</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Cour constitutionnelle (Belgium)</t>
+          <t>Conseil d'État (France)</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Arrêt no. 126/2025 - Brussels Digital ordinance; cumulative non-digital access guarantees</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Decision No. 452798 - partial annulment of the ANEF decree mandating online-only residence permit applications</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>ECLI:BE:GHCC:2025:ARR.126</t>
+          <t>No. 452798</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>https://fr.const-court.be/public/f/2025/2025-126f.pdf</t>
+          <t>https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
@@ -15565,34 +15669,34 @@
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
-          <t>Cour constitutionnelle 2025, Arrêt no. 126/2025, 25 September 2025, ECLI:BE:GHCC:2025:ARR.126, Cour constitutionnelle, Brussels, accessed 13 September 2026, &lt;https://fr.const-court.be/public/f/2025/2025-126f.pdf&gt;.</t>
+          <t>Conseil d'État 2022, Decision No. 452798, 3 June 2022, Conseil d'État, Paris, accessed 13 September 2026, &lt;https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798&gt;.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="46" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>NO1</t>
+          <t>BE1</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsdirektoratet (Digdir)</t>
+          <t>Cour constitutionnelle (Belgium)</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Kontakt- og reservasjonsregisteret and the statutory right to opt out of digital communication under eForvaltningsforskriften</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Arrêt no. 126/2025 - Brussels Digital ordinance; cumulative non-digital access guarantees</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>KRR</t>
+          <t>ECLI:BE:GHCC:2025:ARR.126</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865</t>
+          <t>https://fr.const-court.be/public/f/2025/2025-126f.pdf</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
@@ -15602,108 +15706,145 @@
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsdirektoratet 2025, Kontakt- og reservasjonsregisteret, Norwegian Digitalisation Agency, accessed 13 September 2026, &lt;https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865&gt;.</t>
+          <t>Cour constitutionnelle 2025, Arrêt no. 126/2025, 25 September 2025, ECLI:BE:GHCC:2025:ARR.126, Cour constitutionnelle, Brussels, accessed 13 September 2026, &lt;https://fr.const-court.be/public/f/2025/2025-126f.pdf&gt;.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="46" customHeight="1">
       <c r="A30" s="23" t="inlineStr">
         <is>
-          <t>GS1</t>
+          <t>NO1</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Tran, T.T.</t>
+          <t>Digitaliseringsdirektoratet (Digdir)</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Guest speaker session: corporate sustainability and the adoption of artificial intelligence</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Kontakt- og reservasjonsregisteret and the statutory right to opt out of digital communication under eForvaltningsforskriften</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>ECON1596/ECON1597 guest lecture</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr"/>
-      <c r="F30" s="15" t="inlineStr"/>
+          <t>KRR</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>13 September 2026</t>
+        </is>
+      </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
-          <t>Tran, TT 2026, 'Guest speaker session: corporate sustainability and the adoption of artificial intelligence', guest lecture, ECON1596 Business Challenges in the Digital Economy, RMIT University Vietnam, Ho Chi Minh City, [LECTURE DATE: to be completed by the author].</t>
+          <t>Digitaliseringsdirektoratet 2025, Kontakt- og reservasjonsregisteret, Norwegian Digitalisation Agency, accessed 13 September 2026, &lt;https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865&gt;.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="46" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>HOW1</t>
+          <t>GS1</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Howell, S.T.</t>
+          <t>Tran, T.T.</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Financing Innovation: Evidence from R&amp;D Grants</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Guest speaker session: corporate sustainability and the adoption of artificial intelligence</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>American Economic Review 107(4)</t>
-        </is>
-      </c>
-      <c r="E31" s="15" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/articles?id=10.1257%2Faer.20150808</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="inlineStr">
-        <is>
-          <t>13 September 2026</t>
-        </is>
-      </c>
+          <t>ECON1596/ECON1597 guest lecture</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr"/>
+      <c r="F31" s="15" t="inlineStr"/>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Howell, ST 2017, 'Financing innovation: evidence from R&amp;D grants', American Economic Review, vol. 107, no. 4, pp. 1136-1164.</t>
+          <t>Tran, TT 2026, 'Guest speaker session: corporate sustainability and the adoption of artificial intelligence', guest lecture, ECON1596 Business Challenges in the Digital Economy, RMIT University Vietnam, Ho Chi Minh City, [LECTURE DATE: to be completed by the author].</t>
         </is>
       </c>
     </row>
     <row r="32" ht="46" customHeight="1">
       <c r="A32" s="23" t="inlineStr">
         <is>
+          <t>HOW1</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Howell, S.T.</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Financing Innovation: Evidence from R&amp;D Grants</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>American Economic Review 107(4)</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>https://www.aeaweb.org/articles?id=10.1257%2Faer.20150808</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>13 September 2026</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>Howell, ST 2017, 'Financing innovation: evidence from R&amp;D grants', American Economic Review, vol. 107, no. 4, pp. 1136-1164.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="46" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
           <t>SAN1</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>Santoleri, P., Barrows, G., Caravella, S., Crespi, F. and Pellegrino, G.</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] The Causal Effects of R&amp;D Grants: Evidence from a Regression Discontinuity - the Horizon 2020 SME Instrument scoring threshold</t>
         </is>
       </c>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="D33" s="15" t="inlineStr">
         <is>
           <t>Working paper</t>
         </is>
       </c>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="E33" s="15" t="inlineStr">
         <is>
           <t>https://pietrosantoleri.github.io/files/Santoleri_et_al_The_effects_of_R_D_grants.pdf</t>
         </is>
       </c>
-      <c r="F32" s="15" t="inlineStr">
+      <c r="F33" s="15" t="inlineStr">
         <is>
           <t>13 September 2026</t>
         </is>
       </c>
-      <c r="G32" s="15" t="inlineStr">
+      <c r="G33" s="15" t="inlineStr">
         <is>
           <t>Santoleri, P, Barrows, G, Caravella, S, Crespi, F and Pellegrino, G 2022, The causal effects of R&amp;D grants: evidence from a regression discontinuity, working paper, accessed 13 September 2026, &lt;https://pietrosantoleri.github.io/files/Santoleri_et_al_The_effects_of_R_D_grants.pdf&gt;.</t>
         </is>
@@ -15720,7 +15861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15755,509 +15896,526 @@
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>DK.PAY.CASH.POS</t>
+          <t>DK.DGX.EGOV.USE</t>
         </is>
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>Cash as a share of the NUMBER of payments made at physical points of sale.</t>
+          <t>Share of individuals who used the website or app of a public authority for private purposes in the last 12 months.</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>Not a share of value. Excludes e-commerce entirely.</t>
+          <t>Base is ALL individuals aged 16-74, not internet users, so it is not comparable with the DK.ECM.IND.BUY series. Records whether a person interacted at all, once, in a year: it measures reach, not frequency, competence or independent use.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="25" t="inlineStr">
         <is>
-          <t>DK.PAY.CRD.PHYS</t>
+          <t>DK.PAY.CASH.POS</t>
         </is>
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>Physical payment cards as a share of the number of in-store payments.</t>
+          <t>Cash as a share of the NUMBER of payments made at physical points of sale.</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>Falls partly because wallets replace the physical card, not because card payment declines.</t>
+          <t>Not a share of value. Excludes e-commerce entirely.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
         <is>
-          <t>DK.PAY.WLT.SHR</t>
+          <t>DK.PAY.CRD.PHYS</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Card-based mobile wallets as a share of the number of in-store payments.</t>
+          <t>Physical payment cards as a share of the number of in-store payments.</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>Wallet payments are card payments. Do not add to the card share.</t>
+          <t>Falls partly because wallets replace the physical card, not because card payment declines.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>DK.PAY.WLT.OWN</t>
+          <t>DK.PAY.WLT.SHR</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Share of CITIZENS with a wallet solution on their phone.</t>
+          <t>Card-based mobile wallets as a share of the number of in-store payments.</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>Different denominator from the payment-share series. Memo only - deliberately excluded from Figure 2.</t>
+          <t>Wallet payments are card payments. Do not add to the card share.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>DK.PRD.LP.PER</t>
+          <t>DK.PAY.WLT.OWN</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Nominal labour productivity per person employed, indexed so that the EU27 (2020 composition) equals 100 in each year.</t>
+          <t>Share of CITIZENS with a wallet solution on their phone.</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>RELATIVE measure. A rise means Denmark gained ON THE EU AVERAGE; it is not a Danish growth rate and must never be read as one. Per PERSON, so it is sensitive to part-time work - the per-HOUR variant is the cleaner productivity measure. Current prices in PPS, so nominal.</t>
+          <t>Different denominator from the payment-share series. Memo only - deliberately excluded from Figure 2.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>DK.FIN.BRCH</t>
+          <t>DK.PRD.LP.PER</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Number of retail bank branches operated by Danish credit institutions.</t>
+          <t>Nominal labour productivity per person employed, indexed so that the EU27 (2020 composition) equals 100 in each year.</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Consolidation and digitalisation both reduce this. The series alone cannot separate the two causes.</t>
+          <t>RELATIVE measure. A rise means Denmark gained ON THE EU AVERAGE; it is not a Danish growth rate and must never be read as one. Per PERSON, so it is sensitive to part-time work - the per-HOUR variant is the cleaner productivity measure. Current prices in PPS, so nominal.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>DK.ECM.IND.BUY</t>
+          <t>DK.FIN.BRCH</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>Individuals who purchased goods or services online in the last 12 months.</t>
+          <t>Number of retail bank branches operated by Danish credit institutions.</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>DENOMINATOR BREAK at 2020: % of individuals before, % of internet users after. Never plot 2019 with later years.</t>
+          <t>Consolidation and digitalisation both reduce this. The series alone cannot separate the two causes.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="25" t="inlineStr">
         <is>
-          <t>DK.ECM.ENT.TRN</t>
+          <t>DK.ECM.IND.BUY</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>E-commerce sales as a share of total enterprise turnover.</t>
+          <t>Individuals who purchased goods or services online in the last 12 months.</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Measures INTENSITY of online selling, not how many firms sell online. Pair with DK.ECM.ENT.SHR.</t>
+          <t>DENOMINATOR BREAK at 2020: % of individuals before, % of internet users after. Never plot 2019 with later years.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>DK.ECM.ENT.SHR</t>
+          <t>DK.ECM.ENT.TRN</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>Share of enterprises making any e-sales.</t>
+          <t>E-commerce sales as a share of total enterprise turnover.</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>Measures BREADTH of adoption. Flat breadth with rising intensity means incumbents deepening, not new entrants.</t>
+          <t>Measures INTENSITY of online selling, not how many firms sell online. Pair with DK.ECM.ENT.SHR.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>DK.DGP.EXMP</t>
+          <t>DK.ECM.ENT.SHR</t>
         </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>Citizens formally exempt from mandatory Digital Post under the statutory exemption regime.</t>
+          <t>Share of enterprises making any e-sales.</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>An administrative status, not a measure of capability. A citizen may struggle without being exempt.</t>
+          <t>Measures BREADTH of adoption. Flat breadth with rising intensity means incumbents deepening, not new entrants.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>DK.DGX.DIFF</t>
+          <t>DK.DGP.EXMP</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>Population estimated to face difficulties using digital public services.</t>
+          <t>Citizens formally exempt from mandatory Digital Post under the statutory exemption regime.</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>A capability estimate, not an administrative count. Much larger than the exemption rate - that gap is the analytical point.</t>
+          <t>An administrative status, not a measure of capability. A citizen may struggle without being exempt.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>DK.DGX.JUST</t>
+          <t>DK.DGX.DIFF</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>Justitia's estimate of the digitally disadvantaged adult population.</t>
+          <t>Population estimated to face difficulties using digital public services.</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Think-tank estimate, broadest definition of the five. Cite as an upper bound, not as an official statistic.</t>
+          <t>A capability estimate, not an administrative count. Much larger than the exemption rate - that gap is the analytical point.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="25" t="inlineStr">
         <is>
-          <t>DK.GOV.DPS.CIT</t>
+          <t>DK.DGX.JUST</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>eGovernment Benchmark composite score for citizen-facing digital public services.</t>
+          <t>Justitia's estimate of the digitally disadvantaged adult population.</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>A composite index, not a usage rate. Denmark scores BELOW the EU average despite near-universal mandated use.</t>
+          <t>Think-tank estimate, broadest definition of the five. Cite as an upper bound, not as an official statistic.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="25" t="inlineStr">
         <is>
-          <t>DK.ENV.WEEE</t>
+          <t>DK.GOV.DPS.CIT</t>
         </is>
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>Share of collected ICT-related electrical waste recycled or prepared for reuse.</t>
+          <t>eGovernment Benchmark composite score for citizen-facing digital public services.</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
         <is>
-          <t>Covers two WEEE categories only. Denominator is waste COLLECTED, not waste generated.</t>
+          <t>A composite index, not a usage rate. Denmark scores BELOW the EU average despite near-universal mandated use.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="25" t="inlineStr">
         <is>
-          <t>DK.PAY.DIG.POS.NUM, DK.PAY.DIG.POS.VAL</t>
+          <t>DK.ENV.WEEE</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>Digital share of physical-retail payments, by NUMBER and by VALUE respectively.</t>
+          <t>Share of collected ICT-related electrical waste recycled or prepared for reuse.</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>Two different denominators. The value share exceeds the number share because cash survives in small transactions. Never quote one as the other, and never average them.</t>
+          <t>Covers two WEEE categories only. Denominator is waste COLLECTED, not waste generated.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="25" t="inlineStr">
         <is>
-          <t>DK.FIN.INST</t>
+          <t>DK.PAY.DIG.POS.NUM, DK.PAY.DIG.POS.VAL</t>
         </is>
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>Number of financial institutions (credit institutions) operating in Denmark.</t>
+          <t>Digital share of physical-retail payments, by NUMBER and by VALUE respectively.</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
         <is>
-          <t>Base year 1991. Do NOT difference against DK.FIN.BRCH, which starts in 2004 - see F9_CONSOLIDATION.</t>
+          <t>Two different denominators. The value share exceeds the number share because cash survives in small transactions. Never quote one as the other, and never average them.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>DK.FIN.EMP</t>
+          <t>DK.FIN.INST</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>Number of persons employed by Danish banks.</t>
+          <t>Number of financial institutions (credit institutions) operating in Denmark.</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>Base year 1991, so comparable with DK.FIN.INST but NOT with the branch series. Falls far less than institutions - that asymmetry is the finding in F9_CONSOLIDATION, not a data error.</t>
+          <t>Base year 1991. Do NOT difference against DK.FIN.BRCH, which starts in 2004 - see F9_CONSOLIDATION.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="25" t="inlineStr">
         <is>
+          <t>DK.FIN.EMP</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t>Number of persons employed by Danish banks.</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Base year 1991, so comparable with DK.FIN.INST but NOT with the branch series. Falls far less than institutions - that asymmetry is the finding in F9_CONSOLIDATION, not a data error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
           <t>DK.SKL.1624, DK.SKL.2554, DK.SKL.5574
 (EU.SKL.1624, EU.SKL.2554, EU.SKL.5574)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>Individuals with at least basic overall digital skills, by age band. EU.SKL.* are the matching EU-27 comparators.</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>Age bands, not a time series - all three are the same reference year. The DIGCOMP methodology was revised in 2021; do not join to pre-2021 skills figures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>DK.DGP.EXMP.N</t>
-        </is>
-      </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>Citizens formally exempt from Digital Post, as a HEADCOUNT.</t>
-        </is>
-      </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>A count, not a rate. Converting between this and DK.DGP.EXMP requires DK.POP.TOT and an assumption about the 15+ denominator - see 07_LIMITATIONS.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>DK.DGP.EXMP.7584, DK.DGP.EXMP.85P</t>
+          <t>DK.DGP.EXMP.N</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>Digital Post exemption rate within the 75-84 and 85+ age bands.</t>
+          <t>Citizens formally exempt from Digital Post, as a HEADCOUNT.</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Denominator is the age group, not the population. These are far above the headline 4.7% and must not be compared with it directly.</t>
+          <t>A count, not a rate. Converting between this and DK.DGP.EXMP requires DK.POP.TOT and an assumption about the 15+ denominator - see 07_LIMITATIONS.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="25" t="inlineStr">
         <is>
-          <t>DK.DGX.NOUSE</t>
+          <t>DK.DGP.EXMP.7584, DK.DGP.EXMP.85P</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>Individuals who do not use digital public services at all.</t>
+          <t>Digital Post exemption rate within the 75-84 and 85+ age bands.</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>Non-use, not inability. Includes those with no need to transact as well as those unable to.</t>
+          <t>Denominator is the age group, not the population. These are far above the headline 4.7% and must not be compared with it directly.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>DK.DGX.DISADV.LO, DK.DGX.DISADV.HI</t>
+          <t>DK.DGX.NOUSE</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>Lower and upper bound of the 'digitally disadvantaged' adult population.</t>
+          <t>Individuals who do not use digital public services at all.</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>A RANGE published as a range. Quote both bounds; citing either alone misrepresents the source's own uncertainty.</t>
+          <t>Non-use, not inability. Includes those with no need to transact as well as those unable to.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t>DK.POP.TOT</t>
+          <t>DK.DGX.DISADV.LO, DK.DGX.DISADV.HI</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>Resident population of Denmark.</t>
+          <t>Lower and upper bound of the 'digitally disadvantaged' adult population.</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>Used only as a denominator for converting headcounts to rates. Total residents, not the 15+ base the exemption rate actually uses.</t>
+          <t>A RANGE published as a range. Quote both bounds; citing either alone misrepresents the source's own uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t>DK.TRU.DPS</t>
+          <t>DK.POP.TOT</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Share of the population expressing trust in digital public solutions.</t>
+          <t>Resident population of Denmark.</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>Self-reported attitude, not behaviour. High trust coexists with the exclusion measures in F4 - the two are not in contradiction.</t>
+          <t>Used only as a denominator for converting headcounts to rates. Total residents, not the 15+ base the exemption rate actually uses.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="44" customHeight="1">
       <c r="A27" s="25" t="inlineStr">
         <is>
-          <t>DK.TRU.DGP.SEC</t>
+          <t>DK.TRU.DPS</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Share of the population perceiving Digital Post as secure.</t>
+          <t>Share of the population expressing trust in digital public solutions.</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>Narrower than DK.TRU.DPS: one service, not the whole system. Do not treat the two as one series.</t>
+          <t>Self-reported attitude, not behaviour. High trust coexists with the exclusion measures in F4 - the two are not in contradiction.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="25" t="inlineStr">
         <is>
-          <t>DK.ENT.DII</t>
+          <t>DK.TRU.DGP.SEC</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>SMEs reaching at least basic digital intensity (DII).</t>
+          <t>Share of the population perceiving Digital Post as secure.</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>A composite threshold count of adopted technologies, not an intensity of use. A firm clears it by adopting breadth cheaply.</t>
+          <t>Narrower than DK.TRU.DPS: one service, not the whole system. Do not treat the two as one series.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="44" customHeight="1">
       <c r="A29" s="25" t="inlineStr">
         <is>
-          <t>DK.ENT.AI, DK.ENT.AI.LRG, DK.ENT.AI.SME</t>
+          <t>DK.ENT.DII</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Enterprises adopting AI: all, large (250+) and SMEs (10-249).</t>
+          <t>SMEs reaching at least basic digital intensity (DII).</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>The headline rate is close to the SME rate because SMEs dominate by count. The large-firm gap is the real dispersion - report the split, not just the average.</t>
+          <t>A composite threshold count of adopted technologies, not an intensity of use. A firm clears it by adopting breadth cheaply.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="44" customHeight="1">
       <c r="A30" s="25" t="inlineStr">
         <is>
-          <t>DK.GOV.DPS.XB</t>
+          <t>DK.ENT.AI, DK.ENT.AI.LRG, DK.ENT.AI.SME</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>eGovernment Benchmark score for CROSS-BORDER citizen services.</t>
+          <t>Enterprises adopting AI: all, large (250+) and SMEs (10-249).</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>Scored against a different service basket from DK.GOV.DPS.CIT. Lower is not evidence of decline; it is a different test.</t>
+          <t>The headline rate is close to the SME rate because SMEs dominate by count. The large-firm gap is the real dispersion - report the split, not just the average.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="44" customHeight="1">
       <c r="A31" s="25" t="inlineStr">
         <is>
-          <t>DK.GOV.DGP.SAVE.PLAN, DK.GOV.DGP.SAVE.VERIF</t>
+          <t>DK.GOV.DPS.XB</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Digital Post annual public saving: as projected, and as verifiable by audit.</t>
+          <t>eGovernment Benchmark score for CROSS-BORDER citizen services.</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>The pair exists to be compared - the verified figure is well under half the projection. Never cite the projection alone as a realised saving.</t>
+          <t>Scored against a different service basket from DK.GOV.DPS.CIT. Lower is not evidence of decline; it is a different test.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="44" customHeight="1">
       <c r="A32" s="25" t="inlineStr">
         <is>
+          <t>DK.GOV.DGP.SAVE.PLAN, DK.GOV.DGP.SAVE.VERIF</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>Digital Post annual public saving: as projected, and as verifiable by audit.</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>The pair exists to be compared - the verified figure is well under half the projection. Never cite the projection alone as a realised saving.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="44" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
           <t>DK.SME.SMVD.PROJ, DK.SME.SMVD.INV, DK.SME.SMVD.NOINV</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>SMV:Digital programme: projects supported, and participants who did or did not invest further.</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>Self-reported by participants, with no control group. Cannot support a causal claim about the programme - see the withdrawn claim in 07_LIMITATIONS and 08_AI_LOG.</t>
         </is>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -24,10 +24,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F9_CONSOLIDATION" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F10_SKILLS" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F11_EWASTE" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_RETAIL_GAP" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_LIMITATIONS" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_AI_LOG" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_POLICY" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F12_REACH" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_RETAIL_GAP" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_LIMITATIONS" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_AI_LOG" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_POLICY" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_MASTER'!$A$1:$L$137</definedName>
@@ -6378,120 +6379,146 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="92" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Documented gap - retail trade volume index</t>
+          <t>Figure 12 - Reach, and what reach does not measure</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>Recorded rather than silently omitted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B4" s="45" t="inlineStr">
-        <is>
-          <t>NOT RETRIEVED</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Indicator</t>
-        </is>
-      </c>
-      <c r="B5" s="45" t="inlineStr">
-        <is>
-          <t>Retail trade turnover, volume index (mangdeindeks)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Authority</t>
-        </is>
-      </c>
-      <c r="B6" s="45" t="inlineStr">
-        <is>
-          <t>Danmarks Statistik (DST1); also available via Eurostat sts_trtu_a</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Filters required</t>
-        </is>
-      </c>
-      <c r="B7" s="45" t="inlineStr">
-        <is>
-          <t>geo=DK; nace_r2=G47; indic_bt=VOL; s_adj=SCA; unit=I21 (2021=100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Why not retrieved</t>
-        </is>
-      </c>
-      <c r="B8" s="45" t="inlineStr">
-        <is>
-          <t>Values are published through StatBank and the Eurostat databrowser. This session's network policy blocked direct access to both, and the figure could not be verified by search. A value that cannot be traced is not entered.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Base year caution</t>
-        </is>
-      </c>
-      <c r="B9" s="45" t="inlineStr">
-        <is>
-          <t>Danmarks Statistik rebased the index from 2015=100 to 2021=100. Series retrieved on different bases must not be joined.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Effect on the analysis</t>
-        </is>
-      </c>
-      <c r="B10" s="45" t="inlineStr">
-        <is>
-          <t>The e-commerce section rests on the enterprise e-sales evidence in F3_ESALES instead, which is better sourced. No conclusion in the report depends on this series.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>To fill</t>
-        </is>
-      </c>
-      <c r="B11" s="45" t="inlineStr">
-        <is>
-          <t>Retrieve from statistikbanken.dk, add rows to dataset.py under series_code DK.RET.VOL with unit 'index 2021=100', and re-run build_workbook.py.</t>
+          <t>Panel A and Panel B are NOT comparable. Different sources, different reference years and different denominators. Read each against its own base; never difference them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>PANEL A - reach</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B5" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.EGOV.USE",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.EGOV.USE",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>individuals aged 16-74, 2024 (ES9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="38" t="inlineStr">
+        <is>
+          <t>EU-27 average</t>
+        </is>
+      </c>
+      <c r="B6" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"EU.DGX.EGOV.USE",'02_MASTER'!$E:$E,2024)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"EU.DGX.EGOV.USE",'02_MASTER'!$E:$E,2024))</f>
+        <v/>
+      </c>
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>individuals aged 16-74, 2024 (ES9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>PANEL B - what it does not measure</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="38" t="inlineStr">
+        <is>
+          <t>Report difficulty using them</t>
+        </is>
+      </c>
+      <c r="B9" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.DIFF",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.DIFF",'02_MASTER'!$E:$E,2026))</f>
+        <v/>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>individuals, 2026 (EC1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="38" t="inlineStr">
+        <is>
+          <t>Do not use them at all</t>
+        </is>
+      </c>
+      <c r="B10" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGX.NOUSE",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGX.NOUSE",'02_MASTER'!$E:$E,2026))</f>
+        <v/>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>individuals, 2026 (EC1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="38" t="inlineStr">
+        <is>
+          <t>Formally exempt from Digital Post</t>
+        </is>
+      </c>
+      <c r="B11" s="32">
+        <f>IF(COUNTIFS('02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026)=0,"",SUMIFS('02_MASTER'!$F:$F,'02_MASTER'!$B:$B,"DK.DGP.EXMP",'02_MASTER'!$E:$E,2026))</f>
+        <v/>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>citizens aged 15 and over, Q1 2026 (DG1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="34" t="inlineStr">
+        <is>
+          <t>Sources: Eurostat isoc_ciegi_ac (ES9); European Commission, Digital Decade 2026 country report for Denmark (EC1); Digitaliseringsstyrelsen (DG1). READING: 98.5% of Danish individuals aged 16 to 74 used a public authority website or app at least once during 2024, the highest share in the EU-27 against an average of 70.0%. DENOMINATOR WARNING: the survey records whether a person interacted AT ALL, ONCE, in twelve months. It measures reach, not frequency, competence or independent use, and Panel B is drawn on other bases entirely. The two panels are shown together because the contrast is the argument; they are never differenced.</t>
         </is>
       </c>
     </row>
@@ -6506,252 +6533,120 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="92" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Data quality statement</t>
+          <t>Documented gap - retail trade volume index</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>Read before citing any value.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="62" customHeight="1">
+          <t>Recorded rather than silently omitted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Compiled date is not a per-value retrieval date</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>02_MASTER carries a compiled_date column holding a single build-time constant, identical on all 113 rows. It records when this workbook was generated, NOT when each value was retrieved from its authority - those retrievals were made across several working sessions on different days. The column was named extraction_date until an audit of the generated file found that the name claimed per-observation provenance the data does not hold. It is renamed rather than back-filled, because inventing plausible retrieval dates would be precisely the fabrication this workbook exists to avoid. Recording true retrieval dates requires capturing them at retrieval time, in dataset.py, which is the correct fix and is not retrospective.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="62" customHeight="1">
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B4" s="45" t="inlineStr">
+        <is>
+          <t>NOT RETRIEVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>No inferential statistics</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>The longest series here has six observations. Regression, cointegration and Granger-causality procedures require far more, and any such result on this dataset would be uninterpretable. The workbook supports description and comparison only. Co-movement between digital payment adoption and branch closures is presented as association, never as measured causation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="62" customHeight="1">
+          <t>Indicator</t>
+        </is>
+      </c>
+      <c r="B5" s="45" t="inlineStr">
+        <is>
+          <t>Retail trade turnover, volume index (mangdeindeks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Figure 6 tail selection - RESOLVED, and what it cost</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>The adoption column in Figure 6 was originally assembled from a Eurostat press release naming the highest three countries, the lowest three and two large movers, so most plotted points came from the ends of the EU distribution. Selecting on the extremes of X inflates the correlation coefficient regardless of the underlying relationship, and R-squared was withheld from the chart face for that reason. The column is now the complete isoc_ec_ib20 databrowser extract for all 27 member states, unrounded, so the selection is gone and R-squared is displayed. The measured cost of the bias is retained on F6 because it is informative: on the 6 tail countries the fit was R-squared 0.853 with a slope of +0.655; on the complete cross-section it is R-squared 0.674 with a slope of +0.602. Tail selection barely moved the slope and flattered the fit by 0.18.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="62" customHeight="1">
+          <t>Authority</t>
+        </is>
+      </c>
+      <c r="B6" s="45" t="inlineStr">
+        <is>
+          <t>Danmarks Statistik (DST1); also available via Eurostat sts_trtu_a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>No price deflator on the turnover series</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>E-sales as a share of enterprise turnover runs 2014 to 2024, spanning the pandemic and the 2022 inflation episode. Turnover is nominal, and online and physical retail did not face the same price path. Part of the measured rise in the e-sales share is therefore relative price movement rather than real reallocation of activity. No deflator was available in this session and none has been applied, so the doubling of intensity should be read as nominal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="62" customHeight="1">
+          <t>Filters required</t>
+        </is>
+      </c>
+      <c r="B7" s="45" t="inlineStr">
+        <is>
+          <t>geo=DK; nace_r2=G47; indic_bt=VOL; s_adj=SCA; unit=I21 (2021=100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Banking series use different base years</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>This constrains F9_CONSOLIDATION directly: the three percentage changes on that sheet are not measured over a common window, so they must not be differenced against one another. Institutions and employment are comparable to each other, both 1991-2024. Branch counts begin in 2004; institution counts and employment begin in 1991. A 2004-2024 branch change and a 1991-2024 employment change are not comparable, and placing the two percentages side by side in prose would misrepresent both. 05_CALC labels every window explicitly. Either state both windows or do not draw the comparison.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="62" customHeight="1">
+          <t>Why not retrieved</t>
+        </is>
+      </c>
+      <c r="B8" s="45" t="inlineStr">
+        <is>
+          <t>Values are published through StatBank and the Eurostat databrowser. This session's network policy blocked direct access to both, and the figure could not be verified by search. A value that cannot be traced is not entered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>No sampling error is reported anywhere</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>The Eurostat, Nationalbank and Agency for Digital Government figures are survey estimates and carry sampling error that the issuing authorities publish but this workbook does not reproduce. Small differences should not be treated as established: a 2-3 point gap between two survey proportions, or between two eGovernment Benchmark scores, may not be distinguishable from zero. Directions are more robust than magnitudes throughout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="62" customHeight="1">
+          <t>Base year caution</t>
+        </is>
+      </c>
+      <c r="B9" s="45" t="inlineStr">
+        <is>
+          <t>Danmarks Statistik rebased the index from 2015=100 to 2021=100. Series retrieved on different bases must not be joined.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Headcount conversions rest on an implied denominator</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>A published figure for the Danish population aged 15 and over could not be verified in this session. F4 therefore derives an implied 15+ base by dividing the exempt headcount by the exemption rate, both from the same source. Persons-affected figures built on it are orders of magnitude, not counts, and the capability shares they scale are measured on 'the population' rather than on the 15+ base - the denominators are not identical. Every such cell is marked in place.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="62" customHeight="1">
+          <t>Effect on the analysis</t>
+        </is>
+      </c>
+      <c r="B10" s="45" t="inlineStr">
+        <is>
+          <t>The e-commerce section rests on the enterprise e-sales evidence in F3_ESALES instead, which is better sourced. No conclusion in the report depends on this series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>A withdrawn claim about SMV:Digital</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>An earlier draft of this workbook asserted that SMV:Digital was being defunded, and an argument was built on the contrast between a programme that works and a programme being cut. The claim could not be verified. The scheme's own 2026 grant-pool page documents pools still open and a further pool opening on 26 October 2026. The claim has been removed from the dataset and from the report's argument, and the correction is recorded in 09_POLICY and 08_AI_LOG rather than silently erased.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="62" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Unbalanced panel</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>Observation years differ by series because the underlying sources publish on different cycles - payment habits roughly biennially, Eurostat annually, branch counts irregularly. Gaps are genuine and are not filled.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="62" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Denominator break</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>Danish online-purchasing figures change base between 2019 (% of individuals) and 2020 onward (% of internet users). The 2019 observation carries flag 'b' and is never plotted with later years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="62" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Verbal quantities</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>Values flagged 'e' were published as words, not figures - 'nearly one in five', 'just under 36,000'. They are recorded as the stated approximation with the original wording in the notes column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="62" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Confounded outcome</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>Branch closures reflect both digitalisation and sectoral consolidation (219 institutions in 1991, 51 in 2024). The branch series alone cannot separate these, and the report should not claim that it does.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="62" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Definitional spread in exclusion measures</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>The five exclusion measures range from 4.7% to 25% because they define the population differently. They are not competing estimates of one quantity and must not be averaged or presented as a range.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="62" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Cross-section complete on adoption, incomplete on outcome</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>The adoption measure now covers all 27 member states for 2024, so F5 is a complete EU ranking. The enterprise-turnover measure does not: nine member states hold adoption but not turnover and cannot enter Figure 6. Those nine are dropped by data availability rather than by their position on either axis, which is why the remaining 18 are treated as a usable cross-section.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="62" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Figure 6 sample size</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>The adoption-to-outcome scatter rests on 18 complete country pairs, up from 6. That is enough to report a slope with a standard error and a t-statistic, all three of which are on the sheet as live formulas. It is not enough, and no sample size would be enough here, to support a claim about causal direction: this is one year of cross-sectional data with no control for national income. Say n explicitly, report the slope with its standard error, and keep the language associational.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="62" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Figure 6 measures two sides of the market</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>X is a consumer measure (individuals buying online); Y is an all-enterprise, all-sector measure that includes B2B and EDI ordering. A positive association indicates that digital commerce runs deep in an economy. It is not evidence that consumer purchasing causes enterprise turnover, and must not be written as though it were.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="62" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Mirror-sourced column</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>The 16 country-level e-sales turnover values flagged 'u' were retrieved via search of Eurostat tin00110 rather than from the databrowser directly. Two values in the same column (EU27 19.49 and Ireland 38.25) are independently corroborated by source ES5, which supports the column, but each value should be spot-checked against the databrowser before final submission.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="62" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Search-based verification</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>Direct access to statistical portals was blocked in the build environment. Values were verified against the issuing authority through search results reporting those publications. This is weaker than downloading the dataset: before final submission, spot-check high-stakes figures against the source pages directly.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="62" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Discarded material</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>An earlier candidate dataset was rejected in full after verification found fabricated values carrying authentic dataset codes and extraction dates - including a Eurostat cross-section that inverted the true EU country ranking. None of it survives in this workbook.</t>
+          <t>To fill</t>
+        </is>
+      </c>
+      <c r="B11" s="45" t="inlineStr">
+        <is>
+          <t>Retrieve from statistikbanken.dk, add rows to dataset.py under series_code DK.RET.VOL with unit 'index 2021=100', and re-run build_workbook.py.</t>
         </is>
       </c>
     </row>
@@ -6981,6 +6876,266 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="92" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Data quality statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>Read before citing any value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="62" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Compiled date is not a per-value retrieval date</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>02_MASTER carries a compiled_date column holding a single build-time constant, identical on all 113 rows. It records when this workbook was generated, NOT when each value was retrieved from its authority - those retrievals were made across several working sessions on different days. The column was named extraction_date until an audit of the generated file found that the name claimed per-observation provenance the data does not hold. It is renamed rather than back-filled, because inventing plausible retrieval dates would be precisely the fabrication this workbook exists to avoid. Recording true retrieval dates requires capturing them at retrieval time, in dataset.py, which is the correct fix and is not retrospective.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="62" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>No inferential statistics</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>The longest series here has six observations. Regression, cointegration and Granger-causality procedures require far more, and any such result on this dataset would be uninterpretable. The workbook supports description and comparison only. Co-movement between digital payment adoption and branch closures is presented as association, never as measured causation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="62" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Figure 6 tail selection - RESOLVED, and what it cost</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>The adoption column in Figure 6 was originally assembled from a Eurostat press release naming the highest three countries, the lowest three and two large movers, so most plotted points came from the ends of the EU distribution. Selecting on the extremes of X inflates the correlation coefficient regardless of the underlying relationship, and R-squared was withheld from the chart face for that reason. The column is now the complete isoc_ec_ib20 databrowser extract for all 27 member states, unrounded, so the selection is gone and R-squared is displayed. The measured cost of the bias is retained on F6 because it is informative: on the 6 tail countries the fit was R-squared 0.853 with a slope of +0.655; on the complete cross-section it is R-squared 0.674 with a slope of +0.602. Tail selection barely moved the slope and flattered the fit by 0.18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="62" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>No price deflator on the turnover series</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>E-sales as a share of enterprise turnover runs 2014 to 2024, spanning the pandemic and the 2022 inflation episode. Turnover is nominal, and online and physical retail did not face the same price path. Part of the measured rise in the e-sales share is therefore relative price movement rather than real reallocation of activity. No deflator was available in this session and none has been applied, so the doubling of intensity should be read as nominal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="62" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Banking series use different base years</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>This constrains F9_CONSOLIDATION directly: the three percentage changes on that sheet are not measured over a common window, so they must not be differenced against one another. Institutions and employment are comparable to each other, both 1991-2024. Branch counts begin in 2004; institution counts and employment begin in 1991. A 2004-2024 branch change and a 1991-2024 employment change are not comparable, and placing the two percentages side by side in prose would misrepresent both. 05_CALC labels every window explicitly. Either state both windows or do not draw the comparison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="62" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>No sampling error is reported anywhere</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>The Eurostat, Nationalbank and Agency for Digital Government figures are survey estimates and carry sampling error that the issuing authorities publish but this workbook does not reproduce. Small differences should not be treated as established: a 2-3 point gap between two survey proportions, or between two eGovernment Benchmark scores, may not be distinguishable from zero. Directions are more robust than magnitudes throughout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="62" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Headcount conversions rest on an implied denominator</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A published figure for the Danish population aged 15 and over could not be verified in this session. F4 therefore derives an implied 15+ base by dividing the exempt headcount by the exemption rate, both from the same source. Persons-affected figures built on it are orders of magnitude, not counts, and the capability shares they scale are measured on 'the population' rather than on the 15+ base - the denominators are not identical. Every such cell is marked in place.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="62" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>A withdrawn claim about SMV:Digital</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>An earlier draft of this workbook asserted that SMV:Digital was being defunded, and an argument was built on the contrast between a programme that works and a programme being cut. The claim could not be verified. The scheme's own 2026 grant-pool page documents pools still open and a further pool opening on 26 October 2026. The claim has been removed from the dataset and from the report's argument, and the correction is recorded in 09_POLICY and 08_AI_LOG rather than silently erased.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="62" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Unbalanced panel</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>Observation years differ by series because the underlying sources publish on different cycles - payment habits roughly biennially, Eurostat annually, branch counts irregularly. Gaps are genuine and are not filled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="62" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Denominator break</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>Danish online-purchasing figures change base between 2019 (% of individuals) and 2020 onward (% of internet users). The 2019 observation carries flag 'b' and is never plotted with later years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="62" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Verbal quantities</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Values flagged 'e' were published as words, not figures - 'nearly one in five', 'just under 36,000'. They are recorded as the stated approximation with the original wording in the notes column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="62" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Confounded outcome</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Branch closures reflect both digitalisation and sectoral consolidation (219 institutions in 1991, 51 in 2024). The branch series alone cannot separate these, and the report should not claim that it does.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="62" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Definitional spread in exclusion measures</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>The five exclusion measures range from 4.7% to 25% because they define the population differently. They are not competing estimates of one quantity and must not be averaged or presented as a range.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="62" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Cross-section complete on adoption, incomplete on outcome</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>The adoption measure now covers all 27 member states for 2024, so F5 is a complete EU ranking. The enterprise-turnover measure does not: nine member states hold adoption but not turnover and cannot enter Figure 6. Those nine are dropped by data availability rather than by their position on either axis, which is why the remaining 18 are treated as a usable cross-section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="62" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Figure 6 sample size</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>The adoption-to-outcome scatter rests on 18 complete country pairs, up from 6. That is enough to report a slope with a standard error and a t-statistic, all three of which are on the sheet as live formulas. It is not enough, and no sample size would be enough here, to support a claim about causal direction: this is one year of cross-sectional data with no control for national income. Say n explicitly, report the slope with its standard error, and keep the language associational.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="62" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Figure 6 measures two sides of the market</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>X is a consumer measure (individuals buying online); Y is an all-enterprise, all-sector measure that includes B2B and EDI ordering. A positive association indicates that digital commerce runs deep in an economy. It is not evidence that consumer purchasing causes enterprise turnover, and must not be written as though it were.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="62" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Mirror-sourced column</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>The 16 country-level e-sales turnover values flagged 'u' were retrieved via search of Eurostat tin00110 rather than from the databrowser directly. Two values in the same column (EU27 19.49 and Ireland 38.25) are independently corroborated by source ES5, which supports the column, but each value should be spot-checked against the databrowser before final submission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="62" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Search-based verification</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Direct access to statistical portals was blocked in the build environment. Values were verified against the issuing authority through search results reporting those publications. This is weaker than downloading the dataset: before final submission, spot-check high-stakes figures against the source pages directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="62" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Discarded material</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>An earlier candidate dataset was rejected in full after verification found fabricated values carrying authentic dataset codes and extraction dates - including a Eurostat cross-section that inverted the true EU country ranking. None of it survives in this workbook.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7258,7 +7413,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -7690,7 +7690,7 @@
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>DG4</t>
+          <t>DG5</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
-          <t>DG4</t>
+          <t>DG5</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t>DG4</t>
+          <t>DG5</t>
         </is>
       </c>
       <c r="F13" s="15" t="inlineStr">
@@ -14816,7 +14816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -15671,7 +15671,7 @@
       </c>
       <c r="F24" s="15" t="inlineStr">
         <is>
-          <t>13 September 2026</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G24" s="15" t="inlineStr">
@@ -15708,298 +15708,331 @@
       </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
-          <t>14 September 2026</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>Eurostat 2025, E-government activities of individuals via websites, dataset isoc_ciegi_ac, Eurostat, Luxembourg, accessed 14 September 2026, &lt;https://ec.europa.eu/eurostat/databrowser/view/isoc_ciegi_ac/default/table?lang=en&gt;.</t>
+          <t>Eurostat 2026, E-government activities of individuals via websites, dataset isoc_ciegi_ac, Statistical Office of the European Union, Luxembourg, accessed 14 September 2026, &lt;https://ec.europa.eu/eurostat/databrowser/view/isoc_ciegi_ac/default/table?lang=en&gt;.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="46" customHeight="1">
       <c r="A26" s="23" t="inlineStr">
         <is>
-          <t>LOV1</t>
+          <t>DG5</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>Folketinget</t>
+          <t>Digitaliseringsstyrelsen (Danish Agency for Digital Government)</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Lov om fravigelse fra obligatorisk digital selvbetjening (Act on derogation from mandatory digital self-service)</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>LOV nr 603 af 31/05/2023</t>
-        </is>
-      </c>
+          <t>NemID is about to be closed</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr"/>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>https://www.retsinformation.dk/eli/lta/2023/603</t>
+          <t>https://www.mitid.dk/en-gb/about-mitid/news/nemid-is-about-to-be-closed/</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
         <is>
-          <t>13 September 2026</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
-          <t>Folketinget 2023, Lov om fravigelse fra obligatorisk digital selvbetjening, LOV nr 603 af 31. maj 2023, in force 1 June 2023, Retsinformation, accessed 13 September 2026, &lt;https://www.retsinformation.dk/eli/lta/2023/603&gt;.</t>
+          <t>Digitaliseringsstyrelsen 2023, NemID is about to be closed, MitID, Agency for Digital Government, Copenhagen, accessed 14 September 2026, &lt;https://www.mitid.dk/en-gb/about-mitid/news/nemid-is-about-to-be-closed/&gt;.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="46" customHeight="1">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>BRH1</t>
+          <t>LOV1</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>Bundesrechnungshof</t>
+          <t>Folketinget</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes - findings on the Digital Jetzt lottery allocation</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Lov om fravigelse fra obligatorisk digital selvbetjening (Act on derogation from mandatory digital self-service)</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>Bemerkungen 2022</t>
+          <t>LOV nr 603 af 31/05/2023</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html</t>
+          <t>https://www.retsinformation.dk/eli/lta/2023/603</t>
         </is>
       </c>
       <c r="F27" s="15" t="inlineStr">
         <is>
-          <t>13 September 2026</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>Bundesrechnungshof 2022, Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes, German Federal Court of Auditors, accessed 13 September 2026, &lt;https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html&gt;.</t>
+          <t>Folketinget 2023, Lov om fravigelse fra obligatorisk digital selvbetjening, LOV nr 603 af 31. maj 2023, in force 1 June 2023, Retsinformation, accessed 13 September 2026, &lt;https://www.retsinformation.dk/eli/lta/2023/603&gt;.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="46" customHeight="1">
       <c r="A28" s="23" t="inlineStr">
         <is>
-          <t>CE1</t>
+          <t>BRH1</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>Conseil d'État (France)</t>
+          <t>Bundesrechnungshof</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Decision No. 452798 - partial annulment of the ANEF decree mandating online-only residence permit applications</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes - findings on the Digital Jetzt lottery allocation</t>
         </is>
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>No. 452798</t>
+          <t>Bemerkungen 2022</t>
         </is>
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798</t>
+          <t>https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>13 September 2026</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
-          <t>Conseil d'État 2022, Decision No. 452798, 3 June 2022, Conseil d'État, Paris, accessed 13 September 2026, &lt;https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798&gt;.</t>
+          <t>Bundesrechnungshof 2022, Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes, German Federal Court of Auditors, accessed 13 September 2026, &lt;https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html&gt;.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="46" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>BE1</t>
+          <t>CE1</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>Cour constitutionnelle (Belgium)</t>
+          <t>Conseil d'État (France)</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Arrêt no. 126/2025 - Brussels Digital ordinance; cumulative non-digital access guarantees</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Decision No. 452798 - partial annulment of the ANEF decree mandating online-only residence permit applications</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>ECLI:BE:GHCC:2025:ARR.126</t>
+          <t>No. 452798</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>https://fr.const-court.be/public/f/2025/2025-126f.pdf</t>
+          <t>https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798</t>
         </is>
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
-          <t>13 September 2026</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
-          <t>Cour constitutionnelle 2025, Arrêt no. 126/2025, 25 September 2025, ECLI:BE:GHCC:2025:ARR.126, Cour constitutionnelle, Brussels, accessed 13 September 2026, &lt;https://fr.const-court.be/public/f/2025/2025-126f.pdf&gt;.</t>
+          <t>Conseil d'État 2022, Decision No. 452798, 3 June 2022, Conseil d'État, Paris, accessed 13 September 2026, &lt;https://www.conseil-etat.fr/fr/arianeweb/CE/decision/2022-06-03/452798&gt;.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="46" customHeight="1">
       <c r="A30" s="23" t="inlineStr">
         <is>
-          <t>NO1</t>
+          <t>BE1</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsdirektoratet (Digdir)</t>
+          <t>Cour constitutionnelle (Belgium)</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Kontakt- og reservasjonsregisteret and the statutory right to opt out of digital communication under eForvaltningsforskriften</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Arrêt no. 126/2025 - Brussels Digital ordinance; cumulative non-digital access guarantees</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>KRR</t>
+          <t>ECLI:BE:GHCC:2025:ARR.126</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865</t>
+          <t>https://fr.const-court.be/public/f/2025/2025-126f.pdf</t>
         </is>
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>13 September 2026</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
-          <t>Digitaliseringsdirektoratet 2025, Kontakt- og reservasjonsregisteret, Norwegian Digitalisation Agency, accessed 13 September 2026, &lt;https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865&gt;.</t>
+          <t>Cour constitutionnelle 2025, Arrêt no. 126/2025, 25 September 2025, ECLI:BE:GHCC:2025:ARR.126, Cour constitutionnelle, Brussels, accessed 13 September 2026, &lt;https://fr.const-court.be/public/f/2025/2025-126f.pdf&gt;.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="46" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>GS1</t>
+          <t>NO1</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>Tran, T.T.</t>
+          <t>Digitaliseringsdirektoratet (Digdir)</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Guest speaker session: corporate sustainability and the adoption of artificial intelligence</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Kontakt- og reservasjonsregisteret and the statutory right to opt out of digital communication under eForvaltningsforskriften</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>ECON1596/ECON1597 guest lecture</t>
-        </is>
-      </c>
-      <c r="E31" s="15" t="inlineStr"/>
-      <c r="F31" s="15" t="inlineStr"/>
+          <t>KRR</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
       <c r="G31" s="15" t="inlineStr">
         <is>
-          <t>Tran, TT 2026, 'Guest speaker session: corporate sustainability and the adoption of artificial intelligence', guest lecture, ECON1596 Business Challenges in the Digital Economy, RMIT University Vietnam, Ho Chi Minh City, [LECTURE DATE: to be completed by the author].</t>
+          <t>Digitaliseringsdirektoratet 2025, Kontakt- og reservasjonsregisteret, Norwegian Digitalisation Agency, accessed 13 September 2026, &lt;https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865&gt;.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="46" customHeight="1">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>HOW1</t>
+          <t>GS1</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>Howell, S.T.</t>
+          <t>Tran, T.T.</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Financing Innovation: Evidence from R&amp;D Grants</t>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Guest speaker session: corporate sustainability and the adoption of artificial intelligence</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>American Economic Review 107(4)</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>https://www.aeaweb.org/articles?id=10.1257%2Faer.20150808</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="inlineStr">
-        <is>
-          <t>13 September 2026</t>
-        </is>
-      </c>
+          <t>ECON1596/ECON1597 guest lecture</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr"/>
+      <c r="F32" s="15" t="inlineStr"/>
       <c r="G32" s="15" t="inlineStr">
         <is>
-          <t>Howell, ST 2017, 'Financing innovation: evidence from R&amp;D grants', American Economic Review, vol. 107, no. 4, pp. 1136-1164.</t>
+          <t>Tran, TT 2026, 'Guest speaker session: corporate sustainability and the adoption of artificial intelligence', guest lecture, ECON1596 Business Challenges in the Digital Economy, RMIT University Vietnam, Ho Chi Minh City, [LECTURE DATE: to be completed by the author].</t>
         </is>
       </c>
     </row>
     <row r="33" ht="46" customHeight="1">
       <c r="A33" s="23" t="inlineStr">
         <is>
+          <t>HOW1</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Howell, S.T.</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] Financing Innovation: Evidence from R&amp;D Grants</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>American Economic Review 107(4)</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>https://www.aeaweb.org/articles?id=10.1257%2Faer.20150808</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>Howell, ST 2017, 'Financing innovation: evidence from R&amp;D grants', American Economic Review, vol. 107, no. 4, pp. 1136-1164.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="46" customHeight="1">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
           <t>SAN1</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>Santoleri, P., Barrows, G., Caravella, S., Crespi, F. and Pellegrino, G.</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C34" s="15" t="inlineStr">
         <is>
           <t>[REFERENCE ONLY - supports argument in the report; no workbook value depends on it] The Causal Effects of R&amp;D Grants: Evidence from a Regression Discontinuity - the Horizon 2020 SME Instrument scoring threshold</t>
         </is>
       </c>
-      <c r="D33" s="15" t="inlineStr">
+      <c r="D34" s="15" t="inlineStr">
         <is>
           <t>Working paper</t>
         </is>
       </c>
-      <c r="E33" s="15" t="inlineStr">
+      <c r="E34" s="15" t="inlineStr">
         <is>
           <t>https://pietrosantoleri.github.io/files/Santoleri_et_al_The_effects_of_R_D_grants.pdf</t>
         </is>
       </c>
-      <c r="F33" s="15" t="inlineStr">
-        <is>
-          <t>13 September 2026</t>
-        </is>
-      </c>
-      <c r="G33" s="15" t="inlineStr">
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
         <is>
           <t>Santoleri, P, Barrows, G, Caravella, S, Crespi, F and Pellegrino, G 2022, The causal effects of R&amp;D grants: evidence from a regression discontinuity, working paper, accessed 13 September 2026, &lt;https://pietrosantoleri.github.io/files/Santoleri_et_al_The_effects_of_R_D_grants.pdf&gt;.</t>
         </is>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -3011,6 +3011,8 @@
         <c:axId val="50010002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="80"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines>
@@ -3375,6 +3377,8 @@
         <c:axId val="50020002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="28"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:axPos val="b"/>
         <c:majorGridlines>
@@ -4193,6 +4197,8 @@
         <c:axId val="50030002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="100"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines>
@@ -4354,6 +4360,11 @@
           <c:tx>
             <c:v>Member state</c:v>
           </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
             <c:size val="8"/>
@@ -4783,6 +4794,8 @@
         <c:axId val="50040001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="100"/>
+          <c:min val="50"/>
         </c:scaling>
         <c:axPos val="b"/>
         <c:majorGridlines>
@@ -4856,6 +4869,8 @@
         <c:axId val="50040002"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="40"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:majorGridlines>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -1129,7 +1129,7 @@
     <t>https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html</t>
   </si>
   <si>
-    <t>Bundesrechnungshof 2022, Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes, German Federal Court of Auditors, accessed 13 September 2026, &lt;https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html&gt;.</t>
+    <t>Bundesrechnungshof 2022, Bemerkungen 2022 zur Haushalts- und Wirtschaftsführung des Bundes, German Federal Court of Auditors, Bonn, accessed 13 September 2026, &lt;https://www.bundesrechnungshof.de/SharedDocs/Pressemitteilungen/DE/2022/bemerkungen2022-hauptband.html&gt;.</t>
   </si>
   <si>
     <t>CE1</t>
@@ -1162,7 +1162,7 @@
     <t>https://digst.dk/tal-og-statistik/</t>
   </si>
   <si>
-    <t>Digitaliseringsstyrelsen 2026, Statistik om Digital Post, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
+    <t>Digitaliseringsstyrelsen 2026, Statistik om Digital Post, Agency for Digital Government, Copenhagen, accessed 12 September 2026, &lt;https://digst.dk/tal-og-statistik/&gt;.</t>
   </si>
   <si>
     <t>Hvem oplever udfordringer ved det digitale?</t>
@@ -1171,7 +1171,7 @@
     <t>https://digst.dk/digital-inklusion/viden-om-digital-inklusion/hvem-oplever-udfordringer-ved-det-digitale/</t>
   </si>
   <si>
-    <t>Digitaliseringsstyrelsen 2025, Hvem oplever udfordringer ved det digitale?, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
+    <t>Digitaliseringsstyrelsen 2025, Hvem oplever udfordringer ved det digitale?, Agency for Digital Government, Copenhagen, accessed 12 September 2026, &lt;https://digst.dk/digital-inklusion/viden-om-digital-inklusion/hvem-oplever-udfordringer-ved-det-digitale/&gt;.</t>
   </si>
   <si>
     <t>Digitaliseringsstyrelsen / Danmarks Statistik</t>
@@ -1195,7 +1195,7 @@
     <t>https://digst.dk/it-loesninger/digital-post/lovgivning/</t>
   </si>
   <si>
-    <t>Digitaliseringsstyrelsen 2025, Digital Post – lovgivning, Agency for Digital Government, Copenhagen, accessed 12 September 2026.</t>
+    <t>Digitaliseringsstyrelsen 2025, Digital Post – lovgivning, Agency for Digital Government, Copenhagen, accessed 12 September 2026, &lt;https://digst.dk/it-loesninger/digital-post/lovgivning/&gt;.</t>
   </si>
   <si>
     <t>DG5</t>
@@ -1228,7 +1228,7 @@
     <t>https://www.dst.dk/da/Statistik/dokumentation/statistikdokumentation/detailomsaetningsindeks</t>
   </si>
   <si>
-    <t>Danmarks Statistik 2025, Detailomsætningsindeks, Statistics Denmark, Copenhagen, accessed 12 September 2026.</t>
+    <t>Danmarks Statistik 2025, Detailomsætningsindeks, Statistics Denmark, Copenhagen, accessed 12 September 2026, &lt;https://www.dst.dk/da/Statistik/dokumentation/statistikdokumentation/detailomsaetningsindeks&gt;.</t>
   </si>
   <si>
     <t>Befolkningstal (population figures)</t>
@@ -1240,7 +1240,7 @@
     <t>https://www.dst.dk/da/Statistik/emner/borgere/befolkning/befolkningstal</t>
   </si>
   <si>
-    <t>Danmarks Statistik 2026, Befolkningstal, Statistics Denmark, Copenhagen, accessed 12 September 2026.</t>
+    <t>Danmarks Statistik 2026, Befolkningstal, Statistics Denmark, Copenhagen, accessed 12 September 2026, &lt;https://www.dst.dk/da/Statistik/emner/borgere/befolkning/befolkningstal&gt;.</t>
   </si>
   <si>
     <t>European Commission</t>
@@ -1255,7 +1255,7 @@
     <t>https://digital-strategy.ec.europa.eu/en/policies/desi</t>
   </si>
   <si>
-    <t>European Commission 2026, Digital Decade 2026 country report: Denmark, SWD(2026) 155 final, Part 7/27, European Commission, Brussels.</t>
+    <t>European Commission 2026, Digital Decade 2026 country report: Denmark, SWD(2026) 155 final, Part 7/27, European Commission, Brussels, accessed 12 September 2026, &lt;https://digital-strategy.ec.europa.eu/en/policies/desi&gt;.</t>
   </si>
   <si>
     <t>Eurostat</t>
@@ -1270,7 +1270,7 @@
     <t>https://ec.europa.eu/eurostat/statistics-explained/index.php?title=E-commerce_statistics_for_individuals</t>
   </si>
   <si>
-    <t>Eurostat 2025, E-commerce statistics for individuals, Statistics Explained, European Commission, Luxembourg, accessed 12 September 2026.</t>
+    <t>Eurostat 2025, E-commerce statistics for individuals, Statistics Explained, European Commission, Luxembourg, accessed 12 September 2026, &lt;https://ec.europa.eu/eurostat/statistics-explained/index.php?title=E-commerce_statistics_for_individuals&gt;.</t>
   </si>
   <si>
     <t>Online shopping ever more popular in 2020 (ddn-20210217-1)</t>
@@ -1282,7 +1282,7 @@
     <t>https://ec.europa.eu/eurostat/web/products-eurostat-news/-/ddn-20210217-1</t>
   </si>
   <si>
-    <t>Eurostat 2021, Online shopping ever more popular in 2020, European Commission, Luxembourg, accessed 12 September 2026.</t>
+    <t>Eurostat 2021, Online shopping ever more popular in 2020, European Commission, Luxembourg, accessed 12 September 2026, &lt;https://ec.europa.eu/eurostat/web/products-eurostat-news/-/ddn-20210217-1&gt;.</t>
   </si>
   <si>
     <t>Online shopping ever more popular (ddn-20220202-1)</t>
@@ -1291,7 +1291,7 @@
     <t>https://ec.europa.eu/eurostat/web/products-eurostat-news/-/ddn-20220202-1</t>
   </si>
   <si>
-    <t>Eurostat 2022, Online shopping ever more popular, European Commission, Luxembourg, accessed 12 September 2026.</t>
+    <t>Eurostat 2022, Online shopping ever more popular, European Commission, Luxembourg, accessed 12 September 2026, &lt;https://ec.europa.eu/eurostat/web/products-eurostat-news/-/ddn-20220202-1&gt;.</t>
   </si>
   <si>
     <t>E-commerce statistics for individuals, 2024 reference year (ddn-20250220-3)</t>
@@ -1300,7 +1300,7 @@
     <t>https://ec.europa.eu/eurostat/web/products-eurostat-news/w/ddn-20250220-3</t>
   </si>
   <si>
-    <t>Eurostat 2025, E-commerce statistics for individuals, European Commission, Luxembourg, accessed 12 September 2026.</t>
+    <t>Eurostat 2025, E-commerce statistics for individuals, European Commission, Luxembourg, accessed 12 September 2026, &lt;https://ec.europa.eu/eurostat/web/products-eurostat-news/w/ddn-20250220-3&gt;.</t>
   </si>
   <si>
     <t>EU enterprises' online sales reach new heights in 2023 (ddn-20250227-2)</t>
@@ -1312,7 +1312,7 @@
     <t>https://ec.europa.eu/eurostat/web/products-eurostat-news/w/ddn-20250227-2</t>
   </si>
   <si>
-    <t>Eurostat 2025, EU enterprises' online sales reach new heights, European Commission, Luxembourg, accessed 12 September 2026.</t>
+    <t>Eurostat 2025, EU enterprises' online sales reach new heights, European Commission, Luxembourg, accessed 12 September 2026, &lt;https://ec.europa.eu/eurostat/web/products-eurostat-news/w/ddn-20250227-2&gt;.</t>
   </si>
   <si>
     <t>Share of enterprises' turnover on e-commerce, by country (country-level values retrieved via search of the Eurostat indicator)</t>
@@ -1324,7 +1324,7 @@
     <t>https://ec.europa.eu/eurostat/databrowser/view/tin00110/default/table?lang=en</t>
   </si>
   <si>
-    <t>Eurostat 2025, Share of enterprises' turnover on e-commerce (tin00110), European Commission, Luxembourg, accessed 12 September 2026.</t>
+    <t>Eurostat 2025, Share of enterprises' turnover on e-commerce (tin00110), European Commission, Luxembourg, accessed 12 September 2026, &lt;https://ec.europa.eu/eurostat/databrowser/view/tin00110/default/table?lang=en&gt;.</t>
   </si>
   <si>
     <t>Internet purchases by individuals (2020 onwards) - custom extraction, all individuals, last online purchase in the 12 months, percentage of individuals who used internet within the last year, 2024</t>
@@ -1345,7 +1345,7 @@
     <t>https://ec.europa.eu/eurostat/databrowser/view/tesem160/default/table?lang=en</t>
   </si>
   <si>
-    <t>Eurostat 2026, Labour productivity per person employed and hour worked (EU27_2020=100), dataset tesem160, last updated 9 September 2026, Eurostat, accessed 13 September 2026, &lt;https://ec.europa.eu/eurostat/databrowser/view/tesem160/default/table?lang=en&gt;.</t>
+    <t>Eurostat 2026, Labour productivity per person employed and hour worked (EU27_2020=100), dataset tesem160, Statistical Office of the European Union, Luxembourg, data last updated 9 September 2026, accessed 13 September 2026, &lt;https://ec.europa.eu/eurostat/databrowser/view/tesem160/default/table?lang=en&gt;.</t>
   </si>
   <si>
     <t>E-government activities of individuals via websites - individuals using the internet for interaction with public authorities, last 12 months</t>
@@ -1417,7 +1417,7 @@
     <t>https://menneskeret.dk/sites/menneskeret.dk/files/media/document/Rettigheder%20i%20den%20digitale%20velf%C3%A6rdsstat.%20Analyse,%20Institut%20for%20Menneskerettigheder,%20december%202023.PDF</t>
   </si>
   <si>
-    <t>Institut for Menneskerettigheder 2023, Rettigheder i den digitale velfærdsstat, Danish Institute for Human Rights, Copenhagen, accessed 12 September 2026.</t>
+    <t>Institut for Menneskerettigheder 2023, Rettigheder i den digitale velfærdsstat, Danish Institute for Human Rights, Copenhagen, accessed 12 September 2026, &lt;https://menneskeret.dk/sites/menneskeret.dk/files/media/document/Rettigheder%20i%20den%20digitale%20velf%C3%A6rdsstat.%20Analyse,%20Institut%20for%20Menneskerettigheder,%20december%202023.PDF&gt;.</t>
   </si>
   <si>
     <t>Justitia (independent Danish legal think tank)</t>
@@ -1432,7 +1432,7 @@
     <t>https://justitia-int.org/wp-content/uploads/2022/09/Rapport_Retssikkerhed-for-digitalt-udsatte-borgere-1.pdf</t>
   </si>
   <si>
-    <t>Justitia 2022, Retssikkerhed for digitalt udsatte borgere, Justitia, Copenhagen, accessed 12 September 2026.</t>
+    <t>Justitia 2022, Retssikkerhed for digitalt udsatte borgere, Justitia, Copenhagen, accessed 12 September 2026, &lt;https://justitia-int.org/wp-content/uploads/2022/09/Rapport_Retssikkerhed-for-digitalt-udsatte-borgere-1.pdf&gt;.</t>
   </si>
   <si>
     <t>LOV1</t>
@@ -1450,7 +1450,7 @@
     <t>https://www.retsinformation.dk/eli/lta/2023/603</t>
   </si>
   <si>
-    <t>Folketinget 2023, Lov om fravigelse fra obligatorisk digital selvbetjening, LOV nr 603 af 31. maj 2023, in force 1 June 2023, Retsinformation, accessed 13 September 2026, &lt;https://www.retsinformation.dk/eli/lta/2023/603&gt;.</t>
+    <t>Folketinget 2023, Lov om fravigelse fra obligatorisk digital selvbetjening, LOV nr 603 af 31. maj 2023, in force 1 June 2023, Retsinformation, Copenhagen, accessed 13 September 2026, &lt;https://www.retsinformation.dk/eli/lta/2023/603&gt;.</t>
   </si>
   <si>
     <t>Danmarks Nationalbank</t>
@@ -1480,7 +1480,7 @@
     <t>https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865</t>
   </si>
   <si>
-    <t>Digitaliseringsdirektoratet 2025, Kontakt- og reservasjonsregisteret, Norwegian Digitalisation Agency, accessed 13 September 2026, &lt;https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865&gt;.</t>
+    <t>Digitaliseringsdirektoratet 2025, Kontakt- og reservasjonsregisteret, Norwegian Digitalisation Agency, Oslo, accessed 13 September 2026, &lt;https://www.digdir.no/digitale-felleslosninger/kontakt-og-reservasjonsregisteret-krr/865&gt;.</t>
   </si>
   <si>
     <t>RI1</t>
@@ -1498,7 +1498,7 @@
     <t>https://www.retsinformation.dk/eli/lta/2012/528</t>
   </si>
   <si>
-    <t>Denmark 2012, Lov om Offentlig Digital Post (LOV nr 528 af 11/06/2012), Retsinformation, Copenhagen, accessed 12 September 2026.</t>
+    <t>Folketinget 2012, Lov om Offentlig Digital Post, LOV nr 528 af 11. juni 2012, Retsinformation, Copenhagen, accessed 12 September 2026, &lt;https://www.retsinformation.dk/eli/lta/2012/528&gt;.</t>
   </si>
   <si>
     <t>RI2</t>
@@ -1516,7 +1516,7 @@
     <t>https://www.finanstilsynet.dk/finansielle-temaer/betalingstjenester-og-e-penge/kontantreglen</t>
   </si>
   <si>
-    <t>Finanstilsynet 2025, Kontantreglen, Danish Financial Supervisory Authority, Copenhagen, accessed 12 September 2026.</t>
+    <t>Finanstilsynet 2025, Kontantreglen, Danish Financial Supervisory Authority, Copenhagen, accessed 12 September 2026, &lt;https://www.finanstilsynet.dk/finansielle-temaer/betalingstjenester-og-e-penge/kontantreglen&gt;.</t>
   </si>
   <si>
     <t>Rigsrevisionen (Danish National Audit Office)</t>
@@ -1528,7 +1528,7 @@
     <t>https://www.rigsrevisionen.dk/revisionssager-arkiv/2016/jan/beretning-om-besparelsespotentialet-ved-obligatorisk-digital-post-paa-ca-1-mia-kr-om-aaret</t>
   </si>
   <si>
-    <t>Rigsrevisionen 2016, Beretning om besparelsespotentialet ved obligatorisk Digital Post på ca. 1 mia. kr. om året, National Audit Office of Denmark, Copenhagen, accessed 12 September 2026.</t>
+    <t>Rigsrevisionen 2016, Beretning om besparelsespotentialet ved obligatorisk Digital Post på ca. 1 mia. kr. om året, National Audit Office of Denmark, Copenhagen, accessed 12 September 2026, &lt;https://www.rigsrevisionen.dk/revisionssager-arkiv/2016/jan/beretning-om-besparelsespotentialet-ved-obligatorisk-digital-post-paa-ca-1-mia-kr-om-aaret&gt;.</t>
   </si>
   <si>
     <t>SAN1</t>
@@ -1546,7 +1546,7 @@
     <t>https://pietrosantoleri.github.io/files/Santoleri_et_al_The_effects_of_R_D_grants.pdf</t>
   </si>
   <si>
-    <t>Santoleri, P, Barrows, G, Caravella, S, Crespi, F and Pellegrino, G 2022, The causal effects of R&amp;D grants: evidence from a regression discontinuity, working paper, accessed 13 September 2026, &lt;https://pietrosantoleri.github.io/files/Santoleri_et_al_The_effects_of_R_D_grants.pdf&gt;.</t>
+    <t>Santoleri, P, Barrows, G, Caravella, S, Crespi, F &amp; Pellegrino, G 2022, The causal effects of R&amp;D grants: evidence from a regression discontinuity, working paper, accessed 13 September 2026, &lt;https://pietrosantoleri.github.io/files/Santoleri_et_al_The_effects_of_R_D_grants.pdf&gt;.</t>
   </si>
   <si>
     <t>SMV1</t>
@@ -1561,7 +1561,7 @@
     <t>https://smvdigital.dk/content/ydelser/tilskudspuljer-i-2026/8efa07f4-5032-47f4-b7fa-bab57412b762/</t>
   </si>
   <si>
-    <t>SMV:Digital 2026, Tilskudspuljer i 2026, SMV:Digital, Copenhagen, accessed 12 September 2026.</t>
+    <t>SMV:Digital 2026, Tilskudspuljer i 2026, SMV:Digital, Copenhagen, accessed 12 September 2026, &lt;https://smvdigital.dk/content/ydelser/tilskudspuljer-i-2026/8efa07f4-5032-47f4-b7fa-bab57412b762/&gt;.</t>
   </si>
   <si>
     <t>What each series measures</t>

--- a/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
+++ b/ECON1596_A2_Denmark_DataWorkbook_s4040040.xlsx
@@ -25,7 +25,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'03_SOURCES'!$A$4:$G$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'06_SERIES'!$A$4:$J$38</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'02_MASTER'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'06_SERIES'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'03_SOURCES'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'04_DEFINITIONS'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'05_CALC'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'06_SERIES'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'09_POLICY'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2630,7 +2634,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2672,6 +2676,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6363,144 +6370,144 @@
         <v>709</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="66" customHeight="1">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:2" ht="123.5" customHeight="1">
+      <c r="A7" s="23" t="s">
         <v>710</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="88" customHeight="1">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:2" ht="164" customHeight="1">
+      <c r="A8" s="23" t="s">
         <v>712</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="55" customHeight="1">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:2" ht="96.5" customHeight="1">
+      <c r="A9" s="23" t="s">
         <v>714</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="66" customHeight="1">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:2" ht="123.5" customHeight="1">
+      <c r="A10" s="23" t="s">
         <v>716</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="55" customHeight="1">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:2" ht="96.5" customHeight="1">
+      <c r="A11" s="23" t="s">
         <v>718</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="77" customHeight="1">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:2" ht="137" customHeight="1">
+      <c r="A12" s="23" t="s">
         <v>720</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="66" customHeight="1">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:2" ht="110" customHeight="1">
+      <c r="A13" s="23" t="s">
         <v>722</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="44" customHeight="1">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:2" ht="83" customHeight="1">
+      <c r="A14" s="23" t="s">
         <v>724</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="33" customHeight="1">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:2" ht="56" customHeight="1">
+      <c r="A15" s="23" t="s">
         <v>726</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="33" customHeight="1">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:2" ht="69.5" customHeight="1">
+      <c r="A16" s="23" t="s">
         <v>728</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="33" customHeight="1">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:2" ht="56" customHeight="1">
+      <c r="A17" s="23" t="s">
         <v>730</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="33" customHeight="1">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:2" ht="56" customHeight="1">
+      <c r="A18" s="23" t="s">
         <v>732</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="55" customHeight="1">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:2" ht="96.5" customHeight="1">
+      <c r="A19" s="23" t="s">
         <v>734</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="55" customHeight="1">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:2" ht="96.5" customHeight="1">
+      <c r="A20" s="23" t="s">
         <v>736</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="55" customHeight="1">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:2" ht="96.5" customHeight="1">
+      <c r="A21" s="23" t="s">
         <v>738</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="44" customHeight="1">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:2" ht="83" customHeight="1">
+      <c r="A22" s="23" t="s">
         <v>740</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="33" customHeight="1">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:2" ht="69.5" customHeight="1">
+      <c r="A23" s="23" t="s">
         <v>742</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="77" customHeight="1">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:2" ht="137" customHeight="1">
+      <c r="A24" s="23" t="s">
         <v>744</v>
       </c>
       <c r="B24" s="7" t="s">
@@ -6517,64 +6524,64 @@
         <v>747</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="14" customHeight="1">
-      <c r="A29" s="3" t="s">
+    <row r="29" spans="1:2" ht="15.5" customHeight="1">
+      <c r="A29" s="23" t="s">
         <v>748</v>
       </c>
       <c r="B29" s="22" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="14" customHeight="1">
-      <c r="A30" s="3" t="s">
+    <row r="30" spans="1:2" ht="15.5" customHeight="1">
+      <c r="A30" s="23" t="s">
         <v>750</v>
       </c>
       <c r="B30" s="22" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="14" customHeight="1">
-      <c r="A31" s="3" t="s">
+    <row r="31" spans="1:2" ht="29" customHeight="1">
+      <c r="A31" s="23" t="s">
         <v>752</v>
       </c>
       <c r="B31" s="22" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="14" customHeight="1">
-      <c r="A32" s="3" t="s">
+    <row r="32" spans="1:2" ht="29" customHeight="1">
+      <c r="A32" s="23" t="s">
         <v>754</v>
       </c>
       <c r="B32" s="22" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="33" customHeight="1">
-      <c r="A33" s="3" t="s">
+    <row r="33" spans="1:4" ht="56" customHeight="1">
+      <c r="A33" s="23" t="s">
         <v>756</v>
       </c>
       <c r="B33" s="22" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="22" customHeight="1">
-      <c r="A34" s="3" t="s">
+    <row r="34" spans="1:4" ht="29" customHeight="1">
+      <c r="A34" s="23" t="s">
         <v>758</v>
       </c>
       <c r="B34" s="22" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="22" customHeight="1">
-      <c r="A35" s="3" t="s">
+    <row r="35" spans="1:4" ht="42.5" customHeight="1">
+      <c r="A35" s="23" t="s">
         <v>760</v>
       </c>
       <c r="B35" s="22" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="22" customHeight="1">
-      <c r="A36" s="3" t="s">
+    <row r="36" spans="1:4" ht="42.5" customHeight="1">
+      <c r="A36" s="23" t="s">
         <v>762</v>
       </c>
       <c r="B36" s="22" t="s">
@@ -6605,8 +6612,8 @@
         <v>769</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="22" customHeight="1">
-      <c r="A43" s="3" t="s">
+    <row r="43" spans="1:4" ht="29" customHeight="1">
+      <c r="A43" s="23" t="s">
         <v>770</v>
       </c>
       <c r="B43" s="7" t="s">
@@ -6619,8 +6626,8 @@
         <v>773</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="22" customHeight="1">
-      <c r="A44" s="3" t="s">
+    <row r="44" spans="1:4" ht="29" customHeight="1">
+      <c r="A44" s="23" t="s">
         <v>774</v>
       </c>
       <c r="B44" s="7" t="s">
@@ -6633,8 +6640,8 @@
         <v>777</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="44" customHeight="1">
-      <c r="A45" s="3" t="s">
+    <row r="45" spans="1:4" ht="42.5" customHeight="1">
+      <c r="A45" s="23" t="s">
         <v>778</v>
       </c>
       <c r="B45" s="7" t="s">
@@ -6647,8 +6654,8 @@
         <v>781</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="55" customHeight="1">
-      <c r="A46" s="3" t="s">
+    <row r="46" spans="1:4" ht="56" customHeight="1">
+      <c r="A46" s="23" t="s">
         <v>782</v>
       </c>
       <c r="B46" s="7" t="s">
@@ -6661,8 +6668,8 @@
         <v>785</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="55" customHeight="1">
-      <c r="A47" s="3" t="s">
+    <row r="47" spans="1:4" ht="56" customHeight="1">
+      <c r="A47" s="23" t="s">
         <v>786</v>
       </c>
       <c r="B47" s="7" t="s">
@@ -6675,8 +6682,8 @@
         <v>789</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="77" customHeight="1">
-      <c r="A48" s="3" t="s">
+    <row r="48" spans="1:4" ht="69.5" customHeight="1">
+      <c r="A48" s="23" t="s">
         <v>790</v>
       </c>
       <c r="B48" s="7" t="s">
@@ -6689,8 +6696,8 @@
         <v>793</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="66" customHeight="1">
-      <c r="A49" s="3" t="s">
+    <row r="49" spans="1:4" ht="69.5" customHeight="1">
+      <c r="A49" s="23" t="s">
         <v>794</v>
       </c>
       <c r="B49" s="7" t="s">
@@ -6703,8 +6710,8 @@
         <v>797</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="66" customHeight="1">
-      <c r="A50" s="3" t="s">
+    <row r="50" spans="1:4" ht="69.5" customHeight="1">
+      <c r="A50" s="23" t="s">
         <v>798</v>
       </c>
       <c r="B50" s="7" t="s">
@@ -6717,8 +6724,8 @@
         <v>801</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="77" customHeight="1">
-      <c r="A51" s="3" t="s">
+    <row r="51" spans="1:4" ht="69.5" customHeight="1">
+      <c r="A51" s="23" t="s">
         <v>802</v>
       </c>
       <c r="B51" s="7" t="s">
@@ -6731,8 +6738,8 @@
         <v>805</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="22" customHeight="1">
-      <c r="A52" s="3" t="s">
+    <row r="52" spans="1:4" ht="29" customHeight="1">
+      <c r="A52" s="23" t="s">
         <v>806</v>
       </c>
       <c r="B52" s="7" t="s">
@@ -6745,8 +6752,8 @@
         <v>809</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="33" customHeight="1">
-      <c r="A53" s="3" t="s">
+    <row r="53" spans="1:4" ht="29" customHeight="1">
+      <c r="A53" s="23" t="s">
         <v>810</v>
       </c>
       <c r="B53" s="7" t="s">
@@ -6788,11 +6795,11 @@
     <col min="4" max="4" width="6.7109375" customWidth="1"/>
     <col min="5" max="5" width="7.7109375" customWidth="1"/>
     <col min="6" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" customWidth="1"/>
     <col min="8" max="8" width="34.7109375" customWidth="1"/>
     <col min="9" max="9" width="6.7109375" customWidth="1"/>
     <col min="10" max="10" width="10.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" customWidth="1"/>
     <col min="12" max="12" width="56.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12024,7 +12031,7 @@
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="30.7109375" customWidth="1"/>
     <col min="3" max="3" width="42.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="41.7109375" customWidth="1"/>
     <col min="5" max="5" width="11.7109375" customWidth="1"/>
     <col min="6" max="6" width="48.7109375" customWidth="1"/>
     <col min="7" max="7" width="80.7109375" customWidth="1"/>
@@ -12878,7 +12885,7 @@
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
     <col min="2" max="2" width="46.7109375" customWidth="1"/>
     <col min="3" max="3" width="6.7109375" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
     <col min="5" max="5" width="36.7109375" customWidth="1"/>
     <col min="6" max="6" width="12.7109375" customWidth="1"/>
     <col min="7" max="7" width="11.7109375" customWidth="1"/>
